--- a/server/src/main/resources/templates/confirmation_template.xlsx
+++ b/server/src/main/resources/templates/confirmation_template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★★발송_2026_확인서, 견적서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qaz25\OneDrive\문서\Develop\academy-heungkuk-v2-\server\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D176C5-5920-4540-91D8-C82E43D3EC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835" activeTab="1"/>
+    <workbookView xWindow="2250" yWindow="1560" windowWidth="36180" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="빈문서" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">빈문서!$A$1:$AU$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">준수사항!$A$1:$AU$51</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>흥국생명연수원 사용안내 확인서</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -330,15 +331,6 @@
     <t/>
   </si>
   <si>
-    <t>9140643@heungkuklife.co.kr</t>
-  </si>
-  <si>
-    <t>2일(화)</t>
-  </si>
-  <si>
-    <t>3일(수)</t>
-  </si>
-  <si>
     <t>흥국생명연수원 이용시 준수사항 안내</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -358,7 +350,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="yyyy\.\ mm\.\ dd\ \(aaa\)"/>
@@ -1376,7 +1368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="278">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1506,114 +1498,567 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="179" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1641,24 +2086,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1751,465 +2178,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3659,7 +3627,13 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="그룹 1"/>
+        <xdr:cNvPr id="2" name="그룹 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -3672,7 +3646,13 @@
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="3" name="그룹 2"/>
+          <xdr:cNvPr id="3" name="그룹 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -3685,7 +3665,13 @@
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="타원 4"/>
+            <xdr:cNvPr id="5" name="타원 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3730,7 +3716,13 @@
         </xdr:sp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="타원 5"/>
+            <xdr:cNvPr id="6" name="타원 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3778,7 +3770,13 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="직사각형 3"/>
+          <xdr:cNvPr id="4" name="직사각형 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3841,7 +3839,13 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="7" name="그룹 6"/>
+        <xdr:cNvPr id="7" name="그룹 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -3854,7 +3858,13 @@
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="8" name="그룹 7"/>
+          <xdr:cNvPr id="8" name="그룹 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -3867,7 +3877,13 @@
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="타원 9"/>
+            <xdr:cNvPr id="10" name="타원 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3912,7 +3928,13 @@
         </xdr:sp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="타원 10"/>
+            <xdr:cNvPr id="11" name="타원 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3960,7 +3982,13 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="직사각형 8"/>
+          <xdr:cNvPr id="9" name="직사각형 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -4023,7 +4051,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="이등변 삼각형 11"/>
+        <xdr:cNvPr id="12" name="이등변 삼각형 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4199,7 +4233,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="이등변 삼각형 12"/>
+        <xdr:cNvPr id="13" name="이등변 삼각형 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4375,7 +4415,13 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="그룹 13"/>
+        <xdr:cNvPr id="14" name="그룹 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -4388,7 +4434,13 @@
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="15" name="Picture 2" descr="C:\Users\김충렬\Desktop\연수원지도.PNG"/>
+          <xdr:cNvPr id="15" name="Picture 2" descr="C:\Users\김충렬\Desktop\연수원지도.PNG">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
           </xdr:cNvPicPr>
@@ -4441,7 +4493,13 @@
       </xdr:pic>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="직사각형 15"/>
+          <xdr:cNvPr id="16" name="직사각형 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4612,7 +4670,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="직사각형 16"/>
+          <xdr:cNvPr id="17" name="직사각형 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4783,7 +4847,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="직사각형 17"/>
+          <xdr:cNvPr id="18" name="직사각형 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4954,7 +5024,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="직사각형 18"/>
+          <xdr:cNvPr id="19" name="직사각형 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5125,7 +5201,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="직사각형 19"/>
+          <xdr:cNvPr id="20" name="직사각형 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5296,7 +5378,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="직사각형 20"/>
+          <xdr:cNvPr id="21" name="직사각형 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5509,7 +5597,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="직사각형 21"/>
+          <xdr:cNvPr id="22" name="직사각형 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5722,7 +5816,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="직사각형 22"/>
+          <xdr:cNvPr id="23" name="직사각형 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5909,7 +6009,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="TextBox 11"/>
+        <xdr:cNvPr id="24" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6280,7 +6386,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="TextBox 11"/>
+        <xdr:cNvPr id="25" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6658,7 +6770,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="TextBox 11"/>
+        <xdr:cNvPr id="26" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7236,7 +7354,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="TextBox 11"/>
+        <xdr:cNvPr id="27" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7624,7 +7748,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="TextBox 11"/>
+        <xdr:cNvPr id="28" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8095,7 +8225,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="직사각형 28"/>
+        <xdr:cNvPr id="29" name="직사각형 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8761,7 +8897,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="TextBox 11"/>
+        <xdr:cNvPr id="30" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8989,7 +9131,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="그림 30"/>
+        <xdr:cNvPr id="31" name="그림 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -9294,9 +9442,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="0.625" style="3" customWidth="1"/>
     <col min="2" max="3" width="1.625" style="3" customWidth="1"/>
@@ -9372,39 +9520,39 @@
       <c r="F2" s="4"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="269" t="s">
+      <c r="I2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="270"/>
-      <c r="K2" s="270"/>
-      <c r="L2" s="270"/>
-      <c r="M2" s="270"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="270"/>
-      <c r="P2" s="270"/>
-      <c r="Q2" s="270"/>
-      <c r="R2" s="270"/>
-      <c r="S2" s="270"/>
-      <c r="T2" s="270"/>
-      <c r="U2" s="270"/>
-      <c r="V2" s="270"/>
-      <c r="W2" s="270"/>
-      <c r="X2" s="270"/>
-      <c r="Y2" s="270"/>
-      <c r="Z2" s="270"/>
-      <c r="AA2" s="270"/>
-      <c r="AB2" s="270"/>
-      <c r="AC2" s="270"/>
-      <c r="AD2" s="270"/>
-      <c r="AE2" s="270"/>
-      <c r="AF2" s="270"/>
-      <c r="AG2" s="270"/>
-      <c r="AH2" s="270"/>
-      <c r="AI2" s="270"/>
-      <c r="AJ2" s="270"/>
-      <c r="AK2" s="270"/>
-      <c r="AL2" s="270"/>
-      <c r="AM2" s="270"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
@@ -9422,37 +9570,37 @@
       <c r="E3" s="4"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="270"/>
-      <c r="J3" s="270"/>
-      <c r="K3" s="270"/>
-      <c r="L3" s="270"/>
-      <c r="M3" s="270"/>
-      <c r="N3" s="270"/>
-      <c r="O3" s="270"/>
-      <c r="P3" s="270"/>
-      <c r="Q3" s="270"/>
-      <c r="R3" s="270"/>
-      <c r="S3" s="270"/>
-      <c r="T3" s="270"/>
-      <c r="U3" s="270"/>
-      <c r="V3" s="270"/>
-      <c r="W3" s="270"/>
-      <c r="X3" s="270"/>
-      <c r="Y3" s="270"/>
-      <c r="Z3" s="270"/>
-      <c r="AA3" s="270"/>
-      <c r="AB3" s="270"/>
-      <c r="AC3" s="270"/>
-      <c r="AD3" s="270"/>
-      <c r="AE3" s="270"/>
-      <c r="AF3" s="270"/>
-      <c r="AG3" s="270"/>
-      <c r="AH3" s="270"/>
-      <c r="AI3" s="270"/>
-      <c r="AJ3" s="270"/>
-      <c r="AK3" s="270"/>
-      <c r="AL3" s="270"/>
-      <c r="AM3" s="270"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
@@ -9469,39 +9617,39 @@
       <c r="E4" s="4"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="271" t="s">
+      <c r="I4" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="M4" s="271"/>
-      <c r="N4" s="271"/>
-      <c r="O4" s="271"/>
-      <c r="P4" s="271"/>
-      <c r="Q4" s="271"/>
-      <c r="R4" s="271"/>
-      <c r="S4" s="271"/>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
-      <c r="AA4" s="271"/>
-      <c r="AB4" s="271"/>
-      <c r="AC4" s="271"/>
-      <c r="AD4" s="271"/>
-      <c r="AE4" s="271"/>
-      <c r="AF4" s="271"/>
-      <c r="AG4" s="271"/>
-      <c r="AH4" s="271"/>
-      <c r="AI4" s="271"/>
-      <c r="AJ4" s="271"/>
-      <c r="AK4" s="271"/>
-      <c r="AL4" s="271"/>
-      <c r="AM4" s="271"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="81"/>
+      <c r="AD4" s="81"/>
+      <c r="AE4" s="81"/>
+      <c r="AF4" s="81"/>
+      <c r="AG4" s="81"/>
+      <c r="AH4" s="81"/>
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="81"/>
+      <c r="AK4" s="81"/>
+      <c r="AL4" s="81"/>
+      <c r="AM4" s="81"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
@@ -9563,50 +9711,50 @@
       <c r="A6" s="1"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="203" t="s">
+      <c r="D6" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="272"/>
-      <c r="I6" s="273"/>
-      <c r="J6" s="273"/>
-      <c r="K6" s="273"/>
-      <c r="L6" s="273"/>
-      <c r="M6" s="273"/>
-      <c r="N6" s="273"/>
-      <c r="O6" s="273"/>
-      <c r="P6" s="273"/>
-      <c r="Q6" s="273"/>
-      <c r="R6" s="273"/>
-      <c r="S6" s="273"/>
-      <c r="T6" s="273"/>
-      <c r="U6" s="273"/>
-      <c r="V6" s="273"/>
-      <c r="W6" s="273"/>
-      <c r="X6" s="273"/>
-      <c r="Y6" s="273"/>
-      <c r="Z6" s="273"/>
-      <c r="AA6" s="273"/>
-      <c r="AB6" s="273"/>
-      <c r="AC6" s="273"/>
-      <c r="AD6" s="273"/>
-      <c r="AE6" s="273"/>
-      <c r="AF6" s="273"/>
-      <c r="AG6" s="273"/>
-      <c r="AH6" s="273"/>
-      <c r="AI6" s="273"/>
-      <c r="AJ6" s="273"/>
-      <c r="AK6" s="273"/>
-      <c r="AL6" s="274"/>
-      <c r="AM6" s="274"/>
-      <c r="AN6" s="274"/>
-      <c r="AO6" s="274"/>
-      <c r="AP6" s="274"/>
-      <c r="AQ6" s="274"/>
-      <c r="AR6" s="274"/>
-      <c r="AS6" s="274"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="85"/>
+      <c r="U6" s="85"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="85"/>
+      <c r="X6" s="85"/>
+      <c r="Y6" s="85"/>
+      <c r="Z6" s="85"/>
+      <c r="AA6" s="85"/>
+      <c r="AB6" s="85"/>
+      <c r="AC6" s="85"/>
+      <c r="AD6" s="85"/>
+      <c r="AE6" s="85"/>
+      <c r="AF6" s="85"/>
+      <c r="AG6" s="85"/>
+      <c r="AH6" s="85"/>
+      <c r="AI6" s="85"/>
+      <c r="AJ6" s="85"/>
+      <c r="AK6" s="85"/>
+      <c r="AL6" s="86"/>
+      <c r="AM6" s="86"/>
+      <c r="AN6" s="86"/>
+      <c r="AO6" s="86"/>
+      <c r="AP6" s="86"/>
+      <c r="AQ6" s="86"/>
+      <c r="AR6" s="86"/>
+      <c r="AS6" s="86"/>
       <c r="AT6" s="4"/>
       <c r="AU6" s="1"/>
     </row>
@@ -9614,51 +9762,51 @@
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="205" t="s">
+      <c r="D7" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="206"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="267" t="s">
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="267"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="267"/>
-      <c r="M7" s="267"/>
-      <c r="N7" s="267"/>
-      <c r="O7" s="267"/>
-      <c r="P7" s="267"/>
-      <c r="Q7" s="267"/>
-      <c r="R7" s="267"/>
-      <c r="S7" s="267"/>
-      <c r="T7" s="267"/>
-      <c r="U7" s="267"/>
-      <c r="V7" s="267"/>
-      <c r="W7" s="267"/>
-      <c r="X7" s="267"/>
-      <c r="Y7" s="267"/>
-      <c r="Z7" s="267"/>
-      <c r="AA7" s="267"/>
-      <c r="AB7" s="267"/>
-      <c r="AC7" s="267"/>
-      <c r="AD7" s="267"/>
-      <c r="AE7" s="267"/>
-      <c r="AF7" s="267"/>
-      <c r="AG7" s="267"/>
-      <c r="AH7" s="267"/>
-      <c r="AI7" s="267"/>
-      <c r="AJ7" s="267"/>
-      <c r="AK7" s="267"/>
-      <c r="AL7" s="267"/>
-      <c r="AM7" s="267"/>
-      <c r="AN7" s="267"/>
-      <c r="AO7" s="267"/>
-      <c r="AP7" s="267"/>
-      <c r="AQ7" s="267"/>
-      <c r="AR7" s="268"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="77"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="77"/>
+      <c r="Y7" s="77"/>
+      <c r="Z7" s="77"/>
+      <c r="AA7" s="77"/>
+      <c r="AB7" s="77"/>
+      <c r="AC7" s="77"/>
+      <c r="AD7" s="77"/>
+      <c r="AE7" s="77"/>
+      <c r="AF7" s="77"/>
+      <c r="AG7" s="77"/>
+      <c r="AH7" s="77"/>
+      <c r="AI7" s="77"/>
+      <c r="AJ7" s="77"/>
+      <c r="AK7" s="77"/>
+      <c r="AL7" s="77"/>
+      <c r="AM7" s="77"/>
+      <c r="AN7" s="77"/>
+      <c r="AO7" s="77"/>
+      <c r="AP7" s="77"/>
+      <c r="AQ7" s="77"/>
+      <c r="AR7" s="78"/>
       <c r="AS7" s="6"/>
       <c r="AT7" s="4"/>
       <c r="AU7" s="1"/>
@@ -9667,58 +9815,56 @@
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="205" t="s">
+      <c r="D8" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="206"/>
-      <c r="F8" s="206"/>
-      <c r="G8" s="206"/>
-      <c r="H8" s="261" t="s">
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="261"/>
-      <c r="J8" s="261"/>
-      <c r="K8" s="262"/>
-      <c r="L8" s="263"/>
-      <c r="M8" s="263"/>
-      <c r="N8" s="263"/>
-      <c r="O8" s="263"/>
-      <c r="P8" s="263"/>
-      <c r="Q8" s="261" t="s">
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
+      <c r="N8" s="100"/>
+      <c r="O8" s="100"/>
+      <c r="P8" s="100"/>
+      <c r="Q8" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="261"/>
-      <c r="S8" s="261"/>
-      <c r="T8" s="264"/>
-      <c r="U8" s="265"/>
-      <c r="V8" s="265"/>
-      <c r="W8" s="265"/>
-      <c r="X8" s="265"/>
-      <c r="Y8" s="265"/>
-      <c r="Z8" s="265"/>
-      <c r="AA8" s="265"/>
-      <c r="AB8" s="265"/>
-      <c r="AC8" s="265"/>
-      <c r="AD8" s="265"/>
-      <c r="AE8" s="265"/>
-      <c r="AF8" s="265"/>
-      <c r="AG8" s="266"/>
-      <c r="AH8" s="261" t="s">
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="101"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="102"/>
+      <c r="AD8" s="102"/>
+      <c r="AE8" s="102"/>
+      <c r="AF8" s="102"/>
+      <c r="AG8" s="103"/>
+      <c r="AH8" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="AI8" s="261"/>
-      <c r="AJ8" s="261"/>
-      <c r="AK8" s="261"/>
-      <c r="AL8" s="252" t="s">
-        <v>66</v>
-      </c>
-      <c r="AM8" s="253"/>
-      <c r="AN8" s="253"/>
-      <c r="AO8" s="253"/>
-      <c r="AP8" s="253"/>
-      <c r="AQ8" s="253"/>
-      <c r="AR8" s="253"/>
-      <c r="AS8" s="253"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
+      <c r="AK8" s="98"/>
+      <c r="AL8" s="87"/>
+      <c r="AM8" s="88"/>
+      <c r="AN8" s="88"/>
+      <c r="AO8" s="88"/>
+      <c r="AP8" s="88"/>
+      <c r="AQ8" s="88"/>
+      <c r="AR8" s="88"/>
+      <c r="AS8" s="88"/>
       <c r="AT8" s="4"/>
       <c r="AU8" s="1"/>
     </row>
@@ -9726,54 +9872,54 @@
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="207" t="s">
+      <c r="D9" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="254" t="s">
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="254"/>
-      <c r="J9" s="254"/>
-      <c r="K9" s="255" t="s">
+      <c r="I9" s="91"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="255"/>
-      <c r="M9" s="255"/>
-      <c r="N9" s="255"/>
-      <c r="O9" s="255"/>
-      <c r="P9" s="255"/>
-      <c r="Q9" s="254" t="s">
+      <c r="L9" s="92"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="92"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="254"/>
-      <c r="S9" s="254"/>
-      <c r="T9" s="256" t="s">
+      <c r="R9" s="91"/>
+      <c r="S9" s="91"/>
+      <c r="T9" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
-      <c r="W9" s="257"/>
-      <c r="X9" s="257"/>
-      <c r="Y9" s="257"/>
-      <c r="Z9" s="257"/>
-      <c r="AA9" s="257"/>
-      <c r="AB9" s="257"/>
-      <c r="AC9" s="257"/>
-      <c r="AD9" s="257"/>
-      <c r="AE9" s="257"/>
-      <c r="AF9" s="257"/>
-      <c r="AG9" s="258"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="94"/>
+      <c r="AA9" s="94"/>
+      <c r="AB9" s="94"/>
+      <c r="AC9" s="94"/>
+      <c r="AD9" s="94"/>
+      <c r="AE9" s="94"/>
+      <c r="AF9" s="94"/>
+      <c r="AG9" s="95"/>
       <c r="AH9" s="7"/>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
       <c r="AK9" s="8"/>
       <c r="AL9" s="8"/>
       <c r="AM9" s="8"/>
-      <c r="AN9" s="259"/>
-      <c r="AO9" s="260"/>
+      <c r="AN9" s="96"/>
+      <c r="AO9" s="97"/>
       <c r="AP9" s="8"/>
       <c r="AQ9" s="8"/>
       <c r="AR9" s="8"/>
@@ -9785,10 +9931,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -9834,50 +9980,50 @@
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="220" t="s">
+      <c r="D11" s="131" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="220"/>
-      <c r="F11" s="220"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="221"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="222"/>
-      <c r="K11" s="222"/>
-      <c r="L11" s="222"/>
-      <c r="M11" s="222"/>
-      <c r="N11" s="222"/>
-      <c r="O11" s="222"/>
-      <c r="P11" s="222"/>
-      <c r="Q11" s="222"/>
-      <c r="R11" s="222"/>
-      <c r="S11" s="222"/>
-      <c r="T11" s="222"/>
-      <c r="U11" s="222"/>
-      <c r="V11" s="222"/>
-      <c r="W11" s="222"/>
-      <c r="X11" s="222"/>
-      <c r="Y11" s="222"/>
-      <c r="Z11" s="222"/>
-      <c r="AA11" s="222"/>
-      <c r="AB11" s="222"/>
-      <c r="AC11" s="222"/>
-      <c r="AD11" s="222"/>
-      <c r="AE11" s="222"/>
-      <c r="AF11" s="222"/>
-      <c r="AG11" s="223"/>
-      <c r="AH11" s="224" t="s">
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="133"/>
+      <c r="O11" s="133"/>
+      <c r="P11" s="133"/>
+      <c r="Q11" s="133"/>
+      <c r="R11" s="133"/>
+      <c r="S11" s="133"/>
+      <c r="T11" s="133"/>
+      <c r="U11" s="133"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="133"/>
+      <c r="X11" s="133"/>
+      <c r="Y11" s="133"/>
+      <c r="Z11" s="133"/>
+      <c r="AA11" s="133"/>
+      <c r="AB11" s="133"/>
+      <c r="AC11" s="133"/>
+      <c r="AD11" s="133"/>
+      <c r="AE11" s="133"/>
+      <c r="AF11" s="133"/>
+      <c r="AG11" s="134"/>
+      <c r="AH11" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="AI11" s="225"/>
-      <c r="AJ11" s="225"/>
-      <c r="AK11" s="226"/>
-      <c r="AL11" s="227" t="s">
+      <c r="AI11" s="136"/>
+      <c r="AJ11" s="136"/>
+      <c r="AK11" s="137"/>
+      <c r="AL11" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="AM11" s="228"/>
-      <c r="AN11" s="228"/>
-      <c r="AO11" s="228"/>
+      <c r="AM11" s="139"/>
+      <c r="AN11" s="139"/>
+      <c r="AO11" s="139"/>
       <c r="AP11" s="11"/>
       <c r="AQ11" s="12"/>
       <c r="AR11" s="12"/>
@@ -9889,54 +10035,54 @@
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="229" t="s">
+      <c r="D12" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="229"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="230"/>
-      <c r="H12" s="231" t="s">
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="232"/>
-      <c r="J12" s="233"/>
-      <c r="K12" s="240"/>
-      <c r="L12" s="241"/>
-      <c r="M12" s="241"/>
-      <c r="N12" s="241"/>
-      <c r="O12" s="241"/>
-      <c r="P12" s="241"/>
-      <c r="Q12" s="241"/>
-      <c r="R12" s="241"/>
-      <c r="S12" s="241"/>
-      <c r="T12" s="241"/>
-      <c r="U12" s="241"/>
-      <c r="V12" s="241"/>
-      <c r="W12" s="242"/>
-      <c r="X12" s="242"/>
-      <c r="Y12" s="242"/>
-      <c r="Z12" s="242"/>
-      <c r="AA12" s="243" t="s">
+      <c r="I12" s="111"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="120"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="120"/>
+      <c r="S12" s="120"/>
+      <c r="T12" s="120"/>
+      <c r="U12" s="120"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="121"/>
+      <c r="X12" s="121"/>
+      <c r="Y12" s="121"/>
+      <c r="Z12" s="121"/>
+      <c r="AA12" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="AB12" s="244"/>
-      <c r="AC12" s="245"/>
-      <c r="AD12" s="209"/>
-      <c r="AE12" s="209"/>
-      <c r="AF12" s="209"/>
-      <c r="AG12" s="209"/>
-      <c r="AH12" s="209"/>
-      <c r="AI12" s="209"/>
-      <c r="AJ12" s="209"/>
-      <c r="AK12" s="209"/>
-      <c r="AL12" s="209"/>
-      <c r="AM12" s="209"/>
-      <c r="AN12" s="209"/>
-      <c r="AO12" s="209"/>
-      <c r="AP12" s="210"/>
-      <c r="AQ12" s="210"/>
-      <c r="AR12" s="210"/>
-      <c r="AS12" s="210"/>
+      <c r="AB12" s="123"/>
+      <c r="AC12" s="124"/>
+      <c r="AD12" s="140"/>
+      <c r="AE12" s="140"/>
+      <c r="AF12" s="140"/>
+      <c r="AG12" s="140"/>
+      <c r="AH12" s="140"/>
+      <c r="AI12" s="140"/>
+      <c r="AJ12" s="140"/>
+      <c r="AK12" s="140"/>
+      <c r="AL12" s="140"/>
+      <c r="AM12" s="140"/>
+      <c r="AN12" s="140"/>
+      <c r="AO12" s="140"/>
+      <c r="AP12" s="141"/>
+      <c r="AQ12" s="141"/>
+      <c r="AR12" s="141"/>
+      <c r="AS12" s="141"/>
       <c r="AT12" s="4"/>
       <c r="AU12" s="1"/>
     </row>
@@ -9944,52 +10090,52 @@
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="165"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="235"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="211" t="s">
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="212"/>
-      <c r="M13" s="212"/>
-      <c r="N13" s="215"/>
-      <c r="O13" s="216"/>
-      <c r="P13" s="216"/>
-      <c r="Q13" s="216"/>
-      <c r="R13" s="216"/>
-      <c r="S13" s="216"/>
-      <c r="T13" s="216"/>
-      <c r="U13" s="216"/>
-      <c r="V13" s="216"/>
-      <c r="W13" s="216"/>
-      <c r="X13" s="216"/>
-      <c r="Y13" s="216"/>
-      <c r="Z13" s="217"/>
-      <c r="AA13" s="246"/>
-      <c r="AB13" s="247"/>
-      <c r="AC13" s="248"/>
-      <c r="AD13" s="212" t="s">
+      <c r="L13" s="143"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="146"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="147"/>
+      <c r="Q13" s="147"/>
+      <c r="R13" s="147"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="147"/>
+      <c r="X13" s="147"/>
+      <c r="Y13" s="147"/>
+      <c r="Z13" s="148"/>
+      <c r="AA13" s="125"/>
+      <c r="AB13" s="126"/>
+      <c r="AC13" s="127"/>
+      <c r="AD13" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="AE13" s="212"/>
-      <c r="AF13" s="212"/>
-      <c r="AG13" s="215"/>
-      <c r="AH13" s="216"/>
-      <c r="AI13" s="216"/>
-      <c r="AJ13" s="216"/>
-      <c r="AK13" s="216"/>
-      <c r="AL13" s="216"/>
-      <c r="AM13" s="216"/>
-      <c r="AN13" s="216"/>
-      <c r="AO13" s="216"/>
-      <c r="AP13" s="216"/>
-      <c r="AQ13" s="216"/>
-      <c r="AR13" s="216"/>
-      <c r="AS13" s="216"/>
+      <c r="AE13" s="143"/>
+      <c r="AF13" s="143"/>
+      <c r="AG13" s="146"/>
+      <c r="AH13" s="147"/>
+      <c r="AI13" s="147"/>
+      <c r="AJ13" s="147"/>
+      <c r="AK13" s="147"/>
+      <c r="AL13" s="147"/>
+      <c r="AM13" s="147"/>
+      <c r="AN13" s="147"/>
+      <c r="AO13" s="147"/>
+      <c r="AP13" s="147"/>
+      <c r="AQ13" s="147"/>
+      <c r="AR13" s="147"/>
+      <c r="AS13" s="147"/>
       <c r="AT13" s="4"/>
       <c r="AU13" s="1"/>
     </row>
@@ -9997,48 +10143,48 @@
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="166"/>
-      <c r="G14" s="167"/>
-      <c r="H14" s="237"/>
-      <c r="I14" s="238"/>
-      <c r="J14" s="239"/>
-      <c r="K14" s="213"/>
-      <c r="L14" s="214"/>
-      <c r="M14" s="214"/>
-      <c r="N14" s="218"/>
-      <c r="O14" s="218"/>
-      <c r="P14" s="218"/>
-      <c r="Q14" s="218"/>
-      <c r="R14" s="218"/>
-      <c r="S14" s="218"/>
-      <c r="T14" s="218"/>
-      <c r="U14" s="218"/>
-      <c r="V14" s="218"/>
-      <c r="W14" s="218"/>
-      <c r="X14" s="218"/>
-      <c r="Y14" s="218"/>
-      <c r="Z14" s="219"/>
-      <c r="AA14" s="249"/>
-      <c r="AB14" s="250"/>
-      <c r="AC14" s="251"/>
-      <c r="AD14" s="214"/>
-      <c r="AE14" s="214"/>
-      <c r="AF14" s="214"/>
-      <c r="AG14" s="218"/>
-      <c r="AH14" s="218"/>
-      <c r="AI14" s="218"/>
-      <c r="AJ14" s="218"/>
-      <c r="AK14" s="218"/>
-      <c r="AL14" s="218"/>
-      <c r="AM14" s="218"/>
-      <c r="AN14" s="218"/>
-      <c r="AO14" s="218"/>
-      <c r="AP14" s="218"/>
-      <c r="AQ14" s="218"/>
-      <c r="AR14" s="218"/>
-      <c r="AS14" s="218"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="145"/>
+      <c r="N14" s="149"/>
+      <c r="O14" s="149"/>
+      <c r="P14" s="149"/>
+      <c r="Q14" s="149"/>
+      <c r="R14" s="149"/>
+      <c r="S14" s="149"/>
+      <c r="T14" s="149"/>
+      <c r="U14" s="149"/>
+      <c r="V14" s="149"/>
+      <c r="W14" s="149"/>
+      <c r="X14" s="149"/>
+      <c r="Y14" s="149"/>
+      <c r="Z14" s="150"/>
+      <c r="AA14" s="128"/>
+      <c r="AB14" s="129"/>
+      <c r="AC14" s="130"/>
+      <c r="AD14" s="145"/>
+      <c r="AE14" s="145"/>
+      <c r="AF14" s="145"/>
+      <c r="AG14" s="149"/>
+      <c r="AH14" s="149"/>
+      <c r="AI14" s="149"/>
+      <c r="AJ14" s="149"/>
+      <c r="AK14" s="149"/>
+      <c r="AL14" s="149"/>
+      <c r="AM14" s="149"/>
+      <c r="AN14" s="149"/>
+      <c r="AO14" s="149"/>
+      <c r="AP14" s="149"/>
+      <c r="AQ14" s="149"/>
+      <c r="AR14" s="149"/>
+      <c r="AS14" s="149"/>
       <c r="AT14" s="4"/>
       <c r="AU14" s="1"/>
     </row>
@@ -10097,56 +10243,52 @@
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="203" t="s">
+      <c r="D16" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="204"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="204"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="89"/>
-      <c r="M16" s="89"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="88" t="s">
-        <v>68</v>
-      </c>
-      <c r="P16" s="89"/>
-      <c r="Q16" s="89"/>
-      <c r="R16" s="89"/>
-      <c r="S16" s="89"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="89"/>
-      <c r="W16" s="89"/>
-      <c r="X16" s="89"/>
-      <c r="Y16" s="89"/>
-      <c r="Z16" s="90"/>
-      <c r="AA16" s="79" t="s">
+      <c r="I16" s="162"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="163"/>
+      <c r="L16" s="163"/>
+      <c r="M16" s="163"/>
+      <c r="N16" s="164"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="163"/>
+      <c r="R16" s="163"/>
+      <c r="S16" s="163"/>
+      <c r="T16" s="164"/>
+      <c r="U16" s="162"/>
+      <c r="V16" s="163"/>
+      <c r="W16" s="163"/>
+      <c r="X16" s="163"/>
+      <c r="Y16" s="163"/>
+      <c r="Z16" s="164"/>
+      <c r="AA16" s="230" t="s">
         <v>64</v>
       </c>
-      <c r="AB16" s="80"/>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="80"/>
-      <c r="AE16" s="80"/>
-      <c r="AF16" s="80"/>
-      <c r="AG16" s="80"/>
-      <c r="AH16" s="80"/>
-      <c r="AI16" s="80"/>
-      <c r="AJ16" s="80"/>
-      <c r="AK16" s="80"/>
-      <c r="AL16" s="80"/>
-      <c r="AM16" s="80"/>
-      <c r="AN16" s="80"/>
-      <c r="AO16" s="80"/>
-      <c r="AP16" s="80"/>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="80"/>
-      <c r="AS16" s="81"/>
+      <c r="AB16" s="231"/>
+      <c r="AC16" s="231"/>
+      <c r="AD16" s="231"/>
+      <c r="AE16" s="231"/>
+      <c r="AF16" s="231"/>
+      <c r="AG16" s="231"/>
+      <c r="AH16" s="231"/>
+      <c r="AI16" s="231"/>
+      <c r="AJ16" s="231"/>
+      <c r="AK16" s="231"/>
+      <c r="AL16" s="231"/>
+      <c r="AM16" s="231"/>
+      <c r="AN16" s="231"/>
+      <c r="AO16" s="231"/>
+      <c r="AP16" s="231"/>
+      <c r="AQ16" s="231"/>
+      <c r="AR16" s="231"/>
+      <c r="AS16" s="232"/>
       <c r="AT16" s="4"/>
       <c r="AU16" s="1"/>
     </row>
@@ -10154,50 +10296,50 @@
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="205"/>
-      <c r="E17" s="206"/>
-      <c r="F17" s="206"/>
-      <c r="G17" s="206"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
       <c r="H17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="91"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="92"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="92"/>
-      <c r="Q17" s="92"/>
-      <c r="R17" s="92"/>
-      <c r="S17" s="92"/>
-      <c r="T17" s="93"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="92"/>
-      <c r="W17" s="92"/>
-      <c r="X17" s="92"/>
-      <c r="Y17" s="92"/>
-      <c r="Z17" s="93"/>
-      <c r="AA17" s="82"/>
-      <c r="AB17" s="83"/>
-      <c r="AC17" s="83"/>
-      <c r="AD17" s="83"/>
-      <c r="AE17" s="83"/>
-      <c r="AF17" s="83"/>
-      <c r="AG17" s="83"/>
-      <c r="AH17" s="83"/>
-      <c r="AI17" s="83"/>
-      <c r="AJ17" s="83"/>
-      <c r="AK17" s="83"/>
-      <c r="AL17" s="83"/>
-      <c r="AM17" s="83"/>
-      <c r="AN17" s="83"/>
-      <c r="AO17" s="83"/>
-      <c r="AP17" s="83"/>
-      <c r="AQ17" s="83"/>
-      <c r="AR17" s="83"/>
-      <c r="AS17" s="84"/>
+      <c r="I17" s="165"/>
+      <c r="J17" s="166"/>
+      <c r="K17" s="166"/>
+      <c r="L17" s="166"/>
+      <c r="M17" s="166"/>
+      <c r="N17" s="167"/>
+      <c r="O17" s="165"/>
+      <c r="P17" s="166"/>
+      <c r="Q17" s="166"/>
+      <c r="R17" s="166"/>
+      <c r="S17" s="166"/>
+      <c r="T17" s="167"/>
+      <c r="U17" s="165"/>
+      <c r="V17" s="166"/>
+      <c r="W17" s="166"/>
+      <c r="X17" s="166"/>
+      <c r="Y17" s="166"/>
+      <c r="Z17" s="167"/>
+      <c r="AA17" s="233"/>
+      <c r="AB17" s="234"/>
+      <c r="AC17" s="234"/>
+      <c r="AD17" s="234"/>
+      <c r="AE17" s="234"/>
+      <c r="AF17" s="234"/>
+      <c r="AG17" s="234"/>
+      <c r="AH17" s="234"/>
+      <c r="AI17" s="234"/>
+      <c r="AJ17" s="234"/>
+      <c r="AK17" s="234"/>
+      <c r="AL17" s="234"/>
+      <c r="AM17" s="234"/>
+      <c r="AN17" s="234"/>
+      <c r="AO17" s="234"/>
+      <c r="AP17" s="234"/>
+      <c r="AQ17" s="234"/>
+      <c r="AR17" s="234"/>
+      <c r="AS17" s="235"/>
       <c r="AT17" s="4"/>
       <c r="AU17" s="1"/>
     </row>
@@ -10205,50 +10347,50 @@
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="205"/>
-      <c r="E18" s="206"/>
-      <c r="F18" s="206"/>
-      <c r="G18" s="206"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
       <c r="H18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="91"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="92"/>
-      <c r="M18" s="92"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="92"/>
-      <c r="S18" s="92"/>
-      <c r="T18" s="93"/>
-      <c r="U18" s="91"/>
-      <c r="V18" s="92"/>
-      <c r="W18" s="92"/>
-      <c r="X18" s="92"/>
-      <c r="Y18" s="92"/>
-      <c r="Z18" s="93"/>
-      <c r="AA18" s="82"/>
-      <c r="AB18" s="83"/>
-      <c r="AC18" s="83"/>
-      <c r="AD18" s="83"/>
-      <c r="AE18" s="83"/>
-      <c r="AF18" s="83"/>
-      <c r="AG18" s="83"/>
-      <c r="AH18" s="83"/>
-      <c r="AI18" s="83"/>
-      <c r="AJ18" s="83"/>
-      <c r="AK18" s="83"/>
-      <c r="AL18" s="83"/>
-      <c r="AM18" s="83"/>
-      <c r="AN18" s="83"/>
-      <c r="AO18" s="83"/>
-      <c r="AP18" s="83"/>
-      <c r="AQ18" s="83"/>
-      <c r="AR18" s="83"/>
-      <c r="AS18" s="84"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="166"/>
+      <c r="K18" s="166"/>
+      <c r="L18" s="166"/>
+      <c r="M18" s="166"/>
+      <c r="N18" s="167"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="166"/>
+      <c r="Q18" s="166"/>
+      <c r="R18" s="166"/>
+      <c r="S18" s="166"/>
+      <c r="T18" s="167"/>
+      <c r="U18" s="165"/>
+      <c r="V18" s="166"/>
+      <c r="W18" s="166"/>
+      <c r="X18" s="166"/>
+      <c r="Y18" s="166"/>
+      <c r="Z18" s="167"/>
+      <c r="AA18" s="233"/>
+      <c r="AB18" s="234"/>
+      <c r="AC18" s="234"/>
+      <c r="AD18" s="234"/>
+      <c r="AE18" s="234"/>
+      <c r="AF18" s="234"/>
+      <c r="AG18" s="234"/>
+      <c r="AH18" s="234"/>
+      <c r="AI18" s="234"/>
+      <c r="AJ18" s="234"/>
+      <c r="AK18" s="234"/>
+      <c r="AL18" s="234"/>
+      <c r="AM18" s="234"/>
+      <c r="AN18" s="234"/>
+      <c r="AO18" s="234"/>
+      <c r="AP18" s="234"/>
+      <c r="AQ18" s="234"/>
+      <c r="AR18" s="234"/>
+      <c r="AS18" s="235"/>
       <c r="AT18" s="4"/>
       <c r="AU18" s="1"/>
       <c r="AX18" s="3" t="s">
@@ -10259,50 +10401,50 @@
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="206"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="76"/>
       <c r="H19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="92"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="92"/>
-      <c r="Q19" s="92"/>
-      <c r="R19" s="92"/>
-      <c r="S19" s="92"/>
-      <c r="T19" s="93"/>
-      <c r="U19" s="91"/>
-      <c r="V19" s="92"/>
-      <c r="W19" s="92"/>
-      <c r="X19" s="92"/>
-      <c r="Y19" s="92"/>
-      <c r="Z19" s="93"/>
-      <c r="AA19" s="85"/>
-      <c r="AB19" s="86"/>
-      <c r="AC19" s="86"/>
-      <c r="AD19" s="86"/>
-      <c r="AE19" s="86"/>
-      <c r="AF19" s="86"/>
-      <c r="AG19" s="86"/>
-      <c r="AH19" s="86"/>
-      <c r="AI19" s="86"/>
-      <c r="AJ19" s="86"/>
-      <c r="AK19" s="86"/>
-      <c r="AL19" s="86"/>
-      <c r="AM19" s="86"/>
-      <c r="AN19" s="86"/>
-      <c r="AO19" s="86"/>
-      <c r="AP19" s="86"/>
-      <c r="AQ19" s="86"/>
-      <c r="AR19" s="86"/>
-      <c r="AS19" s="87"/>
+      <c r="I19" s="165"/>
+      <c r="J19" s="166"/>
+      <c r="K19" s="166"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="166"/>
+      <c r="N19" s="167"/>
+      <c r="O19" s="165"/>
+      <c r="P19" s="166"/>
+      <c r="Q19" s="166"/>
+      <c r="R19" s="166"/>
+      <c r="S19" s="166"/>
+      <c r="T19" s="167"/>
+      <c r="U19" s="165"/>
+      <c r="V19" s="166"/>
+      <c r="W19" s="166"/>
+      <c r="X19" s="166"/>
+      <c r="Y19" s="166"/>
+      <c r="Z19" s="167"/>
+      <c r="AA19" s="236"/>
+      <c r="AB19" s="237"/>
+      <c r="AC19" s="237"/>
+      <c r="AD19" s="237"/>
+      <c r="AE19" s="237"/>
+      <c r="AF19" s="237"/>
+      <c r="AG19" s="237"/>
+      <c r="AH19" s="237"/>
+      <c r="AI19" s="237"/>
+      <c r="AJ19" s="237"/>
+      <c r="AK19" s="237"/>
+      <c r="AL19" s="237"/>
+      <c r="AM19" s="237"/>
+      <c r="AN19" s="237"/>
+      <c r="AO19" s="237"/>
+      <c r="AP19" s="237"/>
+      <c r="AQ19" s="237"/>
+      <c r="AR19" s="237"/>
+      <c r="AS19" s="238"/>
       <c r="AT19" s="4"/>
       <c r="AU19" s="1"/>
     </row>
@@ -10310,66 +10452,66 @@
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="207"/>
-      <c r="E20" s="208"/>
-      <c r="F20" s="208"/>
-      <c r="G20" s="208"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
       <c r="H20" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="192">
+      <c r="I20" s="151">
         <f>SUM(I17:Z19)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="193"/>
-      <c r="K20" s="193"/>
-      <c r="L20" s="193"/>
-      <c r="M20" s="193"/>
-      <c r="N20" s="193"/>
-      <c r="O20" s="193"/>
-      <c r="P20" s="193"/>
-      <c r="Q20" s="193"/>
-      <c r="R20" s="193"/>
-      <c r="S20" s="193"/>
-      <c r="T20" s="193"/>
-      <c r="U20" s="193"/>
-      <c r="V20" s="193"/>
-      <c r="W20" s="194"/>
-      <c r="X20" s="194"/>
-      <c r="Y20" s="194"/>
-      <c r="Z20" s="194"/>
-      <c r="AA20" s="194"/>
-      <c r="AB20" s="194"/>
-      <c r="AC20" s="194"/>
-      <c r="AD20" s="194"/>
-      <c r="AE20" s="194"/>
-      <c r="AF20" s="194"/>
-      <c r="AG20" s="194"/>
-      <c r="AH20" s="194"/>
-      <c r="AI20" s="194"/>
-      <c r="AJ20" s="194"/>
-      <c r="AK20" s="194"/>
-      <c r="AL20" s="194"/>
-      <c r="AM20" s="194"/>
-      <c r="AN20" s="194"/>
-      <c r="AO20" s="194"/>
-      <c r="AP20" s="194"/>
-      <c r="AQ20" s="194"/>
-      <c r="AR20" s="194"/>
-      <c r="AS20" s="194"/>
-      <c r="AT20" s="194"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="152"/>
+      <c r="M20" s="152"/>
+      <c r="N20" s="152"/>
+      <c r="O20" s="152"/>
+      <c r="P20" s="152"/>
+      <c r="Q20" s="152"/>
+      <c r="R20" s="152"/>
+      <c r="S20" s="152"/>
+      <c r="T20" s="152"/>
+      <c r="U20" s="152"/>
+      <c r="V20" s="152"/>
+      <c r="W20" s="153"/>
+      <c r="X20" s="153"/>
+      <c r="Y20" s="153"/>
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="153"/>
+      <c r="AB20" s="153"/>
+      <c r="AC20" s="153"/>
+      <c r="AD20" s="153"/>
+      <c r="AE20" s="153"/>
+      <c r="AF20" s="153"/>
+      <c r="AG20" s="153"/>
+      <c r="AH20" s="153"/>
+      <c r="AI20" s="153"/>
+      <c r="AJ20" s="153"/>
+      <c r="AK20" s="153"/>
+      <c r="AL20" s="153"/>
+      <c r="AM20" s="153"/>
+      <c r="AN20" s="153"/>
+      <c r="AO20" s="153"/>
+      <c r="AP20" s="153"/>
+      <c r="AQ20" s="153"/>
+      <c r="AR20" s="153"/>
+      <c r="AS20" s="153"/>
+      <c r="AT20" s="153"/>
       <c r="AU20" s="1"/>
     </row>
     <row r="21" spans="1:50" ht="21" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="195" t="s">
+      <c r="D21" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="195"/>
-      <c r="F21" s="195"/>
-      <c r="G21" s="196"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="155"/>
       <c r="H21" s="17" t="s">
         <v>26</v>
       </c>
@@ -10378,17 +10520,17 @@
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
-      <c r="N21" s="199"/>
-      <c r="O21" s="199"/>
-      <c r="P21" s="199"/>
-      <c r="Q21" s="199"/>
-      <c r="R21" s="199"/>
-      <c r="S21" s="199"/>
-      <c r="T21" s="199"/>
-      <c r="U21" s="199"/>
-      <c r="V21" s="199"/>
-      <c r="W21" s="199"/>
-      <c r="X21" s="199"/>
+      <c r="N21" s="158"/>
+      <c r="O21" s="158"/>
+      <c r="P21" s="158"/>
+      <c r="Q21" s="158"/>
+      <c r="R21" s="158"/>
+      <c r="S21" s="158"/>
+      <c r="T21" s="158"/>
+      <c r="U21" s="158"/>
+      <c r="V21" s="158"/>
+      <c r="W21" s="158"/>
+      <c r="X21" s="158"/>
       <c r="Y21" s="17" t="s">
         <v>27</v>
       </c>
@@ -10419,49 +10561,49 @@
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="197"/>
-      <c r="E22" s="197"/>
-      <c r="F22" s="197"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="200" t="s">
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="156"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="201"/>
-      <c r="J22" s="201"/>
-      <c r="K22" s="201"/>
-      <c r="L22" s="201"/>
-      <c r="M22" s="201"/>
-      <c r="N22" s="201"/>
-      <c r="O22" s="201"/>
-      <c r="P22" s="201"/>
-      <c r="Q22" s="201"/>
-      <c r="R22" s="201"/>
-      <c r="S22" s="201"/>
-      <c r="T22" s="201"/>
-      <c r="U22" s="201"/>
-      <c r="V22" s="201"/>
-      <c r="W22" s="201"/>
-      <c r="X22" s="201"/>
-      <c r="Y22" s="201"/>
-      <c r="Z22" s="201"/>
-      <c r="AA22" s="202" t="s">
+      <c r="I22" s="160"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="160"/>
+      <c r="M22" s="160"/>
+      <c r="N22" s="160"/>
+      <c r="O22" s="160"/>
+      <c r="P22" s="160"/>
+      <c r="Q22" s="160"/>
+      <c r="R22" s="160"/>
+      <c r="S22" s="160"/>
+      <c r="T22" s="160"/>
+      <c r="U22" s="160"/>
+      <c r="V22" s="160"/>
+      <c r="W22" s="160"/>
+      <c r="X22" s="160"/>
+      <c r="Y22" s="160"/>
+      <c r="Z22" s="160"/>
+      <c r="AA22" s="161" t="s">
         <v>29</v>
       </c>
-      <c r="AB22" s="202"/>
-      <c r="AC22" s="202"/>
-      <c r="AD22" s="202"/>
-      <c r="AE22" s="202"/>
-      <c r="AF22" s="202"/>
-      <c r="AG22" s="202"/>
-      <c r="AH22" s="202"/>
-      <c r="AI22" s="202"/>
-      <c r="AJ22" s="202"/>
-      <c r="AK22" s="202"/>
-      <c r="AL22" s="202"/>
-      <c r="AM22" s="202"/>
-      <c r="AN22" s="202"/>
-      <c r="AO22" s="202"/>
-      <c r="AP22" s="202"/>
+      <c r="AB22" s="161"/>
+      <c r="AC22" s="161"/>
+      <c r="AD22" s="161"/>
+      <c r="AE22" s="161"/>
+      <c r="AF22" s="161"/>
+      <c r="AG22" s="161"/>
+      <c r="AH22" s="161"/>
+      <c r="AI22" s="161"/>
+      <c r="AJ22" s="161"/>
+      <c r="AK22" s="161"/>
+      <c r="AL22" s="161"/>
+      <c r="AM22" s="161"/>
+      <c r="AN22" s="161"/>
+      <c r="AO22" s="161"/>
+      <c r="AP22" s="161"/>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="19"/>
       <c r="AS22" s="19"/>
@@ -10472,20 +10614,20 @@
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="162" t="s">
+      <c r="D23" s="178" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="162"/>
-      <c r="F23" s="162"/>
-      <c r="G23" s="163"/>
-      <c r="H23" s="168" t="s">
+      <c r="E23" s="178"/>
+      <c r="F23" s="178"/>
+      <c r="G23" s="179"/>
+      <c r="H23" s="180" t="s">
         <v>31</v>
       </c>
-      <c r="I23" s="169"/>
-      <c r="J23" s="170"/>
-      <c r="K23" s="171"/>
-      <c r="L23" s="172"/>
-      <c r="M23" s="173"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="183"/>
+      <c r="L23" s="168"/>
+      <c r="M23" s="184"/>
       <c r="N23" s="36"/>
       <c r="O23" s="37" t="s">
         <v>58</v>
@@ -10493,9 +10635,9 @@
       <c r="P23" s="37"/>
       <c r="Q23" s="37"/>
       <c r="R23" s="37"/>
-      <c r="S23" s="172"/>
-      <c r="T23" s="172"/>
-      <c r="U23" s="172"/>
+      <c r="S23" s="168"/>
+      <c r="T23" s="168"/>
+      <c r="U23" s="168"/>
       <c r="V23" s="37" t="s">
         <v>59</v>
       </c>
@@ -10507,8 +10649,8 @@
       <c r="Z23" s="37"/>
       <c r="AA23" s="37"/>
       <c r="AB23" s="37"/>
-      <c r="AC23" s="172"/>
-      <c r="AD23" s="172"/>
+      <c r="AC23" s="168"/>
+      <c r="AD23" s="168"/>
       <c r="AE23" s="37" t="s">
         <v>61</v>
       </c>
@@ -10523,8 +10665,8 @@
       <c r="AL23" s="37"/>
       <c r="AM23" s="37"/>
       <c r="AN23" s="37"/>
-      <c r="AO23" s="172"/>
-      <c r="AP23" s="172"/>
+      <c r="AO23" s="168"/>
+      <c r="AP23" s="168"/>
       <c r="AQ23" s="37" t="s">
         <v>63</v>
       </c>
@@ -10537,50 +10679,50 @@
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="164"/>
-      <c r="E24" s="164"/>
-      <c r="F24" s="164"/>
-      <c r="G24" s="165"/>
-      <c r="H24" s="183" t="s">
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="184"/>
-      <c r="J24" s="185"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="186"/>
-      <c r="O24" s="187"/>
-      <c r="P24" s="187"/>
-      <c r="Q24" s="187"/>
-      <c r="R24" s="187"/>
-      <c r="S24" s="187"/>
-      <c r="T24" s="187"/>
-      <c r="U24" s="187"/>
-      <c r="V24" s="187"/>
-      <c r="W24" s="187"/>
-      <c r="X24" s="187"/>
-      <c r="Y24" s="187"/>
-      <c r="Z24" s="187"/>
-      <c r="AA24" s="187"/>
-      <c r="AB24" s="187"/>
-      <c r="AC24" s="187"/>
-      <c r="AD24" s="187"/>
-      <c r="AE24" s="187"/>
-      <c r="AF24" s="187"/>
-      <c r="AG24" s="187"/>
-      <c r="AH24" s="187"/>
-      <c r="AI24" s="187"/>
-      <c r="AJ24" s="187"/>
-      <c r="AK24" s="187"/>
-      <c r="AL24" s="187"/>
-      <c r="AM24" s="187"/>
-      <c r="AN24" s="187"/>
-      <c r="AO24" s="187"/>
-      <c r="AP24" s="187"/>
-      <c r="AQ24" s="187"/>
-      <c r="AR24" s="187"/>
-      <c r="AS24" s="187"/>
+      <c r="I24" s="170"/>
+      <c r="J24" s="171"/>
+      <c r="K24" s="165"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="167"/>
+      <c r="N24" s="172"/>
+      <c r="O24" s="173"/>
+      <c r="P24" s="173"/>
+      <c r="Q24" s="173"/>
+      <c r="R24" s="173"/>
+      <c r="S24" s="173"/>
+      <c r="T24" s="173"/>
+      <c r="U24" s="173"/>
+      <c r="V24" s="173"/>
+      <c r="W24" s="173"/>
+      <c r="X24" s="173"/>
+      <c r="Y24" s="173"/>
+      <c r="Z24" s="173"/>
+      <c r="AA24" s="173"/>
+      <c r="AB24" s="173"/>
+      <c r="AC24" s="173"/>
+      <c r="AD24" s="173"/>
+      <c r="AE24" s="173"/>
+      <c r="AF24" s="173"/>
+      <c r="AG24" s="173"/>
+      <c r="AH24" s="173"/>
+      <c r="AI24" s="173"/>
+      <c r="AJ24" s="173"/>
+      <c r="AK24" s="173"/>
+      <c r="AL24" s="173"/>
+      <c r="AM24" s="173"/>
+      <c r="AN24" s="173"/>
+      <c r="AO24" s="173"/>
+      <c r="AP24" s="173"/>
+      <c r="AQ24" s="173"/>
+      <c r="AR24" s="173"/>
+      <c r="AS24" s="173"/>
       <c r="AT24" s="4"/>
       <c r="AU24" s="1"/>
     </row>
@@ -10588,50 +10730,50 @@
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="164"/>
-      <c r="E25" s="164"/>
-      <c r="F25" s="164"/>
-      <c r="G25" s="165"/>
-      <c r="H25" s="188" t="s">
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="189"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="189"/>
-      <c r="L25" s="189"/>
-      <c r="M25" s="189"/>
-      <c r="N25" s="189"/>
-      <c r="O25" s="189"/>
-      <c r="P25" s="189"/>
-      <c r="Q25" s="189"/>
-      <c r="R25" s="189"/>
-      <c r="S25" s="189"/>
-      <c r="T25" s="189"/>
-      <c r="U25" s="189"/>
-      <c r="V25" s="189"/>
-      <c r="W25" s="189"/>
-      <c r="X25" s="189"/>
-      <c r="Y25" s="189"/>
-      <c r="Z25" s="189"/>
-      <c r="AA25" s="189"/>
-      <c r="AB25" s="189"/>
-      <c r="AC25" s="189"/>
-      <c r="AD25" s="189"/>
-      <c r="AE25" s="189"/>
-      <c r="AF25" s="189"/>
-      <c r="AG25" s="189"/>
-      <c r="AH25" s="189"/>
-      <c r="AI25" s="189"/>
-      <c r="AJ25" s="189"/>
-      <c r="AK25" s="189"/>
-      <c r="AL25" s="189"/>
-      <c r="AM25" s="189"/>
-      <c r="AN25" s="189"/>
-      <c r="AO25" s="189"/>
-      <c r="AP25" s="189"/>
-      <c r="AQ25" s="189"/>
-      <c r="AR25" s="189"/>
-      <c r="AS25" s="189"/>
+      <c r="I25" s="175"/>
+      <c r="J25" s="175"/>
+      <c r="K25" s="175"/>
+      <c r="L25" s="175"/>
+      <c r="M25" s="175"/>
+      <c r="N25" s="175"/>
+      <c r="O25" s="175"/>
+      <c r="P25" s="175"/>
+      <c r="Q25" s="175"/>
+      <c r="R25" s="175"/>
+      <c r="S25" s="175"/>
+      <c r="T25" s="175"/>
+      <c r="U25" s="175"/>
+      <c r="V25" s="175"/>
+      <c r="W25" s="175"/>
+      <c r="X25" s="175"/>
+      <c r="Y25" s="175"/>
+      <c r="Z25" s="175"/>
+      <c r="AA25" s="175"/>
+      <c r="AB25" s="175"/>
+      <c r="AC25" s="175"/>
+      <c r="AD25" s="175"/>
+      <c r="AE25" s="175"/>
+      <c r="AF25" s="175"/>
+      <c r="AG25" s="175"/>
+      <c r="AH25" s="175"/>
+      <c r="AI25" s="175"/>
+      <c r="AJ25" s="175"/>
+      <c r="AK25" s="175"/>
+      <c r="AL25" s="175"/>
+      <c r="AM25" s="175"/>
+      <c r="AN25" s="175"/>
+      <c r="AO25" s="175"/>
+      <c r="AP25" s="175"/>
+      <c r="AQ25" s="175"/>
+      <c r="AR25" s="175"/>
+      <c r="AS25" s="175"/>
       <c r="AT25" s="4"/>
       <c r="AU25" s="1"/>
     </row>
@@ -10639,48 +10781,48 @@
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="164"/>
-      <c r="G26" s="165"/>
-      <c r="H26" s="190"/>
-      <c r="I26" s="191"/>
-      <c r="J26" s="191"/>
-      <c r="K26" s="191"/>
-      <c r="L26" s="191"/>
-      <c r="M26" s="191"/>
-      <c r="N26" s="191"/>
-      <c r="O26" s="191"/>
-      <c r="P26" s="191"/>
-      <c r="Q26" s="191"/>
-      <c r="R26" s="191"/>
-      <c r="S26" s="191"/>
-      <c r="T26" s="191"/>
-      <c r="U26" s="191"/>
-      <c r="V26" s="191"/>
-      <c r="W26" s="191"/>
-      <c r="X26" s="191"/>
-      <c r="Y26" s="191"/>
-      <c r="Z26" s="191"/>
-      <c r="AA26" s="191"/>
-      <c r="AB26" s="191"/>
-      <c r="AC26" s="191"/>
-      <c r="AD26" s="191"/>
-      <c r="AE26" s="191"/>
-      <c r="AF26" s="191"/>
-      <c r="AG26" s="191"/>
-      <c r="AH26" s="191"/>
-      <c r="AI26" s="191"/>
-      <c r="AJ26" s="191"/>
-      <c r="AK26" s="191"/>
-      <c r="AL26" s="191"/>
-      <c r="AM26" s="191"/>
-      <c r="AN26" s="191"/>
-      <c r="AO26" s="191"/>
-      <c r="AP26" s="191"/>
-      <c r="AQ26" s="191"/>
-      <c r="AR26" s="191"/>
-      <c r="AS26" s="191"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="176"/>
+      <c r="I26" s="177"/>
+      <c r="J26" s="177"/>
+      <c r="K26" s="177"/>
+      <c r="L26" s="177"/>
+      <c r="M26" s="177"/>
+      <c r="N26" s="177"/>
+      <c r="O26" s="177"/>
+      <c r="P26" s="177"/>
+      <c r="Q26" s="177"/>
+      <c r="R26" s="177"/>
+      <c r="S26" s="177"/>
+      <c r="T26" s="177"/>
+      <c r="U26" s="177"/>
+      <c r="V26" s="177"/>
+      <c r="W26" s="177"/>
+      <c r="X26" s="177"/>
+      <c r="Y26" s="177"/>
+      <c r="Z26" s="177"/>
+      <c r="AA26" s="177"/>
+      <c r="AB26" s="177"/>
+      <c r="AC26" s="177"/>
+      <c r="AD26" s="177"/>
+      <c r="AE26" s="177"/>
+      <c r="AF26" s="177"/>
+      <c r="AG26" s="177"/>
+      <c r="AH26" s="177"/>
+      <c r="AI26" s="177"/>
+      <c r="AJ26" s="177"/>
+      <c r="AK26" s="177"/>
+      <c r="AL26" s="177"/>
+      <c r="AM26" s="177"/>
+      <c r="AN26" s="177"/>
+      <c r="AO26" s="177"/>
+      <c r="AP26" s="177"/>
+      <c r="AQ26" s="177"/>
+      <c r="AR26" s="177"/>
+      <c r="AS26" s="177"/>
       <c r="AT26" s="4"/>
       <c r="AU26" s="1"/>
     </row>
@@ -10688,56 +10830,56 @@
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="164"/>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="165"/>
-      <c r="H27" s="174" t="s">
+      <c r="D27" s="106"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="175"/>
-      <c r="J27" s="176"/>
-      <c r="K27" s="180" t="s">
+      <c r="I27" s="186"/>
+      <c r="J27" s="187"/>
+      <c r="K27" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="L27" s="181"/>
-      <c r="M27" s="181"/>
-      <c r="N27" s="181"/>
-      <c r="O27" s="181"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="181"/>
-      <c r="R27" s="181"/>
-      <c r="S27" s="182"/>
-      <c r="T27" s="91" t="s">
+      <c r="L27" s="192"/>
+      <c r="M27" s="192"/>
+      <c r="N27" s="192"/>
+      <c r="O27" s="192"/>
+      <c r="P27" s="192"/>
+      <c r="Q27" s="192"/>
+      <c r="R27" s="192"/>
+      <c r="S27" s="193"/>
+      <c r="T27" s="165" t="s">
         <v>65</v>
       </c>
-      <c r="U27" s="92"/>
-      <c r="V27" s="92"/>
-      <c r="W27" s="92"/>
-      <c r="X27" s="92"/>
-      <c r="Y27" s="92"/>
-      <c r="Z27" s="92"/>
-      <c r="AA27" s="92"/>
-      <c r="AB27" s="92"/>
-      <c r="AC27" s="92"/>
-      <c r="AD27" s="93"/>
-      <c r="AE27" s="148" t="s">
+      <c r="U27" s="166"/>
+      <c r="V27" s="166"/>
+      <c r="W27" s="166"/>
+      <c r="X27" s="166"/>
+      <c r="Y27" s="166"/>
+      <c r="Z27" s="166"/>
+      <c r="AA27" s="166"/>
+      <c r="AB27" s="166"/>
+      <c r="AC27" s="166"/>
+      <c r="AD27" s="167"/>
+      <c r="AE27" s="205" t="s">
         <v>36</v>
       </c>
-      <c r="AF27" s="149"/>
-      <c r="AG27" s="149"/>
-      <c r="AH27" s="150"/>
-      <c r="AI27" s="154"/>
-      <c r="AJ27" s="155"/>
-      <c r="AK27" s="155"/>
-      <c r="AL27" s="155"/>
-      <c r="AM27" s="155"/>
-      <c r="AN27" s="155"/>
-      <c r="AO27" s="155"/>
-      <c r="AP27" s="155"/>
-      <c r="AQ27" s="155"/>
-      <c r="AR27" s="155"/>
-      <c r="AS27" s="155"/>
+      <c r="AF27" s="206"/>
+      <c r="AG27" s="206"/>
+      <c r="AH27" s="207"/>
+      <c r="AI27" s="211"/>
+      <c r="AJ27" s="212"/>
+      <c r="AK27" s="212"/>
+      <c r="AL27" s="212"/>
+      <c r="AM27" s="212"/>
+      <c r="AN27" s="212"/>
+      <c r="AO27" s="212"/>
+      <c r="AP27" s="212"/>
+      <c r="AQ27" s="212"/>
+      <c r="AR27" s="212"/>
+      <c r="AS27" s="212"/>
       <c r="AT27" s="4"/>
       <c r="AU27" s="1"/>
     </row>
@@ -10745,49 +10887,49 @@
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="166"/>
-      <c r="G28" s="167"/>
-      <c r="H28" s="177"/>
-      <c r="I28" s="178"/>
-      <c r="J28" s="179"/>
-      <c r="K28" s="156" t="s">
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="188"/>
+      <c r="I28" s="189"/>
+      <c r="J28" s="190"/>
+      <c r="K28" s="213" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="157"/>
-      <c r="M28" s="157"/>
-      <c r="N28" s="157"/>
-      <c r="O28" s="157"/>
-      <c r="P28" s="157"/>
-      <c r="Q28" s="157"/>
-      <c r="R28" s="157"/>
-      <c r="S28" s="158"/>
-      <c r="T28" s="159"/>
-      <c r="U28" s="160"/>
-      <c r="V28" s="160"/>
-      <c r="W28" s="160"/>
-      <c r="X28" s="160"/>
-      <c r="Y28" s="160"/>
-      <c r="Z28" s="160"/>
-      <c r="AA28" s="160"/>
-      <c r="AB28" s="160"/>
-      <c r="AC28" s="160"/>
-      <c r="AD28" s="161"/>
-      <c r="AE28" s="151"/>
-      <c r="AF28" s="152"/>
-      <c r="AG28" s="152"/>
-      <c r="AH28" s="153"/>
-      <c r="AI28" s="159"/>
-      <c r="AJ28" s="160"/>
-      <c r="AK28" s="160"/>
-      <c r="AL28" s="160"/>
-      <c r="AM28" s="160"/>
-      <c r="AN28" s="160"/>
-      <c r="AO28" s="160"/>
-      <c r="AP28" s="160"/>
-      <c r="AQ28" s="160"/>
-      <c r="AR28" s="160"/>
+      <c r="L28" s="214"/>
+      <c r="M28" s="214"/>
+      <c r="N28" s="214"/>
+      <c r="O28" s="214"/>
+      <c r="P28" s="214"/>
+      <c r="Q28" s="214"/>
+      <c r="R28" s="214"/>
+      <c r="S28" s="215"/>
+      <c r="T28" s="216"/>
+      <c r="U28" s="217"/>
+      <c r="V28" s="217"/>
+      <c r="W28" s="217"/>
+      <c r="X28" s="217"/>
+      <c r="Y28" s="217"/>
+      <c r="Z28" s="217"/>
+      <c r="AA28" s="217"/>
+      <c r="AB28" s="217"/>
+      <c r="AC28" s="217"/>
+      <c r="AD28" s="218"/>
+      <c r="AE28" s="208"/>
+      <c r="AF28" s="209"/>
+      <c r="AG28" s="209"/>
+      <c r="AH28" s="210"/>
+      <c r="AI28" s="216"/>
+      <c r="AJ28" s="217"/>
+      <c r="AK28" s="217"/>
+      <c r="AL28" s="217"/>
+      <c r="AM28" s="217"/>
+      <c r="AN28" s="217"/>
+      <c r="AO28" s="217"/>
+      <c r="AP28" s="217"/>
+      <c r="AQ28" s="217"/>
+      <c r="AR28" s="217"/>
       <c r="AS28" s="20"/>
       <c r="AT28" s="4"/>
       <c r="AU28" s="1"/>
@@ -10845,52 +10987,52 @@
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="95" t="s">
+      <c r="D30" s="240" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="95"/>
-      <c r="F30" s="95"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="100" t="s">
+      <c r="E30" s="240"/>
+      <c r="F30" s="240"/>
+      <c r="G30" s="241"/>
+      <c r="H30" s="245" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="101"/>
-      <c r="J30" s="101"/>
-      <c r="K30" s="101"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="101"/>
-      <c r="N30" s="101"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="101"/>
-      <c r="Q30" s="101"/>
-      <c r="R30" s="101"/>
-      <c r="S30" s="101"/>
-      <c r="T30" s="101"/>
-      <c r="U30" s="101"/>
-      <c r="V30" s="101"/>
-      <c r="W30" s="101"/>
-      <c r="X30" s="101"/>
-      <c r="Y30" s="101"/>
-      <c r="Z30" s="101"/>
-      <c r="AA30" s="101"/>
-      <c r="AB30" s="101"/>
-      <c r="AC30" s="101"/>
-      <c r="AD30" s="101"/>
-      <c r="AE30" s="101"/>
-      <c r="AF30" s="101"/>
-      <c r="AG30" s="101"/>
-      <c r="AH30" s="101"/>
-      <c r="AI30" s="101"/>
-      <c r="AJ30" s="101"/>
-      <c r="AK30" s="101"/>
-      <c r="AL30" s="101"/>
-      <c r="AM30" s="101"/>
-      <c r="AN30" s="101"/>
-      <c r="AO30" s="101"/>
-      <c r="AP30" s="101"/>
-      <c r="AQ30" s="101"/>
-      <c r="AR30" s="101"/>
-      <c r="AS30" s="101"/>
+      <c r="I30" s="246"/>
+      <c r="J30" s="246"/>
+      <c r="K30" s="246"/>
+      <c r="L30" s="246"/>
+      <c r="M30" s="246"/>
+      <c r="N30" s="246"/>
+      <c r="O30" s="246"/>
+      <c r="P30" s="246"/>
+      <c r="Q30" s="246"/>
+      <c r="R30" s="246"/>
+      <c r="S30" s="246"/>
+      <c r="T30" s="246"/>
+      <c r="U30" s="246"/>
+      <c r="V30" s="246"/>
+      <c r="W30" s="246"/>
+      <c r="X30" s="246"/>
+      <c r="Y30" s="246"/>
+      <c r="Z30" s="246"/>
+      <c r="AA30" s="246"/>
+      <c r="AB30" s="246"/>
+      <c r="AC30" s="246"/>
+      <c r="AD30" s="246"/>
+      <c r="AE30" s="246"/>
+      <c r="AF30" s="246"/>
+      <c r="AG30" s="246"/>
+      <c r="AH30" s="246"/>
+      <c r="AI30" s="246"/>
+      <c r="AJ30" s="246"/>
+      <c r="AK30" s="246"/>
+      <c r="AL30" s="246"/>
+      <c r="AM30" s="246"/>
+      <c r="AN30" s="246"/>
+      <c r="AO30" s="246"/>
+      <c r="AP30" s="246"/>
+      <c r="AQ30" s="246"/>
+      <c r="AR30" s="246"/>
+      <c r="AS30" s="246"/>
       <c r="AT30" s="4"/>
       <c r="AU30" s="1"/>
     </row>
@@ -10898,58 +11040,58 @@
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="102" t="s">
+      <c r="D31" s="242"/>
+      <c r="E31" s="242"/>
+      <c r="F31" s="242"/>
+      <c r="G31" s="242"/>
+      <c r="H31" s="247" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="103"/>
+      <c r="I31" s="248"/>
       <c r="J31" s="21"/>
-      <c r="K31" s="106" t="s">
+      <c r="K31" s="251" t="s">
         <v>41</v>
       </c>
-      <c r="L31" s="107"/>
-      <c r="M31" s="107"/>
-      <c r="N31" s="107"/>
-      <c r="O31" s="107"/>
-      <c r="P31" s="108"/>
-      <c r="Q31" s="109" t="s">
+      <c r="L31" s="252"/>
+      <c r="M31" s="252"/>
+      <c r="N31" s="252"/>
+      <c r="O31" s="252"/>
+      <c r="P31" s="253"/>
+      <c r="Q31" s="254" t="s">
         <v>42</v>
       </c>
-      <c r="R31" s="110"/>
-      <c r="S31" s="110"/>
-      <c r="T31" s="110"/>
-      <c r="U31" s="110"/>
-      <c r="V31" s="110"/>
-      <c r="W31" s="113" t="s">
+      <c r="R31" s="255"/>
+      <c r="S31" s="255"/>
+      <c r="T31" s="255"/>
+      <c r="U31" s="255"/>
+      <c r="V31" s="255"/>
+      <c r="W31" s="258" t="s">
         <v>43</v>
       </c>
-      <c r="X31" s="114"/>
-      <c r="Y31" s="115"/>
-      <c r="Z31" s="116"/>
-      <c r="AA31" s="117"/>
-      <c r="AB31" s="117"/>
-      <c r="AC31" s="117"/>
-      <c r="AD31" s="117"/>
-      <c r="AE31" s="117"/>
-      <c r="AF31" s="118"/>
-      <c r="AG31" s="119" t="s">
+      <c r="X31" s="259"/>
+      <c r="Y31" s="260"/>
+      <c r="Z31" s="261"/>
+      <c r="AA31" s="262"/>
+      <c r="AB31" s="262"/>
+      <c r="AC31" s="262"/>
+      <c r="AD31" s="262"/>
+      <c r="AE31" s="262"/>
+      <c r="AF31" s="263"/>
+      <c r="AG31" s="264" t="s">
         <v>44</v>
       </c>
-      <c r="AH31" s="119"/>
-      <c r="AI31" s="119"/>
-      <c r="AJ31" s="120"/>
-      <c r="AK31" s="121"/>
-      <c r="AL31" s="121"/>
-      <c r="AM31" s="121"/>
-      <c r="AN31" s="121"/>
-      <c r="AO31" s="121"/>
-      <c r="AP31" s="121"/>
-      <c r="AQ31" s="121"/>
-      <c r="AR31" s="121"/>
-      <c r="AS31" s="122"/>
+      <c r="AH31" s="264"/>
+      <c r="AI31" s="264"/>
+      <c r="AJ31" s="265"/>
+      <c r="AK31" s="266"/>
+      <c r="AL31" s="266"/>
+      <c r="AM31" s="266"/>
+      <c r="AN31" s="266"/>
+      <c r="AO31" s="266"/>
+      <c r="AP31" s="266"/>
+      <c r="AQ31" s="266"/>
+      <c r="AR31" s="266"/>
+      <c r="AS31" s="267"/>
       <c r="AT31" s="4"/>
       <c r="AU31" s="1"/>
     </row>
@@ -10957,54 +11099,54 @@
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="105"/>
+      <c r="D32" s="242"/>
+      <c r="E32" s="242"/>
+      <c r="F32" s="242"/>
+      <c r="G32" s="242"/>
+      <c r="H32" s="249"/>
+      <c r="I32" s="250"/>
       <c r="J32" s="22"/>
-      <c r="K32" s="123" t="s">
+      <c r="K32" s="268" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="123"/>
-      <c r="M32" s="123"/>
-      <c r="N32" s="123"/>
-      <c r="O32" s="123"/>
-      <c r="P32" s="124"/>
-      <c r="Q32" s="111"/>
-      <c r="R32" s="112"/>
-      <c r="S32" s="112"/>
-      <c r="T32" s="112"/>
-      <c r="U32" s="112"/>
-      <c r="V32" s="112"/>
-      <c r="W32" s="125" t="s">
+      <c r="L32" s="268"/>
+      <c r="M32" s="268"/>
+      <c r="N32" s="268"/>
+      <c r="O32" s="268"/>
+      <c r="P32" s="269"/>
+      <c r="Q32" s="256"/>
+      <c r="R32" s="257"/>
+      <c r="S32" s="257"/>
+      <c r="T32" s="257"/>
+      <c r="U32" s="257"/>
+      <c r="V32" s="257"/>
+      <c r="W32" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="X32" s="126"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="125"/>
-      <c r="AA32" s="126"/>
-      <c r="AB32" s="126"/>
-      <c r="AC32" s="126"/>
-      <c r="AD32" s="126"/>
-      <c r="AE32" s="126"/>
-      <c r="AF32" s="127"/>
-      <c r="AG32" s="140" t="s">
+      <c r="X32" s="195"/>
+      <c r="Y32" s="196"/>
+      <c r="Z32" s="194"/>
+      <c r="AA32" s="195"/>
+      <c r="AB32" s="195"/>
+      <c r="AC32" s="195"/>
+      <c r="AD32" s="195"/>
+      <c r="AE32" s="195"/>
+      <c r="AF32" s="196"/>
+      <c r="AG32" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="AH32" s="141"/>
-      <c r="AI32" s="142"/>
-      <c r="AJ32" s="143"/>
-      <c r="AK32" s="144"/>
-      <c r="AL32" s="144"/>
-      <c r="AM32" s="144"/>
-      <c r="AN32" s="144"/>
-      <c r="AO32" s="144"/>
-      <c r="AP32" s="144"/>
-      <c r="AQ32" s="144"/>
-      <c r="AR32" s="144"/>
-      <c r="AS32" s="145"/>
+      <c r="AH32" s="198"/>
+      <c r="AI32" s="199"/>
+      <c r="AJ32" s="200"/>
+      <c r="AK32" s="201"/>
+      <c r="AL32" s="201"/>
+      <c r="AM32" s="201"/>
+      <c r="AN32" s="201"/>
+      <c r="AO32" s="201"/>
+      <c r="AP32" s="201"/>
+      <c r="AQ32" s="201"/>
+      <c r="AR32" s="201"/>
+      <c r="AS32" s="202"/>
       <c r="AT32" s="4"/>
       <c r="AU32" s="1"/>
     </row>
@@ -11012,50 +11154,50 @@
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="146" t="s">
+      <c r="D33" s="243"/>
+      <c r="E33" s="243"/>
+      <c r="F33" s="243"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="I33" s="147"/>
-      <c r="J33" s="147"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="147"/>
-      <c r="M33" s="147"/>
-      <c r="N33" s="147"/>
-      <c r="O33" s="147"/>
-      <c r="P33" s="147"/>
-      <c r="Q33" s="147"/>
-      <c r="R33" s="147"/>
-      <c r="S33" s="147"/>
-      <c r="T33" s="147"/>
-      <c r="U33" s="147"/>
-      <c r="V33" s="147"/>
-      <c r="W33" s="147"/>
-      <c r="X33" s="147"/>
-      <c r="Y33" s="147"/>
-      <c r="Z33" s="147"/>
-      <c r="AA33" s="147"/>
-      <c r="AB33" s="147"/>
-      <c r="AC33" s="147"/>
-      <c r="AD33" s="147"/>
-      <c r="AE33" s="147"/>
-      <c r="AF33" s="147"/>
-      <c r="AG33" s="147"/>
-      <c r="AH33" s="147"/>
-      <c r="AI33" s="147"/>
-      <c r="AJ33" s="147"/>
-      <c r="AK33" s="147"/>
-      <c r="AL33" s="147"/>
-      <c r="AM33" s="147"/>
-      <c r="AN33" s="147"/>
-      <c r="AO33" s="147"/>
-      <c r="AP33" s="147"/>
-      <c r="AQ33" s="147"/>
-      <c r="AR33" s="147"/>
-      <c r="AS33" s="147"/>
+      <c r="I33" s="204"/>
+      <c r="J33" s="204"/>
+      <c r="K33" s="204"/>
+      <c r="L33" s="204"/>
+      <c r="M33" s="204"/>
+      <c r="N33" s="204"/>
+      <c r="O33" s="204"/>
+      <c r="P33" s="204"/>
+      <c r="Q33" s="204"/>
+      <c r="R33" s="204"/>
+      <c r="S33" s="204"/>
+      <c r="T33" s="204"/>
+      <c r="U33" s="204"/>
+      <c r="V33" s="204"/>
+      <c r="W33" s="204"/>
+      <c r="X33" s="204"/>
+      <c r="Y33" s="204"/>
+      <c r="Z33" s="204"/>
+      <c r="AA33" s="204"/>
+      <c r="AB33" s="204"/>
+      <c r="AC33" s="204"/>
+      <c r="AD33" s="204"/>
+      <c r="AE33" s="204"/>
+      <c r="AF33" s="204"/>
+      <c r="AG33" s="204"/>
+      <c r="AH33" s="204"/>
+      <c r="AI33" s="204"/>
+      <c r="AJ33" s="204"/>
+      <c r="AK33" s="204"/>
+      <c r="AL33" s="204"/>
+      <c r="AM33" s="204"/>
+      <c r="AN33" s="204"/>
+      <c r="AO33" s="204"/>
+      <c r="AP33" s="204"/>
+      <c r="AQ33" s="204"/>
+      <c r="AR33" s="204"/>
+      <c r="AS33" s="204"/>
       <c r="AT33" s="4"/>
       <c r="AU33" s="1"/>
     </row>
@@ -11112,15 +11254,15 @@
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="138" t="s">
+      <c r="D35" s="228" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="139"/>
-      <c r="F35" s="139"/>
-      <c r="G35" s="139"/>
-      <c r="H35" s="139"/>
-      <c r="I35" s="139"/>
-      <c r="J35" s="139"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="229"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
@@ -11335,18 +11477,18 @@
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
-      <c r="F40" s="94"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="94"/>
-      <c r="I40" s="94"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="94"/>
-      <c r="L40" s="94"/>
-      <c r="M40" s="94"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="94"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="239"/>
+      <c r="F40" s="239"/>
+      <c r="G40" s="239"/>
+      <c r="H40" s="239"/>
+      <c r="I40" s="239"/>
+      <c r="J40" s="239"/>
+      <c r="K40" s="239"/>
+      <c r="L40" s="239"/>
+      <c r="M40" s="239"/>
+      <c r="N40" s="239"/>
+      <c r="O40" s="239"/>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
@@ -11482,50 +11624,50 @@
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="128">
+      <c r="D43" s="219">
         <f ca="1">TODAY()</f>
-        <v>46175</v>
+        <v>46190</v>
       </c>
-      <c r="E43" s="128"/>
-      <c r="F43" s="128"/>
-      <c r="G43" s="128"/>
-      <c r="H43" s="128"/>
-      <c r="I43" s="128"/>
-      <c r="J43" s="128"/>
-      <c r="K43" s="128"/>
-      <c r="L43" s="128"/>
-      <c r="M43" s="128"/>
-      <c r="N43" s="128"/>
-      <c r="O43" s="128"/>
-      <c r="P43" s="128"/>
-      <c r="Q43" s="128"/>
-      <c r="R43" s="128"/>
-      <c r="S43" s="128"/>
-      <c r="T43" s="128"/>
-      <c r="U43" s="128"/>
-      <c r="V43" s="128"/>
-      <c r="W43" s="128"/>
-      <c r="X43" s="128"/>
-      <c r="Y43" s="128"/>
-      <c r="Z43" s="128"/>
-      <c r="AA43" s="128"/>
-      <c r="AB43" s="128"/>
-      <c r="AC43" s="128"/>
-      <c r="AD43" s="128"/>
-      <c r="AE43" s="128"/>
-      <c r="AF43" s="128"/>
-      <c r="AG43" s="128"/>
-      <c r="AH43" s="128"/>
-      <c r="AI43" s="128"/>
-      <c r="AJ43" s="128"/>
-      <c r="AK43" s="128"/>
-      <c r="AL43" s="128"/>
-      <c r="AM43" s="128"/>
-      <c r="AN43" s="128"/>
-      <c r="AO43" s="128"/>
-      <c r="AP43" s="128"/>
-      <c r="AQ43" s="128"/>
-      <c r="AR43" s="128"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="219"/>
+      <c r="H43" s="219"/>
+      <c r="I43" s="219"/>
+      <c r="J43" s="219"/>
+      <c r="K43" s="219"/>
+      <c r="L43" s="219"/>
+      <c r="M43" s="219"/>
+      <c r="N43" s="219"/>
+      <c r="O43" s="219"/>
+      <c r="P43" s="219"/>
+      <c r="Q43" s="219"/>
+      <c r="R43" s="219"/>
+      <c r="S43" s="219"/>
+      <c r="T43" s="219"/>
+      <c r="U43" s="219"/>
+      <c r="V43" s="219"/>
+      <c r="W43" s="219"/>
+      <c r="X43" s="219"/>
+      <c r="Y43" s="219"/>
+      <c r="Z43" s="219"/>
+      <c r="AA43" s="219"/>
+      <c r="AB43" s="219"/>
+      <c r="AC43" s="219"/>
+      <c r="AD43" s="219"/>
+      <c r="AE43" s="219"/>
+      <c r="AF43" s="219"/>
+      <c r="AG43" s="219"/>
+      <c r="AH43" s="219"/>
+      <c r="AI43" s="219"/>
+      <c r="AJ43" s="219"/>
+      <c r="AK43" s="219"/>
+      <c r="AL43" s="219"/>
+      <c r="AM43" s="219"/>
+      <c r="AN43" s="219"/>
+      <c r="AO43" s="219"/>
+      <c r="AP43" s="219"/>
+      <c r="AQ43" s="219"/>
+      <c r="AR43" s="219"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="4"/>
       <c r="AU43" s="1"/>
@@ -11786,54 +11928,54 @@
       <c r="B49" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="129" t="s">
+      <c r="C49" s="220" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="129"/>
-      <c r="E49" s="129"/>
-      <c r="F49" s="129"/>
-      <c r="G49" s="129"/>
-      <c r="H49" s="129"/>
-      <c r="I49" s="129"/>
-      <c r="J49" s="129"/>
-      <c r="K49" s="129"/>
-      <c r="L49" s="129"/>
-      <c r="M49" s="129"/>
-      <c r="N49" s="129"/>
-      <c r="O49" s="129"/>
-      <c r="P49" s="129"/>
-      <c r="Q49" s="129"/>
-      <c r="R49" s="129"/>
-      <c r="S49" s="129"/>
-      <c r="T49" s="129"/>
-      <c r="U49" s="129"/>
-      <c r="V49" s="130"/>
+      <c r="D49" s="220"/>
+      <c r="E49" s="220"/>
+      <c r="F49" s="220"/>
+      <c r="G49" s="220"/>
+      <c r="H49" s="220"/>
+      <c r="I49" s="220"/>
+      <c r="J49" s="220"/>
+      <c r="K49" s="220"/>
+      <c r="L49" s="220"/>
+      <c r="M49" s="220"/>
+      <c r="N49" s="220"/>
+      <c r="O49" s="220"/>
+      <c r="P49" s="220"/>
+      <c r="Q49" s="220"/>
+      <c r="R49" s="220"/>
+      <c r="S49" s="220"/>
+      <c r="T49" s="220"/>
+      <c r="U49" s="220"/>
+      <c r="V49" s="221"/>
       <c r="W49" s="28"/>
       <c r="X49" s="28"/>
       <c r="Y49" s="28"/>
-      <c r="Z49" s="131" t="s">
+      <c r="Z49" s="222" t="s">
         <v>55</v>
       </c>
-      <c r="AA49" s="132"/>
-      <c r="AB49" s="132"/>
-      <c r="AC49" s="132"/>
-      <c r="AD49" s="132"/>
-      <c r="AE49" s="132"/>
-      <c r="AF49" s="132"/>
-      <c r="AG49" s="132"/>
-      <c r="AH49" s="132"/>
-      <c r="AI49" s="132"/>
-      <c r="AJ49" s="132"/>
-      <c r="AK49" s="132"/>
-      <c r="AL49" s="132"/>
-      <c r="AM49" s="132"/>
-      <c r="AN49" s="132"/>
-      <c r="AO49" s="132"/>
-      <c r="AP49" s="132"/>
-      <c r="AQ49" s="132"/>
-      <c r="AR49" s="132"/>
-      <c r="AS49" s="132"/>
-      <c r="AT49" s="133"/>
+      <c r="AA49" s="223"/>
+      <c r="AB49" s="223"/>
+      <c r="AC49" s="223"/>
+      <c r="AD49" s="223"/>
+      <c r="AE49" s="223"/>
+      <c r="AF49" s="223"/>
+      <c r="AG49" s="223"/>
+      <c r="AH49" s="223"/>
+      <c r="AI49" s="223"/>
+      <c r="AJ49" s="223"/>
+      <c r="AK49" s="223"/>
+      <c r="AL49" s="223"/>
+      <c r="AM49" s="223"/>
+      <c r="AN49" s="223"/>
+      <c r="AO49" s="223"/>
+      <c r="AP49" s="223"/>
+      <c r="AQ49" s="223"/>
+      <c r="AR49" s="223"/>
+      <c r="AS49" s="223"/>
+      <c r="AT49" s="224"/>
       <c r="AU49" s="4"/>
     </row>
     <row r="50" spans="1:47" ht="18.75" customHeight="1" thickBot="1">
@@ -11866,27 +12008,27 @@
       <c r="W50" s="28"/>
       <c r="X50" s="28"/>
       <c r="Y50" s="28"/>
-      <c r="Z50" s="134"/>
-      <c r="AA50" s="135"/>
-      <c r="AB50" s="135"/>
-      <c r="AC50" s="135"/>
-      <c r="AD50" s="135"/>
-      <c r="AE50" s="135"/>
-      <c r="AF50" s="135"/>
-      <c r="AG50" s="135"/>
-      <c r="AH50" s="135"/>
-      <c r="AI50" s="135"/>
-      <c r="AJ50" s="135"/>
-      <c r="AK50" s="135"/>
-      <c r="AL50" s="135"/>
-      <c r="AM50" s="135"/>
-      <c r="AN50" s="135"/>
-      <c r="AO50" s="135"/>
-      <c r="AP50" s="135"/>
-      <c r="AQ50" s="135"/>
-      <c r="AR50" s="135"/>
-      <c r="AS50" s="135"/>
-      <c r="AT50" s="136"/>
+      <c r="Z50" s="225"/>
+      <c r="AA50" s="226"/>
+      <c r="AB50" s="226"/>
+      <c r="AC50" s="226"/>
+      <c r="AD50" s="226"/>
+      <c r="AE50" s="226"/>
+      <c r="AF50" s="226"/>
+      <c r="AG50" s="226"/>
+      <c r="AH50" s="226"/>
+      <c r="AI50" s="226"/>
+      <c r="AJ50" s="226"/>
+      <c r="AK50" s="226"/>
+      <c r="AL50" s="226"/>
+      <c r="AM50" s="226"/>
+      <c r="AN50" s="226"/>
+      <c r="AO50" s="226"/>
+      <c r="AP50" s="226"/>
+      <c r="AQ50" s="226"/>
+      <c r="AR50" s="226"/>
+      <c r="AS50" s="226"/>
+      <c r="AT50" s="227"/>
       <c r="AU50" s="4"/>
     </row>
     <row r="51" spans="1:47" ht="7.5" customHeight="1"/>
@@ -11897,69 +12039,76 @@
     <row r="57" spans="1:47" ht="14.25" customHeight="1">
       <c r="G57" s="34"/>
       <c r="H57" s="34"/>
-      <c r="AP57" s="137"/>
-      <c r="AQ57" s="137"/>
-      <c r="AR57" s="137"/>
-      <c r="AS57" s="137"/>
-      <c r="AT57" s="137"/>
-      <c r="AU57" s="137"/>
+      <c r="AP57" s="74"/>
+      <c r="AQ57" s="74"/>
+      <c r="AR57" s="74"/>
+      <c r="AS57" s="74"/>
+      <c r="AT57" s="74"/>
+      <c r="AU57" s="74"/>
     </row>
     <row r="58" spans="1:47" ht="14.25" customHeight="1">
       <c r="G58" s="35"/>
       <c r="H58" s="35"/>
-      <c r="AP58" s="137"/>
-      <c r="AQ58" s="137"/>
-      <c r="AR58" s="137"/>
-      <c r="AS58" s="137"/>
-      <c r="AT58" s="137"/>
-      <c r="AU58" s="137"/>
+      <c r="AP58" s="74"/>
+      <c r="AQ58" s="74"/>
+      <c r="AR58" s="74"/>
+      <c r="AS58" s="74"/>
+      <c r="AT58" s="74"/>
+      <c r="AU58" s="74"/>
     </row>
     <row r="59" spans="1:47">
-      <c r="AP59" s="137"/>
-      <c r="AQ59" s="137"/>
-      <c r="AR59" s="137"/>
-      <c r="AS59" s="137"/>
-      <c r="AT59" s="137"/>
-      <c r="AU59" s="137"/>
+      <c r="AP59" s="74"/>
+      <c r="AQ59" s="74"/>
+      <c r="AR59" s="74"/>
+      <c r="AS59" s="74"/>
+      <c r="AT59" s="74"/>
+      <c r="AU59" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="H7:AR7"/>
-    <mergeCell ref="I2:AM3"/>
-    <mergeCell ref="I4:AM4"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:AK6"/>
-    <mergeCell ref="AL6:AS6"/>
-    <mergeCell ref="AL8:AS8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="T9:AG9"/>
-    <mergeCell ref="AN9:AO9"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:P8"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="T8:AG8"/>
-    <mergeCell ref="AH8:AK8"/>
-    <mergeCell ref="D12:G14"/>
-    <mergeCell ref="H12:J14"/>
-    <mergeCell ref="K12:V12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="AA12:AC14"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:AG11"/>
-    <mergeCell ref="AH11:AK11"/>
-    <mergeCell ref="AL11:AO11"/>
-    <mergeCell ref="AD12:AO12"/>
-    <mergeCell ref="AP12:AS12"/>
-    <mergeCell ref="K13:M14"/>
-    <mergeCell ref="N13:Z14"/>
-    <mergeCell ref="AD13:AF14"/>
-    <mergeCell ref="AG13:AS14"/>
+    <mergeCell ref="AA16:AS19"/>
+    <mergeCell ref="U16:Z16"/>
+    <mergeCell ref="U17:Z17"/>
+    <mergeCell ref="U18:Z18"/>
+    <mergeCell ref="D40:O40"/>
+    <mergeCell ref="D30:G33"/>
+    <mergeCell ref="H30:AS30"/>
+    <mergeCell ref="H31:I32"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="Q31:V32"/>
+    <mergeCell ref="W31:Y31"/>
+    <mergeCell ref="Z31:AF31"/>
+    <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="AJ31:AS31"/>
+    <mergeCell ref="K32:P32"/>
+    <mergeCell ref="W32:Y32"/>
+    <mergeCell ref="D43:AR43"/>
+    <mergeCell ref="C49:V49"/>
+    <mergeCell ref="Z49:AT50"/>
+    <mergeCell ref="AP57:AU59"/>
+    <mergeCell ref="D35:J35"/>
+    <mergeCell ref="Z32:AF32"/>
+    <mergeCell ref="AG32:AI32"/>
+    <mergeCell ref="AJ32:AS32"/>
+    <mergeCell ref="H33:AS33"/>
+    <mergeCell ref="AE27:AH28"/>
+    <mergeCell ref="AI27:AS27"/>
+    <mergeCell ref="K28:S28"/>
+    <mergeCell ref="T28:AD28"/>
+    <mergeCell ref="AI28:AR28"/>
+    <mergeCell ref="D23:G28"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="H27:J28"/>
+    <mergeCell ref="K27:S27"/>
+    <mergeCell ref="T27:AD27"/>
+    <mergeCell ref="AO23:AP23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:AS24"/>
+    <mergeCell ref="H25:AS26"/>
     <mergeCell ref="I20:V20"/>
     <mergeCell ref="W20:AT20"/>
     <mergeCell ref="D21:G22"/>
@@ -11976,49 +12125,42 @@
     <mergeCell ref="I19:N19"/>
     <mergeCell ref="O19:T19"/>
     <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="AO23:AP23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:AS24"/>
-    <mergeCell ref="H25:AS26"/>
-    <mergeCell ref="D23:G28"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="AC23:AD23"/>
-    <mergeCell ref="H27:J28"/>
-    <mergeCell ref="K27:S27"/>
-    <mergeCell ref="T27:AD27"/>
-    <mergeCell ref="Z32:AF32"/>
-    <mergeCell ref="AG32:AI32"/>
-    <mergeCell ref="AJ32:AS32"/>
-    <mergeCell ref="H33:AS33"/>
-    <mergeCell ref="AE27:AH28"/>
-    <mergeCell ref="AI27:AS27"/>
-    <mergeCell ref="K28:S28"/>
-    <mergeCell ref="T28:AD28"/>
-    <mergeCell ref="AI28:AR28"/>
-    <mergeCell ref="D43:AR43"/>
-    <mergeCell ref="C49:V49"/>
-    <mergeCell ref="Z49:AT50"/>
-    <mergeCell ref="AP57:AU59"/>
-    <mergeCell ref="D35:J35"/>
-    <mergeCell ref="AA16:AS19"/>
-    <mergeCell ref="U16:Z16"/>
-    <mergeCell ref="U17:Z17"/>
-    <mergeCell ref="U18:Z18"/>
-    <mergeCell ref="D40:O40"/>
-    <mergeCell ref="D30:G33"/>
-    <mergeCell ref="H30:AS30"/>
-    <mergeCell ref="H31:I32"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="Q31:V32"/>
-    <mergeCell ref="W31:Y31"/>
-    <mergeCell ref="Z31:AF31"/>
-    <mergeCell ref="AG31:AI31"/>
-    <mergeCell ref="AJ31:AS31"/>
-    <mergeCell ref="K32:P32"/>
-    <mergeCell ref="W32:Y32"/>
+    <mergeCell ref="AD12:AO12"/>
+    <mergeCell ref="AP12:AS12"/>
+    <mergeCell ref="K13:M14"/>
+    <mergeCell ref="N13:Z14"/>
+    <mergeCell ref="AD13:AF14"/>
+    <mergeCell ref="AG13:AS14"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:AG11"/>
+    <mergeCell ref="AH11:AK11"/>
+    <mergeCell ref="AL11:AO11"/>
+    <mergeCell ref="D12:G14"/>
+    <mergeCell ref="H12:J14"/>
+    <mergeCell ref="K12:V12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="AA12:AC14"/>
+    <mergeCell ref="AL8:AS8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="T9:AG9"/>
+    <mergeCell ref="AN9:AO9"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="T8:AG8"/>
+    <mergeCell ref="AH8:AK8"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:AR7"/>
+    <mergeCell ref="I2:AM3"/>
+    <mergeCell ref="I4:AM4"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:AK6"/>
+    <mergeCell ref="AL6:AS6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -12029,12 +12171,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AU59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="1.375" style="3" customWidth="1"/>
     <col min="2" max="3" width="1.75" style="3" customWidth="1"/>
@@ -12095,2375 +12237,2048 @@
     </row>
     <row r="2" spans="1:47" ht="9.75" customHeight="1">
       <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="276" t="s">
-        <v>69</v>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="71" t="s">
+        <v>66</v>
       </c>
-      <c r="J2" s="277"/>
-      <c r="K2" s="277"/>
-      <c r="L2" s="277"/>
-      <c r="M2" s="277"/>
-      <c r="N2" s="277"/>
-      <c r="O2" s="277"/>
-      <c r="P2" s="277"/>
-      <c r="Q2" s="277"/>
-      <c r="R2" s="277"/>
-      <c r="S2" s="277"/>
-      <c r="T2" s="277"/>
-      <c r="U2" s="277"/>
-      <c r="V2" s="277"/>
-      <c r="W2" s="277"/>
-      <c r="X2" s="277"/>
-      <c r="Y2" s="277"/>
-      <c r="Z2" s="277"/>
-      <c r="AA2" s="277"/>
-      <c r="AB2" s="277"/>
-      <c r="AC2" s="277"/>
-      <c r="AD2" s="277"/>
-      <c r="AE2" s="277"/>
-      <c r="AF2" s="277"/>
-      <c r="AG2" s="277"/>
-      <c r="AH2" s="277"/>
-      <c r="AI2" s="277"/>
-      <c r="AJ2" s="277"/>
-      <c r="AK2" s="277"/>
-      <c r="AL2" s="277"/>
-      <c r="AM2" s="277"/>
-      <c r="AN2" s="45"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="43"/>
-      <c r="AS2" s="43"/>
-      <c r="AT2" s="43"/>
-      <c r="AU2" s="46"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
+      <c r="AA2" s="72"/>
+      <c r="AB2" s="72"/>
+      <c r="AC2" s="72"/>
+      <c r="AD2" s="72"/>
+      <c r="AE2" s="72"/>
+      <c r="AF2" s="72"/>
+      <c r="AG2" s="72"/>
+      <c r="AH2" s="72"/>
+      <c r="AI2" s="72"/>
+      <c r="AJ2" s="72"/>
+      <c r="AK2" s="72"/>
+      <c r="AL2" s="72"/>
+      <c r="AM2" s="72"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AU2" s="44"/>
     </row>
     <row r="3" spans="1:47" ht="19.5" customHeight="1">
       <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="277"/>
-      <c r="J3" s="277"/>
-      <c r="K3" s="277"/>
-      <c r="L3" s="277"/>
-      <c r="M3" s="277"/>
-      <c r="N3" s="277"/>
-      <c r="O3" s="277"/>
-      <c r="P3" s="277"/>
-      <c r="Q3" s="277"/>
-      <c r="R3" s="277"/>
-      <c r="S3" s="277"/>
-      <c r="T3" s="277"/>
-      <c r="U3" s="277"/>
-      <c r="V3" s="277"/>
-      <c r="W3" s="277"/>
-      <c r="X3" s="277"/>
-      <c r="Y3" s="277"/>
-      <c r="Z3" s="277"/>
-      <c r="AA3" s="277"/>
-      <c r="AB3" s="277"/>
-      <c r="AC3" s="277"/>
-      <c r="AD3" s="277"/>
-      <c r="AE3" s="277"/>
-      <c r="AF3" s="277"/>
-      <c r="AG3" s="277"/>
-      <c r="AH3" s="277"/>
-      <c r="AI3" s="277"/>
-      <c r="AJ3" s="277"/>
-      <c r="AK3" s="277"/>
-      <c r="AL3" s="277"/>
-      <c r="AM3" s="277"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="46"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="72"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="72"/>
+      <c r="AI3" s="72"/>
+      <c r="AJ3" s="72"/>
+      <c r="AK3" s="72"/>
+      <c r="AL3" s="72"/>
+      <c r="AM3" s="72"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AU3" s="44"/>
     </row>
     <row r="4" spans="1:47" ht="15" customHeight="1">
       <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="275"/>
-      <c r="J4" s="275"/>
-      <c r="K4" s="275"/>
-      <c r="L4" s="275"/>
-      <c r="M4" s="275"/>
-      <c r="N4" s="275"/>
-      <c r="O4" s="275"/>
-      <c r="P4" s="275"/>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275"/>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275"/>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="275"/>
-      <c r="AE4" s="275"/>
-      <c r="AF4" s="275"/>
-      <c r="AG4" s="275"/>
-      <c r="AH4" s="275"/>
-      <c r="AI4" s="275"/>
-      <c r="AJ4" s="275"/>
-      <c r="AK4" s="275"/>
-      <c r="AL4" s="275"/>
-      <c r="AM4" s="275"/>
-      <c r="AN4" s="45"/>
-      <c r="AO4" s="45"/>
-      <c r="AP4" s="45"/>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="43"/>
-      <c r="AS4" s="43"/>
-      <c r="AT4" s="43"/>
-      <c r="AU4" s="46"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
+      <c r="Y4" s="73"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="73"/>
+      <c r="AC4" s="73"/>
+      <c r="AD4" s="73"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
+      <c r="AI4" s="73"/>
+      <c r="AJ4" s="73"/>
+      <c r="AK4" s="73"/>
+      <c r="AL4" s="73"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="43"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AU4" s="44"/>
     </row>
     <row r="5" spans="1:47" ht="10.5" customHeight="1">
       <c r="A5" s="42"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="47"/>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="47"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="44"/>
-      <c r="AR5" s="43"/>
-      <c r="AS5" s="43"/>
-      <c r="AT5" s="43"/>
-      <c r="AU5" s="46"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="45"/>
+      <c r="AC5" s="45"/>
+      <c r="AD5" s="45"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="45"/>
+      <c r="AJ5" s="45"/>
+      <c r="AK5" s="45"/>
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+      <c r="AO5" s="45"/>
+      <c r="AP5" s="45"/>
+      <c r="AU5" s="44"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1">
       <c r="A6" s="42"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="49"/>
-      <c r="AD6" s="49"/>
-      <c r="AE6" s="49"/>
-      <c r="AF6" s="49"/>
-      <c r="AG6" s="49"/>
-      <c r="AH6" s="49"/>
-      <c r="AI6" s="49"/>
-      <c r="AJ6" s="49"/>
-      <c r="AK6" s="49"/>
-      <c r="AL6" s="49"/>
-      <c r="AM6" s="49"/>
-      <c r="AN6" s="49"/>
-      <c r="AO6" s="49"/>
-      <c r="AP6" s="49"/>
-      <c r="AQ6" s="49"/>
-      <c r="AR6" s="49"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="47"/>
+      <c r="AB6" s="47"/>
+      <c r="AC6" s="47"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="47"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="47"/>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="47"/>
+      <c r="AJ6" s="47"/>
+      <c r="AK6" s="47"/>
+      <c r="AL6" s="47"/>
+      <c r="AM6" s="47"/>
+      <c r="AN6" s="47"/>
+      <c r="AO6" s="47"/>
+      <c r="AP6" s="47"/>
+      <c r="AQ6" s="47"/>
+      <c r="AR6" s="47"/>
+      <c r="AU6" s="44"/>
     </row>
     <row r="7" spans="1:47" ht="18" customHeight="1">
       <c r="A7" s="42"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="49" t="s">
-        <v>70</v>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47" t="s">
+        <v>67</v>
       </c>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="49"/>
-      <c r="AE7" s="49"/>
-      <c r="AF7" s="49"/>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="49"/>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
-      <c r="AL7" s="49"/>
-      <c r="AM7" s="49"/>
-      <c r="AN7" s="49"/>
-      <c r="AO7" s="49"/>
-      <c r="AP7" s="49"/>
-      <c r="AQ7" s="49"/>
-      <c r="AR7" s="49"/>
-      <c r="AS7" s="43"/>
-      <c r="AT7" s="43"/>
-      <c r="AU7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="47"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="47"/>
+      <c r="AD7" s="47"/>
+      <c r="AE7" s="47"/>
+      <c r="AF7" s="47"/>
+      <c r="AG7" s="47"/>
+      <c r="AH7" s="47"/>
+      <c r="AI7" s="47"/>
+      <c r="AJ7" s="47"/>
+      <c r="AK7" s="47"/>
+      <c r="AL7" s="47"/>
+      <c r="AM7" s="47"/>
+      <c r="AN7" s="47"/>
+      <c r="AO7" s="47"/>
+      <c r="AP7" s="47"/>
+      <c r="AQ7" s="47"/>
+      <c r="AR7" s="47"/>
+      <c r="AU7" s="44"/>
     </row>
     <row r="8" spans="1:47" ht="18" customHeight="1">
       <c r="A8" s="42"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="49"/>
-      <c r="AI8" s="49"/>
-      <c r="AJ8" s="49"/>
-      <c r="AK8" s="49"/>
-      <c r="AL8" s="51" t="s">
-        <v>71</v>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="49"/>
+      <c r="AB8" s="48"/>
+      <c r="AC8" s="48"/>
+      <c r="AD8" s="48"/>
+      <c r="AE8" s="48"/>
+      <c r="AF8" s="48"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47"/>
+      <c r="AK8" s="47"/>
+      <c r="AL8" s="48" t="s">
+        <v>68</v>
       </c>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="51"/>
-      <c r="AP8" s="51"/>
-      <c r="AQ8" s="51"/>
-      <c r="AR8" s="51"/>
-      <c r="AS8" s="43"/>
-      <c r="AT8" s="43"/>
-      <c r="AU8" s="46"/>
+      <c r="AM8" s="48"/>
+      <c r="AN8" s="48"/>
+      <c r="AO8" s="48"/>
+      <c r="AP8" s="48"/>
+      <c r="AQ8" s="48"/>
+      <c r="AR8" s="48"/>
+      <c r="AU8" s="44"/>
     </row>
     <row r="9" spans="1:47" ht="18" customHeight="1">
       <c r="A9" s="42"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="49"/>
-      <c r="AN9" s="49"/>
-      <c r="AO9" s="49"/>
-      <c r="AP9" s="49"/>
-      <c r="AQ9" s="49"/>
-      <c r="AR9" s="49"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="47"/>
+      <c r="AI9" s="47"/>
+      <c r="AJ9" s="47"/>
+      <c r="AK9" s="47"/>
+      <c r="AL9" s="47"/>
+      <c r="AM9" s="47"/>
+      <c r="AN9" s="47"/>
+      <c r="AO9" s="47"/>
+      <c r="AP9" s="47"/>
+      <c r="AQ9" s="47"/>
+      <c r="AR9" s="47"/>
+      <c r="AU9" s="44"/>
     </row>
     <row r="10" spans="1:47" ht="9" customHeight="1">
       <c r="A10" s="42"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="53"/>
-      <c r="AB10" s="53"/>
-      <c r="AC10" s="53"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="53"/>
-      <c r="AG10" s="53"/>
-      <c r="AH10" s="53"/>
-      <c r="AI10" s="53"/>
-      <c r="AJ10" s="53"/>
-      <c r="AK10" s="53"/>
-      <c r="AL10" s="53"/>
-      <c r="AM10" s="53"/>
-      <c r="AN10" s="53"/>
-      <c r="AO10" s="53"/>
-      <c r="AP10" s="53"/>
-      <c r="AQ10" s="53"/>
-      <c r="AR10" s="53"/>
-      <c r="AS10" s="43"/>
-      <c r="AT10" s="43"/>
-      <c r="AU10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="49"/>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="49"/>
+      <c r="AE10" s="49"/>
+      <c r="AF10" s="49"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
+      <c r="AL10" s="49"/>
+      <c r="AM10" s="49"/>
+      <c r="AN10" s="49"/>
+      <c r="AO10" s="49"/>
+      <c r="AP10" s="49"/>
+      <c r="AQ10" s="49"/>
+      <c r="AR10" s="49"/>
+      <c r="AU10" s="44"/>
     </row>
     <row r="11" spans="1:47" ht="19.5" customHeight="1">
       <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="52"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="52"/>
-      <c r="Z11" s="52"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52"/>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
-      <c r="AL11" s="52">
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
+      <c r="AL11" s="49">
         <v>16</v>
       </c>
-      <c r="AM11" s="52"/>
-      <c r="AN11" s="52"/>
-      <c r="AO11" s="52"/>
-      <c r="AP11" s="52"/>
-      <c r="AQ11" s="52"/>
-      <c r="AR11" s="52"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="46"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
+      <c r="AO11" s="49"/>
+      <c r="AP11" s="49"/>
+      <c r="AQ11" s="49"/>
+      <c r="AR11" s="49"/>
+      <c r="AU11" s="44"/>
     </row>
     <row r="12" spans="1:47" ht="19.5" customHeight="1">
       <c r="A12" s="42"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="54">
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="47"/>
+      <c r="AB12" s="47"/>
+      <c r="AC12" s="47"/>
+      <c r="AD12" s="50">
         <v>45945</v>
       </c>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="54"/>
-      <c r="AH12" s="54"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54"/>
-      <c r="AK12" s="54"/>
-      <c r="AL12" s="54"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="55"/>
-      <c r="AO12" s="55"/>
-      <c r="AP12" s="55"/>
-      <c r="AQ12" s="55"/>
-      <c r="AR12" s="53"/>
-      <c r="AS12" s="43"/>
-      <c r="AT12" s="43"/>
-      <c r="AU12" s="46"/>
+      <c r="AE12" s="50"/>
+      <c r="AF12" s="50"/>
+      <c r="AG12" s="50"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="50"/>
+      <c r="AK12" s="50"/>
+      <c r="AL12" s="50"/>
+      <c r="AM12" s="50"/>
+      <c r="AN12" s="51"/>
+      <c r="AO12" s="51"/>
+      <c r="AP12" s="51"/>
+      <c r="AQ12" s="51"/>
+      <c r="AR12" s="49"/>
+      <c r="AU12" s="44"/>
     </row>
     <row r="13" spans="1:47" ht="12" customHeight="1">
       <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="53"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="53"/>
-      <c r="AB13" s="53"/>
-      <c r="AC13" s="53"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="53"/>
-      <c r="AG13" s="53"/>
-      <c r="AH13" s="53"/>
-      <c r="AI13" s="53"/>
-      <c r="AJ13" s="53"/>
-      <c r="AK13" s="53"/>
-      <c r="AL13" s="53"/>
-      <c r="AM13" s="53"/>
-      <c r="AN13" s="53"/>
-      <c r="AO13" s="53"/>
-      <c r="AP13" s="53"/>
-      <c r="AQ13" s="53"/>
-      <c r="AR13" s="53"/>
-      <c r="AS13" s="43"/>
-      <c r="AT13" s="43"/>
-      <c r="AU13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="49"/>
+      <c r="AE13" s="49"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
+      <c r="AL13" s="49"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="49"/>
+      <c r="AQ13" s="49"/>
+      <c r="AR13" s="49"/>
+      <c r="AU13" s="44"/>
     </row>
     <row r="14" spans="1:47" ht="12" customHeight="1">
       <c r="A14" s="42"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="53"/>
-      <c r="AB14" s="53"/>
-      <c r="AC14" s="53"/>
-      <c r="AD14" s="53"/>
-      <c r="AE14" s="53"/>
-      <c r="AF14" s="53"/>
-      <c r="AG14" s="53"/>
-      <c r="AH14" s="53"/>
-      <c r="AI14" s="53"/>
-      <c r="AJ14" s="53"/>
-      <c r="AK14" s="53"/>
-      <c r="AL14" s="53"/>
-      <c r="AM14" s="53"/>
-      <c r="AN14" s="53"/>
-      <c r="AO14" s="53"/>
-      <c r="AP14" s="53"/>
-      <c r="AQ14" s="53"/>
-      <c r="AR14" s="53"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="49"/>
+      <c r="AC14" s="49"/>
+      <c r="AD14" s="49"/>
+      <c r="AE14" s="49"/>
+      <c r="AF14" s="49"/>
+      <c r="AG14" s="49"/>
+      <c r="AH14" s="49"/>
+      <c r="AI14" s="49"/>
+      <c r="AJ14" s="49"/>
+      <c r="AK14" s="49"/>
+      <c r="AL14" s="49"/>
+      <c r="AM14" s="49"/>
+      <c r="AN14" s="49"/>
+      <c r="AO14" s="49"/>
+      <c r="AP14" s="49"/>
+      <c r="AQ14" s="49"/>
+      <c r="AR14" s="49"/>
+      <c r="AU14" s="44"/>
     </row>
     <row r="15" spans="1:47" ht="9.75" customHeight="1">
       <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="53"/>
-      <c r="V15" s="53"/>
-      <c r="W15" s="53"/>
-      <c r="X15" s="53"/>
-      <c r="Y15" s="53"/>
-      <c r="Z15" s="53"/>
-      <c r="AA15" s="53"/>
-      <c r="AB15" s="53"/>
-      <c r="AC15" s="53"/>
-      <c r="AD15" s="53"/>
-      <c r="AE15" s="53"/>
-      <c r="AF15" s="53"/>
-      <c r="AG15" s="53"/>
-      <c r="AH15" s="53"/>
-      <c r="AI15" s="53"/>
-      <c r="AJ15" s="53"/>
-      <c r="AK15" s="53"/>
-      <c r="AL15" s="53"/>
-      <c r="AM15" s="53"/>
-      <c r="AN15" s="53"/>
-      <c r="AO15" s="53"/>
-      <c r="AP15" s="53"/>
-      <c r="AQ15" s="53"/>
-      <c r="AR15" s="53"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="49"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="49"/>
+      <c r="AM15" s="49"/>
+      <c r="AN15" s="49"/>
+      <c r="AO15" s="49"/>
+      <c r="AP15" s="49"/>
+      <c r="AQ15" s="49"/>
+      <c r="AR15" s="49"/>
+      <c r="AU15" s="44"/>
     </row>
     <row r="16" spans="1:47" ht="15" customHeight="1">
       <c r="A16" s="42"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="57"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
-      <c r="U16" s="57" t="s">
-        <v>72</v>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
+      <c r="U16" s="53" t="s">
+        <v>69</v>
       </c>
-      <c r="V16" s="57"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="57"/>
-      <c r="Y16" s="57"/>
-      <c r="Z16" s="57"/>
-      <c r="AA16" s="57"/>
-      <c r="AB16" s="57"/>
-      <c r="AC16" s="57"/>
-      <c r="AD16" s="57"/>
-      <c r="AE16" s="57"/>
-      <c r="AF16" s="57"/>
-      <c r="AG16" s="57"/>
-      <c r="AH16" s="57"/>
-      <c r="AI16" s="57"/>
-      <c r="AJ16" s="57"/>
-      <c r="AK16" s="57"/>
-      <c r="AL16" s="57"/>
-      <c r="AM16" s="57"/>
-      <c r="AN16" s="57"/>
-      <c r="AO16" s="57"/>
-      <c r="AP16" s="57"/>
-      <c r="AQ16" s="57"/>
-      <c r="AR16" s="57"/>
-      <c r="AS16" s="43"/>
-      <c r="AT16" s="43"/>
-      <c r="AU16" s="46"/>
+      <c r="V16" s="53"/>
+      <c r="W16" s="53"/>
+      <c r="X16" s="53"/>
+      <c r="Y16" s="53"/>
+      <c r="Z16" s="53"/>
+      <c r="AA16" s="53"/>
+      <c r="AB16" s="53"/>
+      <c r="AC16" s="53"/>
+      <c r="AD16" s="53"/>
+      <c r="AE16" s="53"/>
+      <c r="AF16" s="53"/>
+      <c r="AG16" s="53"/>
+      <c r="AH16" s="53"/>
+      <c r="AI16" s="53"/>
+      <c r="AJ16" s="53"/>
+      <c r="AK16" s="53"/>
+      <c r="AL16" s="53"/>
+      <c r="AM16" s="53"/>
+      <c r="AN16" s="53"/>
+      <c r="AO16" s="53"/>
+      <c r="AP16" s="53"/>
+      <c r="AQ16" s="53"/>
+      <c r="AR16" s="53"/>
+      <c r="AU16" s="44"/>
     </row>
     <row r="17" spans="1:47" ht="15" customHeight="1">
       <c r="A17" s="42"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="59">
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="55">
         <v>33</v>
       </c>
-      <c r="P17" s="59">
+      <c r="P17" s="55">
         <v>16</v>
       </c>
-      <c r="Q17" s="59">
+      <c r="Q17" s="55">
         <v>16</v>
       </c>
-      <c r="R17" s="59">
+      <c r="R17" s="55">
         <v>16</v>
       </c>
-      <c r="S17" s="59"/>
-      <c r="T17" s="59"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
-      <c r="AD17" s="60"/>
-      <c r="AE17" s="60"/>
-      <c r="AF17" s="60"/>
-      <c r="AG17" s="60"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="60"/>
-      <c r="AK17" s="60"/>
-      <c r="AL17" s="60"/>
-      <c r="AM17" s="60"/>
-      <c r="AN17" s="60"/>
-      <c r="AO17" s="60"/>
-      <c r="AP17" s="60"/>
-      <c r="AQ17" s="60"/>
-      <c r="AR17" s="60"/>
-      <c r="AS17" s="43"/>
-      <c r="AT17" s="43"/>
-      <c r="AU17" s="46"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="55"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="56"/>
+      <c r="Z17" s="56"/>
+      <c r="AA17" s="56"/>
+      <c r="AB17" s="56"/>
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="56"/>
+      <c r="AG17" s="56"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="56"/>
+      <c r="AJ17" s="56"/>
+      <c r="AK17" s="56"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="56"/>
+      <c r="AO17" s="56"/>
+      <c r="AP17" s="56"/>
+      <c r="AQ17" s="56"/>
+      <c r="AR17" s="56"/>
+      <c r="AU17" s="44"/>
     </row>
     <row r="18" spans="1:47" ht="15" customHeight="1">
       <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="61">
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="57">
         <v>32</v>
       </c>
-      <c r="J18" s="61">
+      <c r="J18" s="57">
         <v>16</v>
       </c>
-      <c r="K18" s="61">
+      <c r="K18" s="57">
         <v>16</v>
       </c>
-      <c r="L18" s="61">
+      <c r="L18" s="57">
         <v>16</v>
       </c>
-      <c r="M18" s="61">
+      <c r="M18" s="57">
         <v>16</v>
       </c>
-      <c r="N18" s="61">
+      <c r="N18" s="57">
         <v>16</v>
       </c>
-      <c r="O18" s="61"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="61"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="61"/>
-      <c r="T18" s="61"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="52"/>
-      <c r="X18" s="52"/>
-      <c r="Y18" s="52"/>
-      <c r="Z18" s="52"/>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="52"/>
-      <c r="AC18" s="52"/>
-      <c r="AD18" s="52"/>
-      <c r="AE18" s="52"/>
-      <c r="AF18" s="52"/>
-      <c r="AG18" s="52"/>
-      <c r="AH18" s="52"/>
-      <c r="AI18" s="52"/>
-      <c r="AJ18" s="52"/>
-      <c r="AK18" s="52"/>
-      <c r="AL18" s="52"/>
-      <c r="AM18" s="52"/>
-      <c r="AN18" s="52"/>
-      <c r="AO18" s="52"/>
-      <c r="AP18" s="52"/>
-      <c r="AQ18" s="52"/>
-      <c r="AR18" s="52"/>
-      <c r="AS18" s="43"/>
-      <c r="AT18" s="43"/>
-      <c r="AU18" s="46"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="47"/>
+      <c r="V18" s="47"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="49"/>
+      <c r="AC18" s="49"/>
+      <c r="AD18" s="49"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="49"/>
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49"/>
+      <c r="AI18" s="49"/>
+      <c r="AJ18" s="49"/>
+      <c r="AK18" s="49"/>
+      <c r="AL18" s="49"/>
+      <c r="AM18" s="49"/>
+      <c r="AN18" s="49"/>
+      <c r="AO18" s="49"/>
+      <c r="AP18" s="49"/>
+      <c r="AQ18" s="49"/>
+      <c r="AR18" s="49"/>
+      <c r="AU18" s="44"/>
     </row>
     <row r="19" spans="1:47" ht="15" customHeight="1">
       <c r="A19" s="42"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="52"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="52"/>
-      <c r="Z19" s="52"/>
-      <c r="AA19" s="52"/>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="52"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="52"/>
-      <c r="AF19" s="52"/>
-      <c r="AG19" s="52"/>
-      <c r="AH19" s="52"/>
-      <c r="AI19" s="52"/>
-      <c r="AJ19" s="52"/>
-      <c r="AK19" s="52"/>
-      <c r="AL19" s="52"/>
-      <c r="AM19" s="52"/>
-      <c r="AN19" s="52"/>
-      <c r="AO19" s="52"/>
-      <c r="AP19" s="52"/>
-      <c r="AQ19" s="52"/>
-      <c r="AR19" s="52"/>
-      <c r="AS19" s="43"/>
-      <c r="AT19" s="43"/>
-      <c r="AU19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="49"/>
+      <c r="AB19" s="49"/>
+      <c r="AC19" s="49"/>
+      <c r="AD19" s="49"/>
+      <c r="AE19" s="49"/>
+      <c r="AF19" s="49"/>
+      <c r="AG19" s="49"/>
+      <c r="AH19" s="49"/>
+      <c r="AI19" s="49"/>
+      <c r="AJ19" s="49"/>
+      <c r="AK19" s="49"/>
+      <c r="AL19" s="49"/>
+      <c r="AM19" s="49"/>
+      <c r="AN19" s="49"/>
+      <c r="AO19" s="49"/>
+      <c r="AP19" s="49"/>
+      <c r="AQ19" s="49"/>
+      <c r="AR19" s="49"/>
+      <c r="AU19" s="44"/>
     </row>
     <row r="20" spans="1:47" ht="15" customHeight="1">
       <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="53"/>
-      <c r="U20" s="53"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="53"/>
-      <c r="AB20" s="53"/>
-      <c r="AC20" s="53"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="53"/>
-      <c r="AF20" s="53"/>
-      <c r="AG20" s="53"/>
-      <c r="AH20" s="53"/>
-      <c r="AI20" s="53"/>
-      <c r="AJ20" s="53"/>
-      <c r="AK20" s="53"/>
-      <c r="AL20" s="53"/>
-      <c r="AM20" s="53"/>
-      <c r="AN20" s="53"/>
-      <c r="AO20" s="53"/>
-      <c r="AP20" s="53"/>
-      <c r="AQ20" s="53"/>
-      <c r="AR20" s="53"/>
-      <c r="AS20" s="43"/>
-      <c r="AT20" s="43"/>
-      <c r="AU20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="49"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="49"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="49"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="49"/>
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="49"/>
+      <c r="AF20" s="49"/>
+      <c r="AG20" s="49"/>
+      <c r="AH20" s="49"/>
+      <c r="AI20" s="49"/>
+      <c r="AJ20" s="49"/>
+      <c r="AK20" s="49"/>
+      <c r="AL20" s="49"/>
+      <c r="AM20" s="49"/>
+      <c r="AN20" s="49"/>
+      <c r="AO20" s="49"/>
+      <c r="AP20" s="49"/>
+      <c r="AQ20" s="49"/>
+      <c r="AR20" s="49"/>
+      <c r="AU20" s="44"/>
     </row>
     <row r="21" spans="1:47" ht="21" customHeight="1">
       <c r="A21" s="42"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="53"/>
-      <c r="U21" s="53"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="53"/>
-      <c r="AA21" s="53"/>
-      <c r="AB21" s="53"/>
-      <c r="AC21" s="53"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="53"/>
-      <c r="AF21" s="53"/>
-      <c r="AG21" s="53"/>
-      <c r="AH21" s="53"/>
-      <c r="AI21" s="53"/>
-      <c r="AJ21" s="53"/>
-      <c r="AK21" s="53"/>
-      <c r="AL21" s="53"/>
-      <c r="AM21" s="53"/>
-      <c r="AN21" s="53"/>
-      <c r="AO21" s="53"/>
-      <c r="AP21" s="53"/>
-      <c r="AQ21" s="53"/>
-      <c r="AR21" s="53"/>
-      <c r="AS21" s="43"/>
-      <c r="AT21" s="43"/>
-      <c r="AU21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49"/>
+      <c r="AE21" s="49"/>
+      <c r="AF21" s="49"/>
+      <c r="AG21" s="49"/>
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="49"/>
+      <c r="AJ21" s="49"/>
+      <c r="AK21" s="49"/>
+      <c r="AL21" s="49"/>
+      <c r="AM21" s="49"/>
+      <c r="AN21" s="49"/>
+      <c r="AO21" s="49"/>
+      <c r="AP21" s="49"/>
+      <c r="AQ21" s="49"/>
+      <c r="AR21" s="49"/>
+      <c r="AU21" s="44"/>
     </row>
     <row r="22" spans="1:47" ht="21" customHeight="1">
       <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="67"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="67"/>
-      <c r="AH22" s="67"/>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="67"/>
-      <c r="AK22" s="67"/>
-      <c r="AL22" s="67"/>
-      <c r="AM22" s="67"/>
-      <c r="AN22" s="67"/>
-      <c r="AO22" s="67"/>
-      <c r="AP22" s="67"/>
-      <c r="AQ22" s="67"/>
-      <c r="AR22" s="67"/>
-      <c r="AS22" s="43"/>
-      <c r="AT22" s="43"/>
-      <c r="AU22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="47"/>
+      <c r="AN22" s="47"/>
+      <c r="AO22" s="47"/>
+      <c r="AP22" s="47"/>
+      <c r="AQ22" s="47"/>
+      <c r="AR22" s="47"/>
+      <c r="AU22" s="44"/>
     </row>
     <row r="23" spans="1:47" ht="20.25" customHeight="1">
       <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="66"/>
-      <c r="AA23" s="66"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="67"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="67"/>
-      <c r="AM23" s="67"/>
-      <c r="AN23" s="67"/>
-      <c r="AO23" s="67"/>
-      <c r="AP23" s="67"/>
-      <c r="AQ23" s="67"/>
-      <c r="AR23" s="67"/>
-      <c r="AS23" s="43"/>
-      <c r="AT23" s="43"/>
-      <c r="AU23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
+      <c r="Z23" s="61"/>
+      <c r="AA23" s="61"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="61"/>
+      <c r="AD23" s="47"/>
+      <c r="AE23" s="47"/>
+      <c r="AF23" s="47"/>
+      <c r="AG23" s="47"/>
+      <c r="AH23" s="47"/>
+      <c r="AI23" s="47"/>
+      <c r="AJ23" s="47"/>
+      <c r="AK23" s="47"/>
+      <c r="AL23" s="47"/>
+      <c r="AM23" s="47"/>
+      <c r="AN23" s="47"/>
+      <c r="AO23" s="47"/>
+      <c r="AP23" s="47"/>
+      <c r="AQ23" s="47"/>
+      <c r="AR23" s="47"/>
+      <c r="AU23" s="44"/>
     </row>
     <row r="24" spans="1:47" ht="20.25" customHeight="1">
       <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="69"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="69"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="69"/>
-      <c r="AD24" s="69"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="69"/>
-      <c r="AG24" s="69"/>
-      <c r="AH24" s="69"/>
-      <c r="AI24" s="69"/>
-      <c r="AJ24" s="69"/>
-      <c r="AK24" s="69"/>
-      <c r="AL24" s="69"/>
-      <c r="AM24" s="69"/>
-      <c r="AN24" s="69"/>
-      <c r="AO24" s="69"/>
-      <c r="AP24" s="69"/>
-      <c r="AQ24" s="69"/>
-      <c r="AR24" s="70"/>
-      <c r="AS24" s="43"/>
-      <c r="AT24" s="43"/>
-      <c r="AU24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="62"/>
+      <c r="AA24" s="62"/>
+      <c r="AB24" s="62"/>
+      <c r="AC24" s="62"/>
+      <c r="AD24" s="62"/>
+      <c r="AE24" s="62"/>
+      <c r="AF24" s="62"/>
+      <c r="AG24" s="62"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="62"/>
+      <c r="AJ24" s="62"/>
+      <c r="AK24" s="62"/>
+      <c r="AL24" s="62"/>
+      <c r="AM24" s="62"/>
+      <c r="AN24" s="62"/>
+      <c r="AO24" s="62"/>
+      <c r="AP24" s="62"/>
+      <c r="AQ24" s="62"/>
+      <c r="AR24" s="63"/>
+      <c r="AU24" s="44"/>
     </row>
     <row r="25" spans="1:47" ht="20.25" customHeight="1">
       <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="69"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="69"/>
-      <c r="AB25" s="69"/>
-      <c r="AC25" s="69"/>
-      <c r="AD25" s="69"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="69"/>
-      <c r="AG25" s="69"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="69"/>
-      <c r="AJ25" s="69"/>
-      <c r="AK25" s="69"/>
-      <c r="AL25" s="69"/>
-      <c r="AM25" s="69"/>
-      <c r="AN25" s="69"/>
-      <c r="AO25" s="69"/>
-      <c r="AP25" s="69"/>
-      <c r="AQ25" s="69"/>
-      <c r="AR25" s="70"/>
-      <c r="AS25" s="43"/>
-      <c r="AT25" s="43"/>
-      <c r="AU25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="62"/>
+      <c r="X25" s="62"/>
+      <c r="Y25" s="62"/>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="62"/>
+      <c r="AB25" s="62"/>
+      <c r="AC25" s="62"/>
+      <c r="AD25" s="62"/>
+      <c r="AE25" s="62"/>
+      <c r="AF25" s="62"/>
+      <c r="AG25" s="62"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="62"/>
+      <c r="AK25" s="62"/>
+      <c r="AL25" s="62"/>
+      <c r="AM25" s="62"/>
+      <c r="AN25" s="62"/>
+      <c r="AO25" s="62"/>
+      <c r="AP25" s="62"/>
+      <c r="AQ25" s="62"/>
+      <c r="AR25" s="63"/>
+      <c r="AU25" s="44"/>
     </row>
     <row r="26" spans="1:47" ht="20.25" customHeight="1">
       <c r="A26" s="42"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="49"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="49"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="49"/>
-      <c r="AE26" s="49"/>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="49"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
-      <c r="AL26" s="49"/>
-      <c r="AM26" s="49"/>
-      <c r="AN26" s="49"/>
-      <c r="AO26" s="49"/>
-      <c r="AP26" s="49"/>
-      <c r="AQ26" s="49"/>
-      <c r="AR26" s="49"/>
-      <c r="AS26" s="43"/>
-      <c r="AT26" s="43"/>
-      <c r="AU26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="47"/>
+      <c r="U26" s="47"/>
+      <c r="V26" s="47"/>
+      <c r="W26" s="47"/>
+      <c r="X26" s="47"/>
+      <c r="Y26" s="47"/>
+      <c r="Z26" s="47"/>
+      <c r="AA26" s="47"/>
+      <c r="AB26" s="47"/>
+      <c r="AC26" s="47"/>
+      <c r="AD26" s="47"/>
+      <c r="AE26" s="47"/>
+      <c r="AF26" s="47"/>
+      <c r="AG26" s="47"/>
+      <c r="AH26" s="47"/>
+      <c r="AI26" s="47"/>
+      <c r="AJ26" s="47"/>
+      <c r="AK26" s="47"/>
+      <c r="AL26" s="47"/>
+      <c r="AM26" s="47"/>
+      <c r="AN26" s="47"/>
+      <c r="AO26" s="47"/>
+      <c r="AP26" s="47"/>
+      <c r="AQ26" s="47"/>
+      <c r="AR26" s="47"/>
+      <c r="AU26" s="44"/>
     </row>
     <row r="27" spans="1:47" ht="20.25" customHeight="1">
       <c r="A27" s="42"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
-      <c r="U27" s="49"/>
-      <c r="V27" s="49"/>
-      <c r="W27" s="49"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="49"/>
-      <c r="AA27" s="49"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="49"/>
-      <c r="AD27" s="49"/>
-      <c r="AE27" s="49"/>
-      <c r="AF27" s="49"/>
-      <c r="AG27" s="49"/>
-      <c r="AH27" s="49"/>
-      <c r="AI27" s="49"/>
-      <c r="AJ27" s="49"/>
-      <c r="AK27" s="49"/>
-      <c r="AL27" s="49"/>
-      <c r="AM27" s="49"/>
-      <c r="AN27" s="49"/>
-      <c r="AO27" s="49"/>
-      <c r="AP27" s="49"/>
-      <c r="AQ27" s="49"/>
-      <c r="AR27" s="49"/>
-      <c r="AS27" s="43"/>
-      <c r="AT27" s="43"/>
-      <c r="AU27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="47"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47"/>
+      <c r="AE27" s="47"/>
+      <c r="AF27" s="47"/>
+      <c r="AG27" s="47"/>
+      <c r="AH27" s="47"/>
+      <c r="AI27" s="47"/>
+      <c r="AJ27" s="47"/>
+      <c r="AK27" s="47"/>
+      <c r="AL27" s="47"/>
+      <c r="AM27" s="47"/>
+      <c r="AN27" s="47"/>
+      <c r="AO27" s="47"/>
+      <c r="AP27" s="47"/>
+      <c r="AQ27" s="47"/>
+      <c r="AR27" s="47"/>
+      <c r="AU27" s="44"/>
     </row>
     <row r="28" spans="1:47" ht="20.25" customHeight="1">
       <c r="A28" s="42"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="53"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="53"/>
-      <c r="AB28" s="53"/>
-      <c r="AC28" s="53"/>
-      <c r="AD28" s="53"/>
-      <c r="AE28" s="53"/>
-      <c r="AF28" s="53"/>
-      <c r="AG28" s="53"/>
-      <c r="AH28" s="53"/>
-      <c r="AI28" s="53"/>
-      <c r="AJ28" s="53"/>
-      <c r="AK28" s="53"/>
-      <c r="AL28" s="53"/>
-      <c r="AM28" s="53"/>
-      <c r="AN28" s="53"/>
-      <c r="AO28" s="53"/>
-      <c r="AP28" s="53"/>
-      <c r="AQ28" s="53"/>
-      <c r="AR28" s="53"/>
-      <c r="AS28" s="43"/>
-      <c r="AT28" s="43"/>
-      <c r="AU28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
+      <c r="AM28" s="49"/>
+      <c r="AN28" s="49"/>
+      <c r="AO28" s="49"/>
+      <c r="AP28" s="49"/>
+      <c r="AQ28" s="49"/>
+      <c r="AR28" s="49"/>
+      <c r="AU28" s="44"/>
     </row>
     <row r="29" spans="1:47" ht="9" customHeight="1">
       <c r="A29" s="42"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="49"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="49"/>
-      <c r="W29" s="49"/>
-      <c r="X29" s="49"/>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="49"/>
-      <c r="AA29" s="49"/>
-      <c r="AB29" s="49"/>
-      <c r="AC29" s="49"/>
-      <c r="AD29" s="49"/>
-      <c r="AE29" s="49"/>
-      <c r="AF29" s="49"/>
-      <c r="AG29" s="49"/>
-      <c r="AH29" s="49"/>
-      <c r="AI29" s="49"/>
-      <c r="AJ29" s="49"/>
-      <c r="AK29" s="49"/>
-      <c r="AL29" s="49"/>
-      <c r="AM29" s="49"/>
-      <c r="AN29" s="49"/>
-      <c r="AO29" s="49"/>
-      <c r="AP29" s="49"/>
-      <c r="AQ29" s="49"/>
-      <c r="AR29" s="49"/>
-      <c r="AS29" s="43"/>
-      <c r="AT29" s="43"/>
-      <c r="AU29" s="46"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="47"/>
+      <c r="V29" s="47"/>
+      <c r="W29" s="47"/>
+      <c r="X29" s="47"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="47"/>
+      <c r="AB29" s="47"/>
+      <c r="AC29" s="47"/>
+      <c r="AD29" s="47"/>
+      <c r="AE29" s="47"/>
+      <c r="AF29" s="47"/>
+      <c r="AG29" s="47"/>
+      <c r="AH29" s="47"/>
+      <c r="AI29" s="47"/>
+      <c r="AJ29" s="47"/>
+      <c r="AK29" s="47"/>
+      <c r="AL29" s="47"/>
+      <c r="AM29" s="47"/>
+      <c r="AN29" s="47"/>
+      <c r="AO29" s="47"/>
+      <c r="AP29" s="47"/>
+      <c r="AQ29" s="47"/>
+      <c r="AR29" s="47"/>
+      <c r="AU29" s="44"/>
     </row>
     <row r="30" spans="1:47" ht="18.75" customHeight="1">
       <c r="A30" s="42"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="73"/>
-      <c r="S30" s="73"/>
-      <c r="T30" s="73"/>
-      <c r="U30" s="73"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="49"/>
-      <c r="X30" s="49"/>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="49"/>
-      <c r="AA30" s="49"/>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="49"/>
-      <c r="AD30" s="49"/>
-      <c r="AE30" s="49"/>
-      <c r="AF30" s="49"/>
-      <c r="AG30" s="49"/>
-      <c r="AH30" s="49"/>
-      <c r="AI30" s="49"/>
-      <c r="AJ30" s="52"/>
-      <c r="AK30" s="52"/>
-      <c r="AL30" s="52"/>
-      <c r="AM30" s="52"/>
-      <c r="AN30" s="52"/>
-      <c r="AO30" s="52"/>
-      <c r="AP30" s="52"/>
-      <c r="AQ30" s="52"/>
-      <c r="AR30" s="52"/>
-      <c r="AS30" s="43"/>
-      <c r="AT30" s="43"/>
-      <c r="AU30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="66"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="66"/>
+      <c r="U30" s="66"/>
+      <c r="V30" s="66"/>
+      <c r="W30" s="47"/>
+      <c r="X30" s="47"/>
+      <c r="Y30" s="47"/>
+      <c r="Z30" s="47"/>
+      <c r="AA30" s="47"/>
+      <c r="AB30" s="47"/>
+      <c r="AC30" s="47"/>
+      <c r="AD30" s="47"/>
+      <c r="AE30" s="47"/>
+      <c r="AF30" s="47"/>
+      <c r="AG30" s="47"/>
+      <c r="AH30" s="47"/>
+      <c r="AI30" s="47"/>
+      <c r="AJ30" s="49"/>
+      <c r="AK30" s="49"/>
+      <c r="AL30" s="49"/>
+      <c r="AM30" s="49"/>
+      <c r="AN30" s="49"/>
+      <c r="AO30" s="49"/>
+      <c r="AP30" s="49"/>
+      <c r="AQ30" s="49"/>
+      <c r="AR30" s="49"/>
+      <c r="AU30" s="44"/>
     </row>
     <row r="31" spans="1:47" ht="18.75" customHeight="1">
       <c r="A31" s="42"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="73"/>
-      <c r="S31" s="73"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="73"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="49"/>
-      <c r="X31" s="49"/>
-      <c r="Y31" s="49"/>
-      <c r="Z31" s="49"/>
-      <c r="AA31" s="49"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="49"/>
-      <c r="AE31" s="49"/>
-      <c r="AF31" s="49"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="52"/>
-      <c r="AK31" s="52"/>
-      <c r="AL31" s="52"/>
-      <c r="AM31" s="52"/>
-      <c r="AN31" s="52"/>
-      <c r="AO31" s="52"/>
-      <c r="AP31" s="52"/>
-      <c r="AQ31" s="52"/>
-      <c r="AR31" s="52"/>
-      <c r="AS31" s="43"/>
-      <c r="AT31" s="43"/>
-      <c r="AU31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="66"/>
+      <c r="U31" s="66"/>
+      <c r="V31" s="66"/>
+      <c r="W31" s="47"/>
+      <c r="X31" s="47"/>
+      <c r="Y31" s="47"/>
+      <c r="Z31" s="47"/>
+      <c r="AA31" s="47"/>
+      <c r="AB31" s="47"/>
+      <c r="AC31" s="47"/>
+      <c r="AD31" s="47"/>
+      <c r="AE31" s="47"/>
+      <c r="AF31" s="47"/>
+      <c r="AG31" s="47"/>
+      <c r="AH31" s="47"/>
+      <c r="AI31" s="47"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
+      <c r="AL31" s="49"/>
+      <c r="AM31" s="49"/>
+      <c r="AN31" s="49"/>
+      <c r="AO31" s="49"/>
+      <c r="AP31" s="49"/>
+      <c r="AQ31" s="49"/>
+      <c r="AR31" s="49"/>
+      <c r="AU31" s="44"/>
     </row>
     <row r="32" spans="1:47" ht="18" customHeight="1">
       <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="73"/>
-      <c r="S32" s="73"/>
-      <c r="T32" s="73"/>
-      <c r="U32" s="73"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="49"/>
-      <c r="X32" s="49"/>
-      <c r="Y32" s="49"/>
-      <c r="Z32" s="49"/>
-      <c r="AA32" s="49"/>
-      <c r="AB32" s="49"/>
-      <c r="AC32" s="49"/>
-      <c r="AD32" s="49"/>
-      <c r="AE32" s="49"/>
-      <c r="AF32" s="49"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="49"/>
-      <c r="AI32" s="49"/>
-      <c r="AJ32" s="52"/>
-      <c r="AK32" s="52"/>
-      <c r="AL32" s="52"/>
-      <c r="AM32" s="52"/>
-      <c r="AN32" s="52"/>
-      <c r="AO32" s="52"/>
-      <c r="AP32" s="52"/>
-      <c r="AQ32" s="52"/>
-      <c r="AR32" s="52"/>
-      <c r="AS32" s="43"/>
-      <c r="AT32" s="43"/>
-      <c r="AU32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="66"/>
+      <c r="V32" s="66"/>
+      <c r="W32" s="47"/>
+      <c r="X32" s="47"/>
+      <c r="Y32" s="47"/>
+      <c r="Z32" s="47"/>
+      <c r="AA32" s="47"/>
+      <c r="AB32" s="47"/>
+      <c r="AC32" s="47"/>
+      <c r="AD32" s="47"/>
+      <c r="AE32" s="47"/>
+      <c r="AF32" s="47"/>
+      <c r="AG32" s="47"/>
+      <c r="AH32" s="47"/>
+      <c r="AI32" s="47"/>
+      <c r="AJ32" s="49"/>
+      <c r="AK32" s="49"/>
+      <c r="AL32" s="49"/>
+      <c r="AM32" s="49"/>
+      <c r="AN32" s="49"/>
+      <c r="AO32" s="49"/>
+      <c r="AP32" s="49"/>
+      <c r="AQ32" s="49"/>
+      <c r="AR32" s="49"/>
+      <c r="AU32" s="44"/>
     </row>
     <row r="33" spans="1:47" ht="18" customHeight="1">
       <c r="A33" s="42"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="53"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="53"/>
-      <c r="AB33" s="53"/>
-      <c r="AC33" s="53"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="53"/>
-      <c r="AG33" s="53"/>
-      <c r="AH33" s="53"/>
-      <c r="AI33" s="53"/>
-      <c r="AJ33" s="53"/>
-      <c r="AK33" s="53"/>
-      <c r="AL33" s="53"/>
-      <c r="AM33" s="53"/>
-      <c r="AN33" s="53"/>
-      <c r="AO33" s="53"/>
-      <c r="AP33" s="53"/>
-      <c r="AQ33" s="53"/>
-      <c r="AR33" s="53"/>
-      <c r="AS33" s="43"/>
-      <c r="AT33" s="43"/>
-      <c r="AU33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="49"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="49"/>
+      <c r="W33" s="49"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="49"/>
+      <c r="AA33" s="49"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="49"/>
+      <c r="AD33" s="49"/>
+      <c r="AE33" s="49"/>
+      <c r="AF33" s="49"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="49"/>
+      <c r="AK33" s="49"/>
+      <c r="AL33" s="49"/>
+      <c r="AM33" s="49"/>
+      <c r="AN33" s="49"/>
+      <c r="AO33" s="49"/>
+      <c r="AP33" s="49"/>
+      <c r="AQ33" s="49"/>
+      <c r="AR33" s="49"/>
+      <c r="AU33" s="44"/>
     </row>
     <row r="34" spans="1:47" ht="9.75" customHeight="1">
       <c r="A34" s="42"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="53"/>
-      <c r="Q34" s="53"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="53"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="53"/>
-      <c r="V34" s="53"/>
-      <c r="W34" s="53"/>
-      <c r="X34" s="53"/>
-      <c r="Y34" s="53"/>
-      <c r="Z34" s="53"/>
-      <c r="AA34" s="53"/>
-      <c r="AB34" s="53"/>
-      <c r="AC34" s="53"/>
-      <c r="AD34" s="53"/>
-      <c r="AE34" s="53"/>
-      <c r="AF34" s="53"/>
-      <c r="AG34" s="53"/>
-      <c r="AH34" s="53"/>
-      <c r="AI34" s="53"/>
-      <c r="AJ34" s="53"/>
-      <c r="AK34" s="53"/>
-      <c r="AL34" s="53"/>
-      <c r="AM34" s="53"/>
-      <c r="AN34" s="53"/>
-      <c r="AO34" s="53"/>
-      <c r="AP34" s="53"/>
-      <c r="AQ34" s="53"/>
-      <c r="AR34" s="53"/>
-      <c r="AS34" s="43"/>
-      <c r="AT34" s="43"/>
-      <c r="AU34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="49"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
+      <c r="AA34" s="49"/>
+      <c r="AB34" s="49"/>
+      <c r="AC34" s="49"/>
+      <c r="AD34" s="49"/>
+      <c r="AE34" s="49"/>
+      <c r="AF34" s="49"/>
+      <c r="AG34" s="49"/>
+      <c r="AH34" s="49"/>
+      <c r="AI34" s="49"/>
+      <c r="AJ34" s="49"/>
+      <c r="AK34" s="49"/>
+      <c r="AL34" s="49"/>
+      <c r="AM34" s="49"/>
+      <c r="AN34" s="49"/>
+      <c r="AO34" s="49"/>
+      <c r="AP34" s="49"/>
+      <c r="AQ34" s="49"/>
+      <c r="AR34" s="49"/>
+      <c r="AU34" s="44"/>
     </row>
     <row r="35" spans="1:47" ht="16.5">
       <c r="A35" s="42"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="53"/>
-      <c r="V35" s="53"/>
-      <c r="W35" s="53"/>
-      <c r="X35" s="53"/>
-      <c r="Y35" s="53"/>
-      <c r="Z35" s="53"/>
-      <c r="AA35" s="53"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="53"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="53"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="53"/>
-      <c r="AH35" s="53"/>
-      <c r="AI35" s="53"/>
-      <c r="AJ35" s="53"/>
-      <c r="AK35" s="53"/>
-      <c r="AL35" s="53"/>
-      <c r="AM35" s="53"/>
-      <c r="AN35" s="53"/>
-      <c r="AO35" s="53"/>
-      <c r="AP35" s="53"/>
-      <c r="AQ35" s="53"/>
-      <c r="AR35" s="53"/>
-      <c r="AS35" s="43"/>
-      <c r="AT35" s="43"/>
-      <c r="AU35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="49"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="49"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
+      <c r="Z35" s="49"/>
+      <c r="AA35" s="49"/>
+      <c r="AB35" s="49"/>
+      <c r="AC35" s="49"/>
+      <c r="AD35" s="49"/>
+      <c r="AE35" s="49"/>
+      <c r="AF35" s="49"/>
+      <c r="AG35" s="49"/>
+      <c r="AH35" s="49"/>
+      <c r="AI35" s="49"/>
+      <c r="AJ35" s="49"/>
+      <c r="AK35" s="49"/>
+      <c r="AL35" s="49"/>
+      <c r="AM35" s="49"/>
+      <c r="AN35" s="49"/>
+      <c r="AO35" s="49"/>
+      <c r="AP35" s="49"/>
+      <c r="AQ35" s="49"/>
+      <c r="AR35" s="49"/>
+      <c r="AU35" s="44"/>
     </row>
     <row r="36" spans="1:47" ht="16.5">
       <c r="A36" s="42"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="53"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="53"/>
-      <c r="U36" s="53"/>
-      <c r="V36" s="53"/>
-      <c r="W36" s="53"/>
-      <c r="X36" s="53"/>
-      <c r="Y36" s="53"/>
-      <c r="Z36" s="53"/>
-      <c r="AA36" s="53"/>
-      <c r="AB36" s="53"/>
-      <c r="AC36" s="53"/>
-      <c r="AD36" s="53"/>
-      <c r="AE36" s="53"/>
-      <c r="AF36" s="53"/>
-      <c r="AG36" s="53"/>
-      <c r="AH36" s="53"/>
-      <c r="AI36" s="53"/>
-      <c r="AJ36" s="53"/>
-      <c r="AK36" s="53"/>
-      <c r="AL36" s="53"/>
-      <c r="AM36" s="53"/>
-      <c r="AN36" s="53"/>
-      <c r="AO36" s="53"/>
-      <c r="AP36" s="53"/>
-      <c r="AQ36" s="53"/>
-      <c r="AR36" s="53"/>
-      <c r="AS36" s="43"/>
-      <c r="AT36" s="43"/>
-      <c r="AU36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="49"/>
+      <c r="P36" s="49"/>
+      <c r="Q36" s="49"/>
+      <c r="R36" s="49"/>
+      <c r="S36" s="49"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
+      <c r="W36" s="49"/>
+      <c r="X36" s="49"/>
+      <c r="Y36" s="49"/>
+      <c r="Z36" s="49"/>
+      <c r="AA36" s="49"/>
+      <c r="AB36" s="49"/>
+      <c r="AC36" s="49"/>
+      <c r="AD36" s="49"/>
+      <c r="AE36" s="49"/>
+      <c r="AF36" s="49"/>
+      <c r="AG36" s="49"/>
+      <c r="AH36" s="49"/>
+      <c r="AI36" s="49"/>
+      <c r="AJ36" s="49"/>
+      <c r="AK36" s="49"/>
+      <c r="AL36" s="49"/>
+      <c r="AM36" s="49"/>
+      <c r="AN36" s="49"/>
+      <c r="AO36" s="49"/>
+      <c r="AP36" s="49"/>
+      <c r="AQ36" s="49"/>
+      <c r="AR36" s="49"/>
+      <c r="AU36" s="44"/>
     </row>
     <row r="37" spans="1:47" ht="12" customHeight="1">
       <c r="A37" s="42"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="53"/>
-      <c r="V37" s="53"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
-      <c r="AA37" s="53"/>
-      <c r="AB37" s="53"/>
-      <c r="AC37" s="53"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="53"/>
-      <c r="AF37" s="53"/>
-      <c r="AG37" s="53"/>
-      <c r="AH37" s="53"/>
-      <c r="AI37" s="53"/>
-      <c r="AJ37" s="53"/>
-      <c r="AK37" s="53"/>
-      <c r="AL37" s="53"/>
-      <c r="AM37" s="53"/>
-      <c r="AN37" s="53"/>
-      <c r="AO37" s="53"/>
-      <c r="AP37" s="53"/>
-      <c r="AQ37" s="53"/>
-      <c r="AR37" s="53"/>
-      <c r="AS37" s="43"/>
-      <c r="AT37" s="43"/>
-      <c r="AU37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49"/>
+      <c r="O37" s="49"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
+      <c r="W37" s="49"/>
+      <c r="X37" s="49"/>
+      <c r="Y37" s="49"/>
+      <c r="Z37" s="49"/>
+      <c r="AA37" s="49"/>
+      <c r="AB37" s="49"/>
+      <c r="AC37" s="49"/>
+      <c r="AD37" s="49"/>
+      <c r="AE37" s="49"/>
+      <c r="AF37" s="49"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
+      <c r="AM37" s="49"/>
+      <c r="AN37" s="49"/>
+      <c r="AO37" s="49"/>
+      <c r="AP37" s="49"/>
+      <c r="AQ37" s="49"/>
+      <c r="AR37" s="49"/>
+      <c r="AU37" s="44"/>
     </row>
     <row r="38" spans="1:47" ht="16.5">
       <c r="A38" s="42"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="53"/>
-      <c r="Q38" s="53"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="53"/>
-      <c r="T38" s="53"/>
-      <c r="U38" s="53"/>
-      <c r="V38" s="53"/>
-      <c r="W38" s="53"/>
-      <c r="X38" s="53"/>
-      <c r="Y38" s="53"/>
-      <c r="Z38" s="53"/>
-      <c r="AA38" s="53"/>
-      <c r="AB38" s="53"/>
-      <c r="AC38" s="53"/>
-      <c r="AD38" s="53"/>
-      <c r="AE38" s="53"/>
-      <c r="AF38" s="53"/>
-      <c r="AG38" s="53"/>
-      <c r="AH38" s="53"/>
-      <c r="AI38" s="53"/>
-      <c r="AJ38" s="53"/>
-      <c r="AK38" s="53"/>
-      <c r="AL38" s="53"/>
-      <c r="AM38" s="53"/>
-      <c r="AN38" s="53"/>
-      <c r="AO38" s="53"/>
-      <c r="AP38" s="53"/>
-      <c r="AQ38" s="53"/>
-      <c r="AR38" s="53"/>
-      <c r="AS38" s="43"/>
-      <c r="AT38" s="43"/>
-      <c r="AU38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="49"/>
+      <c r="P38" s="49"/>
+      <c r="Q38" s="49"/>
+      <c r="R38" s="49"/>
+      <c r="S38" s="49"/>
+      <c r="T38" s="49"/>
+      <c r="U38" s="49"/>
+      <c r="V38" s="49"/>
+      <c r="W38" s="49"/>
+      <c r="X38" s="49"/>
+      <c r="Y38" s="49"/>
+      <c r="Z38" s="49"/>
+      <c r="AA38" s="49"/>
+      <c r="AB38" s="49"/>
+      <c r="AC38" s="49"/>
+      <c r="AD38" s="49"/>
+      <c r="AE38" s="49"/>
+      <c r="AF38" s="49"/>
+      <c r="AG38" s="49"/>
+      <c r="AH38" s="49"/>
+      <c r="AI38" s="49"/>
+      <c r="AJ38" s="49"/>
+      <c r="AK38" s="49"/>
+      <c r="AL38" s="49"/>
+      <c r="AM38" s="49"/>
+      <c r="AN38" s="49"/>
+      <c r="AO38" s="49"/>
+      <c r="AP38" s="49"/>
+      <c r="AQ38" s="49"/>
+      <c r="AR38" s="49"/>
+      <c r="AU38" s="44"/>
     </row>
     <row r="39" spans="1:47" ht="16.5">
       <c r="A39" s="42"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
-      <c r="P39" s="53"/>
-      <c r="Q39" s="53"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="53"/>
-      <c r="T39" s="53"/>
-      <c r="U39" s="53"/>
-      <c r="V39" s="53"/>
-      <c r="W39" s="53"/>
-      <c r="X39" s="53"/>
-      <c r="Y39" s="53"/>
-      <c r="Z39" s="53"/>
-      <c r="AA39" s="53"/>
-      <c r="AB39" s="53"/>
-      <c r="AC39" s="53"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="53"/>
-      <c r="AG39" s="53"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="53"/>
-      <c r="AJ39" s="53"/>
-      <c r="AK39" s="53"/>
-      <c r="AL39" s="53"/>
-      <c r="AM39" s="53"/>
-      <c r="AN39" s="53"/>
-      <c r="AO39" s="53"/>
-      <c r="AP39" s="53"/>
-      <c r="AQ39" s="53"/>
-      <c r="AR39" s="53"/>
-      <c r="AS39" s="43"/>
-      <c r="AT39" s="43"/>
-      <c r="AU39" s="46"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="49"/>
+      <c r="N39" s="49"/>
+      <c r="O39" s="49"/>
+      <c r="P39" s="49"/>
+      <c r="Q39" s="49"/>
+      <c r="R39" s="49"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="49"/>
+      <c r="W39" s="49"/>
+      <c r="X39" s="49"/>
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AE39" s="49"/>
+      <c r="AF39" s="49"/>
+      <c r="AG39" s="49"/>
+      <c r="AH39" s="49"/>
+      <c r="AI39" s="49"/>
+      <c r="AJ39" s="49"/>
+      <c r="AK39" s="49"/>
+      <c r="AL39" s="49"/>
+      <c r="AM39" s="49"/>
+      <c r="AN39" s="49"/>
+      <c r="AO39" s="49"/>
+      <c r="AP39" s="49"/>
+      <c r="AQ39" s="49"/>
+      <c r="AR39" s="49"/>
+      <c r="AU39" s="44"/>
     </row>
     <row r="40" spans="1:47" ht="16.5">
       <c r="A40" s="42"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="53"/>
-      <c r="U40" s="53"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="53"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="53"/>
-      <c r="AC40" s="53"/>
-      <c r="AD40" s="53"/>
-      <c r="AE40" s="53"/>
-      <c r="AF40" s="53"/>
-      <c r="AG40" s="53"/>
-      <c r="AH40" s="53"/>
-      <c r="AI40" s="53"/>
-      <c r="AJ40" s="53"/>
-      <c r="AK40" s="53"/>
-      <c r="AL40" s="53"/>
-      <c r="AM40" s="53"/>
-      <c r="AN40" s="53"/>
-      <c r="AO40" s="53"/>
-      <c r="AP40" s="53"/>
-      <c r="AQ40" s="53"/>
-      <c r="AR40" s="53"/>
-      <c r="AS40" s="43"/>
-      <c r="AT40" s="43"/>
-      <c r="AU40" s="46"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="49"/>
+      <c r="N40" s="49"/>
+      <c r="O40" s="49"/>
+      <c r="P40" s="49"/>
+      <c r="Q40" s="49"/>
+      <c r="R40" s="49"/>
+      <c r="S40" s="49"/>
+      <c r="T40" s="49"/>
+      <c r="U40" s="49"/>
+      <c r="V40" s="49"/>
+      <c r="W40" s="49"/>
+      <c r="X40" s="49"/>
+      <c r="Y40" s="49"/>
+      <c r="Z40" s="49"/>
+      <c r="AA40" s="49"/>
+      <c r="AB40" s="49"/>
+      <c r="AC40" s="49"/>
+      <c r="AD40" s="49"/>
+      <c r="AE40" s="49"/>
+      <c r="AF40" s="49"/>
+      <c r="AG40" s="49"/>
+      <c r="AH40" s="49"/>
+      <c r="AI40" s="49"/>
+      <c r="AJ40" s="49"/>
+      <c r="AK40" s="49"/>
+      <c r="AL40" s="49"/>
+      <c r="AM40" s="49"/>
+      <c r="AN40" s="49"/>
+      <c r="AO40" s="49"/>
+      <c r="AP40" s="49"/>
+      <c r="AQ40" s="49"/>
+      <c r="AR40" s="49"/>
+      <c r="AU40" s="44"/>
     </row>
     <row r="41" spans="1:47" ht="16.5">
       <c r="A41" s="42"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="53"/>
-      <c r="T41" s="53"/>
-      <c r="U41" s="53"/>
-      <c r="V41" s="53"/>
-      <c r="W41" s="53"/>
-      <c r="X41" s="53"/>
-      <c r="Y41" s="53"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="53"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="53"/>
-      <c r="AF41" s="53"/>
-      <c r="AG41" s="53"/>
-      <c r="AH41" s="53"/>
-      <c r="AI41" s="53"/>
-      <c r="AJ41" s="53"/>
-      <c r="AK41" s="53"/>
-      <c r="AL41" s="53"/>
-      <c r="AM41" s="53"/>
-      <c r="AN41" s="53"/>
-      <c r="AO41" s="53"/>
-      <c r="AP41" s="53"/>
-      <c r="AQ41" s="53"/>
-      <c r="AR41" s="53"/>
-      <c r="AS41" s="43"/>
-      <c r="AT41" s="43"/>
-      <c r="AU41" s="46"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
+      <c r="P41" s="49"/>
+      <c r="Q41" s="49"/>
+      <c r="R41" s="49"/>
+      <c r="S41" s="49"/>
+      <c r="T41" s="49"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="49"/>
+      <c r="W41" s="49"/>
+      <c r="X41" s="49"/>
+      <c r="Y41" s="49"/>
+      <c r="Z41" s="49"/>
+      <c r="AA41" s="49"/>
+      <c r="AB41" s="49"/>
+      <c r="AC41" s="49"/>
+      <c r="AD41" s="49"/>
+      <c r="AE41" s="49"/>
+      <c r="AF41" s="49"/>
+      <c r="AG41" s="49"/>
+      <c r="AH41" s="49"/>
+      <c r="AI41" s="49"/>
+      <c r="AJ41" s="49"/>
+      <c r="AK41" s="49"/>
+      <c r="AL41" s="49"/>
+      <c r="AM41" s="49"/>
+      <c r="AN41" s="49"/>
+      <c r="AO41" s="49"/>
+      <c r="AP41" s="49"/>
+      <c r="AQ41" s="49"/>
+      <c r="AR41" s="49"/>
+      <c r="AU41" s="44"/>
     </row>
     <row r="42" spans="1:47" ht="21.75" customHeight="1">
       <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="74"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="74"/>
-      <c r="L42" s="74"/>
-      <c r="M42" s="74"/>
-      <c r="N42" s="74"/>
-      <c r="O42" s="74"/>
-      <c r="P42" s="74"/>
-      <c r="Q42" s="74"/>
-      <c r="R42" s="74"/>
-      <c r="S42" s="74"/>
-      <c r="T42" s="74"/>
-      <c r="U42" s="74"/>
-      <c r="V42" s="74"/>
-      <c r="W42" s="74"/>
-      <c r="X42" s="74"/>
-      <c r="Y42" s="74"/>
-      <c r="Z42" s="74"/>
-      <c r="AA42" s="74"/>
-      <c r="AB42" s="74"/>
-      <c r="AC42" s="74"/>
-      <c r="AD42" s="74"/>
-      <c r="AE42" s="74"/>
-      <c r="AF42" s="74"/>
-      <c r="AG42" s="74"/>
-      <c r="AH42" s="74"/>
-      <c r="AI42" s="74"/>
-      <c r="AJ42" s="74"/>
-      <c r="AK42" s="74"/>
-      <c r="AL42" s="74"/>
-      <c r="AM42" s="74"/>
-      <c r="AN42" s="74"/>
-      <c r="AO42" s="74"/>
-      <c r="AP42" s="74"/>
-      <c r="AQ42" s="74"/>
-      <c r="AR42" s="74"/>
-      <c r="AS42" s="43"/>
-      <c r="AT42" s="43"/>
-      <c r="AU42" s="46"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="67"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="67"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="67"/>
+      <c r="U42" s="67"/>
+      <c r="V42" s="67"/>
+      <c r="W42" s="67"/>
+      <c r="X42" s="67"/>
+      <c r="Y42" s="67"/>
+      <c r="Z42" s="67"/>
+      <c r="AA42" s="67"/>
+      <c r="AB42" s="67"/>
+      <c r="AC42" s="67"/>
+      <c r="AD42" s="67"/>
+      <c r="AE42" s="67"/>
+      <c r="AF42" s="67"/>
+      <c r="AG42" s="67"/>
+      <c r="AH42" s="67"/>
+      <c r="AI42" s="67"/>
+      <c r="AJ42" s="67"/>
+      <c r="AK42" s="67"/>
+      <c r="AL42" s="67"/>
+      <c r="AM42" s="67"/>
+      <c r="AN42" s="67"/>
+      <c r="AO42" s="67"/>
+      <c r="AP42" s="67"/>
+      <c r="AQ42" s="67"/>
+      <c r="AR42" s="67"/>
+      <c r="AU42" s="44"/>
     </row>
     <row r="43" spans="1:47" ht="16.5">
       <c r="A43" s="42"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="53"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="53"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="53"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="53"/>
-      <c r="P43" s="53"/>
-      <c r="Q43" s="53"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
-      <c r="T43" s="53"/>
-      <c r="U43" s="53"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="53"/>
-      <c r="Z43" s="53"/>
-      <c r="AA43" s="53"/>
-      <c r="AB43" s="53"/>
-      <c r="AC43" s="53"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="53"/>
-      <c r="AG43" s="53"/>
-      <c r="AH43" s="53"/>
-      <c r="AI43" s="53"/>
-      <c r="AJ43" s="53"/>
-      <c r="AK43" s="53"/>
-      <c r="AL43" s="53"/>
-      <c r="AM43" s="53"/>
-      <c r="AN43" s="53"/>
-      <c r="AO43" s="53"/>
-      <c r="AP43" s="53"/>
-      <c r="AQ43" s="53"/>
-      <c r="AR43" s="53"/>
-      <c r="AS43" s="43"/>
-      <c r="AT43" s="43"/>
-      <c r="AU43" s="46"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="49"/>
+      <c r="O43" s="49"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="49"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="49"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="49"/>
+      <c r="W43" s="49"/>
+      <c r="X43" s="49"/>
+      <c r="Y43" s="49"/>
+      <c r="Z43" s="49"/>
+      <c r="AA43" s="49"/>
+      <c r="AB43" s="49"/>
+      <c r="AC43" s="49"/>
+      <c r="AD43" s="49"/>
+      <c r="AE43" s="49"/>
+      <c r="AF43" s="49"/>
+      <c r="AG43" s="49"/>
+      <c r="AH43" s="49"/>
+      <c r="AI43" s="49"/>
+      <c r="AJ43" s="49"/>
+      <c r="AK43" s="49"/>
+      <c r="AL43" s="49"/>
+      <c r="AM43" s="49"/>
+      <c r="AN43" s="49"/>
+      <c r="AO43" s="49"/>
+      <c r="AP43" s="49"/>
+      <c r="AQ43" s="49"/>
+      <c r="AR43" s="49"/>
+      <c r="AU43" s="44"/>
     </row>
     <row r="44" spans="1:47" ht="11.25" customHeight="1">
       <c r="A44" s="42"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="53"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="53"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="53"/>
-      <c r="P44" s="53"/>
-      <c r="Q44" s="53"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="53"/>
-      <c r="T44" s="75"/>
-      <c r="U44" s="53"/>
-      <c r="V44" s="53"/>
-      <c r="W44" s="53"/>
-      <c r="X44" s="53"/>
-      <c r="Y44" s="53"/>
-      <c r="Z44" s="67"/>
-      <c r="AA44" s="53"/>
-      <c r="AB44" s="53"/>
-      <c r="AC44" s="53"/>
-      <c r="AD44" s="53"/>
-      <c r="AE44" s="53"/>
-      <c r="AF44" s="53"/>
-      <c r="AG44" s="53"/>
-      <c r="AH44" s="53"/>
-      <c r="AI44" s="53"/>
-      <c r="AJ44" s="53"/>
-      <c r="AK44" s="53"/>
-      <c r="AL44" s="53"/>
-      <c r="AM44" s="53"/>
-      <c r="AN44" s="75"/>
-      <c r="AO44" s="53"/>
-      <c r="AP44" s="53"/>
-      <c r="AQ44" s="53"/>
-      <c r="AR44" s="53"/>
-      <c r="AS44" s="43"/>
-      <c r="AT44" s="43"/>
-      <c r="AU44" s="46"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="49"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="49"/>
+      <c r="P44" s="49"/>
+      <c r="Q44" s="49"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="68"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="49"/>
+      <c r="W44" s="49"/>
+      <c r="X44" s="49"/>
+      <c r="Y44" s="49"/>
+      <c r="Z44" s="47"/>
+      <c r="AA44" s="49"/>
+      <c r="AB44" s="49"/>
+      <c r="AC44" s="49"/>
+      <c r="AD44" s="49"/>
+      <c r="AE44" s="49"/>
+      <c r="AF44" s="49"/>
+      <c r="AG44" s="49"/>
+      <c r="AH44" s="49"/>
+      <c r="AI44" s="49"/>
+      <c r="AJ44" s="49"/>
+      <c r="AK44" s="49"/>
+      <c r="AL44" s="49"/>
+      <c r="AM44" s="49"/>
+      <c r="AN44" s="68"/>
+      <c r="AO44" s="49"/>
+      <c r="AP44" s="49"/>
+      <c r="AQ44" s="49"/>
+      <c r="AR44" s="49"/>
+      <c r="AU44" s="44"/>
     </row>
     <row r="45" spans="1:47">
       <c r="A45" s="42"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
-      <c r="O45" s="43"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="43"/>
-      <c r="X45" s="43"/>
-      <c r="Y45" s="43"/>
-      <c r="Z45" s="43"/>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
-      <c r="AC45" s="43"/>
-      <c r="AD45" s="43"/>
-      <c r="AE45" s="43"/>
-      <c r="AF45" s="43"/>
-      <c r="AG45" s="43"/>
-      <c r="AH45" s="43"/>
-      <c r="AI45" s="43"/>
-      <c r="AJ45" s="43"/>
-      <c r="AK45" s="43"/>
-      <c r="AL45" s="43"/>
-      <c r="AM45" s="43"/>
-      <c r="AN45" s="43"/>
-      <c r="AO45" s="43"/>
-      <c r="AP45" s="43"/>
-      <c r="AQ45" s="43"/>
-      <c r="AR45" s="43"/>
-      <c r="AS45" s="43"/>
-      <c r="AT45" s="43"/>
-      <c r="AU45" s="46"/>
+      <c r="AU45" s="44"/>
     </row>
     <row r="46" spans="1:47" ht="6.75" customHeight="1">
       <c r="A46" s="42"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
-      <c r="M46" s="44"/>
-      <c r="N46" s="44"/>
-      <c r="O46" s="44"/>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="44"/>
-      <c r="R46" s="44"/>
-      <c r="S46" s="44"/>
-      <c r="T46" s="44"/>
-      <c r="U46" s="44"/>
-      <c r="V46" s="44"/>
-      <c r="W46" s="44"/>
-      <c r="X46" s="44"/>
-      <c r="Y46" s="44"/>
-      <c r="Z46" s="44"/>
-      <c r="AA46" s="44"/>
-      <c r="AB46" s="44"/>
-      <c r="AC46" s="44"/>
-      <c r="AD46" s="44"/>
-      <c r="AE46" s="44"/>
-      <c r="AF46" s="44"/>
-      <c r="AG46" s="44"/>
-      <c r="AH46" s="44"/>
-      <c r="AI46" s="44"/>
-      <c r="AJ46" s="44"/>
-      <c r="AK46" s="44"/>
-      <c r="AL46" s="44"/>
-      <c r="AM46" s="44"/>
-      <c r="AN46" s="44"/>
-      <c r="AO46" s="44"/>
-      <c r="AP46" s="44"/>
-      <c r="AQ46" s="44"/>
-      <c r="AR46" s="44"/>
-      <c r="AS46" s="44"/>
-      <c r="AT46" s="44"/>
-      <c r="AU46" s="46"/>
+      <c r="AU46" s="44"/>
     </row>
     <row r="47" spans="1:47" ht="5.0999999999999996" customHeight="1">
-      <c r="A47" s="76"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
-      <c r="M47" s="44"/>
-      <c r="N47" s="44"/>
-      <c r="O47" s="44"/>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="44"/>
-      <c r="S47" s="44"/>
-      <c r="T47" s="44"/>
-      <c r="U47" s="44"/>
-      <c r="V47" s="44"/>
-      <c r="W47" s="44"/>
-      <c r="X47" s="44"/>
-      <c r="Y47" s="44"/>
-      <c r="Z47" s="44"/>
-      <c r="AA47" s="44"/>
-      <c r="AB47" s="44"/>
-      <c r="AC47" s="44"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="44"/>
-      <c r="AF47" s="44"/>
-      <c r="AG47" s="44"/>
-      <c r="AH47" s="44"/>
-      <c r="AI47" s="44"/>
-      <c r="AJ47" s="44"/>
-      <c r="AK47" s="44"/>
-      <c r="AL47" s="44"/>
-      <c r="AM47" s="44"/>
-      <c r="AN47" s="44"/>
-      <c r="AO47" s="44"/>
-      <c r="AP47" s="44"/>
-      <c r="AQ47" s="44"/>
-      <c r="AR47" s="44"/>
-      <c r="AS47" s="44"/>
-      <c r="AT47" s="44"/>
-      <c r="AU47" s="77"/>
+      <c r="A47" s="69"/>
+      <c r="AU47" s="70"/>
     </row>
     <row r="48" spans="1:47" ht="6" customHeight="1">
-      <c r="A48" s="78"/>
-      <c r="AU48" s="78"/>
+      <c r="A48" s="70"/>
+      <c r="AU48" s="70"/>
     </row>
     <row r="49" spans="1:47" ht="18.75" customHeight="1">
-      <c r="A49" s="78"/>
-      <c r="AU49" s="78"/>
+      <c r="A49" s="70"/>
+      <c r="AU49" s="70"/>
     </row>
     <row r="50" spans="1:47" ht="18.75" customHeight="1">
-      <c r="A50" s="78"/>
-      <c r="AU50" s="78"/>
+      <c r="A50" s="70"/>
+      <c r="AU50" s="70"/>
     </row>
     <row r="51" spans="1:47" ht="7.5" customHeight="1">
-      <c r="A51" s="78"/>
-      <c r="B51" s="78"/>
-      <c r="C51" s="78"/>
-      <c r="D51" s="78"/>
-      <c r="E51" s="78"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="78"/>
-      <c r="H51" s="78"/>
-      <c r="I51" s="78"/>
-      <c r="J51" s="78"/>
-      <c r="K51" s="78"/>
-      <c r="L51" s="78"/>
-      <c r="M51" s="78"/>
-      <c r="N51" s="78"/>
-      <c r="O51" s="78"/>
-      <c r="P51" s="78"/>
-      <c r="Q51" s="78"/>
-      <c r="R51" s="78"/>
-      <c r="S51" s="78"/>
-      <c r="T51" s="78"/>
-      <c r="U51" s="78"/>
-      <c r="V51" s="78"/>
-      <c r="W51" s="78"/>
-      <c r="X51" s="78"/>
-      <c r="Y51" s="78"/>
-      <c r="Z51" s="78"/>
-      <c r="AA51" s="78"/>
-      <c r="AB51" s="78"/>
-      <c r="AC51" s="78"/>
-      <c r="AD51" s="78"/>
-      <c r="AE51" s="78"/>
-      <c r="AF51" s="78"/>
-      <c r="AG51" s="78"/>
-      <c r="AH51" s="78"/>
-      <c r="AI51" s="78"/>
-      <c r="AJ51" s="78"/>
-      <c r="AK51" s="78"/>
-      <c r="AL51" s="78"/>
-      <c r="AM51" s="78"/>
-      <c r="AN51" s="78"/>
-      <c r="AO51" s="78"/>
-      <c r="AP51" s="78"/>
-      <c r="AQ51" s="78"/>
-      <c r="AR51" s="78"/>
-      <c r="AS51" s="78"/>
-      <c r="AT51" s="78"/>
-      <c r="AU51" s="78"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="70"/>
+      <c r="M51" s="70"/>
+      <c r="N51" s="70"/>
+      <c r="O51" s="70"/>
+      <c r="P51" s="70"/>
+      <c r="Q51" s="70"/>
+      <c r="R51" s="70"/>
+      <c r="S51" s="70"/>
+      <c r="T51" s="70"/>
+      <c r="U51" s="70"/>
+      <c r="V51" s="70"/>
+      <c r="W51" s="70"/>
+      <c r="X51" s="70"/>
+      <c r="Y51" s="70"/>
+      <c r="Z51" s="70"/>
+      <c r="AA51" s="70"/>
+      <c r="AB51" s="70"/>
+      <c r="AC51" s="70"/>
+      <c r="AD51" s="70"/>
+      <c r="AE51" s="70"/>
+      <c r="AF51" s="70"/>
+      <c r="AG51" s="70"/>
+      <c r="AH51" s="70"/>
+      <c r="AI51" s="70"/>
+      <c r="AJ51" s="70"/>
+      <c r="AK51" s="70"/>
+      <c r="AL51" s="70"/>
+      <c r="AM51" s="70"/>
+      <c r="AN51" s="70"/>
+      <c r="AO51" s="70"/>
+      <c r="AP51" s="70"/>
+      <c r="AQ51" s="70"/>
+      <c r="AR51" s="70"/>
+      <c r="AS51" s="70"/>
+      <c r="AT51" s="70"/>
+      <c r="AU51" s="70"/>
     </row>
     <row r="56" spans="1:47" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:47" ht="14.25" customHeight="1">
-      <c r="A57" s="137"/>
-      <c r="B57" s="137"/>
-      <c r="C57" s="137"/>
-      <c r="D57" s="137"/>
-      <c r="E57" s="137"/>
-      <c r="F57" s="137"/>
+      <c r="A57" s="74"/>
+      <c r="B57" s="74"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="74"/>
     </row>
     <row r="58" spans="1:47" ht="14.25" customHeight="1">
-      <c r="A58" s="137"/>
-      <c r="B58" s="137"/>
-      <c r="C58" s="137"/>
-      <c r="D58" s="137"/>
-      <c r="E58" s="137"/>
-      <c r="F58" s="137"/>
+      <c r="A58" s="74"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
+      <c r="D58" s="74"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="74"/>
     </row>
     <row r="59" spans="1:47">
-      <c r="A59" s="137"/>
-      <c r="B59" s="137"/>
-      <c r="C59" s="137"/>
-      <c r="D59" s="137"/>
-      <c r="E59" s="137"/>
-      <c r="F59" s="137"/>
+      <c r="A59" s="74"/>
+      <c r="B59" s="74"/>
+      <c r="C59" s="74"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/server/src/main/resources/templates/confirmation_template.xlsx
+++ b/server/src/main/resources/templates/confirmation_template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qaz25\OneDrive\문서\Develop\academy-heungkuk-v2-\server\src\main\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★★발송_2026_확인서, 견적서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D176C5-5920-4540-91D8-C82E43D3EC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="1560" windowWidth="36180" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
   </bookViews>
   <sheets>
     <sheet name="빈문서" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">빈문서!$A$1:$AU$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">준수사항!$A$1:$AU$51</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
   <si>
     <t>흥국생명연수원 사용안내 확인서</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -331,6 +330,15 @@
     <t/>
   </si>
   <si>
+    <t>9140643@heungkuklife.co.kr</t>
+  </si>
+  <si>
+    <t>2일(화)</t>
+  </si>
+  <si>
+    <t>3일(수)</t>
+  </si>
+  <si>
     <t>흥국생명연수원 이용시 준수사항 안내</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -350,7 +358,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="10">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="yyyy\.\ mm\.\ dd\ \(aaa\)"/>
@@ -1368,7 +1376,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="270">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1498,561 +1506,576 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="179" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2178,6 +2201,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3607,6 +3639,152 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>10376</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>19855</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>86577</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>43898</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="24" name="그룹 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="305651" y="1829605"/>
+          <a:ext cx="733426" cy="385993"/>
+          <a:chOff x="6664676" y="2510740"/>
+          <a:chExt cx="146177" cy="372923"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="타원 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="6679593" y="2572805"/>
+            <a:ext cx="131260" cy="310858"/>
+          </a:xfrm>
+          <a:prstGeom prst="ellipse">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF00FF"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="26" name="1/2 액자 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="13817943">
+            <a:off x="6687544" y="2487872"/>
+            <a:ext cx="91055" cy="136791"/>
+          </a:xfrm>
+          <a:prstGeom prst="halfFrame">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 25252"/>
+              <a:gd name="adj2" fmla="val 21641"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF00FF"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF00FF"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3627,13 +3805,7 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="그룹 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="그룹 1"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -3646,13 +3818,7 @@
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="3" name="그룹 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="3" name="그룹 2"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -3665,13 +3831,7 @@
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="타원 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
+            <xdr:cNvPr id="5" name="타원 4"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3716,13 +3876,7 @@
         </xdr:sp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="타원 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
+            <xdr:cNvPr id="6" name="타원 5"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3770,13 +3924,7 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="직사각형 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="4" name="직사각형 3"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3839,13 +3987,7 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="7" name="그룹 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="7" name="그룹 6"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -3858,13 +4000,7 @@
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="8" name="그룹 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="8" name="그룹 7"/>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -3877,13 +4013,7 @@
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="타원 9">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
+            <xdr:cNvPr id="10" name="타원 9"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3928,13 +4058,7 @@
         </xdr:sp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="타원 10">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
+            <xdr:cNvPr id="11" name="타원 10"/>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3982,13 +4106,7 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="직사각형 8">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="9" name="직사각형 8"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -4051,13 +4169,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="이등변 삼각형 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="12" name="이등변 삼각형 11"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4233,13 +4345,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="이등변 삼각형 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="13" name="이등변 삼각형 12"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4415,13 +4521,7 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="그룹 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="14" name="그룹 13"/>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
@@ -4434,13 +4534,7 @@
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="15" name="Picture 2" descr="C:\Users\김충렬\Desktop\연수원지도.PNG">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="15" name="Picture 2" descr="C:\Users\김충렬\Desktop\연수원지도.PNG"/>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
           </xdr:cNvPicPr>
@@ -4493,13 +4587,7 @@
       </xdr:pic>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="직사각형 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="16" name="직사각형 15"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4670,13 +4758,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="직사각형 16">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="17" name="직사각형 16"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4847,13 +4929,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="직사각형 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="18" name="직사각형 17"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5024,13 +5100,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="직사각형 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="19" name="직사각형 18"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5201,13 +5271,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="직사각형 19">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="20" name="직사각형 19"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5378,13 +5442,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="직사각형 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="21" name="직사각형 20"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5597,13 +5655,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="직사각형 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="22" name="직사각형 21"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5816,13 +5868,7 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="직사각형 22">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
+          <xdr:cNvPr id="23" name="직사각형 22"/>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -6009,13 +6055,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="24" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6386,13 +6426,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="25" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6770,13 +6804,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="26" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7354,13 +7382,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="27" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7748,13 +7770,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="28" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8225,13 +8241,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="직사각형 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="29" name="직사각형 28"/>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8897,13 +8907,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="30" name="TextBox 11"/>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -9131,13 +9135,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="그림 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="31" name="그림 30"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -9442,9 +9440,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AX59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="0.625" style="3" customWidth="1"/>
     <col min="2" max="3" width="1.625" style="3" customWidth="1"/>
@@ -9520,39 +9518,39 @@
       <c r="F2" s="4"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="80"/>
-      <c r="AI2" s="80"/>
-      <c r="AJ2" s="80"/>
-      <c r="AK2" s="80"/>
-      <c r="AL2" s="80"/>
-      <c r="AM2" s="80"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="84"/>
+      <c r="AE2" s="84"/>
+      <c r="AF2" s="84"/>
+      <c r="AG2" s="84"/>
+      <c r="AH2" s="84"/>
+      <c r="AI2" s="84"/>
+      <c r="AJ2" s="84"/>
+      <c r="AK2" s="84"/>
+      <c r="AL2" s="84"/>
+      <c r="AM2" s="84"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
@@ -9570,37 +9568,37 @@
       <c r="E3" s="4"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="80"/>
-      <c r="AC3" s="80"/>
-      <c r="AD3" s="80"/>
-      <c r="AE3" s="80"/>
-      <c r="AF3" s="80"/>
-      <c r="AG3" s="80"/>
-      <c r="AH3" s="80"/>
-      <c r="AI3" s="80"/>
-      <c r="AJ3" s="80"/>
-      <c r="AK3" s="80"/>
-      <c r="AL3" s="80"/>
-      <c r="AM3" s="80"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="84"/>
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="84"/>
+      <c r="AI3" s="84"/>
+      <c r="AJ3" s="84"/>
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
@@ -9617,39 +9615,39 @@
       <c r="E4" s="4"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="81" t="s">
+      <c r="I4" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="81"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="81"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="81"/>
-      <c r="U4" s="81"/>
-      <c r="V4" s="81"/>
-      <c r="W4" s="81"/>
-      <c r="X4" s="81"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
-      <c r="AB4" s="81"/>
-      <c r="AC4" s="81"/>
-      <c r="AD4" s="81"/>
-      <c r="AE4" s="81"/>
-      <c r="AF4" s="81"/>
-      <c r="AG4" s="81"/>
-      <c r="AH4" s="81"/>
-      <c r="AI4" s="81"/>
-      <c r="AJ4" s="81"/>
-      <c r="AK4" s="81"/>
-      <c r="AL4" s="81"/>
-      <c r="AM4" s="81"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="85"/>
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="85"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="85"/>
+      <c r="AE4" s="85"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="85"/>
+      <c r="AH4" s="85"/>
+      <c r="AI4" s="85"/>
+      <c r="AJ4" s="85"/>
+      <c r="AK4" s="85"/>
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
@@ -9711,50 +9709,50 @@
       <c r="A6" s="1"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="85"/>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="85"/>
-      <c r="X6" s="85"/>
-      <c r="Y6" s="85"/>
-      <c r="Z6" s="85"/>
-      <c r="AA6" s="85"/>
-      <c r="AB6" s="85"/>
-      <c r="AC6" s="85"/>
-      <c r="AD6" s="85"/>
-      <c r="AE6" s="85"/>
-      <c r="AF6" s="85"/>
-      <c r="AG6" s="85"/>
-      <c r="AH6" s="85"/>
-      <c r="AI6" s="85"/>
-      <c r="AJ6" s="85"/>
-      <c r="AK6" s="85"/>
-      <c r="AL6" s="86"/>
-      <c r="AM6" s="86"/>
-      <c r="AN6" s="86"/>
-      <c r="AO6" s="86"/>
-      <c r="AP6" s="86"/>
-      <c r="AQ6" s="86"/>
-      <c r="AR6" s="86"/>
-      <c r="AS6" s="86"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="89"/>
+      <c r="N6" s="89"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="89"/>
+      <c r="Q6" s="89"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="89"/>
+      <c r="T6" s="89"/>
+      <c r="U6" s="89"/>
+      <c r="V6" s="89"/>
+      <c r="W6" s="89"/>
+      <c r="X6" s="89"/>
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="89"/>
+      <c r="AB6" s="89"/>
+      <c r="AC6" s="89"/>
+      <c r="AD6" s="89"/>
+      <c r="AE6" s="89"/>
+      <c r="AF6" s="89"/>
+      <c r="AG6" s="89"/>
+      <c r="AH6" s="89"/>
+      <c r="AI6" s="89"/>
+      <c r="AJ6" s="89"/>
+      <c r="AK6" s="89"/>
+      <c r="AL6" s="90"/>
+      <c r="AM6" s="90"/>
+      <c r="AN6" s="90"/>
+      <c r="AO6" s="90"/>
+      <c r="AP6" s="90"/>
+      <c r="AQ6" s="90"/>
+      <c r="AR6" s="90"/>
+      <c r="AS6" s="90"/>
       <c r="AT6" s="4"/>
       <c r="AU6" s="1"/>
     </row>
@@ -9762,51 +9760,51 @@
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="77" t="s">
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="77"/>
-      <c r="Y7" s="77"/>
-      <c r="Z7" s="77"/>
-      <c r="AA7" s="77"/>
-      <c r="AB7" s="77"/>
-      <c r="AC7" s="77"/>
-      <c r="AD7" s="77"/>
-      <c r="AE7" s="77"/>
-      <c r="AF7" s="77"/>
-      <c r="AG7" s="77"/>
-      <c r="AH7" s="77"/>
-      <c r="AI7" s="77"/>
-      <c r="AJ7" s="77"/>
-      <c r="AK7" s="77"/>
-      <c r="AL7" s="77"/>
-      <c r="AM7" s="77"/>
-      <c r="AN7" s="77"/>
-      <c r="AO7" s="77"/>
-      <c r="AP7" s="77"/>
-      <c r="AQ7" s="77"/>
-      <c r="AR7" s="78"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="81"/>
+      <c r="AB7" s="81"/>
+      <c r="AC7" s="81"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="81"/>
+      <c r="AF7" s="81"/>
+      <c r="AG7" s="81"/>
+      <c r="AH7" s="81"/>
+      <c r="AI7" s="81"/>
+      <c r="AJ7" s="81"/>
+      <c r="AK7" s="81"/>
+      <c r="AL7" s="81"/>
+      <c r="AM7" s="81"/>
+      <c r="AN7" s="81"/>
+      <c r="AO7" s="81"/>
+      <c r="AP7" s="81"/>
+      <c r="AQ7" s="81"/>
+      <c r="AR7" s="82"/>
       <c r="AS7" s="6"/>
       <c r="AT7" s="4"/>
       <c r="AU7" s="1"/>
@@ -9815,56 +9813,58 @@
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="98" t="s">
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="100"/>
-      <c r="O8" s="100"/>
-      <c r="P8" s="100"/>
-      <c r="Q8" s="98" t="s">
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
+      <c r="K8" s="103"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="104"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="104"/>
+      <c r="Q8" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="101"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="102"/>
-      <c r="AE8" s="102"/>
-      <c r="AF8" s="102"/>
-      <c r="AG8" s="103"/>
-      <c r="AH8" s="98" t="s">
+      <c r="R8" s="102"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="105"/>
+      <c r="U8" s="106"/>
+      <c r="V8" s="106"/>
+      <c r="W8" s="106"/>
+      <c r="X8" s="106"/>
+      <c r="Y8" s="106"/>
+      <c r="Z8" s="106"/>
+      <c r="AA8" s="106"/>
+      <c r="AB8" s="106"/>
+      <c r="AC8" s="106"/>
+      <c r="AD8" s="106"/>
+      <c r="AE8" s="106"/>
+      <c r="AF8" s="106"/>
+      <c r="AG8" s="107"/>
+      <c r="AH8" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="AI8" s="98"/>
-      <c r="AJ8" s="98"/>
-      <c r="AK8" s="98"/>
-      <c r="AL8" s="87"/>
-      <c r="AM8" s="88"/>
-      <c r="AN8" s="88"/>
-      <c r="AO8" s="88"/>
-      <c r="AP8" s="88"/>
-      <c r="AQ8" s="88"/>
-      <c r="AR8" s="88"/>
-      <c r="AS8" s="88"/>
+      <c r="AI8" s="102"/>
+      <c r="AJ8" s="102"/>
+      <c r="AK8" s="102"/>
+      <c r="AL8" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM8" s="92"/>
+      <c r="AN8" s="92"/>
+      <c r="AO8" s="92"/>
+      <c r="AP8" s="92"/>
+      <c r="AQ8" s="92"/>
+      <c r="AR8" s="92"/>
+      <c r="AS8" s="92"/>
       <c r="AT8" s="4"/>
       <c r="AU8" s="1"/>
     </row>
@@ -9872,54 +9872,54 @@
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="89" t="s">
+      <c r="D9" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="91" t="s">
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="91"/>
-      <c r="J9" s="91"/>
-      <c r="K9" s="92" t="s">
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="91" t="s">
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="91"/>
-      <c r="S9" s="91"/>
-      <c r="T9" s="93" t="s">
+      <c r="R9" s="95"/>
+      <c r="S9" s="95"/>
+      <c r="T9" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="U9" s="94"/>
-      <c r="V9" s="94"/>
-      <c r="W9" s="94"/>
-      <c r="X9" s="94"/>
-      <c r="Y9" s="94"/>
-      <c r="Z9" s="94"/>
-      <c r="AA9" s="94"/>
-      <c r="AB9" s="94"/>
-      <c r="AC9" s="94"/>
-      <c r="AD9" s="94"/>
-      <c r="AE9" s="94"/>
-      <c r="AF9" s="94"/>
-      <c r="AG9" s="95"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
+      <c r="W9" s="98"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="98"/>
+      <c r="AB9" s="98"/>
+      <c r="AC9" s="98"/>
+      <c r="AD9" s="98"/>
+      <c r="AE9" s="98"/>
+      <c r="AF9" s="98"/>
+      <c r="AG9" s="99"/>
       <c r="AH9" s="7"/>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
       <c r="AK9" s="8"/>
       <c r="AL9" s="8"/>
       <c r="AM9" s="8"/>
-      <c r="AN9" s="96"/>
-      <c r="AO9" s="97"/>
+      <c r="AN9" s="100"/>
+      <c r="AO9" s="101"/>
       <c r="AP9" s="8"/>
       <c r="AQ9" s="8"/>
       <c r="AR9" s="8"/>
@@ -9931,10 +9931,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -9980,50 +9980,50 @@
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="131" t="s">
+      <c r="D11" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-      <c r="N11" s="133"/>
-      <c r="O11" s="133"/>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
-      <c r="R11" s="133"/>
-      <c r="S11" s="133"/>
-      <c r="T11" s="133"/>
-      <c r="U11" s="133"/>
-      <c r="V11" s="133"/>
-      <c r="W11" s="133"/>
-      <c r="X11" s="133"/>
-      <c r="Y11" s="133"/>
-      <c r="Z11" s="133"/>
-      <c r="AA11" s="133"/>
-      <c r="AB11" s="133"/>
-      <c r="AC11" s="133"/>
-      <c r="AD11" s="133"/>
-      <c r="AE11" s="133"/>
-      <c r="AF11" s="133"/>
-      <c r="AG11" s="134"/>
-      <c r="AH11" s="135" t="s">
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="137"/>
+      <c r="U11" s="137"/>
+      <c r="V11" s="137"/>
+      <c r="W11" s="137"/>
+      <c r="X11" s="137"/>
+      <c r="Y11" s="137"/>
+      <c r="Z11" s="137"/>
+      <c r="AA11" s="137"/>
+      <c r="AB11" s="137"/>
+      <c r="AC11" s="137"/>
+      <c r="AD11" s="137"/>
+      <c r="AE11" s="137"/>
+      <c r="AF11" s="137"/>
+      <c r="AG11" s="138"/>
+      <c r="AH11" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="AI11" s="136"/>
-      <c r="AJ11" s="136"/>
-      <c r="AK11" s="137"/>
-      <c r="AL11" s="138" t="s">
+      <c r="AI11" s="140"/>
+      <c r="AJ11" s="140"/>
+      <c r="AK11" s="141"/>
+      <c r="AL11" s="142" t="s">
         <v>13</v>
       </c>
-      <c r="AM11" s="139"/>
-      <c r="AN11" s="139"/>
-      <c r="AO11" s="139"/>
+      <c r="AM11" s="143"/>
+      <c r="AN11" s="143"/>
+      <c r="AO11" s="143"/>
       <c r="AP11" s="11"/>
       <c r="AQ11" s="12"/>
       <c r="AR11" s="12"/>
@@ -10035,54 +10035,54 @@
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="110" t="s">
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="111"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="119"/>
-      <c r="L12" s="120"/>
-      <c r="M12" s="120"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="120"/>
-      <c r="P12" s="120"/>
-      <c r="Q12" s="120"/>
-      <c r="R12" s="120"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="120"/>
-      <c r="U12" s="120"/>
-      <c r="V12" s="120"/>
-      <c r="W12" s="121"/>
-      <c r="X12" s="121"/>
-      <c r="Y12" s="121"/>
-      <c r="Z12" s="121"/>
-      <c r="AA12" s="122" t="s">
+      <c r="I12" s="115"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="124"/>
+      <c r="R12" s="124"/>
+      <c r="S12" s="124"/>
+      <c r="T12" s="124"/>
+      <c r="U12" s="124"/>
+      <c r="V12" s="124"/>
+      <c r="W12" s="125"/>
+      <c r="X12" s="125"/>
+      <c r="Y12" s="125"/>
+      <c r="Z12" s="125"/>
+      <c r="AA12" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="AB12" s="123"/>
-      <c r="AC12" s="124"/>
-      <c r="AD12" s="140"/>
-      <c r="AE12" s="140"/>
-      <c r="AF12" s="140"/>
-      <c r="AG12" s="140"/>
-      <c r="AH12" s="140"/>
-      <c r="AI12" s="140"/>
-      <c r="AJ12" s="140"/>
-      <c r="AK12" s="140"/>
-      <c r="AL12" s="140"/>
-      <c r="AM12" s="140"/>
-      <c r="AN12" s="140"/>
-      <c r="AO12" s="140"/>
-      <c r="AP12" s="141"/>
-      <c r="AQ12" s="141"/>
-      <c r="AR12" s="141"/>
-      <c r="AS12" s="141"/>
+      <c r="AB12" s="127"/>
+      <c r="AC12" s="128"/>
+      <c r="AD12" s="144"/>
+      <c r="AE12" s="144"/>
+      <c r="AF12" s="144"/>
+      <c r="AG12" s="144"/>
+      <c r="AH12" s="144"/>
+      <c r="AI12" s="144"/>
+      <c r="AJ12" s="144"/>
+      <c r="AK12" s="144"/>
+      <c r="AL12" s="144"/>
+      <c r="AM12" s="144"/>
+      <c r="AN12" s="144"/>
+      <c r="AO12" s="144"/>
+      <c r="AP12" s="145"/>
+      <c r="AQ12" s="145"/>
+      <c r="AR12" s="145"/>
+      <c r="AS12" s="145"/>
       <c r="AT12" s="4"/>
       <c r="AU12" s="1"/>
     </row>
@@ -10090,52 +10090,52 @@
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="114"/>
-      <c r="J13" s="115"/>
-      <c r="K13" s="142" t="s">
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="143"/>
-      <c r="M13" s="143"/>
-      <c r="N13" s="146"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="147"/>
-      <c r="T13" s="147"/>
-      <c r="U13" s="147"/>
-      <c r="V13" s="147"/>
-      <c r="W13" s="147"/>
-      <c r="X13" s="147"/>
-      <c r="Y13" s="147"/>
-      <c r="Z13" s="148"/>
-      <c r="AA13" s="125"/>
-      <c r="AB13" s="126"/>
-      <c r="AC13" s="127"/>
-      <c r="AD13" s="143" t="s">
+      <c r="L13" s="147"/>
+      <c r="M13" s="147"/>
+      <c r="N13" s="150"/>
+      <c r="O13" s="151"/>
+      <c r="P13" s="151"/>
+      <c r="Q13" s="151"/>
+      <c r="R13" s="151"/>
+      <c r="S13" s="151"/>
+      <c r="T13" s="151"/>
+      <c r="U13" s="151"/>
+      <c r="V13" s="151"/>
+      <c r="W13" s="151"/>
+      <c r="X13" s="151"/>
+      <c r="Y13" s="151"/>
+      <c r="Z13" s="152"/>
+      <c r="AA13" s="129"/>
+      <c r="AB13" s="130"/>
+      <c r="AC13" s="131"/>
+      <c r="AD13" s="147" t="s">
         <v>18</v>
       </c>
-      <c r="AE13" s="143"/>
-      <c r="AF13" s="143"/>
-      <c r="AG13" s="146"/>
-      <c r="AH13" s="147"/>
-      <c r="AI13" s="147"/>
-      <c r="AJ13" s="147"/>
-      <c r="AK13" s="147"/>
-      <c r="AL13" s="147"/>
-      <c r="AM13" s="147"/>
-      <c r="AN13" s="147"/>
-      <c r="AO13" s="147"/>
-      <c r="AP13" s="147"/>
-      <c r="AQ13" s="147"/>
-      <c r="AR13" s="147"/>
-      <c r="AS13" s="147"/>
+      <c r="AE13" s="147"/>
+      <c r="AF13" s="147"/>
+      <c r="AG13" s="150"/>
+      <c r="AH13" s="151"/>
+      <c r="AI13" s="151"/>
+      <c r="AJ13" s="151"/>
+      <c r="AK13" s="151"/>
+      <c r="AL13" s="151"/>
+      <c r="AM13" s="151"/>
+      <c r="AN13" s="151"/>
+      <c r="AO13" s="151"/>
+      <c r="AP13" s="151"/>
+      <c r="AQ13" s="151"/>
+      <c r="AR13" s="151"/>
+      <c r="AS13" s="151"/>
       <c r="AT13" s="4"/>
       <c r="AU13" s="1"/>
     </row>
@@ -10143,48 +10143,48 @@
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="108"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="145"/>
-      <c r="N14" s="149"/>
-      <c r="O14" s="149"/>
-      <c r="P14" s="149"/>
-      <c r="Q14" s="149"/>
-      <c r="R14" s="149"/>
-      <c r="S14" s="149"/>
-      <c r="T14" s="149"/>
-      <c r="U14" s="149"/>
-      <c r="V14" s="149"/>
-      <c r="W14" s="149"/>
-      <c r="X14" s="149"/>
-      <c r="Y14" s="149"/>
-      <c r="Z14" s="150"/>
-      <c r="AA14" s="128"/>
-      <c r="AB14" s="129"/>
-      <c r="AC14" s="130"/>
-      <c r="AD14" s="145"/>
-      <c r="AE14" s="145"/>
-      <c r="AF14" s="145"/>
-      <c r="AG14" s="149"/>
-      <c r="AH14" s="149"/>
-      <c r="AI14" s="149"/>
-      <c r="AJ14" s="149"/>
-      <c r="AK14" s="149"/>
-      <c r="AL14" s="149"/>
-      <c r="AM14" s="149"/>
-      <c r="AN14" s="149"/>
-      <c r="AO14" s="149"/>
-      <c r="AP14" s="149"/>
-      <c r="AQ14" s="149"/>
-      <c r="AR14" s="149"/>
-      <c r="AS14" s="149"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="149"/>
+      <c r="M14" s="149"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="153"/>
+      <c r="P14" s="153"/>
+      <c r="Q14" s="153"/>
+      <c r="R14" s="153"/>
+      <c r="S14" s="153"/>
+      <c r="T14" s="153"/>
+      <c r="U14" s="153"/>
+      <c r="V14" s="153"/>
+      <c r="W14" s="153"/>
+      <c r="X14" s="153"/>
+      <c r="Y14" s="153"/>
+      <c r="Z14" s="154"/>
+      <c r="AA14" s="132"/>
+      <c r="AB14" s="133"/>
+      <c r="AC14" s="134"/>
+      <c r="AD14" s="149"/>
+      <c r="AE14" s="149"/>
+      <c r="AF14" s="149"/>
+      <c r="AG14" s="153"/>
+      <c r="AH14" s="153"/>
+      <c r="AI14" s="153"/>
+      <c r="AJ14" s="153"/>
+      <c r="AK14" s="153"/>
+      <c r="AL14" s="153"/>
+      <c r="AM14" s="153"/>
+      <c r="AN14" s="153"/>
+      <c r="AO14" s="153"/>
+      <c r="AP14" s="153"/>
+      <c r="AQ14" s="153"/>
+      <c r="AR14" s="153"/>
+      <c r="AS14" s="153"/>
       <c r="AT14" s="4"/>
       <c r="AU14" s="1"/>
     </row>
@@ -10243,52 +10243,56 @@
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="163"/>
-      <c r="K16" s="163"/>
-      <c r="L16" s="163"/>
-      <c r="M16" s="163"/>
-      <c r="N16" s="164"/>
-      <c r="O16" s="162"/>
-      <c r="P16" s="163"/>
-      <c r="Q16" s="163"/>
-      <c r="R16" s="163"/>
-      <c r="S16" s="163"/>
-      <c r="T16" s="164"/>
-      <c r="U16" s="162"/>
-      <c r="V16" s="163"/>
-      <c r="W16" s="163"/>
-      <c r="X16" s="163"/>
-      <c r="Y16" s="163"/>
-      <c r="Z16" s="164"/>
-      <c r="AA16" s="230" t="s">
+      <c r="I16" s="166" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="167"/>
+      <c r="K16" s="167"/>
+      <c r="L16" s="167"/>
+      <c r="M16" s="167"/>
+      <c r="N16" s="168"/>
+      <c r="O16" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="P16" s="167"/>
+      <c r="Q16" s="167"/>
+      <c r="R16" s="167"/>
+      <c r="S16" s="167"/>
+      <c r="T16" s="168"/>
+      <c r="U16" s="166"/>
+      <c r="V16" s="167"/>
+      <c r="W16" s="167"/>
+      <c r="X16" s="167"/>
+      <c r="Y16" s="167"/>
+      <c r="Z16" s="168"/>
+      <c r="AA16" s="235" t="s">
         <v>64</v>
       </c>
-      <c r="AB16" s="231"/>
-      <c r="AC16" s="231"/>
-      <c r="AD16" s="231"/>
-      <c r="AE16" s="231"/>
-      <c r="AF16" s="231"/>
-      <c r="AG16" s="231"/>
-      <c r="AH16" s="231"/>
-      <c r="AI16" s="231"/>
-      <c r="AJ16" s="231"/>
-      <c r="AK16" s="231"/>
-      <c r="AL16" s="231"/>
-      <c r="AM16" s="231"/>
-      <c r="AN16" s="231"/>
-      <c r="AO16" s="231"/>
-      <c r="AP16" s="231"/>
-      <c r="AQ16" s="231"/>
-      <c r="AR16" s="231"/>
-      <c r="AS16" s="232"/>
+      <c r="AB16" s="236"/>
+      <c r="AC16" s="236"/>
+      <c r="AD16" s="236"/>
+      <c r="AE16" s="236"/>
+      <c r="AF16" s="236"/>
+      <c r="AG16" s="236"/>
+      <c r="AH16" s="236"/>
+      <c r="AI16" s="236"/>
+      <c r="AJ16" s="236"/>
+      <c r="AK16" s="236"/>
+      <c r="AL16" s="236"/>
+      <c r="AM16" s="236"/>
+      <c r="AN16" s="236"/>
+      <c r="AO16" s="236"/>
+      <c r="AP16" s="236"/>
+      <c r="AQ16" s="236"/>
+      <c r="AR16" s="236"/>
+      <c r="AS16" s="237"/>
       <c r="AT16" s="4"/>
       <c r="AU16" s="1"/>
     </row>
@@ -10296,50 +10300,50 @@
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
       <c r="H17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="165"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
-      <c r="L17" s="166"/>
-      <c r="M17" s="166"/>
-      <c r="N17" s="167"/>
-      <c r="O17" s="165"/>
-      <c r="P17" s="166"/>
-      <c r="Q17" s="166"/>
-      <c r="R17" s="166"/>
-      <c r="S17" s="166"/>
-      <c r="T17" s="167"/>
-      <c r="U17" s="165"/>
-      <c r="V17" s="166"/>
-      <c r="W17" s="166"/>
-      <c r="X17" s="166"/>
-      <c r="Y17" s="166"/>
-      <c r="Z17" s="167"/>
-      <c r="AA17" s="233"/>
-      <c r="AB17" s="234"/>
-      <c r="AC17" s="234"/>
-      <c r="AD17" s="234"/>
-      <c r="AE17" s="234"/>
-      <c r="AF17" s="234"/>
-      <c r="AG17" s="234"/>
-      <c r="AH17" s="234"/>
-      <c r="AI17" s="234"/>
-      <c r="AJ17" s="234"/>
-      <c r="AK17" s="234"/>
-      <c r="AL17" s="234"/>
-      <c r="AM17" s="234"/>
-      <c r="AN17" s="234"/>
-      <c r="AO17" s="234"/>
-      <c r="AP17" s="234"/>
-      <c r="AQ17" s="234"/>
-      <c r="AR17" s="234"/>
-      <c r="AS17" s="235"/>
+      <c r="I17" s="169"/>
+      <c r="J17" s="170"/>
+      <c r="K17" s="170"/>
+      <c r="L17" s="170"/>
+      <c r="M17" s="170"/>
+      <c r="N17" s="171"/>
+      <c r="O17" s="169"/>
+      <c r="P17" s="170"/>
+      <c r="Q17" s="170"/>
+      <c r="R17" s="170"/>
+      <c r="S17" s="170"/>
+      <c r="T17" s="171"/>
+      <c r="U17" s="169"/>
+      <c r="V17" s="170"/>
+      <c r="W17" s="170"/>
+      <c r="X17" s="170"/>
+      <c r="Y17" s="170"/>
+      <c r="Z17" s="171"/>
+      <c r="AA17" s="238"/>
+      <c r="AB17" s="239"/>
+      <c r="AC17" s="239"/>
+      <c r="AD17" s="239"/>
+      <c r="AE17" s="239"/>
+      <c r="AF17" s="239"/>
+      <c r="AG17" s="239"/>
+      <c r="AH17" s="239"/>
+      <c r="AI17" s="239"/>
+      <c r="AJ17" s="239"/>
+      <c r="AK17" s="239"/>
+      <c r="AL17" s="239"/>
+      <c r="AM17" s="239"/>
+      <c r="AN17" s="239"/>
+      <c r="AO17" s="239"/>
+      <c r="AP17" s="239"/>
+      <c r="AQ17" s="239"/>
+      <c r="AR17" s="239"/>
+      <c r="AS17" s="240"/>
       <c r="AT17" s="4"/>
       <c r="AU17" s="1"/>
     </row>
@@ -10347,50 +10351,50 @@
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
       <c r="H18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="165"/>
-      <c r="J18" s="166"/>
-      <c r="K18" s="166"/>
-      <c r="L18" s="166"/>
-      <c r="M18" s="166"/>
-      <c r="N18" s="167"/>
-      <c r="O18" s="165"/>
-      <c r="P18" s="166"/>
-      <c r="Q18" s="166"/>
-      <c r="R18" s="166"/>
-      <c r="S18" s="166"/>
-      <c r="T18" s="167"/>
-      <c r="U18" s="165"/>
-      <c r="V18" s="166"/>
-      <c r="W18" s="166"/>
-      <c r="X18" s="166"/>
-      <c r="Y18" s="166"/>
-      <c r="Z18" s="167"/>
-      <c r="AA18" s="233"/>
-      <c r="AB18" s="234"/>
-      <c r="AC18" s="234"/>
-      <c r="AD18" s="234"/>
-      <c r="AE18" s="234"/>
-      <c r="AF18" s="234"/>
-      <c r="AG18" s="234"/>
-      <c r="AH18" s="234"/>
-      <c r="AI18" s="234"/>
-      <c r="AJ18" s="234"/>
-      <c r="AK18" s="234"/>
-      <c r="AL18" s="234"/>
-      <c r="AM18" s="234"/>
-      <c r="AN18" s="234"/>
-      <c r="AO18" s="234"/>
-      <c r="AP18" s="234"/>
-      <c r="AQ18" s="234"/>
-      <c r="AR18" s="234"/>
-      <c r="AS18" s="235"/>
+      <c r="I18" s="169"/>
+      <c r="J18" s="170"/>
+      <c r="K18" s="170"/>
+      <c r="L18" s="170"/>
+      <c r="M18" s="170"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="169"/>
+      <c r="P18" s="170"/>
+      <c r="Q18" s="170"/>
+      <c r="R18" s="170"/>
+      <c r="S18" s="170"/>
+      <c r="T18" s="171"/>
+      <c r="U18" s="169"/>
+      <c r="V18" s="170"/>
+      <c r="W18" s="170"/>
+      <c r="X18" s="170"/>
+      <c r="Y18" s="170"/>
+      <c r="Z18" s="171"/>
+      <c r="AA18" s="238"/>
+      <c r="AB18" s="239"/>
+      <c r="AC18" s="239"/>
+      <c r="AD18" s="239"/>
+      <c r="AE18" s="239"/>
+      <c r="AF18" s="239"/>
+      <c r="AG18" s="239"/>
+      <c r="AH18" s="239"/>
+      <c r="AI18" s="239"/>
+      <c r="AJ18" s="239"/>
+      <c r="AK18" s="239"/>
+      <c r="AL18" s="239"/>
+      <c r="AM18" s="239"/>
+      <c r="AN18" s="239"/>
+      <c r="AO18" s="239"/>
+      <c r="AP18" s="239"/>
+      <c r="AQ18" s="239"/>
+      <c r="AR18" s="239"/>
+      <c r="AS18" s="240"/>
       <c r="AT18" s="4"/>
       <c r="AU18" s="1"/>
       <c r="AX18" s="3" t="s">
@@ -10401,50 +10405,50 @@
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
       <c r="H19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="165"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="166"/>
-      <c r="L19" s="166"/>
-      <c r="M19" s="166"/>
-      <c r="N19" s="167"/>
-      <c r="O19" s="165"/>
-      <c r="P19" s="166"/>
-      <c r="Q19" s="166"/>
-      <c r="R19" s="166"/>
-      <c r="S19" s="166"/>
-      <c r="T19" s="167"/>
-      <c r="U19" s="165"/>
-      <c r="V19" s="166"/>
-      <c r="W19" s="166"/>
-      <c r="X19" s="166"/>
-      <c r="Y19" s="166"/>
-      <c r="Z19" s="167"/>
-      <c r="AA19" s="236"/>
-      <c r="AB19" s="237"/>
-      <c r="AC19" s="237"/>
-      <c r="AD19" s="237"/>
-      <c r="AE19" s="237"/>
-      <c r="AF19" s="237"/>
-      <c r="AG19" s="237"/>
-      <c r="AH19" s="237"/>
-      <c r="AI19" s="237"/>
-      <c r="AJ19" s="237"/>
-      <c r="AK19" s="237"/>
-      <c r="AL19" s="237"/>
-      <c r="AM19" s="237"/>
-      <c r="AN19" s="237"/>
-      <c r="AO19" s="237"/>
-      <c r="AP19" s="237"/>
-      <c r="AQ19" s="237"/>
-      <c r="AR19" s="237"/>
-      <c r="AS19" s="238"/>
+      <c r="I19" s="169"/>
+      <c r="J19" s="170"/>
+      <c r="K19" s="170"/>
+      <c r="L19" s="170"/>
+      <c r="M19" s="170"/>
+      <c r="N19" s="171"/>
+      <c r="O19" s="169"/>
+      <c r="P19" s="170"/>
+      <c r="Q19" s="170"/>
+      <c r="R19" s="170"/>
+      <c r="S19" s="170"/>
+      <c r="T19" s="171"/>
+      <c r="U19" s="169"/>
+      <c r="V19" s="170"/>
+      <c r="W19" s="170"/>
+      <c r="X19" s="170"/>
+      <c r="Y19" s="170"/>
+      <c r="Z19" s="171"/>
+      <c r="AA19" s="241"/>
+      <c r="AB19" s="242"/>
+      <c r="AC19" s="242"/>
+      <c r="AD19" s="242"/>
+      <c r="AE19" s="242"/>
+      <c r="AF19" s="242"/>
+      <c r="AG19" s="242"/>
+      <c r="AH19" s="242"/>
+      <c r="AI19" s="242"/>
+      <c r="AJ19" s="242"/>
+      <c r="AK19" s="242"/>
+      <c r="AL19" s="242"/>
+      <c r="AM19" s="242"/>
+      <c r="AN19" s="242"/>
+      <c r="AO19" s="242"/>
+      <c r="AP19" s="242"/>
+      <c r="AQ19" s="242"/>
+      <c r="AR19" s="242"/>
+      <c r="AS19" s="243"/>
       <c r="AT19" s="4"/>
       <c r="AU19" s="1"/>
     </row>
@@ -10452,66 +10456,66 @@
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="94"/>
       <c r="H20" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="151">
+      <c r="I20" s="155">
         <f>SUM(I17:Z19)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="152"/>
-      <c r="K20" s="152"/>
-      <c r="L20" s="152"/>
-      <c r="M20" s="152"/>
-      <c r="N20" s="152"/>
-      <c r="O20" s="152"/>
-      <c r="P20" s="152"/>
-      <c r="Q20" s="152"/>
-      <c r="R20" s="152"/>
-      <c r="S20" s="152"/>
-      <c r="T20" s="152"/>
-      <c r="U20" s="152"/>
-      <c r="V20" s="152"/>
-      <c r="W20" s="153"/>
-      <c r="X20" s="153"/>
-      <c r="Y20" s="153"/>
-      <c r="Z20" s="153"/>
-      <c r="AA20" s="153"/>
-      <c r="AB20" s="153"/>
-      <c r="AC20" s="153"/>
-      <c r="AD20" s="153"/>
-      <c r="AE20" s="153"/>
-      <c r="AF20" s="153"/>
-      <c r="AG20" s="153"/>
-      <c r="AH20" s="153"/>
-      <c r="AI20" s="153"/>
-      <c r="AJ20" s="153"/>
-      <c r="AK20" s="153"/>
-      <c r="AL20" s="153"/>
-      <c r="AM20" s="153"/>
-      <c r="AN20" s="153"/>
-      <c r="AO20" s="153"/>
-      <c r="AP20" s="153"/>
-      <c r="AQ20" s="153"/>
-      <c r="AR20" s="153"/>
-      <c r="AS20" s="153"/>
-      <c r="AT20" s="153"/>
+      <c r="J20" s="156"/>
+      <c r="K20" s="156"/>
+      <c r="L20" s="156"/>
+      <c r="M20" s="156"/>
+      <c r="N20" s="156"/>
+      <c r="O20" s="156"/>
+      <c r="P20" s="156"/>
+      <c r="Q20" s="156"/>
+      <c r="R20" s="156"/>
+      <c r="S20" s="156"/>
+      <c r="T20" s="156"/>
+      <c r="U20" s="156"/>
+      <c r="V20" s="156"/>
+      <c r="W20" s="157"/>
+      <c r="X20" s="157"/>
+      <c r="Y20" s="157"/>
+      <c r="Z20" s="157"/>
+      <c r="AA20" s="157"/>
+      <c r="AB20" s="157"/>
+      <c r="AC20" s="157"/>
+      <c r="AD20" s="157"/>
+      <c r="AE20" s="157"/>
+      <c r="AF20" s="157"/>
+      <c r="AG20" s="157"/>
+      <c r="AH20" s="157"/>
+      <c r="AI20" s="157"/>
+      <c r="AJ20" s="157"/>
+      <c r="AK20" s="157"/>
+      <c r="AL20" s="157"/>
+      <c r="AM20" s="157"/>
+      <c r="AN20" s="157"/>
+      <c r="AO20" s="157"/>
+      <c r="AP20" s="157"/>
+      <c r="AQ20" s="157"/>
+      <c r="AR20" s="157"/>
+      <c r="AS20" s="157"/>
+      <c r="AT20" s="157"/>
       <c r="AU20" s="1"/>
     </row>
     <row r="21" spans="1:50" ht="21" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="154" t="s">
+      <c r="D21" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="155"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="159"/>
       <c r="H21" s="17" t="s">
         <v>26</v>
       </c>
@@ -10520,17 +10524,17 @@
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
-      <c r="N21" s="158"/>
-      <c r="O21" s="158"/>
-      <c r="P21" s="158"/>
-      <c r="Q21" s="158"/>
-      <c r="R21" s="158"/>
-      <c r="S21" s="158"/>
-      <c r="T21" s="158"/>
-      <c r="U21" s="158"/>
-      <c r="V21" s="158"/>
-      <c r="W21" s="158"/>
-      <c r="X21" s="158"/>
+      <c r="N21" s="162"/>
+      <c r="O21" s="162"/>
+      <c r="P21" s="162"/>
+      <c r="Q21" s="162"/>
+      <c r="R21" s="162"/>
+      <c r="S21" s="162"/>
+      <c r="T21" s="162"/>
+      <c r="U21" s="162"/>
+      <c r="V21" s="162"/>
+      <c r="W21" s="162"/>
+      <c r="X21" s="162"/>
       <c r="Y21" s="17" t="s">
         <v>27</v>
       </c>
@@ -10561,49 +10565,49 @@
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="156"/>
-      <c r="G22" s="157"/>
-      <c r="H22" s="159" t="s">
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="161"/>
+      <c r="H22" s="163" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="160"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="160"/>
-      <c r="N22" s="160"/>
-      <c r="O22" s="160"/>
-      <c r="P22" s="160"/>
-      <c r="Q22" s="160"/>
-      <c r="R22" s="160"/>
-      <c r="S22" s="160"/>
-      <c r="T22" s="160"/>
-      <c r="U22" s="160"/>
-      <c r="V22" s="160"/>
-      <c r="W22" s="160"/>
-      <c r="X22" s="160"/>
-      <c r="Y22" s="160"/>
-      <c r="Z22" s="160"/>
-      <c r="AA22" s="161" t="s">
+      <c r="I22" s="164"/>
+      <c r="J22" s="164"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="164"/>
+      <c r="M22" s="164"/>
+      <c r="N22" s="164"/>
+      <c r="O22" s="164"/>
+      <c r="P22" s="164"/>
+      <c r="Q22" s="164"/>
+      <c r="R22" s="164"/>
+      <c r="S22" s="164"/>
+      <c r="T22" s="164"/>
+      <c r="U22" s="164"/>
+      <c r="V22" s="164"/>
+      <c r="W22" s="164"/>
+      <c r="X22" s="164"/>
+      <c r="Y22" s="164"/>
+      <c r="Z22" s="164"/>
+      <c r="AA22" s="165" t="s">
         <v>29</v>
       </c>
-      <c r="AB22" s="161"/>
-      <c r="AC22" s="161"/>
-      <c r="AD22" s="161"/>
-      <c r="AE22" s="161"/>
-      <c r="AF22" s="161"/>
-      <c r="AG22" s="161"/>
-      <c r="AH22" s="161"/>
-      <c r="AI22" s="161"/>
-      <c r="AJ22" s="161"/>
-      <c r="AK22" s="161"/>
-      <c r="AL22" s="161"/>
-      <c r="AM22" s="161"/>
-      <c r="AN22" s="161"/>
-      <c r="AO22" s="161"/>
-      <c r="AP22" s="161"/>
+      <c r="AB22" s="165"/>
+      <c r="AC22" s="165"/>
+      <c r="AD22" s="165"/>
+      <c r="AE22" s="165"/>
+      <c r="AF22" s="165"/>
+      <c r="AG22" s="165"/>
+      <c r="AH22" s="165"/>
+      <c r="AI22" s="165"/>
+      <c r="AJ22" s="165"/>
+      <c r="AK22" s="165"/>
+      <c r="AL22" s="165"/>
+      <c r="AM22" s="165"/>
+      <c r="AN22" s="165"/>
+      <c r="AO22" s="165"/>
+      <c r="AP22" s="165"/>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="19"/>
       <c r="AS22" s="19"/>
@@ -10614,20 +10618,20 @@
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="178" t="s">
+      <c r="D23" s="182" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="178"/>
-      <c r="F23" s="178"/>
-      <c r="G23" s="179"/>
-      <c r="H23" s="180" t="s">
+      <c r="E23" s="182"/>
+      <c r="F23" s="182"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="184" t="s">
         <v>31</v>
       </c>
-      <c r="I23" s="181"/>
-      <c r="J23" s="182"/>
-      <c r="K23" s="183"/>
-      <c r="L23" s="168"/>
-      <c r="M23" s="184"/>
+      <c r="I23" s="185"/>
+      <c r="J23" s="186"/>
+      <c r="K23" s="187"/>
+      <c r="L23" s="172"/>
+      <c r="M23" s="188"/>
       <c r="N23" s="36"/>
       <c r="O23" s="37" t="s">
         <v>58</v>
@@ -10635,9 +10639,9 @@
       <c r="P23" s="37"/>
       <c r="Q23" s="37"/>
       <c r="R23" s="37"/>
-      <c r="S23" s="168"/>
-      <c r="T23" s="168"/>
-      <c r="U23" s="168"/>
+      <c r="S23" s="172"/>
+      <c r="T23" s="172"/>
+      <c r="U23" s="172"/>
       <c r="V23" s="37" t="s">
         <v>59</v>
       </c>
@@ -10649,8 +10653,8 @@
       <c r="Z23" s="37"/>
       <c r="AA23" s="37"/>
       <c r="AB23" s="37"/>
-      <c r="AC23" s="168"/>
-      <c r="AD23" s="168"/>
+      <c r="AC23" s="172"/>
+      <c r="AD23" s="172"/>
       <c r="AE23" s="37" t="s">
         <v>61</v>
       </c>
@@ -10665,8 +10669,8 @@
       <c r="AL23" s="37"/>
       <c r="AM23" s="37"/>
       <c r="AN23" s="37"/>
-      <c r="AO23" s="168"/>
-      <c r="AP23" s="168"/>
+      <c r="AO23" s="172"/>
+      <c r="AP23" s="172"/>
       <c r="AQ23" s="37" t="s">
         <v>63</v>
       </c>
@@ -10679,50 +10683,50 @@
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="107"/>
-      <c r="H24" s="169" t="s">
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="173" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="170"/>
-      <c r="J24" s="171"/>
-      <c r="K24" s="165"/>
-      <c r="L24" s="166"/>
-      <c r="M24" s="167"/>
-      <c r="N24" s="172"/>
-      <c r="O24" s="173"/>
-      <c r="P24" s="173"/>
-      <c r="Q24" s="173"/>
-      <c r="R24" s="173"/>
-      <c r="S24" s="173"/>
-      <c r="T24" s="173"/>
-      <c r="U24" s="173"/>
-      <c r="V24" s="173"/>
-      <c r="W24" s="173"/>
-      <c r="X24" s="173"/>
-      <c r="Y24" s="173"/>
-      <c r="Z24" s="173"/>
-      <c r="AA24" s="173"/>
-      <c r="AB24" s="173"/>
-      <c r="AC24" s="173"/>
-      <c r="AD24" s="173"/>
-      <c r="AE24" s="173"/>
-      <c r="AF24" s="173"/>
-      <c r="AG24" s="173"/>
-      <c r="AH24" s="173"/>
-      <c r="AI24" s="173"/>
-      <c r="AJ24" s="173"/>
-      <c r="AK24" s="173"/>
-      <c r="AL24" s="173"/>
-      <c r="AM24" s="173"/>
-      <c r="AN24" s="173"/>
-      <c r="AO24" s="173"/>
-      <c r="AP24" s="173"/>
-      <c r="AQ24" s="173"/>
-      <c r="AR24" s="173"/>
-      <c r="AS24" s="173"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="175"/>
+      <c r="K24" s="169"/>
+      <c r="L24" s="170"/>
+      <c r="M24" s="171"/>
+      <c r="N24" s="176"/>
+      <c r="O24" s="177"/>
+      <c r="P24" s="177"/>
+      <c r="Q24" s="177"/>
+      <c r="R24" s="177"/>
+      <c r="S24" s="177"/>
+      <c r="T24" s="177"/>
+      <c r="U24" s="177"/>
+      <c r="V24" s="177"/>
+      <c r="W24" s="177"/>
+      <c r="X24" s="177"/>
+      <c r="Y24" s="177"/>
+      <c r="Z24" s="177"/>
+      <c r="AA24" s="177"/>
+      <c r="AB24" s="177"/>
+      <c r="AC24" s="177"/>
+      <c r="AD24" s="177"/>
+      <c r="AE24" s="177"/>
+      <c r="AF24" s="177"/>
+      <c r="AG24" s="177"/>
+      <c r="AH24" s="177"/>
+      <c r="AI24" s="177"/>
+      <c r="AJ24" s="177"/>
+      <c r="AK24" s="177"/>
+      <c r="AL24" s="177"/>
+      <c r="AM24" s="177"/>
+      <c r="AN24" s="177"/>
+      <c r="AO24" s="177"/>
+      <c r="AP24" s="177"/>
+      <c r="AQ24" s="177"/>
+      <c r="AR24" s="177"/>
+      <c r="AS24" s="177"/>
       <c r="AT24" s="4"/>
       <c r="AU24" s="1"/>
     </row>
@@ -10730,50 +10734,50 @@
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="174" t="s">
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="178" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="175"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="175"/>
-      <c r="L25" s="175"/>
-      <c r="M25" s="175"/>
-      <c r="N25" s="175"/>
-      <c r="O25" s="175"/>
-      <c r="P25" s="175"/>
-      <c r="Q25" s="175"/>
-      <c r="R25" s="175"/>
-      <c r="S25" s="175"/>
-      <c r="T25" s="175"/>
-      <c r="U25" s="175"/>
-      <c r="V25" s="175"/>
-      <c r="W25" s="175"/>
-      <c r="X25" s="175"/>
-      <c r="Y25" s="175"/>
-      <c r="Z25" s="175"/>
-      <c r="AA25" s="175"/>
-      <c r="AB25" s="175"/>
-      <c r="AC25" s="175"/>
-      <c r="AD25" s="175"/>
-      <c r="AE25" s="175"/>
-      <c r="AF25" s="175"/>
-      <c r="AG25" s="175"/>
-      <c r="AH25" s="175"/>
-      <c r="AI25" s="175"/>
-      <c r="AJ25" s="175"/>
-      <c r="AK25" s="175"/>
-      <c r="AL25" s="175"/>
-      <c r="AM25" s="175"/>
-      <c r="AN25" s="175"/>
-      <c r="AO25" s="175"/>
-      <c r="AP25" s="175"/>
-      <c r="AQ25" s="175"/>
-      <c r="AR25" s="175"/>
-      <c r="AS25" s="175"/>
+      <c r="I25" s="179"/>
+      <c r="J25" s="179"/>
+      <c r="K25" s="179"/>
+      <c r="L25" s="179"/>
+      <c r="M25" s="179"/>
+      <c r="N25" s="179"/>
+      <c r="O25" s="179"/>
+      <c r="P25" s="179"/>
+      <c r="Q25" s="179"/>
+      <c r="R25" s="179"/>
+      <c r="S25" s="179"/>
+      <c r="T25" s="179"/>
+      <c r="U25" s="179"/>
+      <c r="V25" s="179"/>
+      <c r="W25" s="179"/>
+      <c r="X25" s="179"/>
+      <c r="Y25" s="179"/>
+      <c r="Z25" s="179"/>
+      <c r="AA25" s="179"/>
+      <c r="AB25" s="179"/>
+      <c r="AC25" s="179"/>
+      <c r="AD25" s="179"/>
+      <c r="AE25" s="179"/>
+      <c r="AF25" s="179"/>
+      <c r="AG25" s="179"/>
+      <c r="AH25" s="179"/>
+      <c r="AI25" s="179"/>
+      <c r="AJ25" s="179"/>
+      <c r="AK25" s="179"/>
+      <c r="AL25" s="179"/>
+      <c r="AM25" s="179"/>
+      <c r="AN25" s="179"/>
+      <c r="AO25" s="179"/>
+      <c r="AP25" s="179"/>
+      <c r="AQ25" s="179"/>
+      <c r="AR25" s="179"/>
+      <c r="AS25" s="179"/>
       <c r="AT25" s="4"/>
       <c r="AU25" s="1"/>
     </row>
@@ -10781,48 +10785,48 @@
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="107"/>
-      <c r="H26" s="176"/>
-      <c r="I26" s="177"/>
-      <c r="J26" s="177"/>
-      <c r="K26" s="177"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="177"/>
-      <c r="N26" s="177"/>
-      <c r="O26" s="177"/>
-      <c r="P26" s="177"/>
-      <c r="Q26" s="177"/>
-      <c r="R26" s="177"/>
-      <c r="S26" s="177"/>
-      <c r="T26" s="177"/>
-      <c r="U26" s="177"/>
-      <c r="V26" s="177"/>
-      <c r="W26" s="177"/>
-      <c r="X26" s="177"/>
-      <c r="Y26" s="177"/>
-      <c r="Z26" s="177"/>
-      <c r="AA26" s="177"/>
-      <c r="AB26" s="177"/>
-      <c r="AC26" s="177"/>
-      <c r="AD26" s="177"/>
-      <c r="AE26" s="177"/>
-      <c r="AF26" s="177"/>
-      <c r="AG26" s="177"/>
-      <c r="AH26" s="177"/>
-      <c r="AI26" s="177"/>
-      <c r="AJ26" s="177"/>
-      <c r="AK26" s="177"/>
-      <c r="AL26" s="177"/>
-      <c r="AM26" s="177"/>
-      <c r="AN26" s="177"/>
-      <c r="AO26" s="177"/>
-      <c r="AP26" s="177"/>
-      <c r="AQ26" s="177"/>
-      <c r="AR26" s="177"/>
-      <c r="AS26" s="177"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="180"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="181"/>
+      <c r="L26" s="181"/>
+      <c r="M26" s="181"/>
+      <c r="N26" s="181"/>
+      <c r="O26" s="181"/>
+      <c r="P26" s="181"/>
+      <c r="Q26" s="181"/>
+      <c r="R26" s="181"/>
+      <c r="S26" s="181"/>
+      <c r="T26" s="181"/>
+      <c r="U26" s="181"/>
+      <c r="V26" s="181"/>
+      <c r="W26" s="181"/>
+      <c r="X26" s="181"/>
+      <c r="Y26" s="181"/>
+      <c r="Z26" s="181"/>
+      <c r="AA26" s="181"/>
+      <c r="AB26" s="181"/>
+      <c r="AC26" s="181"/>
+      <c r="AD26" s="181"/>
+      <c r="AE26" s="181"/>
+      <c r="AF26" s="181"/>
+      <c r="AG26" s="181"/>
+      <c r="AH26" s="181"/>
+      <c r="AI26" s="181"/>
+      <c r="AJ26" s="181"/>
+      <c r="AK26" s="181"/>
+      <c r="AL26" s="181"/>
+      <c r="AM26" s="181"/>
+      <c r="AN26" s="181"/>
+      <c r="AO26" s="181"/>
+      <c r="AP26" s="181"/>
+      <c r="AQ26" s="181"/>
+      <c r="AR26" s="181"/>
+      <c r="AS26" s="181"/>
       <c r="AT26" s="4"/>
       <c r="AU26" s="1"/>
     </row>
@@ -10830,56 +10834,56 @@
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="185" t="s">
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="186"/>
-      <c r="J27" s="187"/>
-      <c r="K27" s="191" t="s">
+      <c r="I27" s="190"/>
+      <c r="J27" s="191"/>
+      <c r="K27" s="195" t="s">
         <v>35</v>
       </c>
-      <c r="L27" s="192"/>
-      <c r="M27" s="192"/>
-      <c r="N27" s="192"/>
-      <c r="O27" s="192"/>
-      <c r="P27" s="192"/>
-      <c r="Q27" s="192"/>
-      <c r="R27" s="192"/>
-      <c r="S27" s="193"/>
-      <c r="T27" s="165" t="s">
+      <c r="L27" s="196"/>
+      <c r="M27" s="196"/>
+      <c r="N27" s="196"/>
+      <c r="O27" s="196"/>
+      <c r="P27" s="196"/>
+      <c r="Q27" s="196"/>
+      <c r="R27" s="196"/>
+      <c r="S27" s="197"/>
+      <c r="T27" s="169" t="s">
         <v>65</v>
       </c>
-      <c r="U27" s="166"/>
-      <c r="V27" s="166"/>
-      <c r="W27" s="166"/>
-      <c r="X27" s="166"/>
-      <c r="Y27" s="166"/>
-      <c r="Z27" s="166"/>
-      <c r="AA27" s="166"/>
-      <c r="AB27" s="166"/>
-      <c r="AC27" s="166"/>
-      <c r="AD27" s="167"/>
-      <c r="AE27" s="205" t="s">
+      <c r="U27" s="170"/>
+      <c r="V27" s="170"/>
+      <c r="W27" s="170"/>
+      <c r="X27" s="170"/>
+      <c r="Y27" s="170"/>
+      <c r="Z27" s="170"/>
+      <c r="AA27" s="170"/>
+      <c r="AB27" s="170"/>
+      <c r="AC27" s="170"/>
+      <c r="AD27" s="171"/>
+      <c r="AE27" s="209" t="s">
         <v>36</v>
       </c>
-      <c r="AF27" s="206"/>
-      <c r="AG27" s="206"/>
-      <c r="AH27" s="207"/>
-      <c r="AI27" s="211"/>
-      <c r="AJ27" s="212"/>
-      <c r="AK27" s="212"/>
-      <c r="AL27" s="212"/>
-      <c r="AM27" s="212"/>
-      <c r="AN27" s="212"/>
-      <c r="AO27" s="212"/>
-      <c r="AP27" s="212"/>
-      <c r="AQ27" s="212"/>
-      <c r="AR27" s="212"/>
-      <c r="AS27" s="212"/>
+      <c r="AF27" s="210"/>
+      <c r="AG27" s="210"/>
+      <c r="AH27" s="211"/>
+      <c r="AI27" s="215"/>
+      <c r="AJ27" s="216"/>
+      <c r="AK27" s="216"/>
+      <c r="AL27" s="216"/>
+      <c r="AM27" s="216"/>
+      <c r="AN27" s="216"/>
+      <c r="AO27" s="216"/>
+      <c r="AP27" s="216"/>
+      <c r="AQ27" s="216"/>
+      <c r="AR27" s="216"/>
+      <c r="AS27" s="216"/>
       <c r="AT27" s="4"/>
       <c r="AU27" s="1"/>
     </row>
@@ -10887,49 +10891,49 @@
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="188"/>
-      <c r="I28" s="189"/>
-      <c r="J28" s="190"/>
-      <c r="K28" s="213" t="s">
+      <c r="D28" s="112"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="192"/>
+      <c r="I28" s="193"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="217" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="214"/>
-      <c r="M28" s="214"/>
-      <c r="N28" s="214"/>
-      <c r="O28" s="214"/>
-      <c r="P28" s="214"/>
-      <c r="Q28" s="214"/>
-      <c r="R28" s="214"/>
-      <c r="S28" s="215"/>
-      <c r="T28" s="216"/>
-      <c r="U28" s="217"/>
-      <c r="V28" s="217"/>
-      <c r="W28" s="217"/>
-      <c r="X28" s="217"/>
-      <c r="Y28" s="217"/>
-      <c r="Z28" s="217"/>
-      <c r="AA28" s="217"/>
-      <c r="AB28" s="217"/>
-      <c r="AC28" s="217"/>
-      <c r="AD28" s="218"/>
-      <c r="AE28" s="208"/>
-      <c r="AF28" s="209"/>
-      <c r="AG28" s="209"/>
-      <c r="AH28" s="210"/>
-      <c r="AI28" s="216"/>
-      <c r="AJ28" s="217"/>
-      <c r="AK28" s="217"/>
-      <c r="AL28" s="217"/>
-      <c r="AM28" s="217"/>
-      <c r="AN28" s="217"/>
-      <c r="AO28" s="217"/>
-      <c r="AP28" s="217"/>
-      <c r="AQ28" s="217"/>
-      <c r="AR28" s="217"/>
+      <c r="L28" s="218"/>
+      <c r="M28" s="218"/>
+      <c r="N28" s="218"/>
+      <c r="O28" s="218"/>
+      <c r="P28" s="218"/>
+      <c r="Q28" s="218"/>
+      <c r="R28" s="218"/>
+      <c r="S28" s="219"/>
+      <c r="T28" s="220"/>
+      <c r="U28" s="221"/>
+      <c r="V28" s="221"/>
+      <c r="W28" s="221"/>
+      <c r="X28" s="221"/>
+      <c r="Y28" s="221"/>
+      <c r="Z28" s="221"/>
+      <c r="AA28" s="221"/>
+      <c r="AB28" s="221"/>
+      <c r="AC28" s="221"/>
+      <c r="AD28" s="222"/>
+      <c r="AE28" s="212"/>
+      <c r="AF28" s="213"/>
+      <c r="AG28" s="213"/>
+      <c r="AH28" s="214"/>
+      <c r="AI28" s="220"/>
+      <c r="AJ28" s="221"/>
+      <c r="AK28" s="221"/>
+      <c r="AL28" s="221"/>
+      <c r="AM28" s="221"/>
+      <c r="AN28" s="221"/>
+      <c r="AO28" s="221"/>
+      <c r="AP28" s="221"/>
+      <c r="AQ28" s="221"/>
+      <c r="AR28" s="221"/>
       <c r="AS28" s="20"/>
       <c r="AT28" s="4"/>
       <c r="AU28" s="1"/>
@@ -10987,52 +10991,52 @@
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="240" t="s">
+      <c r="D30" s="245" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="240"/>
-      <c r="F30" s="240"/>
-      <c r="G30" s="241"/>
-      <c r="H30" s="245" t="s">
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="246"/>
+      <c r="H30" s="250" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="246"/>
-      <c r="J30" s="246"/>
-      <c r="K30" s="246"/>
-      <c r="L30" s="246"/>
-      <c r="M30" s="246"/>
-      <c r="N30" s="246"/>
-      <c r="O30" s="246"/>
-      <c r="P30" s="246"/>
-      <c r="Q30" s="246"/>
-      <c r="R30" s="246"/>
-      <c r="S30" s="246"/>
-      <c r="T30" s="246"/>
-      <c r="U30" s="246"/>
-      <c r="V30" s="246"/>
-      <c r="W30" s="246"/>
-      <c r="X30" s="246"/>
-      <c r="Y30" s="246"/>
-      <c r="Z30" s="246"/>
-      <c r="AA30" s="246"/>
-      <c r="AB30" s="246"/>
-      <c r="AC30" s="246"/>
-      <c r="AD30" s="246"/>
-      <c r="AE30" s="246"/>
-      <c r="AF30" s="246"/>
-      <c r="AG30" s="246"/>
-      <c r="AH30" s="246"/>
-      <c r="AI30" s="246"/>
-      <c r="AJ30" s="246"/>
-      <c r="AK30" s="246"/>
-      <c r="AL30" s="246"/>
-      <c r="AM30" s="246"/>
-      <c r="AN30" s="246"/>
-      <c r="AO30" s="246"/>
-      <c r="AP30" s="246"/>
-      <c r="AQ30" s="246"/>
-      <c r="AR30" s="246"/>
-      <c r="AS30" s="246"/>
+      <c r="I30" s="251"/>
+      <c r="J30" s="251"/>
+      <c r="K30" s="251"/>
+      <c r="L30" s="251"/>
+      <c r="M30" s="251"/>
+      <c r="N30" s="251"/>
+      <c r="O30" s="251"/>
+      <c r="P30" s="251"/>
+      <c r="Q30" s="251"/>
+      <c r="R30" s="251"/>
+      <c r="S30" s="251"/>
+      <c r="T30" s="251"/>
+      <c r="U30" s="251"/>
+      <c r="V30" s="251"/>
+      <c r="W30" s="251"/>
+      <c r="X30" s="251"/>
+      <c r="Y30" s="251"/>
+      <c r="Z30" s="251"/>
+      <c r="AA30" s="251"/>
+      <c r="AB30" s="251"/>
+      <c r="AC30" s="251"/>
+      <c r="AD30" s="251"/>
+      <c r="AE30" s="251"/>
+      <c r="AF30" s="251"/>
+      <c r="AG30" s="251"/>
+      <c r="AH30" s="251"/>
+      <c r="AI30" s="251"/>
+      <c r="AJ30" s="251"/>
+      <c r="AK30" s="251"/>
+      <c r="AL30" s="251"/>
+      <c r="AM30" s="251"/>
+      <c r="AN30" s="251"/>
+      <c r="AO30" s="251"/>
+      <c r="AP30" s="251"/>
+      <c r="AQ30" s="251"/>
+      <c r="AR30" s="251"/>
+      <c r="AS30" s="251"/>
       <c r="AT30" s="4"/>
       <c r="AU30" s="1"/>
     </row>
@@ -11040,58 +11044,58 @@
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="242"/>
-      <c r="H31" s="247" t="s">
+      <c r="D31" s="247"/>
+      <c r="E31" s="247"/>
+      <c r="F31" s="247"/>
+      <c r="G31" s="247"/>
+      <c r="H31" s="252" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="248"/>
+      <c r="I31" s="253"/>
       <c r="J31" s="21"/>
-      <c r="K31" s="251" t="s">
+      <c r="K31" s="256" t="s">
         <v>41</v>
       </c>
-      <c r="L31" s="252"/>
-      <c r="M31" s="252"/>
-      <c r="N31" s="252"/>
-      <c r="O31" s="252"/>
-      <c r="P31" s="253"/>
-      <c r="Q31" s="254" t="s">
+      <c r="L31" s="257"/>
+      <c r="M31" s="257"/>
+      <c r="N31" s="257"/>
+      <c r="O31" s="257"/>
+      <c r="P31" s="258"/>
+      <c r="Q31" s="259" t="s">
         <v>42</v>
       </c>
-      <c r="R31" s="255"/>
-      <c r="S31" s="255"/>
-      <c r="T31" s="255"/>
-      <c r="U31" s="255"/>
-      <c r="V31" s="255"/>
-      <c r="W31" s="258" t="s">
+      <c r="R31" s="260"/>
+      <c r="S31" s="260"/>
+      <c r="T31" s="260"/>
+      <c r="U31" s="260"/>
+      <c r="V31" s="260"/>
+      <c r="W31" s="263" t="s">
         <v>43</v>
       </c>
-      <c r="X31" s="259"/>
-      <c r="Y31" s="260"/>
-      <c r="Z31" s="261"/>
-      <c r="AA31" s="262"/>
-      <c r="AB31" s="262"/>
-      <c r="AC31" s="262"/>
-      <c r="AD31" s="262"/>
-      <c r="AE31" s="262"/>
-      <c r="AF31" s="263"/>
-      <c r="AG31" s="264" t="s">
+      <c r="X31" s="264"/>
+      <c r="Y31" s="265"/>
+      <c r="Z31" s="266"/>
+      <c r="AA31" s="267"/>
+      <c r="AB31" s="267"/>
+      <c r="AC31" s="267"/>
+      <c r="AD31" s="267"/>
+      <c r="AE31" s="267"/>
+      <c r="AF31" s="268"/>
+      <c r="AG31" s="269" t="s">
         <v>44</v>
       </c>
-      <c r="AH31" s="264"/>
-      <c r="AI31" s="264"/>
-      <c r="AJ31" s="265"/>
-      <c r="AK31" s="266"/>
-      <c r="AL31" s="266"/>
-      <c r="AM31" s="266"/>
-      <c r="AN31" s="266"/>
-      <c r="AO31" s="266"/>
-      <c r="AP31" s="266"/>
-      <c r="AQ31" s="266"/>
-      <c r="AR31" s="266"/>
-      <c r="AS31" s="267"/>
+      <c r="AH31" s="269"/>
+      <c r="AI31" s="269"/>
+      <c r="AJ31" s="270"/>
+      <c r="AK31" s="271"/>
+      <c r="AL31" s="271"/>
+      <c r="AM31" s="271"/>
+      <c r="AN31" s="271"/>
+      <c r="AO31" s="271"/>
+      <c r="AP31" s="271"/>
+      <c r="AQ31" s="271"/>
+      <c r="AR31" s="271"/>
+      <c r="AS31" s="272"/>
       <c r="AT31" s="4"/>
       <c r="AU31" s="1"/>
     </row>
@@ -11099,54 +11103,54 @@
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="242"/>
-      <c r="E32" s="242"/>
-      <c r="F32" s="242"/>
-      <c r="G32" s="242"/>
-      <c r="H32" s="249"/>
-      <c r="I32" s="250"/>
+      <c r="D32" s="247"/>
+      <c r="E32" s="247"/>
+      <c r="F32" s="247"/>
+      <c r="G32" s="247"/>
+      <c r="H32" s="254"/>
+      <c r="I32" s="255"/>
       <c r="J32" s="22"/>
-      <c r="K32" s="268" t="s">
+      <c r="K32" s="273" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="268"/>
-      <c r="M32" s="268"/>
-      <c r="N32" s="268"/>
-      <c r="O32" s="268"/>
-      <c r="P32" s="269"/>
-      <c r="Q32" s="256"/>
-      <c r="R32" s="257"/>
-      <c r="S32" s="257"/>
-      <c r="T32" s="257"/>
-      <c r="U32" s="257"/>
-      <c r="V32" s="257"/>
-      <c r="W32" s="194" t="s">
+      <c r="L32" s="273"/>
+      <c r="M32" s="273"/>
+      <c r="N32" s="273"/>
+      <c r="O32" s="273"/>
+      <c r="P32" s="274"/>
+      <c r="Q32" s="261"/>
+      <c r="R32" s="262"/>
+      <c r="S32" s="262"/>
+      <c r="T32" s="262"/>
+      <c r="U32" s="262"/>
+      <c r="V32" s="262"/>
+      <c r="W32" s="198" t="s">
         <v>46</v>
       </c>
-      <c r="X32" s="195"/>
-      <c r="Y32" s="196"/>
-      <c r="Z32" s="194"/>
-      <c r="AA32" s="195"/>
-      <c r="AB32" s="195"/>
-      <c r="AC32" s="195"/>
-      <c r="AD32" s="195"/>
-      <c r="AE32" s="195"/>
-      <c r="AF32" s="196"/>
-      <c r="AG32" s="197" t="s">
+      <c r="X32" s="199"/>
+      <c r="Y32" s="200"/>
+      <c r="Z32" s="198"/>
+      <c r="AA32" s="199"/>
+      <c r="AB32" s="199"/>
+      <c r="AC32" s="199"/>
+      <c r="AD32" s="199"/>
+      <c r="AE32" s="199"/>
+      <c r="AF32" s="200"/>
+      <c r="AG32" s="201" t="s">
         <v>47</v>
       </c>
-      <c r="AH32" s="198"/>
-      <c r="AI32" s="199"/>
-      <c r="AJ32" s="200"/>
-      <c r="AK32" s="201"/>
-      <c r="AL32" s="201"/>
-      <c r="AM32" s="201"/>
-      <c r="AN32" s="201"/>
-      <c r="AO32" s="201"/>
-      <c r="AP32" s="201"/>
-      <c r="AQ32" s="201"/>
-      <c r="AR32" s="201"/>
-      <c r="AS32" s="202"/>
+      <c r="AH32" s="202"/>
+      <c r="AI32" s="203"/>
+      <c r="AJ32" s="204"/>
+      <c r="AK32" s="205"/>
+      <c r="AL32" s="205"/>
+      <c r="AM32" s="205"/>
+      <c r="AN32" s="205"/>
+      <c r="AO32" s="205"/>
+      <c r="AP32" s="205"/>
+      <c r="AQ32" s="205"/>
+      <c r="AR32" s="205"/>
+      <c r="AS32" s="206"/>
       <c r="AT32" s="4"/>
       <c r="AU32" s="1"/>
     </row>
@@ -11154,50 +11158,50 @@
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="203" t="s">
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="207" t="s">
         <v>48</v>
       </c>
-      <c r="I33" s="204"/>
-      <c r="J33" s="204"/>
-      <c r="K33" s="204"/>
-      <c r="L33" s="204"/>
-      <c r="M33" s="204"/>
-      <c r="N33" s="204"/>
-      <c r="O33" s="204"/>
-      <c r="P33" s="204"/>
-      <c r="Q33" s="204"/>
-      <c r="R33" s="204"/>
-      <c r="S33" s="204"/>
-      <c r="T33" s="204"/>
-      <c r="U33" s="204"/>
-      <c r="V33" s="204"/>
-      <c r="W33" s="204"/>
-      <c r="X33" s="204"/>
-      <c r="Y33" s="204"/>
-      <c r="Z33" s="204"/>
-      <c r="AA33" s="204"/>
-      <c r="AB33" s="204"/>
-      <c r="AC33" s="204"/>
-      <c r="AD33" s="204"/>
-      <c r="AE33" s="204"/>
-      <c r="AF33" s="204"/>
-      <c r="AG33" s="204"/>
-      <c r="AH33" s="204"/>
-      <c r="AI33" s="204"/>
-      <c r="AJ33" s="204"/>
-      <c r="AK33" s="204"/>
-      <c r="AL33" s="204"/>
-      <c r="AM33" s="204"/>
-      <c r="AN33" s="204"/>
-      <c r="AO33" s="204"/>
-      <c r="AP33" s="204"/>
-      <c r="AQ33" s="204"/>
-      <c r="AR33" s="204"/>
-      <c r="AS33" s="204"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="208"/>
+      <c r="N33" s="208"/>
+      <c r="O33" s="208"/>
+      <c r="P33" s="208"/>
+      <c r="Q33" s="208"/>
+      <c r="R33" s="208"/>
+      <c r="S33" s="208"/>
+      <c r="T33" s="208"/>
+      <c r="U33" s="208"/>
+      <c r="V33" s="208"/>
+      <c r="W33" s="208"/>
+      <c r="X33" s="208"/>
+      <c r="Y33" s="208"/>
+      <c r="Z33" s="208"/>
+      <c r="AA33" s="208"/>
+      <c r="AB33" s="208"/>
+      <c r="AC33" s="208"/>
+      <c r="AD33" s="208"/>
+      <c r="AE33" s="208"/>
+      <c r="AF33" s="208"/>
+      <c r="AG33" s="208"/>
+      <c r="AH33" s="208"/>
+      <c r="AI33" s="208"/>
+      <c r="AJ33" s="208"/>
+      <c r="AK33" s="208"/>
+      <c r="AL33" s="208"/>
+      <c r="AM33" s="208"/>
+      <c r="AN33" s="208"/>
+      <c r="AO33" s="208"/>
+      <c r="AP33" s="208"/>
+      <c r="AQ33" s="208"/>
+      <c r="AR33" s="208"/>
+      <c r="AS33" s="208"/>
       <c r="AT33" s="4"/>
       <c r="AU33" s="1"/>
     </row>
@@ -11254,15 +11258,15 @@
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="228" t="s">
+      <c r="D35" s="233" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
+      <c r="E35" s="234"/>
+      <c r="F35" s="234"/>
+      <c r="G35" s="234"/>
+      <c r="H35" s="234"/>
+      <c r="I35" s="234"/>
+      <c r="J35" s="234"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
@@ -11477,18 +11481,18 @@
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="239"/>
-      <c r="E40" s="239"/>
-      <c r="F40" s="239"/>
-      <c r="G40" s="239"/>
-      <c r="H40" s="239"/>
-      <c r="I40" s="239"/>
-      <c r="J40" s="239"/>
-      <c r="K40" s="239"/>
-      <c r="L40" s="239"/>
-      <c r="M40" s="239"/>
-      <c r="N40" s="239"/>
-      <c r="O40" s="239"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
+      <c r="M40" s="244"/>
+      <c r="N40" s="244"/>
+      <c r="O40" s="244"/>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
@@ -11624,50 +11628,50 @@
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="219">
+      <c r="D43" s="223">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46226</v>
       </c>
-      <c r="E43" s="219"/>
-      <c r="F43" s="219"/>
-      <c r="G43" s="219"/>
-      <c r="H43" s="219"/>
-      <c r="I43" s="219"/>
-      <c r="J43" s="219"/>
-      <c r="K43" s="219"/>
-      <c r="L43" s="219"/>
-      <c r="M43" s="219"/>
-      <c r="N43" s="219"/>
-      <c r="O43" s="219"/>
-      <c r="P43" s="219"/>
-      <c r="Q43" s="219"/>
-      <c r="R43" s="219"/>
-      <c r="S43" s="219"/>
-      <c r="T43" s="219"/>
-      <c r="U43" s="219"/>
-      <c r="V43" s="219"/>
-      <c r="W43" s="219"/>
-      <c r="X43" s="219"/>
-      <c r="Y43" s="219"/>
-      <c r="Z43" s="219"/>
-      <c r="AA43" s="219"/>
-      <c r="AB43" s="219"/>
-      <c r="AC43" s="219"/>
-      <c r="AD43" s="219"/>
-      <c r="AE43" s="219"/>
-      <c r="AF43" s="219"/>
-      <c r="AG43" s="219"/>
-      <c r="AH43" s="219"/>
-      <c r="AI43" s="219"/>
-      <c r="AJ43" s="219"/>
-      <c r="AK43" s="219"/>
-      <c r="AL43" s="219"/>
-      <c r="AM43" s="219"/>
-      <c r="AN43" s="219"/>
-      <c r="AO43" s="219"/>
-      <c r="AP43" s="219"/>
-      <c r="AQ43" s="219"/>
-      <c r="AR43" s="219"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="223"/>
+      <c r="I43" s="223"/>
+      <c r="J43" s="223"/>
+      <c r="K43" s="223"/>
+      <c r="L43" s="223"/>
+      <c r="M43" s="223"/>
+      <c r="N43" s="223"/>
+      <c r="O43" s="223"/>
+      <c r="P43" s="223"/>
+      <c r="Q43" s="223"/>
+      <c r="R43" s="223"/>
+      <c r="S43" s="223"/>
+      <c r="T43" s="223"/>
+      <c r="U43" s="223"/>
+      <c r="V43" s="223"/>
+      <c r="W43" s="223"/>
+      <c r="X43" s="223"/>
+      <c r="Y43" s="223"/>
+      <c r="Z43" s="223"/>
+      <c r="AA43" s="223"/>
+      <c r="AB43" s="223"/>
+      <c r="AC43" s="223"/>
+      <c r="AD43" s="223"/>
+      <c r="AE43" s="223"/>
+      <c r="AF43" s="223"/>
+      <c r="AG43" s="223"/>
+      <c r="AH43" s="223"/>
+      <c r="AI43" s="223"/>
+      <c r="AJ43" s="223"/>
+      <c r="AK43" s="223"/>
+      <c r="AL43" s="223"/>
+      <c r="AM43" s="223"/>
+      <c r="AN43" s="223"/>
+      <c r="AO43" s="223"/>
+      <c r="AP43" s="223"/>
+      <c r="AQ43" s="223"/>
+      <c r="AR43" s="223"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="4"/>
       <c r="AU43" s="1"/>
@@ -11928,54 +11932,54 @@
       <c r="B49" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="220" t="s">
+      <c r="C49" s="224" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="220"/>
-      <c r="E49" s="220"/>
-      <c r="F49" s="220"/>
-      <c r="G49" s="220"/>
-      <c r="H49" s="220"/>
-      <c r="I49" s="220"/>
-      <c r="J49" s="220"/>
-      <c r="K49" s="220"/>
-      <c r="L49" s="220"/>
-      <c r="M49" s="220"/>
-      <c r="N49" s="220"/>
-      <c r="O49" s="220"/>
-      <c r="P49" s="220"/>
-      <c r="Q49" s="220"/>
-      <c r="R49" s="220"/>
-      <c r="S49" s="220"/>
-      <c r="T49" s="220"/>
-      <c r="U49" s="220"/>
-      <c r="V49" s="221"/>
+      <c r="D49" s="224"/>
+      <c r="E49" s="224"/>
+      <c r="F49" s="224"/>
+      <c r="G49" s="224"/>
+      <c r="H49" s="224"/>
+      <c r="I49" s="224"/>
+      <c r="J49" s="224"/>
+      <c r="K49" s="224"/>
+      <c r="L49" s="224"/>
+      <c r="M49" s="224"/>
+      <c r="N49" s="224"/>
+      <c r="O49" s="224"/>
+      <c r="P49" s="224"/>
+      <c r="Q49" s="224"/>
+      <c r="R49" s="224"/>
+      <c r="S49" s="224"/>
+      <c r="T49" s="224"/>
+      <c r="U49" s="224"/>
+      <c r="V49" s="225"/>
       <c r="W49" s="28"/>
       <c r="X49" s="28"/>
       <c r="Y49" s="28"/>
-      <c r="Z49" s="222" t="s">
+      <c r="Z49" s="226" t="s">
         <v>55</v>
       </c>
-      <c r="AA49" s="223"/>
-      <c r="AB49" s="223"/>
-      <c r="AC49" s="223"/>
-      <c r="AD49" s="223"/>
-      <c r="AE49" s="223"/>
-      <c r="AF49" s="223"/>
-      <c r="AG49" s="223"/>
-      <c r="AH49" s="223"/>
-      <c r="AI49" s="223"/>
-      <c r="AJ49" s="223"/>
-      <c r="AK49" s="223"/>
-      <c r="AL49" s="223"/>
-      <c r="AM49" s="223"/>
-      <c r="AN49" s="223"/>
-      <c r="AO49" s="223"/>
-      <c r="AP49" s="223"/>
-      <c r="AQ49" s="223"/>
-      <c r="AR49" s="223"/>
-      <c r="AS49" s="223"/>
-      <c r="AT49" s="224"/>
+      <c r="AA49" s="227"/>
+      <c r="AB49" s="227"/>
+      <c r="AC49" s="227"/>
+      <c r="AD49" s="227"/>
+      <c r="AE49" s="227"/>
+      <c r="AF49" s="227"/>
+      <c r="AG49" s="227"/>
+      <c r="AH49" s="227"/>
+      <c r="AI49" s="227"/>
+      <c r="AJ49" s="227"/>
+      <c r="AK49" s="227"/>
+      <c r="AL49" s="227"/>
+      <c r="AM49" s="227"/>
+      <c r="AN49" s="227"/>
+      <c r="AO49" s="227"/>
+      <c r="AP49" s="227"/>
+      <c r="AQ49" s="227"/>
+      <c r="AR49" s="227"/>
+      <c r="AS49" s="227"/>
+      <c r="AT49" s="228"/>
       <c r="AU49" s="4"/>
     </row>
     <row r="50" spans="1:47" ht="18.75" customHeight="1" thickBot="1">
@@ -12008,27 +12012,27 @@
       <c r="W50" s="28"/>
       <c r="X50" s="28"/>
       <c r="Y50" s="28"/>
-      <c r="Z50" s="225"/>
-      <c r="AA50" s="226"/>
-      <c r="AB50" s="226"/>
-      <c r="AC50" s="226"/>
-      <c r="AD50" s="226"/>
-      <c r="AE50" s="226"/>
-      <c r="AF50" s="226"/>
-      <c r="AG50" s="226"/>
-      <c r="AH50" s="226"/>
-      <c r="AI50" s="226"/>
-      <c r="AJ50" s="226"/>
-      <c r="AK50" s="226"/>
-      <c r="AL50" s="226"/>
-      <c r="AM50" s="226"/>
-      <c r="AN50" s="226"/>
-      <c r="AO50" s="226"/>
-      <c r="AP50" s="226"/>
-      <c r="AQ50" s="226"/>
-      <c r="AR50" s="226"/>
-      <c r="AS50" s="226"/>
-      <c r="AT50" s="227"/>
+      <c r="Z50" s="229"/>
+      <c r="AA50" s="230"/>
+      <c r="AB50" s="230"/>
+      <c r="AC50" s="230"/>
+      <c r="AD50" s="230"/>
+      <c r="AE50" s="230"/>
+      <c r="AF50" s="230"/>
+      <c r="AG50" s="230"/>
+      <c r="AH50" s="230"/>
+      <c r="AI50" s="230"/>
+      <c r="AJ50" s="230"/>
+      <c r="AK50" s="230"/>
+      <c r="AL50" s="230"/>
+      <c r="AM50" s="230"/>
+      <c r="AN50" s="230"/>
+      <c r="AO50" s="230"/>
+      <c r="AP50" s="230"/>
+      <c r="AQ50" s="230"/>
+      <c r="AR50" s="230"/>
+      <c r="AS50" s="230"/>
+      <c r="AT50" s="231"/>
       <c r="AU50" s="4"/>
     </row>
     <row r="51" spans="1:47" ht="7.5" customHeight="1"/>
@@ -12039,30 +12043,30 @@
     <row r="57" spans="1:47" ht="14.25" customHeight="1">
       <c r="G57" s="34"/>
       <c r="H57" s="34"/>
-      <c r="AP57" s="74"/>
-      <c r="AQ57" s="74"/>
-      <c r="AR57" s="74"/>
-      <c r="AS57" s="74"/>
-      <c r="AT57" s="74"/>
-      <c r="AU57" s="74"/>
+      <c r="AP57" s="232"/>
+      <c r="AQ57" s="232"/>
+      <c r="AR57" s="232"/>
+      <c r="AS57" s="232"/>
+      <c r="AT57" s="232"/>
+      <c r="AU57" s="232"/>
     </row>
     <row r="58" spans="1:47" ht="14.25" customHeight="1">
       <c r="G58" s="35"/>
       <c r="H58" s="35"/>
-      <c r="AP58" s="74"/>
-      <c r="AQ58" s="74"/>
-      <c r="AR58" s="74"/>
-      <c r="AS58" s="74"/>
-      <c r="AT58" s="74"/>
-      <c r="AU58" s="74"/>
+      <c r="AP58" s="232"/>
+      <c r="AQ58" s="232"/>
+      <c r="AR58" s="232"/>
+      <c r="AS58" s="232"/>
+      <c r="AT58" s="232"/>
+      <c r="AU58" s="232"/>
     </row>
     <row r="59" spans="1:47">
-      <c r="AP59" s="74"/>
-      <c r="AQ59" s="74"/>
-      <c r="AR59" s="74"/>
-      <c r="AS59" s="74"/>
-      <c r="AT59" s="74"/>
-      <c r="AU59" s="74"/>
+      <c r="AP59" s="232"/>
+      <c r="AQ59" s="232"/>
+      <c r="AR59" s="232"/>
+      <c r="AS59" s="232"/>
+      <c r="AT59" s="232"/>
+      <c r="AU59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="95">
@@ -12171,12 +12175,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AU59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="1.375" style="3" customWidth="1"/>
     <col min="2" max="3" width="1.75" style="3" customWidth="1"/>
@@ -12237,2048 +12241,2375 @@
     </row>
     <row r="2" spans="1:47" ht="9.75" customHeight="1">
       <c r="A2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="71" t="s">
-        <v>66</v>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="275" t="s">
+        <v>69</v>
       </c>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
-      <c r="Y2" s="72"/>
-      <c r="Z2" s="72"/>
-      <c r="AA2" s="72"/>
-      <c r="AB2" s="72"/>
-      <c r="AC2" s="72"/>
-      <c r="AD2" s="72"/>
-      <c r="AE2" s="72"/>
-      <c r="AF2" s="72"/>
-      <c r="AG2" s="72"/>
-      <c r="AH2" s="72"/>
-      <c r="AI2" s="72"/>
-      <c r="AJ2" s="72"/>
-      <c r="AK2" s="72"/>
-      <c r="AL2" s="72"/>
-      <c r="AM2" s="72"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
-      <c r="AU2" s="44"/>
+      <c r="J2" s="276"/>
+      <c r="K2" s="276"/>
+      <c r="L2" s="276"/>
+      <c r="M2" s="276"/>
+      <c r="N2" s="276"/>
+      <c r="O2" s="276"/>
+      <c r="P2" s="276"/>
+      <c r="Q2" s="276"/>
+      <c r="R2" s="276"/>
+      <c r="S2" s="276"/>
+      <c r="T2" s="276"/>
+      <c r="U2" s="276"/>
+      <c r="V2" s="276"/>
+      <c r="W2" s="276"/>
+      <c r="X2" s="276"/>
+      <c r="Y2" s="276"/>
+      <c r="Z2" s="276"/>
+      <c r="AA2" s="276"/>
+      <c r="AB2" s="276"/>
+      <c r="AC2" s="276"/>
+      <c r="AD2" s="276"/>
+      <c r="AE2" s="276"/>
+      <c r="AF2" s="276"/>
+      <c r="AG2" s="276"/>
+      <c r="AH2" s="276"/>
+      <c r="AI2" s="276"/>
+      <c r="AJ2" s="276"/>
+      <c r="AK2" s="276"/>
+      <c r="AL2" s="276"/>
+      <c r="AM2" s="276"/>
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="43"/>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="46"/>
     </row>
     <row r="3" spans="1:47" ht="19.5" customHeight="1">
       <c r="A3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="72"/>
-      <c r="AK3" s="72"/>
-      <c r="AL3" s="72"/>
-      <c r="AM3" s="72"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AU3" s="44"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="276"/>
+      <c r="K3" s="276"/>
+      <c r="L3" s="276"/>
+      <c r="M3" s="276"/>
+      <c r="N3" s="276"/>
+      <c r="O3" s="276"/>
+      <c r="P3" s="276"/>
+      <c r="Q3" s="276"/>
+      <c r="R3" s="276"/>
+      <c r="S3" s="276"/>
+      <c r="T3" s="276"/>
+      <c r="U3" s="276"/>
+      <c r="V3" s="276"/>
+      <c r="W3" s="276"/>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="276"/>
+      <c r="Z3" s="276"/>
+      <c r="AA3" s="276"/>
+      <c r="AB3" s="276"/>
+      <c r="AC3" s="276"/>
+      <c r="AD3" s="276"/>
+      <c r="AE3" s="276"/>
+      <c r="AF3" s="276"/>
+      <c r="AG3" s="276"/>
+      <c r="AH3" s="276"/>
+      <c r="AI3" s="276"/>
+      <c r="AJ3" s="276"/>
+      <c r="AK3" s="276"/>
+      <c r="AL3" s="276"/>
+      <c r="AM3" s="276"/>
+      <c r="AN3" s="45"/>
+      <c r="AO3" s="45"/>
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="46"/>
     </row>
     <row r="4" spans="1:47" ht="15" customHeight="1">
       <c r="A4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="73"/>
-      <c r="AA4" s="73"/>
-      <c r="AB4" s="73"/>
-      <c r="AC4" s="73"/>
-      <c r="AD4" s="73"/>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="73"/>
-      <c r="AH4" s="73"/>
-      <c r="AI4" s="73"/>
-      <c r="AJ4" s="73"/>
-      <c r="AK4" s="73"/>
-      <c r="AL4" s="73"/>
-      <c r="AM4" s="73"/>
-      <c r="AN4" s="43"/>
-      <c r="AO4" s="43"/>
-      <c r="AP4" s="43"/>
-      <c r="AU4" s="44"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="277"/>
+      <c r="J4" s="277"/>
+      <c r="K4" s="277"/>
+      <c r="L4" s="277"/>
+      <c r="M4" s="277"/>
+      <c r="N4" s="277"/>
+      <c r="O4" s="277"/>
+      <c r="P4" s="277"/>
+      <c r="Q4" s="277"/>
+      <c r="R4" s="277"/>
+      <c r="S4" s="277"/>
+      <c r="T4" s="277"/>
+      <c r="U4" s="277"/>
+      <c r="V4" s="277"/>
+      <c r="W4" s="277"/>
+      <c r="X4" s="277"/>
+      <c r="Y4" s="277"/>
+      <c r="Z4" s="277"/>
+      <c r="AA4" s="277"/>
+      <c r="AB4" s="277"/>
+      <c r="AC4" s="277"/>
+      <c r="AD4" s="277"/>
+      <c r="AE4" s="277"/>
+      <c r="AF4" s="277"/>
+      <c r="AG4" s="277"/>
+      <c r="AH4" s="277"/>
+      <c r="AI4" s="277"/>
+      <c r="AJ4" s="277"/>
+      <c r="AK4" s="277"/>
+      <c r="AL4" s="277"/>
+      <c r="AM4" s="277"/>
+      <c r="AN4" s="45"/>
+      <c r="AO4" s="45"/>
+      <c r="AP4" s="45"/>
+      <c r="AQ4" s="43"/>
+      <c r="AR4" s="43"/>
+      <c r="AS4" s="43"/>
+      <c r="AT4" s="43"/>
+      <c r="AU4" s="46"/>
     </row>
     <row r="5" spans="1:47" ht="10.5" customHeight="1">
       <c r="A5" s="42"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="45"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="45"/>
-      <c r="AD5" s="45"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="45"/>
-      <c r="AJ5" s="45"/>
-      <c r="AK5" s="45"/>
-      <c r="AL5" s="45"/>
-      <c r="AM5" s="45"/>
-      <c r="AN5" s="45"/>
-      <c r="AO5" s="45"/>
-      <c r="AP5" s="45"/>
-      <c r="AU5" s="44"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="44"/>
+      <c r="AR5" s="43"/>
+      <c r="AS5" s="43"/>
+      <c r="AT5" s="43"/>
+      <c r="AU5" s="46"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1">
       <c r="A6" s="42"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="47"/>
-      <c r="AC6" s="47"/>
-      <c r="AD6" s="47"/>
-      <c r="AE6" s="47"/>
-      <c r="AF6" s="47"/>
-      <c r="AG6" s="47"/>
-      <c r="AH6" s="47"/>
-      <c r="AI6" s="47"/>
-      <c r="AJ6" s="47"/>
-      <c r="AK6" s="47"/>
-      <c r="AL6" s="47"/>
-      <c r="AM6" s="47"/>
-      <c r="AN6" s="47"/>
-      <c r="AO6" s="47"/>
-      <c r="AP6" s="47"/>
-      <c r="AQ6" s="47"/>
-      <c r="AR6" s="47"/>
-      <c r="AU6" s="44"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="49"/>
+      <c r="AE6" s="49"/>
+      <c r="AF6" s="49"/>
+      <c r="AG6" s="49"/>
+      <c r="AH6" s="49"/>
+      <c r="AI6" s="49"/>
+      <c r="AJ6" s="49"/>
+      <c r="AK6" s="49"/>
+      <c r="AL6" s="49"/>
+      <c r="AM6" s="49"/>
+      <c r="AN6" s="49"/>
+      <c r="AO6" s="49"/>
+      <c r="AP6" s="49"/>
+      <c r="AQ6" s="49"/>
+      <c r="AR6" s="49"/>
+      <c r="AS6" s="43"/>
+      <c r="AT6" s="43"/>
+      <c r="AU6" s="46"/>
     </row>
     <row r="7" spans="1:47" ht="18" customHeight="1">
       <c r="A7" s="42"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="47" t="s">
-        <v>67</v>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="49" t="s">
+        <v>70</v>
       </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47"/>
-      <c r="U7" s="47"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
-      <c r="AA7" s="47"/>
-      <c r="AB7" s="47"/>
-      <c r="AC7" s="47"/>
-      <c r="AD7" s="47"/>
-      <c r="AE7" s="47"/>
-      <c r="AF7" s="47"/>
-      <c r="AG7" s="47"/>
-      <c r="AH7" s="47"/>
-      <c r="AI7" s="47"/>
-      <c r="AJ7" s="47"/>
-      <c r="AK7" s="47"/>
-      <c r="AL7" s="47"/>
-      <c r="AM7" s="47"/>
-      <c r="AN7" s="47"/>
-      <c r="AO7" s="47"/>
-      <c r="AP7" s="47"/>
-      <c r="AQ7" s="47"/>
-      <c r="AR7" s="47"/>
-      <c r="AU7" s="44"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="49"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="49"/>
+      <c r="AE7" s="49"/>
+      <c r="AF7" s="49"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
+      <c r="AL7" s="49"/>
+      <c r="AM7" s="49"/>
+      <c r="AN7" s="49"/>
+      <c r="AO7" s="49"/>
+      <c r="AP7" s="49"/>
+      <c r="AQ7" s="49"/>
+      <c r="AR7" s="49"/>
+      <c r="AS7" s="43"/>
+      <c r="AT7" s="43"/>
+      <c r="AU7" s="46"/>
     </row>
     <row r="8" spans="1:47" ht="18" customHeight="1">
       <c r="A8" s="42"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-      <c r="V8" s="48"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="48"/>
-      <c r="Y8" s="48"/>
-      <c r="Z8" s="48"/>
-      <c r="AA8" s="49"/>
-      <c r="AB8" s="48"/>
-      <c r="AC8" s="48"/>
-      <c r="AD8" s="48"/>
-      <c r="AE8" s="48"/>
-      <c r="AF8" s="48"/>
-      <c r="AG8" s="48"/>
-      <c r="AH8" s="47"/>
-      <c r="AI8" s="47"/>
-      <c r="AJ8" s="47"/>
-      <c r="AK8" s="47"/>
-      <c r="AL8" s="48" t="s">
-        <v>68</v>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="51"/>
+      <c r="AC8" s="51"/>
+      <c r="AD8" s="51"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="51"/>
+      <c r="AG8" s="51"/>
+      <c r="AH8" s="49"/>
+      <c r="AI8" s="49"/>
+      <c r="AJ8" s="49"/>
+      <c r="AK8" s="49"/>
+      <c r="AL8" s="51" t="s">
+        <v>71</v>
       </c>
-      <c r="AM8" s="48"/>
-      <c r="AN8" s="48"/>
-      <c r="AO8" s="48"/>
-      <c r="AP8" s="48"/>
-      <c r="AQ8" s="48"/>
-      <c r="AR8" s="48"/>
-      <c r="AU8" s="44"/>
+      <c r="AM8" s="51"/>
+      <c r="AN8" s="51"/>
+      <c r="AO8" s="51"/>
+      <c r="AP8" s="51"/>
+      <c r="AQ8" s="51"/>
+      <c r="AR8" s="51"/>
+      <c r="AS8" s="43"/>
+      <c r="AT8" s="43"/>
+      <c r="AU8" s="46"/>
     </row>
     <row r="9" spans="1:47" ht="18" customHeight="1">
       <c r="A9" s="42"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="48"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="47"/>
-      <c r="AI9" s="47"/>
-      <c r="AJ9" s="47"/>
-      <c r="AK9" s="47"/>
-      <c r="AL9" s="47"/>
-      <c r="AM9" s="47"/>
-      <c r="AN9" s="47"/>
-      <c r="AO9" s="47"/>
-      <c r="AP9" s="47"/>
-      <c r="AQ9" s="47"/>
-      <c r="AR9" s="47"/>
-      <c r="AU9" s="44"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="51"/>
+      <c r="AB9" s="51"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="51"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="51"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49"/>
+      <c r="AK9" s="49"/>
+      <c r="AL9" s="49"/>
+      <c r="AM9" s="49"/>
+      <c r="AN9" s="49"/>
+      <c r="AO9" s="49"/>
+      <c r="AP9" s="49"/>
+      <c r="AQ9" s="49"/>
+      <c r="AR9" s="49"/>
+      <c r="AS9" s="43"/>
+      <c r="AT9" s="43"/>
+      <c r="AU9" s="46"/>
     </row>
     <row r="10" spans="1:47" ht="9" customHeight="1">
       <c r="A10" s="42"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="49"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="49"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="49"/>
-      <c r="AG10" s="49"/>
-      <c r="AH10" s="49"/>
-      <c r="AI10" s="49"/>
-      <c r="AJ10" s="49"/>
-      <c r="AK10" s="49"/>
-      <c r="AL10" s="49"/>
-      <c r="AM10" s="49"/>
-      <c r="AN10" s="49"/>
-      <c r="AO10" s="49"/>
-      <c r="AP10" s="49"/>
-      <c r="AQ10" s="49"/>
-      <c r="AR10" s="49"/>
-      <c r="AU10" s="44"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="53"/>
+      <c r="X10" s="53"/>
+      <c r="Y10" s="53"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="53"/>
+      <c r="AB10" s="53"/>
+      <c r="AC10" s="53"/>
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="53"/>
+      <c r="AF10" s="53"/>
+      <c r="AG10" s="53"/>
+      <c r="AH10" s="53"/>
+      <c r="AI10" s="53"/>
+      <c r="AJ10" s="53"/>
+      <c r="AK10" s="53"/>
+      <c r="AL10" s="53"/>
+      <c r="AM10" s="53"/>
+      <c r="AN10" s="53"/>
+      <c r="AO10" s="53"/>
+      <c r="AP10" s="53"/>
+      <c r="AQ10" s="53"/>
+      <c r="AR10" s="53"/>
+      <c r="AS10" s="43"/>
+      <c r="AT10" s="43"/>
+      <c r="AU10" s="46"/>
     </row>
     <row r="11" spans="1:47" ht="19.5" customHeight="1">
       <c r="A11" s="42"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="49"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="49"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="49"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="49"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="49"/>
-      <c r="AG11" s="49"/>
-      <c r="AH11" s="49"/>
-      <c r="AI11" s="49"/>
-      <c r="AJ11" s="49"/>
-      <c r="AK11" s="49"/>
-      <c r="AL11" s="49">
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="52"/>
+      <c r="W11" s="52"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="52"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
+      <c r="AL11" s="52">
         <v>16</v>
       </c>
-      <c r="AM11" s="49"/>
-      <c r="AN11" s="49"/>
-      <c r="AO11" s="49"/>
-      <c r="AP11" s="49"/>
-      <c r="AQ11" s="49"/>
-      <c r="AR11" s="49"/>
-      <c r="AU11" s="44"/>
+      <c r="AM11" s="52"/>
+      <c r="AN11" s="52"/>
+      <c r="AO11" s="52"/>
+      <c r="AP11" s="52"/>
+      <c r="AQ11" s="52"/>
+      <c r="AR11" s="52"/>
+      <c r="AS11" s="43"/>
+      <c r="AT11" s="43"/>
+      <c r="AU11" s="46"/>
     </row>
     <row r="12" spans="1:47" ht="19.5" customHeight="1">
       <c r="A12" s="42"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-      <c r="AC12" s="47"/>
-      <c r="AD12" s="50">
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="53"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="54">
         <v>45945</v>
       </c>
-      <c r="AE12" s="50"/>
-      <c r="AF12" s="50"/>
-      <c r="AG12" s="50"/>
-      <c r="AH12" s="50"/>
-      <c r="AI12" s="50"/>
-      <c r="AJ12" s="50"/>
-      <c r="AK12" s="50"/>
-      <c r="AL12" s="50"/>
-      <c r="AM12" s="50"/>
-      <c r="AN12" s="51"/>
-      <c r="AO12" s="51"/>
-      <c r="AP12" s="51"/>
-      <c r="AQ12" s="51"/>
-      <c r="AR12" s="49"/>
-      <c r="AU12" s="44"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="54"/>
+      <c r="AG12" s="54"/>
+      <c r="AH12" s="54"/>
+      <c r="AI12" s="54"/>
+      <c r="AJ12" s="54"/>
+      <c r="AK12" s="54"/>
+      <c r="AL12" s="54"/>
+      <c r="AM12" s="54"/>
+      <c r="AN12" s="55"/>
+      <c r="AO12" s="55"/>
+      <c r="AP12" s="55"/>
+      <c r="AQ12" s="55"/>
+      <c r="AR12" s="53"/>
+      <c r="AS12" s="43"/>
+      <c r="AT12" s="43"/>
+      <c r="AU12" s="46"/>
     </row>
     <row r="13" spans="1:47" ht="12" customHeight="1">
       <c r="A13" s="42"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="49"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="49"/>
-      <c r="AG13" s="49"/>
-      <c r="AH13" s="49"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
-      <c r="AL13" s="49"/>
-      <c r="AM13" s="49"/>
-      <c r="AN13" s="49"/>
-      <c r="AO13" s="49"/>
-      <c r="AP13" s="49"/>
-      <c r="AQ13" s="49"/>
-      <c r="AR13" s="49"/>
-      <c r="AU13" s="44"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="53"/>
+      <c r="V13" s="53"/>
+      <c r="W13" s="53"/>
+      <c r="X13" s="53"/>
+      <c r="Y13" s="53"/>
+      <c r="Z13" s="53"/>
+      <c r="AA13" s="53"/>
+      <c r="AB13" s="53"/>
+      <c r="AC13" s="53"/>
+      <c r="AD13" s="53"/>
+      <c r="AE13" s="53"/>
+      <c r="AF13" s="53"/>
+      <c r="AG13" s="53"/>
+      <c r="AH13" s="53"/>
+      <c r="AI13" s="53"/>
+      <c r="AJ13" s="53"/>
+      <c r="AK13" s="53"/>
+      <c r="AL13" s="53"/>
+      <c r="AM13" s="53"/>
+      <c r="AN13" s="53"/>
+      <c r="AO13" s="53"/>
+      <c r="AP13" s="53"/>
+      <c r="AQ13" s="53"/>
+      <c r="AR13" s="53"/>
+      <c r="AS13" s="43"/>
+      <c r="AT13" s="43"/>
+      <c r="AU13" s="46"/>
     </row>
     <row r="14" spans="1:47" ht="12" customHeight="1">
       <c r="A14" s="42"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="49"/>
-      <c r="S14" s="49"/>
-      <c r="T14" s="49"/>
-      <c r="U14" s="49"/>
-      <c r="V14" s="49"/>
-      <c r="W14" s="49"/>
-      <c r="X14" s="49"/>
-      <c r="Y14" s="49"/>
-      <c r="Z14" s="49"/>
-      <c r="AA14" s="49"/>
-      <c r="AB14" s="49"/>
-      <c r="AC14" s="49"/>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="49"/>
-      <c r="AF14" s="49"/>
-      <c r="AG14" s="49"/>
-      <c r="AH14" s="49"/>
-      <c r="AI14" s="49"/>
-      <c r="AJ14" s="49"/>
-      <c r="AK14" s="49"/>
-      <c r="AL14" s="49"/>
-      <c r="AM14" s="49"/>
-      <c r="AN14" s="49"/>
-      <c r="AO14" s="49"/>
-      <c r="AP14" s="49"/>
-      <c r="AQ14" s="49"/>
-      <c r="AR14" s="49"/>
-      <c r="AU14" s="44"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
+      <c r="V14" s="53"/>
+      <c r="W14" s="53"/>
+      <c r="X14" s="53"/>
+      <c r="Y14" s="53"/>
+      <c r="Z14" s="53"/>
+      <c r="AA14" s="53"/>
+      <c r="AB14" s="53"/>
+      <c r="AC14" s="53"/>
+      <c r="AD14" s="53"/>
+      <c r="AE14" s="53"/>
+      <c r="AF14" s="53"/>
+      <c r="AG14" s="53"/>
+      <c r="AH14" s="53"/>
+      <c r="AI14" s="53"/>
+      <c r="AJ14" s="53"/>
+      <c r="AK14" s="53"/>
+      <c r="AL14" s="53"/>
+      <c r="AM14" s="53"/>
+      <c r="AN14" s="53"/>
+      <c r="AO14" s="53"/>
+      <c r="AP14" s="53"/>
+      <c r="AQ14" s="53"/>
+      <c r="AR14" s="53"/>
+      <c r="AS14" s="43"/>
+      <c r="AT14" s="43"/>
+      <c r="AU14" s="46"/>
     </row>
     <row r="15" spans="1:47" ht="9.75" customHeight="1">
       <c r="A15" s="42"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="49"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="49"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="49"/>
-      <c r="AA15" s="49"/>
-      <c r="AB15" s="49"/>
-      <c r="AC15" s="49"/>
-      <c r="AD15" s="49"/>
-      <c r="AE15" s="49"/>
-      <c r="AF15" s="49"/>
-      <c r="AG15" s="49"/>
-      <c r="AH15" s="49"/>
-      <c r="AI15" s="49"/>
-      <c r="AJ15" s="49"/>
-      <c r="AK15" s="49"/>
-      <c r="AL15" s="49"/>
-      <c r="AM15" s="49"/>
-      <c r="AN15" s="49"/>
-      <c r="AO15" s="49"/>
-      <c r="AP15" s="49"/>
-      <c r="AQ15" s="49"/>
-      <c r="AR15" s="49"/>
-      <c r="AU15" s="44"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
+      <c r="V15" s="53"/>
+      <c r="W15" s="53"/>
+      <c r="X15" s="53"/>
+      <c r="Y15" s="53"/>
+      <c r="Z15" s="53"/>
+      <c r="AA15" s="53"/>
+      <c r="AB15" s="53"/>
+      <c r="AC15" s="53"/>
+      <c r="AD15" s="53"/>
+      <c r="AE15" s="53"/>
+      <c r="AF15" s="53"/>
+      <c r="AG15" s="53"/>
+      <c r="AH15" s="53"/>
+      <c r="AI15" s="53"/>
+      <c r="AJ15" s="53"/>
+      <c r="AK15" s="53"/>
+      <c r="AL15" s="53"/>
+      <c r="AM15" s="53"/>
+      <c r="AN15" s="53"/>
+      <c r="AO15" s="53"/>
+      <c r="AP15" s="53"/>
+      <c r="AQ15" s="53"/>
+      <c r="AR15" s="53"/>
+      <c r="AS15" s="43"/>
+      <c r="AT15" s="43"/>
+      <c r="AU15" s="46"/>
     </row>
     <row r="16" spans="1:47" ht="15" customHeight="1">
       <c r="A16" s="42"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="53"/>
-      <c r="P16" s="53"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="53"/>
-      <c r="S16" s="53"/>
-      <c r="T16" s="53"/>
-      <c r="U16" s="53" t="s">
-        <v>69</v>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57" t="s">
+        <v>72</v>
       </c>
-      <c r="V16" s="53"/>
-      <c r="W16" s="53"/>
-      <c r="X16" s="53"/>
-      <c r="Y16" s="53"/>
-      <c r="Z16" s="53"/>
-      <c r="AA16" s="53"/>
-      <c r="AB16" s="53"/>
-      <c r="AC16" s="53"/>
-      <c r="AD16" s="53"/>
-      <c r="AE16" s="53"/>
-      <c r="AF16" s="53"/>
-      <c r="AG16" s="53"/>
-      <c r="AH16" s="53"/>
-      <c r="AI16" s="53"/>
-      <c r="AJ16" s="53"/>
-      <c r="AK16" s="53"/>
-      <c r="AL16" s="53"/>
-      <c r="AM16" s="53"/>
-      <c r="AN16" s="53"/>
-      <c r="AO16" s="53"/>
-      <c r="AP16" s="53"/>
-      <c r="AQ16" s="53"/>
-      <c r="AR16" s="53"/>
-      <c r="AU16" s="44"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="57"/>
+      <c r="X16" s="57"/>
+      <c r="Y16" s="57"/>
+      <c r="Z16" s="57"/>
+      <c r="AA16" s="57"/>
+      <c r="AB16" s="57"/>
+      <c r="AC16" s="57"/>
+      <c r="AD16" s="57"/>
+      <c r="AE16" s="57"/>
+      <c r="AF16" s="57"/>
+      <c r="AG16" s="57"/>
+      <c r="AH16" s="57"/>
+      <c r="AI16" s="57"/>
+      <c r="AJ16" s="57"/>
+      <c r="AK16" s="57"/>
+      <c r="AL16" s="57"/>
+      <c r="AM16" s="57"/>
+      <c r="AN16" s="57"/>
+      <c r="AO16" s="57"/>
+      <c r="AP16" s="57"/>
+      <c r="AQ16" s="57"/>
+      <c r="AR16" s="57"/>
+      <c r="AS16" s="43"/>
+      <c r="AT16" s="43"/>
+      <c r="AU16" s="46"/>
     </row>
     <row r="17" spans="1:47" ht="15" customHeight="1">
       <c r="A17" s="42"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="55">
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="59">
         <v>33</v>
       </c>
-      <c r="P17" s="55">
+      <c r="P17" s="59">
         <v>16</v>
       </c>
-      <c r="Q17" s="55">
+      <c r="Q17" s="59">
         <v>16</v>
       </c>
-      <c r="R17" s="55">
+      <c r="R17" s="59">
         <v>16</v>
       </c>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="56"/>
-      <c r="Y17" s="56"/>
-      <c r="Z17" s="56"/>
-      <c r="AA17" s="56"/>
-      <c r="AB17" s="56"/>
-      <c r="AC17" s="56"/>
-      <c r="AD17" s="56"/>
-      <c r="AE17" s="56"/>
-      <c r="AF17" s="56"/>
-      <c r="AG17" s="56"/>
-      <c r="AH17" s="56"/>
-      <c r="AI17" s="56"/>
-      <c r="AJ17" s="56"/>
-      <c r="AK17" s="56"/>
-      <c r="AL17" s="56"/>
-      <c r="AM17" s="56"/>
-      <c r="AN17" s="56"/>
-      <c r="AO17" s="56"/>
-      <c r="AP17" s="56"/>
-      <c r="AQ17" s="56"/>
-      <c r="AR17" s="56"/>
-      <c r="AU17" s="44"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="59"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="58"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="60"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="43"/>
+      <c r="AT17" s="43"/>
+      <c r="AU17" s="46"/>
     </row>
     <row r="18" spans="1:47" ht="15" customHeight="1">
       <c r="A18" s="42"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="57">
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="61">
         <v>32</v>
       </c>
-      <c r="J18" s="57">
+      <c r="J18" s="61">
         <v>16</v>
       </c>
-      <c r="K18" s="57">
+      <c r="K18" s="61">
         <v>16</v>
       </c>
-      <c r="L18" s="57">
+      <c r="L18" s="61">
         <v>16</v>
       </c>
-      <c r="M18" s="57">
+      <c r="M18" s="61">
         <v>16</v>
       </c>
-      <c r="N18" s="57">
+      <c r="N18" s="61">
         <v>16</v>
       </c>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="T18" s="57"/>
-      <c r="U18" s="47"/>
-      <c r="V18" s="47"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-      <c r="AA18" s="49"/>
-      <c r="AB18" s="49"/>
-      <c r="AC18" s="49"/>
-      <c r="AD18" s="49"/>
-      <c r="AE18" s="49"/>
-      <c r="AF18" s="49"/>
-      <c r="AG18" s="49"/>
-      <c r="AH18" s="49"/>
-      <c r="AI18" s="49"/>
-      <c r="AJ18" s="49"/>
-      <c r="AK18" s="49"/>
-      <c r="AL18" s="49"/>
-      <c r="AM18" s="49"/>
-      <c r="AN18" s="49"/>
-      <c r="AO18" s="49"/>
-      <c r="AP18" s="49"/>
-      <c r="AQ18" s="49"/>
-      <c r="AR18" s="49"/>
-      <c r="AU18" s="44"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="61"/>
+      <c r="R18" s="61"/>
+      <c r="S18" s="61"/>
+      <c r="T18" s="61"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="52"/>
+      <c r="X18" s="52"/>
+      <c r="Y18" s="52"/>
+      <c r="Z18" s="52"/>
+      <c r="AA18" s="52"/>
+      <c r="AB18" s="52"/>
+      <c r="AC18" s="52"/>
+      <c r="AD18" s="52"/>
+      <c r="AE18" s="52"/>
+      <c r="AF18" s="52"/>
+      <c r="AG18" s="52"/>
+      <c r="AH18" s="52"/>
+      <c r="AI18" s="52"/>
+      <c r="AJ18" s="52"/>
+      <c r="AK18" s="52"/>
+      <c r="AL18" s="52"/>
+      <c r="AM18" s="52"/>
+      <c r="AN18" s="52"/>
+      <c r="AO18" s="52"/>
+      <c r="AP18" s="52"/>
+      <c r="AQ18" s="52"/>
+      <c r="AR18" s="52"/>
+      <c r="AS18" s="43"/>
+      <c r="AT18" s="43"/>
+      <c r="AU18" s="46"/>
     </row>
     <row r="19" spans="1:47" ht="15" customHeight="1">
       <c r="A19" s="42"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="49"/>
-      <c r="AA19" s="49"/>
-      <c r="AB19" s="49"/>
-      <c r="AC19" s="49"/>
-      <c r="AD19" s="49"/>
-      <c r="AE19" s="49"/>
-      <c r="AF19" s="49"/>
-      <c r="AG19" s="49"/>
-      <c r="AH19" s="49"/>
-      <c r="AI19" s="49"/>
-      <c r="AJ19" s="49"/>
-      <c r="AK19" s="49"/>
-      <c r="AL19" s="49"/>
-      <c r="AM19" s="49"/>
-      <c r="AN19" s="49"/>
-      <c r="AO19" s="49"/>
-      <c r="AP19" s="49"/>
-      <c r="AQ19" s="49"/>
-      <c r="AR19" s="49"/>
-      <c r="AU19" s="44"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="52"/>
+      <c r="X19" s="52"/>
+      <c r="Y19" s="52"/>
+      <c r="Z19" s="52"/>
+      <c r="AA19" s="52"/>
+      <c r="AB19" s="52"/>
+      <c r="AC19" s="52"/>
+      <c r="AD19" s="52"/>
+      <c r="AE19" s="52"/>
+      <c r="AF19" s="52"/>
+      <c r="AG19" s="52"/>
+      <c r="AH19" s="52"/>
+      <c r="AI19" s="52"/>
+      <c r="AJ19" s="52"/>
+      <c r="AK19" s="52"/>
+      <c r="AL19" s="52"/>
+      <c r="AM19" s="52"/>
+      <c r="AN19" s="52"/>
+      <c r="AO19" s="52"/>
+      <c r="AP19" s="52"/>
+      <c r="AQ19" s="52"/>
+      <c r="AR19" s="52"/>
+      <c r="AS19" s="43"/>
+      <c r="AT19" s="43"/>
+      <c r="AU19" s="46"/>
     </row>
     <row r="20" spans="1:47" ht="15" customHeight="1">
       <c r="A20" s="42"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="49"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="49"/>
-      <c r="R20" s="49"/>
-      <c r="S20" s="49"/>
-      <c r="T20" s="49"/>
-      <c r="U20" s="49"/>
-      <c r="V20" s="49"/>
-      <c r="W20" s="49"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="49"/>
-      <c r="AA20" s="49"/>
-      <c r="AB20" s="49"/>
-      <c r="AC20" s="49"/>
-      <c r="AD20" s="49"/>
-      <c r="AE20" s="49"/>
-      <c r="AF20" s="49"/>
-      <c r="AG20" s="49"/>
-      <c r="AH20" s="49"/>
-      <c r="AI20" s="49"/>
-      <c r="AJ20" s="49"/>
-      <c r="AK20" s="49"/>
-      <c r="AL20" s="49"/>
-      <c r="AM20" s="49"/>
-      <c r="AN20" s="49"/>
-      <c r="AO20" s="49"/>
-      <c r="AP20" s="49"/>
-      <c r="AQ20" s="49"/>
-      <c r="AR20" s="49"/>
-      <c r="AU20" s="44"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="53"/>
+      <c r="U20" s="53"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="53"/>
+      <c r="Z20" s="53"/>
+      <c r="AA20" s="53"/>
+      <c r="AB20" s="53"/>
+      <c r="AC20" s="53"/>
+      <c r="AD20" s="53"/>
+      <c r="AE20" s="53"/>
+      <c r="AF20" s="53"/>
+      <c r="AG20" s="53"/>
+      <c r="AH20" s="53"/>
+      <c r="AI20" s="53"/>
+      <c r="AJ20" s="53"/>
+      <c r="AK20" s="53"/>
+      <c r="AL20" s="53"/>
+      <c r="AM20" s="53"/>
+      <c r="AN20" s="53"/>
+      <c r="AO20" s="53"/>
+      <c r="AP20" s="53"/>
+      <c r="AQ20" s="53"/>
+      <c r="AR20" s="53"/>
+      <c r="AS20" s="43"/>
+      <c r="AT20" s="43"/>
+      <c r="AU20" s="46"/>
     </row>
     <row r="21" spans="1:47" ht="21" customHeight="1">
       <c r="A21" s="42"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="49"/>
-      <c r="R21" s="49"/>
-      <c r="S21" s="49"/>
-      <c r="T21" s="49"/>
-      <c r="U21" s="49"/>
-      <c r="V21" s="49"/>
-      <c r="W21" s="49"/>
-      <c r="X21" s="49"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="49"/>
-      <c r="AA21" s="49"/>
-      <c r="AB21" s="49"/>
-      <c r="AC21" s="49"/>
-      <c r="AD21" s="49"/>
-      <c r="AE21" s="49"/>
-      <c r="AF21" s="49"/>
-      <c r="AG21" s="49"/>
-      <c r="AH21" s="49"/>
-      <c r="AI21" s="49"/>
-      <c r="AJ21" s="49"/>
-      <c r="AK21" s="49"/>
-      <c r="AL21" s="49"/>
-      <c r="AM21" s="49"/>
-      <c r="AN21" s="49"/>
-      <c r="AO21" s="49"/>
-      <c r="AP21" s="49"/>
-      <c r="AQ21" s="49"/>
-      <c r="AR21" s="49"/>
-      <c r="AU21" s="44"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="53"/>
+      <c r="U21" s="53"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="53"/>
+      <c r="AA21" s="53"/>
+      <c r="AB21" s="53"/>
+      <c r="AC21" s="53"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="53"/>
+      <c r="AF21" s="53"/>
+      <c r="AG21" s="53"/>
+      <c r="AH21" s="53"/>
+      <c r="AI21" s="53"/>
+      <c r="AJ21" s="53"/>
+      <c r="AK21" s="53"/>
+      <c r="AL21" s="53"/>
+      <c r="AM21" s="53"/>
+      <c r="AN21" s="53"/>
+      <c r="AO21" s="53"/>
+      <c r="AP21" s="53"/>
+      <c r="AQ21" s="53"/>
+      <c r="AR21" s="53"/>
+      <c r="AS21" s="43"/>
+      <c r="AT21" s="43"/>
+      <c r="AU21" s="46"/>
     </row>
     <row r="22" spans="1:47" ht="21" customHeight="1">
       <c r="A22" s="42"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="61"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="61"/>
-      <c r="R22" s="61"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="61"/>
-      <c r="V22" s="61"/>
-      <c r="W22" s="61"/>
-      <c r="X22" s="61"/>
-      <c r="Y22" s="61"/>
-      <c r="Z22" s="61"/>
-      <c r="AA22" s="61"/>
-      <c r="AB22" s="61"/>
-      <c r="AC22" s="61"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="47"/>
-      <c r="AF22" s="47"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="47"/>
-      <c r="AI22" s="47"/>
-      <c r="AJ22" s="47"/>
-      <c r="AK22" s="47"/>
-      <c r="AL22" s="47"/>
-      <c r="AM22" s="47"/>
-      <c r="AN22" s="47"/>
-      <c r="AO22" s="47"/>
-      <c r="AP22" s="47"/>
-      <c r="AQ22" s="47"/>
-      <c r="AR22" s="47"/>
-      <c r="AU22" s="44"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
+      <c r="AL22" s="67"/>
+      <c r="AM22" s="67"/>
+      <c r="AN22" s="67"/>
+      <c r="AO22" s="67"/>
+      <c r="AP22" s="67"/>
+      <c r="AQ22" s="67"/>
+      <c r="AR22" s="67"/>
+      <c r="AS22" s="43"/>
+      <c r="AT22" s="43"/>
+      <c r="AU22" s="46"/>
     </row>
     <row r="23" spans="1:47" ht="20.25" customHeight="1">
       <c r="A23" s="42"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="61"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="61"/>
-      <c r="T23" s="61"/>
-      <c r="U23" s="61"/>
-      <c r="V23" s="61"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="61"/>
-      <c r="Y23" s="61"/>
-      <c r="Z23" s="61"/>
-      <c r="AA23" s="61"/>
-      <c r="AB23" s="61"/>
-      <c r="AC23" s="61"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="47"/>
-      <c r="AF23" s="47"/>
-      <c r="AG23" s="47"/>
-      <c r="AH23" s="47"/>
-      <c r="AI23" s="47"/>
-      <c r="AJ23" s="47"/>
-      <c r="AK23" s="47"/>
-      <c r="AL23" s="47"/>
-      <c r="AM23" s="47"/>
-      <c r="AN23" s="47"/>
-      <c r="AO23" s="47"/>
-      <c r="AP23" s="47"/>
-      <c r="AQ23" s="47"/>
-      <c r="AR23" s="47"/>
-      <c r="AU23" s="44"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="67"/>
+      <c r="AM23" s="67"/>
+      <c r="AN23" s="67"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="67"/>
+      <c r="AQ23" s="67"/>
+      <c r="AR23" s="67"/>
+      <c r="AS23" s="43"/>
+      <c r="AT23" s="43"/>
+      <c r="AU23" s="46"/>
     </row>
     <row r="24" spans="1:47" ht="20.25" customHeight="1">
       <c r="A24" s="42"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="62"/>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="62"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="62"/>
-      <c r="AA24" s="62"/>
-      <c r="AB24" s="62"/>
-      <c r="AC24" s="62"/>
-      <c r="AD24" s="62"/>
-      <c r="AE24" s="62"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
-      <c r="AI24" s="62"/>
-      <c r="AJ24" s="62"/>
-      <c r="AK24" s="62"/>
-      <c r="AL24" s="62"/>
-      <c r="AM24" s="62"/>
-      <c r="AN24" s="62"/>
-      <c r="AO24" s="62"/>
-      <c r="AP24" s="62"/>
-      <c r="AQ24" s="62"/>
-      <c r="AR24" s="63"/>
-      <c r="AU24" s="44"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="68"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="69"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="69"/>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="69"/>
+      <c r="AE24" s="69"/>
+      <c r="AF24" s="69"/>
+      <c r="AG24" s="69"/>
+      <c r="AH24" s="69"/>
+      <c r="AI24" s="69"/>
+      <c r="AJ24" s="69"/>
+      <c r="AK24" s="69"/>
+      <c r="AL24" s="69"/>
+      <c r="AM24" s="69"/>
+      <c r="AN24" s="69"/>
+      <c r="AO24" s="69"/>
+      <c r="AP24" s="69"/>
+      <c r="AQ24" s="69"/>
+      <c r="AR24" s="70"/>
+      <c r="AS24" s="43"/>
+      <c r="AT24" s="43"/>
+      <c r="AU24" s="46"/>
     </row>
     <row r="25" spans="1:47" ht="20.25" customHeight="1">
       <c r="A25" s="42"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="62"/>
-      <c r="P25" s="62"/>
-      <c r="Q25" s="62"/>
-      <c r="R25" s="62"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="62"/>
-      <c r="U25" s="62"/>
-      <c r="V25" s="62"/>
-      <c r="W25" s="62"/>
-      <c r="X25" s="62"/>
-      <c r="Y25" s="62"/>
-      <c r="Z25" s="62"/>
-      <c r="AA25" s="62"/>
-      <c r="AB25" s="62"/>
-      <c r="AC25" s="62"/>
-      <c r="AD25" s="62"/>
-      <c r="AE25" s="62"/>
-      <c r="AF25" s="62"/>
-      <c r="AG25" s="62"/>
-      <c r="AH25" s="62"/>
-      <c r="AI25" s="62"/>
-      <c r="AJ25" s="62"/>
-      <c r="AK25" s="62"/>
-      <c r="AL25" s="62"/>
-      <c r="AM25" s="62"/>
-      <c r="AN25" s="62"/>
-      <c r="AO25" s="62"/>
-      <c r="AP25" s="62"/>
-      <c r="AQ25" s="62"/>
-      <c r="AR25" s="63"/>
-      <c r="AU25" s="44"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="69"/>
+      <c r="AB25" s="69"/>
+      <c r="AC25" s="69"/>
+      <c r="AD25" s="69"/>
+      <c r="AE25" s="69"/>
+      <c r="AF25" s="69"/>
+      <c r="AG25" s="69"/>
+      <c r="AH25" s="69"/>
+      <c r="AI25" s="69"/>
+      <c r="AJ25" s="69"/>
+      <c r="AK25" s="69"/>
+      <c r="AL25" s="69"/>
+      <c r="AM25" s="69"/>
+      <c r="AN25" s="69"/>
+      <c r="AO25" s="69"/>
+      <c r="AP25" s="69"/>
+      <c r="AQ25" s="69"/>
+      <c r="AR25" s="70"/>
+      <c r="AS25" s="43"/>
+      <c r="AT25" s="43"/>
+      <c r="AU25" s="46"/>
     </row>
     <row r="26" spans="1:47" ht="20.25" customHeight="1">
       <c r="A26" s="42"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="47"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="47"/>
-      <c r="W26" s="47"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="47"/>
-      <c r="Z26" s="47"/>
-      <c r="AA26" s="47"/>
-      <c r="AB26" s="47"/>
-      <c r="AC26" s="47"/>
-      <c r="AD26" s="47"/>
-      <c r="AE26" s="47"/>
-      <c r="AF26" s="47"/>
-      <c r="AG26" s="47"/>
-      <c r="AH26" s="47"/>
-      <c r="AI26" s="47"/>
-      <c r="AJ26" s="47"/>
-      <c r="AK26" s="47"/>
-      <c r="AL26" s="47"/>
-      <c r="AM26" s="47"/>
-      <c r="AN26" s="47"/>
-      <c r="AO26" s="47"/>
-      <c r="AP26" s="47"/>
-      <c r="AQ26" s="47"/>
-      <c r="AR26" s="47"/>
-      <c r="AU26" s="44"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="49"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
+      <c r="AL26" s="49"/>
+      <c r="AM26" s="49"/>
+      <c r="AN26" s="49"/>
+      <c r="AO26" s="49"/>
+      <c r="AP26" s="49"/>
+      <c r="AQ26" s="49"/>
+      <c r="AR26" s="49"/>
+      <c r="AS26" s="43"/>
+      <c r="AT26" s="43"/>
+      <c r="AU26" s="46"/>
     </row>
     <row r="27" spans="1:47" ht="20.25" customHeight="1">
       <c r="A27" s="42"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="47"/>
-      <c r="AF27" s="47"/>
-      <c r="AG27" s="47"/>
-      <c r="AH27" s="47"/>
-      <c r="AI27" s="47"/>
-      <c r="AJ27" s="47"/>
-      <c r="AK27" s="47"/>
-      <c r="AL27" s="47"/>
-      <c r="AM27" s="47"/>
-      <c r="AN27" s="47"/>
-      <c r="AO27" s="47"/>
-      <c r="AP27" s="47"/>
-      <c r="AQ27" s="47"/>
-      <c r="AR27" s="47"/>
-      <c r="AU27" s="44"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="49"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="49"/>
+      <c r="AE27" s="49"/>
+      <c r="AF27" s="49"/>
+      <c r="AG27" s="49"/>
+      <c r="AH27" s="49"/>
+      <c r="AI27" s="49"/>
+      <c r="AJ27" s="49"/>
+      <c r="AK27" s="49"/>
+      <c r="AL27" s="49"/>
+      <c r="AM27" s="49"/>
+      <c r="AN27" s="49"/>
+      <c r="AO27" s="49"/>
+      <c r="AP27" s="49"/>
+      <c r="AQ27" s="49"/>
+      <c r="AR27" s="49"/>
+      <c r="AS27" s="43"/>
+      <c r="AT27" s="43"/>
+      <c r="AU27" s="46"/>
     </row>
     <row r="28" spans="1:47" ht="20.25" customHeight="1">
       <c r="A28" s="42"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="49"/>
-      <c r="W28" s="49"/>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="49"/>
-      <c r="AA28" s="49"/>
-      <c r="AB28" s="49"/>
-      <c r="AC28" s="49"/>
-      <c r="AD28" s="49"/>
-      <c r="AE28" s="49"/>
-      <c r="AF28" s="49"/>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
-      <c r="AM28" s="49"/>
-      <c r="AN28" s="49"/>
-      <c r="AO28" s="49"/>
-      <c r="AP28" s="49"/>
-      <c r="AQ28" s="49"/>
-      <c r="AR28" s="49"/>
-      <c r="AU28" s="44"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
+      <c r="U28" s="53"/>
+      <c r="V28" s="53"/>
+      <c r="W28" s="53"/>
+      <c r="X28" s="53"/>
+      <c r="Y28" s="53"/>
+      <c r="Z28" s="53"/>
+      <c r="AA28" s="53"/>
+      <c r="AB28" s="53"/>
+      <c r="AC28" s="53"/>
+      <c r="AD28" s="53"/>
+      <c r="AE28" s="53"/>
+      <c r="AF28" s="53"/>
+      <c r="AG28" s="53"/>
+      <c r="AH28" s="53"/>
+      <c r="AI28" s="53"/>
+      <c r="AJ28" s="53"/>
+      <c r="AK28" s="53"/>
+      <c r="AL28" s="53"/>
+      <c r="AM28" s="53"/>
+      <c r="AN28" s="53"/>
+      <c r="AO28" s="53"/>
+      <c r="AP28" s="53"/>
+      <c r="AQ28" s="53"/>
+      <c r="AR28" s="53"/>
+      <c r="AS28" s="43"/>
+      <c r="AT28" s="43"/>
+      <c r="AU28" s="46"/>
     </row>
     <row r="29" spans="1:47" ht="9" customHeight="1">
       <c r="A29" s="42"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="47"/>
-      <c r="V29" s="47"/>
-      <c r="W29" s="47"/>
-      <c r="X29" s="47"/>
-      <c r="Y29" s="47"/>
-      <c r="Z29" s="47"/>
-      <c r="AA29" s="47"/>
-      <c r="AB29" s="47"/>
-      <c r="AC29" s="47"/>
-      <c r="AD29" s="47"/>
-      <c r="AE29" s="47"/>
-      <c r="AF29" s="47"/>
-      <c r="AG29" s="47"/>
-      <c r="AH29" s="47"/>
-      <c r="AI29" s="47"/>
-      <c r="AJ29" s="47"/>
-      <c r="AK29" s="47"/>
-      <c r="AL29" s="47"/>
-      <c r="AM29" s="47"/>
-      <c r="AN29" s="47"/>
-      <c r="AO29" s="47"/>
-      <c r="AP29" s="47"/>
-      <c r="AQ29" s="47"/>
-      <c r="AR29" s="47"/>
-      <c r="AU29" s="44"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="49"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="49"/>
+      <c r="AE29" s="49"/>
+      <c r="AF29" s="49"/>
+      <c r="AG29" s="49"/>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
+      <c r="AL29" s="49"/>
+      <c r="AM29" s="49"/>
+      <c r="AN29" s="49"/>
+      <c r="AO29" s="49"/>
+      <c r="AP29" s="49"/>
+      <c r="AQ29" s="49"/>
+      <c r="AR29" s="49"/>
+      <c r="AS29" s="43"/>
+      <c r="AT29" s="43"/>
+      <c r="AU29" s="46"/>
     </row>
     <row r="30" spans="1:47" ht="18.75" customHeight="1">
       <c r="A30" s="42"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="66"/>
-      <c r="V30" s="66"/>
-      <c r="W30" s="47"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="47"/>
-      <c r="Z30" s="47"/>
-      <c r="AA30" s="47"/>
-      <c r="AB30" s="47"/>
-      <c r="AC30" s="47"/>
-      <c r="AD30" s="47"/>
-      <c r="AE30" s="47"/>
-      <c r="AF30" s="47"/>
-      <c r="AG30" s="47"/>
-      <c r="AH30" s="47"/>
-      <c r="AI30" s="47"/>
-      <c r="AJ30" s="49"/>
-      <c r="AK30" s="49"/>
-      <c r="AL30" s="49"/>
-      <c r="AM30" s="49"/>
-      <c r="AN30" s="49"/>
-      <c r="AO30" s="49"/>
-      <c r="AP30" s="49"/>
-      <c r="AQ30" s="49"/>
-      <c r="AR30" s="49"/>
-      <c r="AU30" s="44"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="73"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="73"/>
+      <c r="T30" s="73"/>
+      <c r="U30" s="73"/>
+      <c r="V30" s="73"/>
+      <c r="W30" s="49"/>
+      <c r="X30" s="49"/>
+      <c r="Y30" s="49"/>
+      <c r="Z30" s="49"/>
+      <c r="AA30" s="49"/>
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="49"/>
+      <c r="AD30" s="49"/>
+      <c r="AE30" s="49"/>
+      <c r="AF30" s="49"/>
+      <c r="AG30" s="49"/>
+      <c r="AH30" s="49"/>
+      <c r="AI30" s="49"/>
+      <c r="AJ30" s="52"/>
+      <c r="AK30" s="52"/>
+      <c r="AL30" s="52"/>
+      <c r="AM30" s="52"/>
+      <c r="AN30" s="52"/>
+      <c r="AO30" s="52"/>
+      <c r="AP30" s="52"/>
+      <c r="AQ30" s="52"/>
+      <c r="AR30" s="52"/>
+      <c r="AS30" s="43"/>
+      <c r="AT30" s="43"/>
+      <c r="AU30" s="46"/>
     </row>
     <row r="31" spans="1:47" ht="18.75" customHeight="1">
       <c r="A31" s="42"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="66"/>
-      <c r="O31" s="66"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-      <c r="V31" s="66"/>
-      <c r="W31" s="47"/>
-      <c r="X31" s="47"/>
-      <c r="Y31" s="47"/>
-      <c r="Z31" s="47"/>
-      <c r="AA31" s="47"/>
-      <c r="AB31" s="47"/>
-      <c r="AC31" s="47"/>
-      <c r="AD31" s="47"/>
-      <c r="AE31" s="47"/>
-      <c r="AF31" s="47"/>
-      <c r="AG31" s="47"/>
-      <c r="AH31" s="47"/>
-      <c r="AI31" s="47"/>
-      <c r="AJ31" s="49"/>
-      <c r="AK31" s="49"/>
-      <c r="AL31" s="49"/>
-      <c r="AM31" s="49"/>
-      <c r="AN31" s="49"/>
-      <c r="AO31" s="49"/>
-      <c r="AP31" s="49"/>
-      <c r="AQ31" s="49"/>
-      <c r="AR31" s="49"/>
-      <c r="AU31" s="44"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="73"/>
+      <c r="V31" s="73"/>
+      <c r="W31" s="49"/>
+      <c r="X31" s="49"/>
+      <c r="Y31" s="49"/>
+      <c r="Z31" s="49"/>
+      <c r="AA31" s="49"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="49"/>
+      <c r="AD31" s="49"/>
+      <c r="AE31" s="49"/>
+      <c r="AF31" s="49"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="52"/>
+      <c r="AK31" s="52"/>
+      <c r="AL31" s="52"/>
+      <c r="AM31" s="52"/>
+      <c r="AN31" s="52"/>
+      <c r="AO31" s="52"/>
+      <c r="AP31" s="52"/>
+      <c r="AQ31" s="52"/>
+      <c r="AR31" s="52"/>
+      <c r="AS31" s="43"/>
+      <c r="AT31" s="43"/>
+      <c r="AU31" s="46"/>
     </row>
     <row r="32" spans="1:47" ht="18" customHeight="1">
       <c r="A32" s="42"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="47"/>
-      <c r="X32" s="47"/>
-      <c r="Y32" s="47"/>
-      <c r="Z32" s="47"/>
-      <c r="AA32" s="47"/>
-      <c r="AB32" s="47"/>
-      <c r="AC32" s="47"/>
-      <c r="AD32" s="47"/>
-      <c r="AE32" s="47"/>
-      <c r="AF32" s="47"/>
-      <c r="AG32" s="47"/>
-      <c r="AH32" s="47"/>
-      <c r="AI32" s="47"/>
-      <c r="AJ32" s="49"/>
-      <c r="AK32" s="49"/>
-      <c r="AL32" s="49"/>
-      <c r="AM32" s="49"/>
-      <c r="AN32" s="49"/>
-      <c r="AO32" s="49"/>
-      <c r="AP32" s="49"/>
-      <c r="AQ32" s="49"/>
-      <c r="AR32" s="49"/>
-      <c r="AU32" s="44"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="73"/>
+      <c r="T32" s="73"/>
+      <c r="U32" s="73"/>
+      <c r="V32" s="73"/>
+      <c r="W32" s="49"/>
+      <c r="X32" s="49"/>
+      <c r="Y32" s="49"/>
+      <c r="Z32" s="49"/>
+      <c r="AA32" s="49"/>
+      <c r="AB32" s="49"/>
+      <c r="AC32" s="49"/>
+      <c r="AD32" s="49"/>
+      <c r="AE32" s="49"/>
+      <c r="AF32" s="49"/>
+      <c r="AG32" s="49"/>
+      <c r="AH32" s="49"/>
+      <c r="AI32" s="49"/>
+      <c r="AJ32" s="52"/>
+      <c r="AK32" s="52"/>
+      <c r="AL32" s="52"/>
+      <c r="AM32" s="52"/>
+      <c r="AN32" s="52"/>
+      <c r="AO32" s="52"/>
+      <c r="AP32" s="52"/>
+      <c r="AQ32" s="52"/>
+      <c r="AR32" s="52"/>
+      <c r="AS32" s="43"/>
+      <c r="AT32" s="43"/>
+      <c r="AU32" s="46"/>
     </row>
     <row r="33" spans="1:47" ht="18" customHeight="1">
       <c r="A33" s="42"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="49"/>
-      <c r="M33" s="49"/>
-      <c r="N33" s="49"/>
-      <c r="O33" s="49"/>
-      <c r="P33" s="49"/>
-      <c r="Q33" s="49"/>
-      <c r="R33" s="49"/>
-      <c r="S33" s="49"/>
-      <c r="T33" s="49"/>
-      <c r="U33" s="49"/>
-      <c r="V33" s="49"/>
-      <c r="W33" s="49"/>
-      <c r="X33" s="49"/>
-      <c r="Y33" s="49"/>
-      <c r="Z33" s="49"/>
-      <c r="AA33" s="49"/>
-      <c r="AB33" s="49"/>
-      <c r="AC33" s="49"/>
-      <c r="AD33" s="49"/>
-      <c r="AE33" s="49"/>
-      <c r="AF33" s="49"/>
-      <c r="AG33" s="49"/>
-      <c r="AH33" s="49"/>
-      <c r="AI33" s="49"/>
-      <c r="AJ33" s="49"/>
-      <c r="AK33" s="49"/>
-      <c r="AL33" s="49"/>
-      <c r="AM33" s="49"/>
-      <c r="AN33" s="49"/>
-      <c r="AO33" s="49"/>
-      <c r="AP33" s="49"/>
-      <c r="AQ33" s="49"/>
-      <c r="AR33" s="49"/>
-      <c r="AU33" s="44"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="53"/>
+      <c r="T33" s="53"/>
+      <c r="U33" s="53"/>
+      <c r="V33" s="53"/>
+      <c r="W33" s="53"/>
+      <c r="X33" s="53"/>
+      <c r="Y33" s="53"/>
+      <c r="Z33" s="53"/>
+      <c r="AA33" s="53"/>
+      <c r="AB33" s="53"/>
+      <c r="AC33" s="53"/>
+      <c r="AD33" s="53"/>
+      <c r="AE33" s="53"/>
+      <c r="AF33" s="53"/>
+      <c r="AG33" s="53"/>
+      <c r="AH33" s="53"/>
+      <c r="AI33" s="53"/>
+      <c r="AJ33" s="53"/>
+      <c r="AK33" s="53"/>
+      <c r="AL33" s="53"/>
+      <c r="AM33" s="53"/>
+      <c r="AN33" s="53"/>
+      <c r="AO33" s="53"/>
+      <c r="AP33" s="53"/>
+      <c r="AQ33" s="53"/>
+      <c r="AR33" s="53"/>
+      <c r="AS33" s="43"/>
+      <c r="AT33" s="43"/>
+      <c r="AU33" s="46"/>
     </row>
     <row r="34" spans="1:47" ht="9.75" customHeight="1">
       <c r="A34" s="42"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="49"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="49"/>
-      <c r="P34" s="49"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="49"/>
-      <c r="S34" s="49"/>
-      <c r="T34" s="49"/>
-      <c r="U34" s="49"/>
-      <c r="V34" s="49"/>
-      <c r="W34" s="49"/>
-      <c r="X34" s="49"/>
-      <c r="Y34" s="49"/>
-      <c r="Z34" s="49"/>
-      <c r="AA34" s="49"/>
-      <c r="AB34" s="49"/>
-      <c r="AC34" s="49"/>
-      <c r="AD34" s="49"/>
-      <c r="AE34" s="49"/>
-      <c r="AF34" s="49"/>
-      <c r="AG34" s="49"/>
-      <c r="AH34" s="49"/>
-      <c r="AI34" s="49"/>
-      <c r="AJ34" s="49"/>
-      <c r="AK34" s="49"/>
-      <c r="AL34" s="49"/>
-      <c r="AM34" s="49"/>
-      <c r="AN34" s="49"/>
-      <c r="AO34" s="49"/>
-      <c r="AP34" s="49"/>
-      <c r="AQ34" s="49"/>
-      <c r="AR34" s="49"/>
-      <c r="AU34" s="44"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="53"/>
+      <c r="Q34" s="53"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="53"/>
+      <c r="T34" s="53"/>
+      <c r="U34" s="53"/>
+      <c r="V34" s="53"/>
+      <c r="W34" s="53"/>
+      <c r="X34" s="53"/>
+      <c r="Y34" s="53"/>
+      <c r="Z34" s="53"/>
+      <c r="AA34" s="53"/>
+      <c r="AB34" s="53"/>
+      <c r="AC34" s="53"/>
+      <c r="AD34" s="53"/>
+      <c r="AE34" s="53"/>
+      <c r="AF34" s="53"/>
+      <c r="AG34" s="53"/>
+      <c r="AH34" s="53"/>
+      <c r="AI34" s="53"/>
+      <c r="AJ34" s="53"/>
+      <c r="AK34" s="53"/>
+      <c r="AL34" s="53"/>
+      <c r="AM34" s="53"/>
+      <c r="AN34" s="53"/>
+      <c r="AO34" s="53"/>
+      <c r="AP34" s="53"/>
+      <c r="AQ34" s="53"/>
+      <c r="AR34" s="53"/>
+      <c r="AS34" s="43"/>
+      <c r="AT34" s="43"/>
+      <c r="AU34" s="46"/>
     </row>
     <row r="35" spans="1:47" ht="16.5">
       <c r="A35" s="42"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="49"/>
-      <c r="S35" s="49"/>
-      <c r="T35" s="49"/>
-      <c r="U35" s="49"/>
-      <c r="V35" s="49"/>
-      <c r="W35" s="49"/>
-      <c r="X35" s="49"/>
-      <c r="Y35" s="49"/>
-      <c r="Z35" s="49"/>
-      <c r="AA35" s="49"/>
-      <c r="AB35" s="49"/>
-      <c r="AC35" s="49"/>
-      <c r="AD35" s="49"/>
-      <c r="AE35" s="49"/>
-      <c r="AF35" s="49"/>
-      <c r="AG35" s="49"/>
-      <c r="AH35" s="49"/>
-      <c r="AI35" s="49"/>
-      <c r="AJ35" s="49"/>
-      <c r="AK35" s="49"/>
-      <c r="AL35" s="49"/>
-      <c r="AM35" s="49"/>
-      <c r="AN35" s="49"/>
-      <c r="AO35" s="49"/>
-      <c r="AP35" s="49"/>
-      <c r="AQ35" s="49"/>
-      <c r="AR35" s="49"/>
-      <c r="AU35" s="44"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="53"/>
+      <c r="Q35" s="53"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="53"/>
+      <c r="T35" s="53"/>
+      <c r="U35" s="53"/>
+      <c r="V35" s="53"/>
+      <c r="W35" s="53"/>
+      <c r="X35" s="53"/>
+      <c r="Y35" s="53"/>
+      <c r="Z35" s="53"/>
+      <c r="AA35" s="53"/>
+      <c r="AB35" s="53"/>
+      <c r="AC35" s="53"/>
+      <c r="AD35" s="53"/>
+      <c r="AE35" s="53"/>
+      <c r="AF35" s="53"/>
+      <c r="AG35" s="53"/>
+      <c r="AH35" s="53"/>
+      <c r="AI35" s="53"/>
+      <c r="AJ35" s="53"/>
+      <c r="AK35" s="53"/>
+      <c r="AL35" s="53"/>
+      <c r="AM35" s="53"/>
+      <c r="AN35" s="53"/>
+      <c r="AO35" s="53"/>
+      <c r="AP35" s="53"/>
+      <c r="AQ35" s="53"/>
+      <c r="AR35" s="53"/>
+      <c r="AS35" s="43"/>
+      <c r="AT35" s="43"/>
+      <c r="AU35" s="46"/>
     </row>
     <row r="36" spans="1:47" ht="16.5">
       <c r="A36" s="42"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="49"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="49"/>
-      <c r="T36" s="49"/>
-      <c r="U36" s="49"/>
-      <c r="V36" s="49"/>
-      <c r="W36" s="49"/>
-      <c r="X36" s="49"/>
-      <c r="Y36" s="49"/>
-      <c r="Z36" s="49"/>
-      <c r="AA36" s="49"/>
-      <c r="AB36" s="49"/>
-      <c r="AC36" s="49"/>
-      <c r="AD36" s="49"/>
-      <c r="AE36" s="49"/>
-      <c r="AF36" s="49"/>
-      <c r="AG36" s="49"/>
-      <c r="AH36" s="49"/>
-      <c r="AI36" s="49"/>
-      <c r="AJ36" s="49"/>
-      <c r="AK36" s="49"/>
-      <c r="AL36" s="49"/>
-      <c r="AM36" s="49"/>
-      <c r="AN36" s="49"/>
-      <c r="AO36" s="49"/>
-      <c r="AP36" s="49"/>
-      <c r="AQ36" s="49"/>
-      <c r="AR36" s="49"/>
-      <c r="AU36" s="44"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="53"/>
+      <c r="Q36" s="53"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="53"/>
+      <c r="T36" s="53"/>
+      <c r="U36" s="53"/>
+      <c r="V36" s="53"/>
+      <c r="W36" s="53"/>
+      <c r="X36" s="53"/>
+      <c r="Y36" s="53"/>
+      <c r="Z36" s="53"/>
+      <c r="AA36" s="53"/>
+      <c r="AB36" s="53"/>
+      <c r="AC36" s="53"/>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="53"/>
+      <c r="AF36" s="53"/>
+      <c r="AG36" s="53"/>
+      <c r="AH36" s="53"/>
+      <c r="AI36" s="53"/>
+      <c r="AJ36" s="53"/>
+      <c r="AK36" s="53"/>
+      <c r="AL36" s="53"/>
+      <c r="AM36" s="53"/>
+      <c r="AN36" s="53"/>
+      <c r="AO36" s="53"/>
+      <c r="AP36" s="53"/>
+      <c r="AQ36" s="53"/>
+      <c r="AR36" s="53"/>
+      <c r="AS36" s="43"/>
+      <c r="AT36" s="43"/>
+      <c r="AU36" s="46"/>
     </row>
     <row r="37" spans="1:47" ht="12" customHeight="1">
       <c r="A37" s="42"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="49"/>
-      <c r="W37" s="49"/>
-      <c r="X37" s="49"/>
-      <c r="Y37" s="49"/>
-      <c r="Z37" s="49"/>
-      <c r="AA37" s="49"/>
-      <c r="AB37" s="49"/>
-      <c r="AC37" s="49"/>
-      <c r="AD37" s="49"/>
-      <c r="AE37" s="49"/>
-      <c r="AF37" s="49"/>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
-      <c r="AM37" s="49"/>
-      <c r="AN37" s="49"/>
-      <c r="AO37" s="49"/>
-      <c r="AP37" s="49"/>
-      <c r="AQ37" s="49"/>
-      <c r="AR37" s="49"/>
-      <c r="AU37" s="44"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="53"/>
+      <c r="U37" s="53"/>
+      <c r="V37" s="53"/>
+      <c r="W37" s="53"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
+      <c r="AA37" s="53"/>
+      <c r="AB37" s="53"/>
+      <c r="AC37" s="53"/>
+      <c r="AD37" s="53"/>
+      <c r="AE37" s="53"/>
+      <c r="AF37" s="53"/>
+      <c r="AG37" s="53"/>
+      <c r="AH37" s="53"/>
+      <c r="AI37" s="53"/>
+      <c r="AJ37" s="53"/>
+      <c r="AK37" s="53"/>
+      <c r="AL37" s="53"/>
+      <c r="AM37" s="53"/>
+      <c r="AN37" s="53"/>
+      <c r="AO37" s="53"/>
+      <c r="AP37" s="53"/>
+      <c r="AQ37" s="53"/>
+      <c r="AR37" s="53"/>
+      <c r="AS37" s="43"/>
+      <c r="AT37" s="43"/>
+      <c r="AU37" s="46"/>
     </row>
     <row r="38" spans="1:47" ht="16.5">
       <c r="A38" s="42"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="49"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
-      <c r="U38" s="49"/>
-      <c r="V38" s="49"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
-      <c r="Z38" s="49"/>
-      <c r="AA38" s="49"/>
-      <c r="AB38" s="49"/>
-      <c r="AC38" s="49"/>
-      <c r="AD38" s="49"/>
-      <c r="AE38" s="49"/>
-      <c r="AF38" s="49"/>
-      <c r="AG38" s="49"/>
-      <c r="AH38" s="49"/>
-      <c r="AI38" s="49"/>
-      <c r="AJ38" s="49"/>
-      <c r="AK38" s="49"/>
-      <c r="AL38" s="49"/>
-      <c r="AM38" s="49"/>
-      <c r="AN38" s="49"/>
-      <c r="AO38" s="49"/>
-      <c r="AP38" s="49"/>
-      <c r="AQ38" s="49"/>
-      <c r="AR38" s="49"/>
-      <c r="AU38" s="44"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="53"/>
+      <c r="N38" s="53"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="53"/>
+      <c r="Q38" s="53"/>
+      <c r="R38" s="53"/>
+      <c r="S38" s="53"/>
+      <c r="T38" s="53"/>
+      <c r="U38" s="53"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="53"/>
+      <c r="X38" s="53"/>
+      <c r="Y38" s="53"/>
+      <c r="Z38" s="53"/>
+      <c r="AA38" s="53"/>
+      <c r="AB38" s="53"/>
+      <c r="AC38" s="53"/>
+      <c r="AD38" s="53"/>
+      <c r="AE38" s="53"/>
+      <c r="AF38" s="53"/>
+      <c r="AG38" s="53"/>
+      <c r="AH38" s="53"/>
+      <c r="AI38" s="53"/>
+      <c r="AJ38" s="53"/>
+      <c r="AK38" s="53"/>
+      <c r="AL38" s="53"/>
+      <c r="AM38" s="53"/>
+      <c r="AN38" s="53"/>
+      <c r="AO38" s="53"/>
+      <c r="AP38" s="53"/>
+      <c r="AQ38" s="53"/>
+      <c r="AR38" s="53"/>
+      <c r="AS38" s="43"/>
+      <c r="AT38" s="43"/>
+      <c r="AU38" s="46"/>
     </row>
     <row r="39" spans="1:47" ht="16.5">
       <c r="A39" s="42"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="49"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="49"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="49"/>
-      <c r="U39" s="49"/>
-      <c r="V39" s="49"/>
-      <c r="W39" s="49"/>
-      <c r="X39" s="49"/>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AE39" s="49"/>
-      <c r="AF39" s="49"/>
-      <c r="AG39" s="49"/>
-      <c r="AH39" s="49"/>
-      <c r="AI39" s="49"/>
-      <c r="AJ39" s="49"/>
-      <c r="AK39" s="49"/>
-      <c r="AL39" s="49"/>
-      <c r="AM39" s="49"/>
-      <c r="AN39" s="49"/>
-      <c r="AO39" s="49"/>
-      <c r="AP39" s="49"/>
-      <c r="AQ39" s="49"/>
-      <c r="AR39" s="49"/>
-      <c r="AU39" s="44"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="53"/>
+      <c r="N39" s="53"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="53"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="53"/>
+      <c r="S39" s="53"/>
+      <c r="T39" s="53"/>
+      <c r="U39" s="53"/>
+      <c r="V39" s="53"/>
+      <c r="W39" s="53"/>
+      <c r="X39" s="53"/>
+      <c r="Y39" s="53"/>
+      <c r="Z39" s="53"/>
+      <c r="AA39" s="53"/>
+      <c r="AB39" s="53"/>
+      <c r="AC39" s="53"/>
+      <c r="AD39" s="53"/>
+      <c r="AE39" s="53"/>
+      <c r="AF39" s="53"/>
+      <c r="AG39" s="53"/>
+      <c r="AH39" s="53"/>
+      <c r="AI39" s="53"/>
+      <c r="AJ39" s="53"/>
+      <c r="AK39" s="53"/>
+      <c r="AL39" s="53"/>
+      <c r="AM39" s="53"/>
+      <c r="AN39" s="53"/>
+      <c r="AO39" s="53"/>
+      <c r="AP39" s="53"/>
+      <c r="AQ39" s="53"/>
+      <c r="AR39" s="53"/>
+      <c r="AS39" s="43"/>
+      <c r="AT39" s="43"/>
+      <c r="AU39" s="46"/>
     </row>
     <row r="40" spans="1:47" ht="16.5">
       <c r="A40" s="42"/>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="49"/>
-      <c r="N40" s="49"/>
-      <c r="O40" s="49"/>
-      <c r="P40" s="49"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="49"/>
-      <c r="S40" s="49"/>
-      <c r="T40" s="49"/>
-      <c r="U40" s="49"/>
-      <c r="V40" s="49"/>
-      <c r="W40" s="49"/>
-      <c r="X40" s="49"/>
-      <c r="Y40" s="49"/>
-      <c r="Z40" s="49"/>
-      <c r="AA40" s="49"/>
-      <c r="AB40" s="49"/>
-      <c r="AC40" s="49"/>
-      <c r="AD40" s="49"/>
-      <c r="AE40" s="49"/>
-      <c r="AF40" s="49"/>
-      <c r="AG40" s="49"/>
-      <c r="AH40" s="49"/>
-      <c r="AI40" s="49"/>
-      <c r="AJ40" s="49"/>
-      <c r="AK40" s="49"/>
-      <c r="AL40" s="49"/>
-      <c r="AM40" s="49"/>
-      <c r="AN40" s="49"/>
-      <c r="AO40" s="49"/>
-      <c r="AP40" s="49"/>
-      <c r="AQ40" s="49"/>
-      <c r="AR40" s="49"/>
-      <c r="AU40" s="44"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="53"/>
+      <c r="N40" s="53"/>
+      <c r="O40" s="53"/>
+      <c r="P40" s="53"/>
+      <c r="Q40" s="53"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="53"/>
+      <c r="T40" s="53"/>
+      <c r="U40" s="53"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="53"/>
+      <c r="X40" s="53"/>
+      <c r="Y40" s="53"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="53"/>
+      <c r="AC40" s="53"/>
+      <c r="AD40" s="53"/>
+      <c r="AE40" s="53"/>
+      <c r="AF40" s="53"/>
+      <c r="AG40" s="53"/>
+      <c r="AH40" s="53"/>
+      <c r="AI40" s="53"/>
+      <c r="AJ40" s="53"/>
+      <c r="AK40" s="53"/>
+      <c r="AL40" s="53"/>
+      <c r="AM40" s="53"/>
+      <c r="AN40" s="53"/>
+      <c r="AO40" s="53"/>
+      <c r="AP40" s="53"/>
+      <c r="AQ40" s="53"/>
+      <c r="AR40" s="53"/>
+      <c r="AS40" s="43"/>
+      <c r="AT40" s="43"/>
+      <c r="AU40" s="46"/>
     </row>
     <row r="41" spans="1:47" ht="16.5">
       <c r="A41" s="42"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="49"/>
-      <c r="N41" s="49"/>
-      <c r="O41" s="49"/>
-      <c r="P41" s="49"/>
-      <c r="Q41" s="49"/>
-      <c r="R41" s="49"/>
-      <c r="S41" s="49"/>
-      <c r="T41" s="49"/>
-      <c r="U41" s="49"/>
-      <c r="V41" s="49"/>
-      <c r="W41" s="49"/>
-      <c r="X41" s="49"/>
-      <c r="Y41" s="49"/>
-      <c r="Z41" s="49"/>
-      <c r="AA41" s="49"/>
-      <c r="AB41" s="49"/>
-      <c r="AC41" s="49"/>
-      <c r="AD41" s="49"/>
-      <c r="AE41" s="49"/>
-      <c r="AF41" s="49"/>
-      <c r="AG41" s="49"/>
-      <c r="AH41" s="49"/>
-      <c r="AI41" s="49"/>
-      <c r="AJ41" s="49"/>
-      <c r="AK41" s="49"/>
-      <c r="AL41" s="49"/>
-      <c r="AM41" s="49"/>
-      <c r="AN41" s="49"/>
-      <c r="AO41" s="49"/>
-      <c r="AP41" s="49"/>
-      <c r="AQ41" s="49"/>
-      <c r="AR41" s="49"/>
-      <c r="AU41" s="44"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="53"/>
+      <c r="N41" s="53"/>
+      <c r="O41" s="53"/>
+      <c r="P41" s="53"/>
+      <c r="Q41" s="53"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="53"/>
+      <c r="T41" s="53"/>
+      <c r="U41" s="53"/>
+      <c r="V41" s="53"/>
+      <c r="W41" s="53"/>
+      <c r="X41" s="53"/>
+      <c r="Y41" s="53"/>
+      <c r="Z41" s="53"/>
+      <c r="AA41" s="53"/>
+      <c r="AB41" s="53"/>
+      <c r="AC41" s="53"/>
+      <c r="AD41" s="53"/>
+      <c r="AE41" s="53"/>
+      <c r="AF41" s="53"/>
+      <c r="AG41" s="53"/>
+      <c r="AH41" s="53"/>
+      <c r="AI41" s="53"/>
+      <c r="AJ41" s="53"/>
+      <c r="AK41" s="53"/>
+      <c r="AL41" s="53"/>
+      <c r="AM41" s="53"/>
+      <c r="AN41" s="53"/>
+      <c r="AO41" s="53"/>
+      <c r="AP41" s="53"/>
+      <c r="AQ41" s="53"/>
+      <c r="AR41" s="53"/>
+      <c r="AS41" s="43"/>
+      <c r="AT41" s="43"/>
+      <c r="AU41" s="46"/>
     </row>
     <row r="42" spans="1:47" ht="21.75" customHeight="1">
       <c r="A42" s="42"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="67"/>
-      <c r="K42" s="67"/>
-      <c r="L42" s="67"/>
-      <c r="M42" s="67"/>
-      <c r="N42" s="67"/>
-      <c r="O42" s="67"/>
-      <c r="P42" s="67"/>
-      <c r="Q42" s="67"/>
-      <c r="R42" s="67"/>
-      <c r="S42" s="67"/>
-      <c r="T42" s="67"/>
-      <c r="U42" s="67"/>
-      <c r="V42" s="67"/>
-      <c r="W42" s="67"/>
-      <c r="X42" s="67"/>
-      <c r="Y42" s="67"/>
-      <c r="Z42" s="67"/>
-      <c r="AA42" s="67"/>
-      <c r="AB42" s="67"/>
-      <c r="AC42" s="67"/>
-      <c r="AD42" s="67"/>
-      <c r="AE42" s="67"/>
-      <c r="AF42" s="67"/>
-      <c r="AG42" s="67"/>
-      <c r="AH42" s="67"/>
-      <c r="AI42" s="67"/>
-      <c r="AJ42" s="67"/>
-      <c r="AK42" s="67"/>
-      <c r="AL42" s="67"/>
-      <c r="AM42" s="67"/>
-      <c r="AN42" s="67"/>
-      <c r="AO42" s="67"/>
-      <c r="AP42" s="67"/>
-      <c r="AQ42" s="67"/>
-      <c r="AR42" s="67"/>
-      <c r="AU42" s="44"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="74"/>
+      <c r="P42" s="74"/>
+      <c r="Q42" s="74"/>
+      <c r="R42" s="74"/>
+      <c r="S42" s="74"/>
+      <c r="T42" s="74"/>
+      <c r="U42" s="74"/>
+      <c r="V42" s="74"/>
+      <c r="W42" s="74"/>
+      <c r="X42" s="74"/>
+      <c r="Y42" s="74"/>
+      <c r="Z42" s="74"/>
+      <c r="AA42" s="74"/>
+      <c r="AB42" s="74"/>
+      <c r="AC42" s="74"/>
+      <c r="AD42" s="74"/>
+      <c r="AE42" s="74"/>
+      <c r="AF42" s="74"/>
+      <c r="AG42" s="74"/>
+      <c r="AH42" s="74"/>
+      <c r="AI42" s="74"/>
+      <c r="AJ42" s="74"/>
+      <c r="AK42" s="74"/>
+      <c r="AL42" s="74"/>
+      <c r="AM42" s="74"/>
+      <c r="AN42" s="74"/>
+      <c r="AO42" s="74"/>
+      <c r="AP42" s="74"/>
+      <c r="AQ42" s="74"/>
+      <c r="AR42" s="74"/>
+      <c r="AS42" s="43"/>
+      <c r="AT42" s="43"/>
+      <c r="AU42" s="46"/>
     </row>
     <row r="43" spans="1:47" ht="16.5">
       <c r="A43" s="42"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="49"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="49"/>
-      <c r="T43" s="49"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="49"/>
-      <c r="W43" s="49"/>
-      <c r="X43" s="49"/>
-      <c r="Y43" s="49"/>
-      <c r="Z43" s="49"/>
-      <c r="AA43" s="49"/>
-      <c r="AB43" s="49"/>
-      <c r="AC43" s="49"/>
-      <c r="AD43" s="49"/>
-      <c r="AE43" s="49"/>
-      <c r="AF43" s="49"/>
-      <c r="AG43" s="49"/>
-      <c r="AH43" s="49"/>
-      <c r="AI43" s="49"/>
-      <c r="AJ43" s="49"/>
-      <c r="AK43" s="49"/>
-      <c r="AL43" s="49"/>
-      <c r="AM43" s="49"/>
-      <c r="AN43" s="49"/>
-      <c r="AO43" s="49"/>
-      <c r="AP43" s="49"/>
-      <c r="AQ43" s="49"/>
-      <c r="AR43" s="49"/>
-      <c r="AU43" s="44"/>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="53"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="53"/>
+      <c r="P43" s="53"/>
+      <c r="Q43" s="53"/>
+      <c r="R43" s="53"/>
+      <c r="S43" s="53"/>
+      <c r="T43" s="53"/>
+      <c r="U43" s="53"/>
+      <c r="V43" s="53"/>
+      <c r="W43" s="53"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="53"/>
+      <c r="AA43" s="53"/>
+      <c r="AB43" s="53"/>
+      <c r="AC43" s="53"/>
+      <c r="AD43" s="53"/>
+      <c r="AE43" s="53"/>
+      <c r="AF43" s="53"/>
+      <c r="AG43" s="53"/>
+      <c r="AH43" s="53"/>
+      <c r="AI43" s="53"/>
+      <c r="AJ43" s="53"/>
+      <c r="AK43" s="53"/>
+      <c r="AL43" s="53"/>
+      <c r="AM43" s="53"/>
+      <c r="AN43" s="53"/>
+      <c r="AO43" s="53"/>
+      <c r="AP43" s="53"/>
+      <c r="AQ43" s="53"/>
+      <c r="AR43" s="53"/>
+      <c r="AS43" s="43"/>
+      <c r="AT43" s="43"/>
+      <c r="AU43" s="46"/>
     </row>
     <row r="44" spans="1:47" ht="11.25" customHeight="1">
       <c r="A44" s="42"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="49"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="49"/>
-      <c r="M44" s="49"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="49"/>
-      <c r="P44" s="49"/>
-      <c r="Q44" s="49"/>
-      <c r="R44" s="49"/>
-      <c r="S44" s="49"/>
-      <c r="T44" s="68"/>
-      <c r="U44" s="49"/>
-      <c r="V44" s="49"/>
-      <c r="W44" s="49"/>
-      <c r="X44" s="49"/>
-      <c r="Y44" s="49"/>
-      <c r="Z44" s="47"/>
-      <c r="AA44" s="49"/>
-      <c r="AB44" s="49"/>
-      <c r="AC44" s="49"/>
-      <c r="AD44" s="49"/>
-      <c r="AE44" s="49"/>
-      <c r="AF44" s="49"/>
-      <c r="AG44" s="49"/>
-      <c r="AH44" s="49"/>
-      <c r="AI44" s="49"/>
-      <c r="AJ44" s="49"/>
-      <c r="AK44" s="49"/>
-      <c r="AL44" s="49"/>
-      <c r="AM44" s="49"/>
-      <c r="AN44" s="68"/>
-      <c r="AO44" s="49"/>
-      <c r="AP44" s="49"/>
-      <c r="AQ44" s="49"/>
-      <c r="AR44" s="49"/>
-      <c r="AU44" s="44"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="53"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="53"/>
+      <c r="P44" s="53"/>
+      <c r="Q44" s="53"/>
+      <c r="R44" s="53"/>
+      <c r="S44" s="53"/>
+      <c r="T44" s="75"/>
+      <c r="U44" s="53"/>
+      <c r="V44" s="53"/>
+      <c r="W44" s="53"/>
+      <c r="X44" s="53"/>
+      <c r="Y44" s="53"/>
+      <c r="Z44" s="67"/>
+      <c r="AA44" s="53"/>
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="53"/>
+      <c r="AD44" s="53"/>
+      <c r="AE44" s="53"/>
+      <c r="AF44" s="53"/>
+      <c r="AG44" s="53"/>
+      <c r="AH44" s="53"/>
+      <c r="AI44" s="53"/>
+      <c r="AJ44" s="53"/>
+      <c r="AK44" s="53"/>
+      <c r="AL44" s="53"/>
+      <c r="AM44" s="53"/>
+      <c r="AN44" s="75"/>
+      <c r="AO44" s="53"/>
+      <c r="AP44" s="53"/>
+      <c r="AQ44" s="53"/>
+      <c r="AR44" s="53"/>
+      <c r="AS44" s="43"/>
+      <c r="AT44" s="43"/>
+      <c r="AU44" s="46"/>
     </row>
     <row r="45" spans="1:47">
       <c r="A45" s="42"/>
-      <c r="AU45" s="44"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="43"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="43"/>
+      <c r="O45" s="43"/>
+      <c r="P45" s="43"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="43"/>
+      <c r="Z45" s="43"/>
+      <c r="AA45" s="43"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="43"/>
+      <c r="AD45" s="43"/>
+      <c r="AE45" s="43"/>
+      <c r="AF45" s="43"/>
+      <c r="AG45" s="43"/>
+      <c r="AH45" s="43"/>
+      <c r="AI45" s="43"/>
+      <c r="AJ45" s="43"/>
+      <c r="AK45" s="43"/>
+      <c r="AL45" s="43"/>
+      <c r="AM45" s="43"/>
+      <c r="AN45" s="43"/>
+      <c r="AO45" s="43"/>
+      <c r="AP45" s="43"/>
+      <c r="AQ45" s="43"/>
+      <c r="AR45" s="43"/>
+      <c r="AS45" s="43"/>
+      <c r="AT45" s="43"/>
+      <c r="AU45" s="46"/>
     </row>
     <row r="46" spans="1:47" ht="6.75" customHeight="1">
       <c r="A46" s="42"/>
-      <c r="AU46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="44"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="44"/>
+      <c r="P46" s="44"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="44"/>
+      <c r="S46" s="44"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="44"/>
+      <c r="V46" s="44"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
+      <c r="Y46" s="44"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
+      <c r="AB46" s="44"/>
+      <c r="AC46" s="44"/>
+      <c r="AD46" s="44"/>
+      <c r="AE46" s="44"/>
+      <c r="AF46" s="44"/>
+      <c r="AG46" s="44"/>
+      <c r="AH46" s="44"/>
+      <c r="AI46" s="44"/>
+      <c r="AJ46" s="44"/>
+      <c r="AK46" s="44"/>
+      <c r="AL46" s="44"/>
+      <c r="AM46" s="44"/>
+      <c r="AN46" s="44"/>
+      <c r="AO46" s="44"/>
+      <c r="AP46" s="44"/>
+      <c r="AQ46" s="44"/>
+      <c r="AR46" s="44"/>
+      <c r="AS46" s="44"/>
+      <c r="AT46" s="44"/>
+      <c r="AU46" s="46"/>
     </row>
     <row r="47" spans="1:47" ht="5.0999999999999996" customHeight="1">
-      <c r="A47" s="69"/>
-      <c r="AU47" s="70"/>
+      <c r="A47" s="76"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="44"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="44"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="44"/>
+      <c r="U47" s="44"/>
+      <c r="V47" s="44"/>
+      <c r="W47" s="44"/>
+      <c r="X47" s="44"/>
+      <c r="Y47" s="44"/>
+      <c r="Z47" s="44"/>
+      <c r="AA47" s="44"/>
+      <c r="AB47" s="44"/>
+      <c r="AC47" s="44"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="44"/>
+      <c r="AF47" s="44"/>
+      <c r="AG47" s="44"/>
+      <c r="AH47" s="44"/>
+      <c r="AI47" s="44"/>
+      <c r="AJ47" s="44"/>
+      <c r="AK47" s="44"/>
+      <c r="AL47" s="44"/>
+      <c r="AM47" s="44"/>
+      <c r="AN47" s="44"/>
+      <c r="AO47" s="44"/>
+      <c r="AP47" s="44"/>
+      <c r="AQ47" s="44"/>
+      <c r="AR47" s="44"/>
+      <c r="AS47" s="44"/>
+      <c r="AT47" s="44"/>
+      <c r="AU47" s="77"/>
     </row>
     <row r="48" spans="1:47" ht="6" customHeight="1">
-      <c r="A48" s="70"/>
-      <c r="AU48" s="70"/>
+      <c r="A48" s="78"/>
+      <c r="AU48" s="78"/>
     </row>
     <row r="49" spans="1:47" ht="18.75" customHeight="1">
-      <c r="A49" s="70"/>
-      <c r="AU49" s="70"/>
+      <c r="A49" s="78"/>
+      <c r="AU49" s="78"/>
     </row>
     <row r="50" spans="1:47" ht="18.75" customHeight="1">
-      <c r="A50" s="70"/>
-      <c r="AU50" s="70"/>
+      <c r="A50" s="78"/>
+      <c r="AU50" s="78"/>
     </row>
     <row r="51" spans="1:47" ht="7.5" customHeight="1">
-      <c r="A51" s="70"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="70"/>
-      <c r="K51" s="70"/>
-      <c r="L51" s="70"/>
-      <c r="M51" s="70"/>
-      <c r="N51" s="70"/>
-      <c r="O51" s="70"/>
-      <c r="P51" s="70"/>
-      <c r="Q51" s="70"/>
-      <c r="R51" s="70"/>
-      <c r="S51" s="70"/>
-      <c r="T51" s="70"/>
-      <c r="U51" s="70"/>
-      <c r="V51" s="70"/>
-      <c r="W51" s="70"/>
-      <c r="X51" s="70"/>
-      <c r="Y51" s="70"/>
-      <c r="Z51" s="70"/>
-      <c r="AA51" s="70"/>
-      <c r="AB51" s="70"/>
-      <c r="AC51" s="70"/>
-      <c r="AD51" s="70"/>
-      <c r="AE51" s="70"/>
-      <c r="AF51" s="70"/>
-      <c r="AG51" s="70"/>
-      <c r="AH51" s="70"/>
-      <c r="AI51" s="70"/>
-      <c r="AJ51" s="70"/>
-      <c r="AK51" s="70"/>
-      <c r="AL51" s="70"/>
-      <c r="AM51" s="70"/>
-      <c r="AN51" s="70"/>
-      <c r="AO51" s="70"/>
-      <c r="AP51" s="70"/>
-      <c r="AQ51" s="70"/>
-      <c r="AR51" s="70"/>
-      <c r="AS51" s="70"/>
-      <c r="AT51" s="70"/>
-      <c r="AU51" s="70"/>
+      <c r="A51" s="78"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="78"/>
+      <c r="H51" s="78"/>
+      <c r="I51" s="78"/>
+      <c r="J51" s="78"/>
+      <c r="K51" s="78"/>
+      <c r="L51" s="78"/>
+      <c r="M51" s="78"/>
+      <c r="N51" s="78"/>
+      <c r="O51" s="78"/>
+      <c r="P51" s="78"/>
+      <c r="Q51" s="78"/>
+      <c r="R51" s="78"/>
+      <c r="S51" s="78"/>
+      <c r="T51" s="78"/>
+      <c r="U51" s="78"/>
+      <c r="V51" s="78"/>
+      <c r="W51" s="78"/>
+      <c r="X51" s="78"/>
+      <c r="Y51" s="78"/>
+      <c r="Z51" s="78"/>
+      <c r="AA51" s="78"/>
+      <c r="AB51" s="78"/>
+      <c r="AC51" s="78"/>
+      <c r="AD51" s="78"/>
+      <c r="AE51" s="78"/>
+      <c r="AF51" s="78"/>
+      <c r="AG51" s="78"/>
+      <c r="AH51" s="78"/>
+      <c r="AI51" s="78"/>
+      <c r="AJ51" s="78"/>
+      <c r="AK51" s="78"/>
+      <c r="AL51" s="78"/>
+      <c r="AM51" s="78"/>
+      <c r="AN51" s="78"/>
+      <c r="AO51" s="78"/>
+      <c r="AP51" s="78"/>
+      <c r="AQ51" s="78"/>
+      <c r="AR51" s="78"/>
+      <c r="AS51" s="78"/>
+      <c r="AT51" s="78"/>
+      <c r="AU51" s="78"/>
     </row>
     <row r="56" spans="1:47" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:47" ht="14.25" customHeight="1">
-      <c r="A57" s="74"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="74"/>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
+      <c r="A57" s="232"/>
+      <c r="B57" s="232"/>
+      <c r="C57" s="232"/>
+      <c r="D57" s="232"/>
+      <c r="E57" s="232"/>
+      <c r="F57" s="232"/>
     </row>
     <row r="58" spans="1:47" ht="14.25" customHeight="1">
-      <c r="A58" s="74"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
+      <c r="A58" s="232"/>
+      <c r="B58" s="232"/>
+      <c r="C58" s="232"/>
+      <c r="D58" s="232"/>
+      <c r="E58" s="232"/>
+      <c r="F58" s="232"/>
     </row>
     <row r="59" spans="1:47">
-      <c r="A59" s="74"/>
-      <c r="B59" s="74"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
+      <c r="A59" s="232"/>
+      <c r="B59" s="232"/>
+      <c r="C59" s="232"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/server/src/main/resources/templates/confirmation_template.xlsx
+++ b/server/src/main/resources/templates/confirmation_template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\★★발송_2026_확인서, 견적서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dongwoo/code/academy-heungkuk-v2-/server/src/main/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F42ADB1-11FC-EE40-9A07-7E3A0C0FA662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="빈문서" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">빈문서!$A$1:$AU$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">준수사항!$A$1:$AU$51</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>흥국생명연수원 사용안내 확인서</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -333,12 +334,6 @@
     <t>9140643@heungkuklife.co.kr</t>
   </si>
   <si>
-    <t>2일(화)</t>
-  </si>
-  <si>
-    <t>3일(수)</t>
-  </si>
-  <si>
     <t>흥국생명연수원 이용시 준수사항 안내</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -358,18 +353,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="10">
-    <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="yyyy\.\ mm\.\ dd\ \(aaa\)"/>
-    <numFmt numFmtId="177" formatCode="dd&quot;일&quot;\(aaa\)"/>
-    <numFmt numFmtId="178" formatCode="###&quot;식&quot;"/>
-    <numFmt numFmtId="179" formatCode="##&quot;일&quot;"/>
-    <numFmt numFmtId="180" formatCode="yyyy&quot;년&quot;\ mm&quot;월&quot;\ dd&quot;일&quot;\(aaa\)"/>
-    <numFmt numFmtId="181" formatCode="###&quot;호&quot;"/>
-    <numFmt numFmtId="182" formatCode="yyyy\.\ mm\.\ dd"/>
-    <numFmt numFmtId="183" formatCode="###."/>
-    <numFmt numFmtId="184" formatCode="\(##&quot;실&quot;\)"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\.\ mm\.\ dd\ \(aaa\)"/>
+    <numFmt numFmtId="178" formatCode="dd&quot;일&quot;\(aaa\)"/>
+    <numFmt numFmtId="179" formatCode="###&quot;식&quot;"/>
+    <numFmt numFmtId="180" formatCode="##&quot;일&quot;"/>
+    <numFmt numFmtId="181" formatCode="yyyy&quot;년&quot;\ mm&quot;월&quot;\ dd&quot;일&quot;\(aaa\)"/>
+    <numFmt numFmtId="182" formatCode="###&quot;호&quot;"/>
+    <numFmt numFmtId="183" formatCode="yyyy\.\ mm\.\ dd"/>
+    <numFmt numFmtId="184" formatCode="###."/>
+    <numFmt numFmtId="185" formatCode="\(##&quot;실&quot;\)"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -1369,14 +1364,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="278">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1431,7 +1426,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1476,10 +1471,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1506,120 +1501,654 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="180" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="3" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1635,12 +2164,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1650,565 +2173,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="3" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="3" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -2585,8 +2556,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3771901" y="8362950"/>
-          <a:ext cx="838280" cy="685797"/>
+          <a:off x="3686176" y="8308975"/>
+          <a:ext cx="793830" cy="676272"/>
           <a:chOff x="6664676" y="2510740"/>
           <a:chExt cx="146177" cy="372923"/>
         </a:xfrm>
@@ -3081,8 +3052,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="314324" y="1457325"/>
-          <a:ext cx="733426" cy="390525"/>
+          <a:off x="323849" y="1438275"/>
+          <a:ext cx="723901" cy="390525"/>
           <a:chOff x="6664676" y="2510740"/>
           <a:chExt cx="146177" cy="372923"/>
         </a:xfrm>
@@ -3227,8 +3198,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="324701" y="2172505"/>
-          <a:ext cx="733426" cy="385993"/>
+          <a:off x="334226" y="2147105"/>
+          <a:ext cx="723901" cy="373293"/>
           <a:chOff x="6664676" y="2510740"/>
           <a:chExt cx="146177" cy="372923"/>
         </a:xfrm>
@@ -3373,8 +3344,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="285749" y="5867400"/>
-          <a:ext cx="847726" cy="638175"/>
+          <a:off x="292099" y="5794375"/>
+          <a:ext cx="841376" cy="628650"/>
           <a:chOff x="6664676" y="2510740"/>
           <a:chExt cx="146177" cy="372923"/>
         </a:xfrm>
@@ -3519,8 +3490,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5543134" y="3903594"/>
-          <a:ext cx="590318" cy="326749"/>
+          <a:off x="5368509" y="3849619"/>
+          <a:ext cx="571268" cy="326749"/>
           <a:chOff x="6664676" y="2510740"/>
           <a:chExt cx="146177" cy="372923"/>
         </a:xfrm>
@@ -3657,7 +3628,7 @@
         <xdr:cNvPr id="24" name="그룹 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3665,8 +3636,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="305651" y="1829605"/>
-          <a:ext cx="733426" cy="385993"/>
+          <a:off x="315176" y="1810555"/>
+          <a:ext cx="723901" cy="379643"/>
           <a:chOff x="6664676" y="2510740"/>
           <a:chExt cx="146177" cy="372923"/>
         </a:xfrm>
@@ -3676,7 +3647,7 @@
           <xdr:cNvPr id="25" name="타원 24">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3727,7 +3698,7 @@
           <xdr:cNvPr id="26" name="1/2 액자 25">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -3805,20 +3776,32 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="그룹 1"/>
+        <xdr:cNvPr id="2" name="그룹 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="622979" y="8283"/>
-          <a:ext cx="359637" cy="628768"/>
+          <a:off x="607104" y="8283"/>
+          <a:ext cx="359637" cy="609718"/>
           <a:chOff x="615298" y="8283"/>
           <a:chExt cx="552103" cy="771336"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="3" name="그룹 2"/>
+          <xdr:cNvPr id="3" name="그룹 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -3831,7 +3814,13 @@
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="타원 4"/>
+            <xdr:cNvPr id="5" name="타원 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3876,7 +3865,13 @@
         </xdr:sp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="타원 5"/>
+            <xdr:cNvPr id="6" name="타원 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -3924,7 +3919,13 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="직사각형 3"/>
+          <xdr:cNvPr id="4" name="직사각형 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3987,20 +3988,32 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="7" name="그룹 6"/>
+        <xdr:cNvPr id="7" name="그룹 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5923847" y="8283"/>
-          <a:ext cx="626005" cy="628768"/>
+          <a:off x="5907972" y="8283"/>
+          <a:ext cx="626005" cy="609718"/>
           <a:chOff x="5464496" y="8283"/>
           <a:chExt cx="544889" cy="771336"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="8" name="그룹 7"/>
+          <xdr:cNvPr id="8" name="그룹 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -4013,7 +4026,13 @@
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="타원 9"/>
+            <xdr:cNvPr id="10" name="타원 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -4058,7 +4077,13 @@
         </xdr:sp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="타원 10"/>
+            <xdr:cNvPr id="11" name="타원 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -4106,7 +4131,13 @@
       </xdr:grpSp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="직사각형 8"/>
+          <xdr:cNvPr id="9" name="직사각형 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -4169,7 +4200,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="이등변 삼각형 11"/>
+        <xdr:cNvPr id="12" name="이등변 삼각형 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4345,7 +4382,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="이등변 삼각형 12"/>
+        <xdr:cNvPr id="13" name="이등변 삼각형 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4521,20 +4564,32 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="그룹 13"/>
+        <xdr:cNvPr id="14" name="그룹 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="676278" y="629777"/>
-          <a:ext cx="5272220" cy="2707749"/>
+          <a:off x="660403" y="610727"/>
+          <a:ext cx="5272220" cy="2679174"/>
           <a:chOff x="7228771" y="841569"/>
           <a:chExt cx="5159576" cy="2717274"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="15" name="Picture 2" descr="C:\Users\김충렬\Desktop\연수원지도.PNG"/>
+          <xdr:cNvPr id="15" name="Picture 2" descr="C:\Users\김충렬\Desktop\연수원지도.PNG">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
           </xdr:cNvPicPr>
@@ -4587,7 +4642,13 @@
       </xdr:pic>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="직사각형 15"/>
+          <xdr:cNvPr id="16" name="직사각형 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4758,7 +4819,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="17" name="직사각형 16"/>
+          <xdr:cNvPr id="17" name="직사각형 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -4929,7 +4996,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="직사각형 17"/>
+          <xdr:cNvPr id="18" name="직사각형 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5100,7 +5173,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="직사각형 18"/>
+          <xdr:cNvPr id="19" name="직사각형 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5271,7 +5350,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="직사각형 19"/>
+          <xdr:cNvPr id="20" name="직사각형 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5442,7 +5527,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="직사각형 20"/>
+          <xdr:cNvPr id="21" name="직사각형 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5655,7 +5746,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="직사각형 21"/>
+          <xdr:cNvPr id="22" name="직사각형 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -5868,7 +5965,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="직사각형 22"/>
+          <xdr:cNvPr id="23" name="직사각형 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr bwMode="auto">
@@ -6055,7 +6158,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="TextBox 11"/>
+        <xdr:cNvPr id="24" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6426,7 +6535,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="TextBox 11"/>
+        <xdr:cNvPr id="25" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6804,7 +6919,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="TextBox 11"/>
+        <xdr:cNvPr id="26" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7382,7 +7503,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="TextBox 11"/>
+        <xdr:cNvPr id="27" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7770,7 +7897,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="TextBox 11"/>
+        <xdr:cNvPr id="28" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8241,7 +8374,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="직사각형 28"/>
+        <xdr:cNvPr id="29" name="직사각형 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8907,7 +9046,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="TextBox 11"/>
+        <xdr:cNvPr id="30" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -9135,7 +9280,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="그림 30"/>
+        <xdr:cNvPr id="31" name="그림 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -9440,23 +9591,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="0.625" style="3" customWidth="1"/>
-    <col min="2" max="3" width="1.625" style="3" customWidth="1"/>
-    <col min="4" max="7" width="2.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="3.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="2.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="0.6640625" style="3" customWidth="1"/>
+    <col min="2" max="3" width="1.6640625" style="3" customWidth="1"/>
+    <col min="4" max="7" width="2.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="3.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="2.1640625" style="3" customWidth="1"/>
     <col min="10" max="10" width="2.5" style="3" customWidth="1"/>
-    <col min="11" max="39" width="1.75" style="3" customWidth="1"/>
-    <col min="40" max="40" width="2.75" style="3" customWidth="1"/>
-    <col min="41" max="43" width="1.75" style="3" customWidth="1"/>
-    <col min="44" max="44" width="1.875" style="3" customWidth="1"/>
-    <col min="45" max="45" width="3.625" style="3" customWidth="1"/>
-    <col min="46" max="46" width="1.625" style="3" customWidth="1"/>
-    <col min="47" max="47" width="0.625" style="3" customWidth="1"/>
+    <col min="11" max="39" width="1.6640625" style="3" customWidth="1"/>
+    <col min="40" max="40" width="2.6640625" style="3" customWidth="1"/>
+    <col min="41" max="43" width="1.6640625" style="3" customWidth="1"/>
+    <col min="44" max="44" width="1.83203125" style="3" customWidth="1"/>
+    <col min="45" max="45" width="3.6640625" style="3" customWidth="1"/>
+    <col min="46" max="46" width="1.6640625" style="3" customWidth="1"/>
+    <col min="47" max="47" width="0.6640625" style="3" customWidth="1"/>
     <col min="48" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -9518,39 +9669,39 @@
       <c r="F2" s="4"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="261" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="84"/>
-      <c r="S2" s="84"/>
-      <c r="T2" s="84"/>
-      <c r="U2" s="84"/>
-      <c r="V2" s="84"/>
-      <c r="W2" s="84"/>
-      <c r="X2" s="84"/>
-      <c r="Y2" s="84"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="84"/>
-      <c r="AE2" s="84"/>
-      <c r="AF2" s="84"/>
-      <c r="AG2" s="84"/>
-      <c r="AH2" s="84"/>
-      <c r="AI2" s="84"/>
-      <c r="AJ2" s="84"/>
-      <c r="AK2" s="84"/>
-      <c r="AL2" s="84"/>
-      <c r="AM2" s="84"/>
+      <c r="J2" s="262"/>
+      <c r="K2" s="262"/>
+      <c r="L2" s="262"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="262"/>
+      <c r="P2" s="262"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
+      <c r="AA2" s="262"/>
+      <c r="AB2" s="262"/>
+      <c r="AC2" s="262"/>
+      <c r="AD2" s="262"/>
+      <c r="AE2" s="262"/>
+      <c r="AF2" s="262"/>
+      <c r="AG2" s="262"/>
+      <c r="AH2" s="262"/>
+      <c r="AI2" s="262"/>
+      <c r="AJ2" s="262"/>
+      <c r="AK2" s="262"/>
+      <c r="AL2" s="262"/>
+      <c r="AM2" s="262"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
@@ -9568,37 +9719,37 @@
       <c r="E3" s="4"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="84"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="84"/>
-      <c r="AC3" s="84"/>
-      <c r="AD3" s="84"/>
-      <c r="AE3" s="84"/>
-      <c r="AF3" s="84"/>
-      <c r="AG3" s="84"/>
-      <c r="AH3" s="84"/>
-      <c r="AI3" s="84"/>
-      <c r="AJ3" s="84"/>
-      <c r="AK3" s="84"/>
-      <c r="AL3" s="84"/>
-      <c r="AM3" s="84"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="M3" s="262"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="262"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
+      <c r="AA3" s="262"/>
+      <c r="AB3" s="262"/>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="262"/>
+      <c r="AE3" s="262"/>
+      <c r="AF3" s="262"/>
+      <c r="AG3" s="262"/>
+      <c r="AH3" s="262"/>
+      <c r="AI3" s="262"/>
+      <c r="AJ3" s="262"/>
+      <c r="AK3" s="262"/>
+      <c r="AL3" s="262"/>
+      <c r="AM3" s="262"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
@@ -9615,39 +9766,39 @@
       <c r="E4" s="4"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="85" t="s">
+      <c r="I4" s="263" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="85"/>
-      <c r="W4" s="85"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="85"/>
-      <c r="Z4" s="85"/>
-      <c r="AA4" s="85"/>
-      <c r="AB4" s="85"/>
-      <c r="AC4" s="85"/>
-      <c r="AD4" s="85"/>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85"/>
-      <c r="AG4" s="85"/>
-      <c r="AH4" s="85"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="85"/>
-      <c r="AK4" s="85"/>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
+      <c r="J4" s="263"/>
+      <c r="K4" s="263"/>
+      <c r="L4" s="263"/>
+      <c r="M4" s="263"/>
+      <c r="N4" s="263"/>
+      <c r="O4" s="263"/>
+      <c r="P4" s="263"/>
+      <c r="Q4" s="263"/>
+      <c r="R4" s="263"/>
+      <c r="S4" s="263"/>
+      <c r="T4" s="263"/>
+      <c r="U4" s="263"/>
+      <c r="V4" s="263"/>
+      <c r="W4" s="263"/>
+      <c r="X4" s="263"/>
+      <c r="Y4" s="263"/>
+      <c r="Z4" s="263"/>
+      <c r="AA4" s="263"/>
+      <c r="AB4" s="263"/>
+      <c r="AC4" s="263"/>
+      <c r="AD4" s="263"/>
+      <c r="AE4" s="263"/>
+      <c r="AF4" s="263"/>
+      <c r="AG4" s="263"/>
+      <c r="AH4" s="263"/>
+      <c r="AI4" s="263"/>
+      <c r="AJ4" s="263"/>
+      <c r="AK4" s="263"/>
+      <c r="AL4" s="263"/>
+      <c r="AM4" s="263"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
@@ -9709,50 +9860,50 @@
       <c r="A6" s="1"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="86" t="s">
+      <c r="D6" s="195" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="89"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="89"/>
-      <c r="O6" s="89"/>
-      <c r="P6" s="89"/>
-      <c r="Q6" s="89"/>
-      <c r="R6" s="89"/>
-      <c r="S6" s="89"/>
-      <c r="T6" s="89"/>
-      <c r="U6" s="89"/>
-      <c r="V6" s="89"/>
-      <c r="W6" s="89"/>
-      <c r="X6" s="89"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="89"/>
-      <c r="AA6" s="89"/>
-      <c r="AB6" s="89"/>
-      <c r="AC6" s="89"/>
-      <c r="AD6" s="89"/>
-      <c r="AE6" s="89"/>
-      <c r="AF6" s="89"/>
-      <c r="AG6" s="89"/>
-      <c r="AH6" s="89"/>
-      <c r="AI6" s="89"/>
-      <c r="AJ6" s="89"/>
-      <c r="AK6" s="89"/>
-      <c r="AL6" s="90"/>
-      <c r="AM6" s="90"/>
-      <c r="AN6" s="90"/>
-      <c r="AO6" s="90"/>
-      <c r="AP6" s="90"/>
-      <c r="AQ6" s="90"/>
-      <c r="AR6" s="90"/>
-      <c r="AS6" s="90"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="264"/>
+      <c r="I6" s="265"/>
+      <c r="J6" s="265"/>
+      <c r="K6" s="265"/>
+      <c r="L6" s="265"/>
+      <c r="M6" s="265"/>
+      <c r="N6" s="265"/>
+      <c r="O6" s="265"/>
+      <c r="P6" s="265"/>
+      <c r="Q6" s="265"/>
+      <c r="R6" s="265"/>
+      <c r="S6" s="265"/>
+      <c r="T6" s="265"/>
+      <c r="U6" s="265"/>
+      <c r="V6" s="265"/>
+      <c r="W6" s="265"/>
+      <c r="X6" s="265"/>
+      <c r="Y6" s="265"/>
+      <c r="Z6" s="265"/>
+      <c r="AA6" s="265"/>
+      <c r="AB6" s="265"/>
+      <c r="AC6" s="265"/>
+      <c r="AD6" s="265"/>
+      <c r="AE6" s="265"/>
+      <c r="AF6" s="265"/>
+      <c r="AG6" s="265"/>
+      <c r="AH6" s="265"/>
+      <c r="AI6" s="265"/>
+      <c r="AJ6" s="265"/>
+      <c r="AK6" s="265"/>
+      <c r="AL6" s="266"/>
+      <c r="AM6" s="266"/>
+      <c r="AN6" s="266"/>
+      <c r="AO6" s="266"/>
+      <c r="AP6" s="266"/>
+      <c r="AQ6" s="266"/>
+      <c r="AR6" s="266"/>
+      <c r="AS6" s="266"/>
       <c r="AT6" s="4"/>
       <c r="AU6" s="1"/>
     </row>
@@ -9760,51 +9911,51 @@
       <c r="A7" s="1"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="197" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="81" t="s">
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+      <c r="G7" s="198"/>
+      <c r="H7" s="259" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81"/>
-      <c r="T7" s="81"/>
-      <c r="U7" s="81"/>
-      <c r="V7" s="81"/>
-      <c r="W7" s="81"/>
-      <c r="X7" s="81"/>
-      <c r="Y7" s="81"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="81"/>
-      <c r="AB7" s="81"/>
-      <c r="AC7" s="81"/>
-      <c r="AD7" s="81"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="81"/>
-      <c r="AG7" s="81"/>
-      <c r="AH7" s="81"/>
-      <c r="AI7" s="81"/>
-      <c r="AJ7" s="81"/>
-      <c r="AK7" s="81"/>
-      <c r="AL7" s="81"/>
-      <c r="AM7" s="81"/>
-      <c r="AN7" s="81"/>
-      <c r="AO7" s="81"/>
-      <c r="AP7" s="81"/>
-      <c r="AQ7" s="81"/>
-      <c r="AR7" s="82"/>
+      <c r="I7" s="259"/>
+      <c r="J7" s="259"/>
+      <c r="K7" s="259"/>
+      <c r="L7" s="259"/>
+      <c r="M7" s="259"/>
+      <c r="N7" s="259"/>
+      <c r="O7" s="259"/>
+      <c r="P7" s="259"/>
+      <c r="Q7" s="259"/>
+      <c r="R7" s="259"/>
+      <c r="S7" s="259"/>
+      <c r="T7" s="259"/>
+      <c r="U7" s="259"/>
+      <c r="V7" s="259"/>
+      <c r="W7" s="259"/>
+      <c r="X7" s="259"/>
+      <c r="Y7" s="259"/>
+      <c r="Z7" s="259"/>
+      <c r="AA7" s="259"/>
+      <c r="AB7" s="259"/>
+      <c r="AC7" s="259"/>
+      <c r="AD7" s="259"/>
+      <c r="AE7" s="259"/>
+      <c r="AF7" s="259"/>
+      <c r="AG7" s="259"/>
+      <c r="AH7" s="259"/>
+      <c r="AI7" s="259"/>
+      <c r="AJ7" s="259"/>
+      <c r="AK7" s="259"/>
+      <c r="AL7" s="259"/>
+      <c r="AM7" s="259"/>
+      <c r="AN7" s="259"/>
+      <c r="AO7" s="259"/>
+      <c r="AP7" s="259"/>
+      <c r="AQ7" s="259"/>
+      <c r="AR7" s="260"/>
       <c r="AS7" s="6"/>
       <c r="AT7" s="4"/>
       <c r="AU7" s="1"/>
@@ -9813,58 +9964,58 @@
       <c r="A8" s="1"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="197" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="102" t="s">
+      <c r="E8" s="198"/>
+      <c r="F8" s="198"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="253" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="103"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="104"/>
-      <c r="Q8" s="102" t="s">
+      <c r="I8" s="253"/>
+      <c r="J8" s="253"/>
+      <c r="K8" s="254"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="255"/>
+      <c r="N8" s="255"/>
+      <c r="O8" s="255"/>
+      <c r="P8" s="255"/>
+      <c r="Q8" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="105"/>
-      <c r="U8" s="106"/>
-      <c r="V8" s="106"/>
-      <c r="W8" s="106"/>
-      <c r="X8" s="106"/>
-      <c r="Y8" s="106"/>
-      <c r="Z8" s="106"/>
-      <c r="AA8" s="106"/>
-      <c r="AB8" s="106"/>
-      <c r="AC8" s="106"/>
-      <c r="AD8" s="106"/>
-      <c r="AE8" s="106"/>
-      <c r="AF8" s="106"/>
-      <c r="AG8" s="107"/>
-      <c r="AH8" s="102" t="s">
+      <c r="R8" s="253"/>
+      <c r="S8" s="253"/>
+      <c r="T8" s="256"/>
+      <c r="U8" s="257"/>
+      <c r="V8" s="257"/>
+      <c r="W8" s="257"/>
+      <c r="X8" s="257"/>
+      <c r="Y8" s="257"/>
+      <c r="Z8" s="257"/>
+      <c r="AA8" s="257"/>
+      <c r="AB8" s="257"/>
+      <c r="AC8" s="257"/>
+      <c r="AD8" s="257"/>
+      <c r="AE8" s="257"/>
+      <c r="AF8" s="257"/>
+      <c r="AG8" s="258"/>
+      <c r="AH8" s="253" t="s">
         <v>7</v>
       </c>
-      <c r="AI8" s="102"/>
-      <c r="AJ8" s="102"/>
-      <c r="AK8" s="102"/>
-      <c r="AL8" s="91" t="s">
+      <c r="AI8" s="253"/>
+      <c r="AJ8" s="253"/>
+      <c r="AK8" s="253"/>
+      <c r="AL8" s="244" t="s">
         <v>66</v>
       </c>
-      <c r="AM8" s="92"/>
-      <c r="AN8" s="92"/>
-      <c r="AO8" s="92"/>
-      <c r="AP8" s="92"/>
-      <c r="AQ8" s="92"/>
-      <c r="AR8" s="92"/>
-      <c r="AS8" s="92"/>
+      <c r="AM8" s="245"/>
+      <c r="AN8" s="245"/>
+      <c r="AO8" s="245"/>
+      <c r="AP8" s="245"/>
+      <c r="AQ8" s="245"/>
+      <c r="AR8" s="245"/>
+      <c r="AS8" s="245"/>
       <c r="AT8" s="4"/>
       <c r="AU8" s="1"/>
     </row>
@@ -9872,54 +10023,54 @@
       <c r="A9" s="1"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="93" t="s">
+      <c r="D9" s="199" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="95" t="s">
+      <c r="E9" s="200"/>
+      <c r="F9" s="200"/>
+      <c r="G9" s="200"/>
+      <c r="H9" s="246" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="96" t="s">
+      <c r="I9" s="246"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="247" t="s">
         <v>65</v>
       </c>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="95" t="s">
+      <c r="L9" s="247"/>
+      <c r="M9" s="247"/>
+      <c r="N9" s="247"/>
+      <c r="O9" s="247"/>
+      <c r="P9" s="247"/>
+      <c r="Q9" s="246" t="s">
         <v>10</v>
       </c>
-      <c r="R9" s="95"/>
-      <c r="S9" s="95"/>
-      <c r="T9" s="97" t="s">
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="248" t="s">
         <v>65</v>
       </c>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
-      <c r="W9" s="98"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
-      <c r="AA9" s="98"/>
-      <c r="AB9" s="98"/>
-      <c r="AC9" s="98"/>
-      <c r="AD9" s="98"/>
-      <c r="AE9" s="98"/>
-      <c r="AF9" s="98"/>
-      <c r="AG9" s="99"/>
+      <c r="U9" s="249"/>
+      <c r="V9" s="249"/>
+      <c r="W9" s="249"/>
+      <c r="X9" s="249"/>
+      <c r="Y9" s="249"/>
+      <c r="Z9" s="249"/>
+      <c r="AA9" s="249"/>
+      <c r="AB9" s="249"/>
+      <c r="AC9" s="249"/>
+      <c r="AD9" s="249"/>
+      <c r="AE9" s="249"/>
+      <c r="AF9" s="249"/>
+      <c r="AG9" s="250"/>
       <c r="AH9" s="7"/>
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
       <c r="AK9" s="8"/>
       <c r="AL9" s="8"/>
       <c r="AM9" s="8"/>
-      <c r="AN9" s="100"/>
-      <c r="AO9" s="101"/>
+      <c r="AN9" s="251"/>
+      <c r="AO9" s="252"/>
       <c r="AP9" s="8"/>
       <c r="AQ9" s="8"/>
       <c r="AR9" s="8"/>
@@ -9931,10 +10082,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -9980,50 +10131,50 @@
       <c r="A11" s="1"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="135" t="s">
+      <c r="D11" s="212" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="135"/>
-      <c r="F11" s="135"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
-      <c r="S11" s="137"/>
-      <c r="T11" s="137"/>
-      <c r="U11" s="137"/>
-      <c r="V11" s="137"/>
-      <c r="W11" s="137"/>
-      <c r="X11" s="137"/>
-      <c r="Y11" s="137"/>
-      <c r="Z11" s="137"/>
-      <c r="AA11" s="137"/>
-      <c r="AB11" s="137"/>
-      <c r="AC11" s="137"/>
-      <c r="AD11" s="137"/>
-      <c r="AE11" s="137"/>
-      <c r="AF11" s="137"/>
-      <c r="AG11" s="138"/>
-      <c r="AH11" s="139" t="s">
+      <c r="E11" s="212"/>
+      <c r="F11" s="212"/>
+      <c r="G11" s="195"/>
+      <c r="H11" s="213"/>
+      <c r="I11" s="214"/>
+      <c r="J11" s="214"/>
+      <c r="K11" s="214"/>
+      <c r="L11" s="214"/>
+      <c r="M11" s="214"/>
+      <c r="N11" s="214"/>
+      <c r="O11" s="214"/>
+      <c r="P11" s="214"/>
+      <c r="Q11" s="214"/>
+      <c r="R11" s="214"/>
+      <c r="S11" s="214"/>
+      <c r="T11" s="214"/>
+      <c r="U11" s="214"/>
+      <c r="V11" s="214"/>
+      <c r="W11" s="214"/>
+      <c r="X11" s="214"/>
+      <c r="Y11" s="214"/>
+      <c r="Z11" s="214"/>
+      <c r="AA11" s="214"/>
+      <c r="AB11" s="214"/>
+      <c r="AC11" s="214"/>
+      <c r="AD11" s="214"/>
+      <c r="AE11" s="214"/>
+      <c r="AF11" s="214"/>
+      <c r="AG11" s="215"/>
+      <c r="AH11" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="AI11" s="140"/>
-      <c r="AJ11" s="140"/>
-      <c r="AK11" s="141"/>
-      <c r="AL11" s="142" t="s">
+      <c r="AI11" s="217"/>
+      <c r="AJ11" s="217"/>
+      <c r="AK11" s="218"/>
+      <c r="AL11" s="219" t="s">
         <v>13</v>
       </c>
-      <c r="AM11" s="143"/>
-      <c r="AN11" s="143"/>
-      <c r="AO11" s="143"/>
+      <c r="AM11" s="220"/>
+      <c r="AN11" s="220"/>
+      <c r="AO11" s="220"/>
       <c r="AP11" s="11"/>
       <c r="AQ11" s="12"/>
       <c r="AR11" s="12"/>
@@ -10035,54 +10186,54 @@
       <c r="A12" s="1"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="108" t="s">
+      <c r="D12" s="221" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="114" t="s">
+      <c r="E12" s="221"/>
+      <c r="F12" s="221"/>
+      <c r="G12" s="222"/>
+      <c r="H12" s="223" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="115"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="124"/>
-      <c r="R12" s="124"/>
-      <c r="S12" s="124"/>
-      <c r="T12" s="124"/>
-      <c r="U12" s="124"/>
-      <c r="V12" s="124"/>
-      <c r="W12" s="125"/>
-      <c r="X12" s="125"/>
-      <c r="Y12" s="125"/>
-      <c r="Z12" s="125"/>
-      <c r="AA12" s="126" t="s">
+      <c r="I12" s="224"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="232"/>
+      <c r="L12" s="233"/>
+      <c r="M12" s="233"/>
+      <c r="N12" s="233"/>
+      <c r="O12" s="233"/>
+      <c r="P12" s="233"/>
+      <c r="Q12" s="233"/>
+      <c r="R12" s="233"/>
+      <c r="S12" s="233"/>
+      <c r="T12" s="233"/>
+      <c r="U12" s="233"/>
+      <c r="V12" s="233"/>
+      <c r="W12" s="234"/>
+      <c r="X12" s="234"/>
+      <c r="Y12" s="234"/>
+      <c r="Z12" s="234"/>
+      <c r="AA12" s="235" t="s">
         <v>16</v>
       </c>
-      <c r="AB12" s="127"/>
-      <c r="AC12" s="128"/>
-      <c r="AD12" s="144"/>
-      <c r="AE12" s="144"/>
-      <c r="AF12" s="144"/>
-      <c r="AG12" s="144"/>
-      <c r="AH12" s="144"/>
-      <c r="AI12" s="144"/>
-      <c r="AJ12" s="144"/>
-      <c r="AK12" s="144"/>
-      <c r="AL12" s="144"/>
-      <c r="AM12" s="144"/>
-      <c r="AN12" s="144"/>
-      <c r="AO12" s="144"/>
-      <c r="AP12" s="145"/>
-      <c r="AQ12" s="145"/>
-      <c r="AR12" s="145"/>
-      <c r="AS12" s="145"/>
+      <c r="AB12" s="236"/>
+      <c r="AC12" s="237"/>
+      <c r="AD12" s="201"/>
+      <c r="AE12" s="201"/>
+      <c r="AF12" s="201"/>
+      <c r="AG12" s="201"/>
+      <c r="AH12" s="201"/>
+      <c r="AI12" s="201"/>
+      <c r="AJ12" s="201"/>
+      <c r="AK12" s="201"/>
+      <c r="AL12" s="201"/>
+      <c r="AM12" s="201"/>
+      <c r="AN12" s="201"/>
+      <c r="AO12" s="201"/>
+      <c r="AP12" s="202"/>
+      <c r="AQ12" s="202"/>
+      <c r="AR12" s="202"/>
+      <c r="AS12" s="202"/>
       <c r="AT12" s="4"/>
       <c r="AU12" s="1"/>
     </row>
@@ -10090,52 +10241,52 @@
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="146" t="s">
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="157"/>
+      <c r="H13" s="226"/>
+      <c r="I13" s="227"/>
+      <c r="J13" s="228"/>
+      <c r="K13" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="150"/>
-      <c r="O13" s="151"/>
-      <c r="P13" s="151"/>
-      <c r="Q13" s="151"/>
-      <c r="R13" s="151"/>
-      <c r="S13" s="151"/>
-      <c r="T13" s="151"/>
-      <c r="U13" s="151"/>
-      <c r="V13" s="151"/>
-      <c r="W13" s="151"/>
-      <c r="X13" s="151"/>
-      <c r="Y13" s="151"/>
-      <c r="Z13" s="152"/>
-      <c r="AA13" s="129"/>
-      <c r="AB13" s="130"/>
-      <c r="AC13" s="131"/>
-      <c r="AD13" s="147" t="s">
+      <c r="L13" s="204"/>
+      <c r="M13" s="204"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="208"/>
+      <c r="P13" s="208"/>
+      <c r="Q13" s="208"/>
+      <c r="R13" s="208"/>
+      <c r="S13" s="208"/>
+      <c r="T13" s="208"/>
+      <c r="U13" s="208"/>
+      <c r="V13" s="208"/>
+      <c r="W13" s="208"/>
+      <c r="X13" s="208"/>
+      <c r="Y13" s="208"/>
+      <c r="Z13" s="209"/>
+      <c r="AA13" s="238"/>
+      <c r="AB13" s="239"/>
+      <c r="AC13" s="240"/>
+      <c r="AD13" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="AE13" s="147"/>
-      <c r="AF13" s="147"/>
-      <c r="AG13" s="150"/>
-      <c r="AH13" s="151"/>
-      <c r="AI13" s="151"/>
-      <c r="AJ13" s="151"/>
-      <c r="AK13" s="151"/>
-      <c r="AL13" s="151"/>
-      <c r="AM13" s="151"/>
-      <c r="AN13" s="151"/>
-      <c r="AO13" s="151"/>
-      <c r="AP13" s="151"/>
-      <c r="AQ13" s="151"/>
-      <c r="AR13" s="151"/>
-      <c r="AS13" s="151"/>
+      <c r="AE13" s="204"/>
+      <c r="AF13" s="204"/>
+      <c r="AG13" s="207"/>
+      <c r="AH13" s="208"/>
+      <c r="AI13" s="208"/>
+      <c r="AJ13" s="208"/>
+      <c r="AK13" s="208"/>
+      <c r="AL13" s="208"/>
+      <c r="AM13" s="208"/>
+      <c r="AN13" s="208"/>
+      <c r="AO13" s="208"/>
+      <c r="AP13" s="208"/>
+      <c r="AQ13" s="208"/>
+      <c r="AR13" s="208"/>
+      <c r="AS13" s="208"/>
       <c r="AT13" s="4"/>
       <c r="AU13" s="1"/>
     </row>
@@ -10143,48 +10294,48 @@
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="148"/>
-      <c r="L14" s="149"/>
-      <c r="M14" s="149"/>
-      <c r="N14" s="153"/>
-      <c r="O14" s="153"/>
-      <c r="P14" s="153"/>
-      <c r="Q14" s="153"/>
-      <c r="R14" s="153"/>
-      <c r="S14" s="153"/>
-      <c r="T14" s="153"/>
-      <c r="U14" s="153"/>
-      <c r="V14" s="153"/>
-      <c r="W14" s="153"/>
-      <c r="X14" s="153"/>
-      <c r="Y14" s="153"/>
-      <c r="Z14" s="154"/>
-      <c r="AA14" s="132"/>
-      <c r="AB14" s="133"/>
-      <c r="AC14" s="134"/>
-      <c r="AD14" s="149"/>
-      <c r="AE14" s="149"/>
-      <c r="AF14" s="149"/>
-      <c r="AG14" s="153"/>
-      <c r="AH14" s="153"/>
-      <c r="AI14" s="153"/>
-      <c r="AJ14" s="153"/>
-      <c r="AK14" s="153"/>
-      <c r="AL14" s="153"/>
-      <c r="AM14" s="153"/>
-      <c r="AN14" s="153"/>
-      <c r="AO14" s="153"/>
-      <c r="AP14" s="153"/>
-      <c r="AQ14" s="153"/>
-      <c r="AR14" s="153"/>
-      <c r="AS14" s="153"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="158"/>
+      <c r="F14" s="158"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="229"/>
+      <c r="I14" s="230"/>
+      <c r="J14" s="231"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="206"/>
+      <c r="M14" s="206"/>
+      <c r="N14" s="210"/>
+      <c r="O14" s="210"/>
+      <c r="P14" s="210"/>
+      <c r="Q14" s="210"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
+      <c r="T14" s="210"/>
+      <c r="U14" s="210"/>
+      <c r="V14" s="210"/>
+      <c r="W14" s="210"/>
+      <c r="X14" s="210"/>
+      <c r="Y14" s="210"/>
+      <c r="Z14" s="211"/>
+      <c r="AA14" s="241"/>
+      <c r="AB14" s="242"/>
+      <c r="AC14" s="243"/>
+      <c r="AD14" s="206"/>
+      <c r="AE14" s="206"/>
+      <c r="AF14" s="206"/>
+      <c r="AG14" s="210"/>
+      <c r="AH14" s="210"/>
+      <c r="AI14" s="210"/>
+      <c r="AJ14" s="210"/>
+      <c r="AK14" s="210"/>
+      <c r="AL14" s="210"/>
+      <c r="AM14" s="210"/>
+      <c r="AN14" s="210"/>
+      <c r="AO14" s="210"/>
+      <c r="AP14" s="210"/>
+      <c r="AQ14" s="210"/>
+      <c r="AR14" s="210"/>
+      <c r="AS14" s="210"/>
       <c r="AT14" s="4"/>
       <c r="AU14" s="1"/>
     </row>
@@ -10243,56 +10394,52 @@
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="195" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
+      <c r="E16" s="196"/>
+      <c r="F16" s="196"/>
+      <c r="G16" s="196"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="166" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="167"/>
-      <c r="K16" s="167"/>
-      <c r="L16" s="167"/>
-      <c r="M16" s="167"/>
-      <c r="N16" s="168"/>
-      <c r="O16" s="166" t="s">
-        <v>68</v>
-      </c>
-      <c r="P16" s="167"/>
-      <c r="Q16" s="167"/>
-      <c r="R16" s="167"/>
-      <c r="S16" s="167"/>
-      <c r="T16" s="168"/>
-      <c r="U16" s="166"/>
-      <c r="V16" s="167"/>
-      <c r="W16" s="167"/>
-      <c r="X16" s="167"/>
-      <c r="Y16" s="167"/>
-      <c r="Z16" s="168"/>
-      <c r="AA16" s="235" t="s">
+      <c r="I16" s="80"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="80"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="82"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="81"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="82"/>
+      <c r="AA16" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="AB16" s="236"/>
-      <c r="AC16" s="236"/>
-      <c r="AD16" s="236"/>
-      <c r="AE16" s="236"/>
-      <c r="AF16" s="236"/>
-      <c r="AG16" s="236"/>
-      <c r="AH16" s="236"/>
-      <c r="AI16" s="236"/>
-      <c r="AJ16" s="236"/>
-      <c r="AK16" s="236"/>
-      <c r="AL16" s="236"/>
-      <c r="AM16" s="236"/>
-      <c r="AN16" s="236"/>
-      <c r="AO16" s="236"/>
-      <c r="AP16" s="236"/>
-      <c r="AQ16" s="236"/>
-      <c r="AR16" s="236"/>
-      <c r="AS16" s="237"/>
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="72"/>
+      <c r="AD16" s="72"/>
+      <c r="AE16" s="72"/>
+      <c r="AF16" s="72"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="72"/>
+      <c r="AL16" s="72"/>
+      <c r="AM16" s="72"/>
+      <c r="AN16" s="72"/>
+      <c r="AO16" s="72"/>
+      <c r="AP16" s="72"/>
+      <c r="AQ16" s="72"/>
+      <c r="AR16" s="72"/>
+      <c r="AS16" s="73"/>
       <c r="AT16" s="4"/>
       <c r="AU16" s="1"/>
     </row>
@@ -10300,50 +10447,50 @@
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
+      <c r="D17" s="197"/>
+      <c r="E17" s="198"/>
+      <c r="F17" s="198"/>
+      <c r="G17" s="198"/>
       <c r="H17" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="169"/>
-      <c r="J17" s="170"/>
-      <c r="K17" s="170"/>
-      <c r="L17" s="170"/>
-      <c r="M17" s="170"/>
-      <c r="N17" s="171"/>
-      <c r="O17" s="169"/>
-      <c r="P17" s="170"/>
-      <c r="Q17" s="170"/>
-      <c r="R17" s="170"/>
-      <c r="S17" s="170"/>
-      <c r="T17" s="171"/>
-      <c r="U17" s="169"/>
-      <c r="V17" s="170"/>
-      <c r="W17" s="170"/>
-      <c r="X17" s="170"/>
-      <c r="Y17" s="170"/>
-      <c r="Z17" s="171"/>
-      <c r="AA17" s="238"/>
-      <c r="AB17" s="239"/>
-      <c r="AC17" s="239"/>
-      <c r="AD17" s="239"/>
-      <c r="AE17" s="239"/>
-      <c r="AF17" s="239"/>
-      <c r="AG17" s="239"/>
-      <c r="AH17" s="239"/>
-      <c r="AI17" s="239"/>
-      <c r="AJ17" s="239"/>
-      <c r="AK17" s="239"/>
-      <c r="AL17" s="239"/>
-      <c r="AM17" s="239"/>
-      <c r="AN17" s="239"/>
-      <c r="AO17" s="239"/>
-      <c r="AP17" s="239"/>
-      <c r="AQ17" s="239"/>
-      <c r="AR17" s="239"/>
-      <c r="AS17" s="240"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="83"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="84"/>
+      <c r="T17" s="85"/>
+      <c r="U17" s="83"/>
+      <c r="V17" s="84"/>
+      <c r="W17" s="84"/>
+      <c r="X17" s="84"/>
+      <c r="Y17" s="84"/>
+      <c r="Z17" s="85"/>
+      <c r="AA17" s="74"/>
+      <c r="AB17" s="75"/>
+      <c r="AC17" s="75"/>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="75"/>
+      <c r="AF17" s="75"/>
+      <c r="AG17" s="75"/>
+      <c r="AH17" s="75"/>
+      <c r="AI17" s="75"/>
+      <c r="AJ17" s="75"/>
+      <c r="AK17" s="75"/>
+      <c r="AL17" s="75"/>
+      <c r="AM17" s="75"/>
+      <c r="AN17" s="75"/>
+      <c r="AO17" s="75"/>
+      <c r="AP17" s="75"/>
+      <c r="AQ17" s="75"/>
+      <c r="AR17" s="75"/>
+      <c r="AS17" s="76"/>
       <c r="AT17" s="4"/>
       <c r="AU17" s="1"/>
     </row>
@@ -10351,50 +10498,50 @@
       <c r="A18" s="1"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
+      <c r="D18" s="197"/>
+      <c r="E18" s="198"/>
+      <c r="F18" s="198"/>
+      <c r="G18" s="198"/>
       <c r="H18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="169"/>
-      <c r="J18" s="170"/>
-      <c r="K18" s="170"/>
-      <c r="L18" s="170"/>
-      <c r="M18" s="170"/>
-      <c r="N18" s="171"/>
-      <c r="O18" s="169"/>
-      <c r="P18" s="170"/>
-      <c r="Q18" s="170"/>
-      <c r="R18" s="170"/>
-      <c r="S18" s="170"/>
-      <c r="T18" s="171"/>
-      <c r="U18" s="169"/>
-      <c r="V18" s="170"/>
-      <c r="W18" s="170"/>
-      <c r="X18" s="170"/>
-      <c r="Y18" s="170"/>
-      <c r="Z18" s="171"/>
-      <c r="AA18" s="238"/>
-      <c r="AB18" s="239"/>
-      <c r="AC18" s="239"/>
-      <c r="AD18" s="239"/>
-      <c r="AE18" s="239"/>
-      <c r="AF18" s="239"/>
-      <c r="AG18" s="239"/>
-      <c r="AH18" s="239"/>
-      <c r="AI18" s="239"/>
-      <c r="AJ18" s="239"/>
-      <c r="AK18" s="239"/>
-      <c r="AL18" s="239"/>
-      <c r="AM18" s="239"/>
-      <c r="AN18" s="239"/>
-      <c r="AO18" s="239"/>
-      <c r="AP18" s="239"/>
-      <c r="AQ18" s="239"/>
-      <c r="AR18" s="239"/>
-      <c r="AS18" s="240"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="84"/>
+      <c r="W18" s="84"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="74"/>
+      <c r="AB18" s="75"/>
+      <c r="AC18" s="75"/>
+      <c r="AD18" s="75"/>
+      <c r="AE18" s="75"/>
+      <c r="AF18" s="75"/>
+      <c r="AG18" s="75"/>
+      <c r="AH18" s="75"/>
+      <c r="AI18" s="75"/>
+      <c r="AJ18" s="75"/>
+      <c r="AK18" s="75"/>
+      <c r="AL18" s="75"/>
+      <c r="AM18" s="75"/>
+      <c r="AN18" s="75"/>
+      <c r="AO18" s="75"/>
+      <c r="AP18" s="75"/>
+      <c r="AQ18" s="75"/>
+      <c r="AR18" s="75"/>
+      <c r="AS18" s="76"/>
       <c r="AT18" s="4"/>
       <c r="AU18" s="1"/>
       <c r="AX18" s="3" t="s">
@@ -10405,50 +10552,50 @@
       <c r="A19" s="1"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
+      <c r="D19" s="197"/>
+      <c r="E19" s="198"/>
+      <c r="F19" s="198"/>
+      <c r="G19" s="198"/>
       <c r="H19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="169"/>
-      <c r="J19" s="170"/>
-      <c r="K19" s="170"/>
-      <c r="L19" s="170"/>
-      <c r="M19" s="170"/>
-      <c r="N19" s="171"/>
-      <c r="O19" s="169"/>
-      <c r="P19" s="170"/>
-      <c r="Q19" s="170"/>
-      <c r="R19" s="170"/>
-      <c r="S19" s="170"/>
-      <c r="T19" s="171"/>
-      <c r="U19" s="169"/>
-      <c r="V19" s="170"/>
-      <c r="W19" s="170"/>
-      <c r="X19" s="170"/>
-      <c r="Y19" s="170"/>
-      <c r="Z19" s="171"/>
-      <c r="AA19" s="241"/>
-      <c r="AB19" s="242"/>
-      <c r="AC19" s="242"/>
-      <c r="AD19" s="242"/>
-      <c r="AE19" s="242"/>
-      <c r="AF19" s="242"/>
-      <c r="AG19" s="242"/>
-      <c r="AH19" s="242"/>
-      <c r="AI19" s="242"/>
-      <c r="AJ19" s="242"/>
-      <c r="AK19" s="242"/>
-      <c r="AL19" s="242"/>
-      <c r="AM19" s="242"/>
-      <c r="AN19" s="242"/>
-      <c r="AO19" s="242"/>
-      <c r="AP19" s="242"/>
-      <c r="AQ19" s="242"/>
-      <c r="AR19" s="242"/>
-      <c r="AS19" s="243"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="85"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="85"/>
+      <c r="AA19" s="77"/>
+      <c r="AB19" s="78"/>
+      <c r="AC19" s="78"/>
+      <c r="AD19" s="78"/>
+      <c r="AE19" s="78"/>
+      <c r="AF19" s="78"/>
+      <c r="AG19" s="78"/>
+      <c r="AH19" s="78"/>
+      <c r="AI19" s="78"/>
+      <c r="AJ19" s="78"/>
+      <c r="AK19" s="78"/>
+      <c r="AL19" s="78"/>
+      <c r="AM19" s="78"/>
+      <c r="AN19" s="78"/>
+      <c r="AO19" s="78"/>
+      <c r="AP19" s="78"/>
+      <c r="AQ19" s="78"/>
+      <c r="AR19" s="78"/>
+      <c r="AS19" s="79"/>
       <c r="AT19" s="4"/>
       <c r="AU19" s="1"/>
     </row>
@@ -10456,66 +10603,66 @@
       <c r="A20" s="1"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="94"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
+      <c r="G20" s="200"/>
       <c r="H20" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="155">
+      <c r="I20" s="184">
         <f>SUM(I17:Z19)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="156"/>
-      <c r="K20" s="156"/>
-      <c r="L20" s="156"/>
-      <c r="M20" s="156"/>
-      <c r="N20" s="156"/>
-      <c r="O20" s="156"/>
-      <c r="P20" s="156"/>
-      <c r="Q20" s="156"/>
-      <c r="R20" s="156"/>
-      <c r="S20" s="156"/>
-      <c r="T20" s="156"/>
-      <c r="U20" s="156"/>
-      <c r="V20" s="156"/>
-      <c r="W20" s="157"/>
-      <c r="X20" s="157"/>
-      <c r="Y20" s="157"/>
-      <c r="Z20" s="157"/>
-      <c r="AA20" s="157"/>
-      <c r="AB20" s="157"/>
-      <c r="AC20" s="157"/>
-      <c r="AD20" s="157"/>
-      <c r="AE20" s="157"/>
-      <c r="AF20" s="157"/>
-      <c r="AG20" s="157"/>
-      <c r="AH20" s="157"/>
-      <c r="AI20" s="157"/>
-      <c r="AJ20" s="157"/>
-      <c r="AK20" s="157"/>
-      <c r="AL20" s="157"/>
-      <c r="AM20" s="157"/>
-      <c r="AN20" s="157"/>
-      <c r="AO20" s="157"/>
-      <c r="AP20" s="157"/>
-      <c r="AQ20" s="157"/>
-      <c r="AR20" s="157"/>
-      <c r="AS20" s="157"/>
-      <c r="AT20" s="157"/>
+      <c r="J20" s="185"/>
+      <c r="K20" s="185"/>
+      <c r="L20" s="185"/>
+      <c r="M20" s="185"/>
+      <c r="N20" s="185"/>
+      <c r="O20" s="185"/>
+      <c r="P20" s="185"/>
+      <c r="Q20" s="185"/>
+      <c r="R20" s="185"/>
+      <c r="S20" s="185"/>
+      <c r="T20" s="185"/>
+      <c r="U20" s="185"/>
+      <c r="V20" s="185"/>
+      <c r="W20" s="186"/>
+      <c r="X20" s="186"/>
+      <c r="Y20" s="186"/>
+      <c r="Z20" s="186"/>
+      <c r="AA20" s="186"/>
+      <c r="AB20" s="186"/>
+      <c r="AC20" s="186"/>
+      <c r="AD20" s="186"/>
+      <c r="AE20" s="186"/>
+      <c r="AF20" s="186"/>
+      <c r="AG20" s="186"/>
+      <c r="AH20" s="186"/>
+      <c r="AI20" s="186"/>
+      <c r="AJ20" s="186"/>
+      <c r="AK20" s="186"/>
+      <c r="AL20" s="186"/>
+      <c r="AM20" s="186"/>
+      <c r="AN20" s="186"/>
+      <c r="AO20" s="186"/>
+      <c r="AP20" s="186"/>
+      <c r="AQ20" s="186"/>
+      <c r="AR20" s="186"/>
+      <c r="AS20" s="186"/>
+      <c r="AT20" s="186"/>
       <c r="AU20" s="1"/>
     </row>
     <row r="21" spans="1:50" ht="21" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="158" t="s">
+      <c r="D21" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="158"/>
-      <c r="F21" s="158"/>
-      <c r="G21" s="159"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="188"/>
       <c r="H21" s="17" t="s">
         <v>26</v>
       </c>
@@ -10524,17 +10671,17 @@
       <c r="K21" s="17"/>
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
-      <c r="N21" s="162"/>
-      <c r="O21" s="162"/>
-      <c r="P21" s="162"/>
-      <c r="Q21" s="162"/>
-      <c r="R21" s="162"/>
-      <c r="S21" s="162"/>
-      <c r="T21" s="162"/>
-      <c r="U21" s="162"/>
-      <c r="V21" s="162"/>
-      <c r="W21" s="162"/>
-      <c r="X21" s="162"/>
+      <c r="N21" s="191"/>
+      <c r="O21" s="191"/>
+      <c r="P21" s="191"/>
+      <c r="Q21" s="191"/>
+      <c r="R21" s="191"/>
+      <c r="S21" s="191"/>
+      <c r="T21" s="191"/>
+      <c r="U21" s="191"/>
+      <c r="V21" s="191"/>
+      <c r="W21" s="191"/>
+      <c r="X21" s="191"/>
       <c r="Y21" s="17" t="s">
         <v>27</v>
       </c>
@@ -10565,49 +10712,49 @@
       <c r="A22" s="1"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="160"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="161"/>
-      <c r="H22" s="163" t="s">
+      <c r="D22" s="189"/>
+      <c r="E22" s="189"/>
+      <c r="F22" s="189"/>
+      <c r="G22" s="190"/>
+      <c r="H22" s="192" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="164"/>
-      <c r="J22" s="164"/>
-      <c r="K22" s="164"/>
-      <c r="L22" s="164"/>
-      <c r="M22" s="164"/>
-      <c r="N22" s="164"/>
-      <c r="O22" s="164"/>
-      <c r="P22" s="164"/>
-      <c r="Q22" s="164"/>
-      <c r="R22" s="164"/>
-      <c r="S22" s="164"/>
-      <c r="T22" s="164"/>
-      <c r="U22" s="164"/>
-      <c r="V22" s="164"/>
-      <c r="W22" s="164"/>
-      <c r="X22" s="164"/>
-      <c r="Y22" s="164"/>
-      <c r="Z22" s="164"/>
-      <c r="AA22" s="165" t="s">
+      <c r="I22" s="193"/>
+      <c r="J22" s="193"/>
+      <c r="K22" s="193"/>
+      <c r="L22" s="193"/>
+      <c r="M22" s="193"/>
+      <c r="N22" s="193"/>
+      <c r="O22" s="193"/>
+      <c r="P22" s="193"/>
+      <c r="Q22" s="193"/>
+      <c r="R22" s="193"/>
+      <c r="S22" s="193"/>
+      <c r="T22" s="193"/>
+      <c r="U22" s="193"/>
+      <c r="V22" s="193"/>
+      <c r="W22" s="193"/>
+      <c r="X22" s="193"/>
+      <c r="Y22" s="193"/>
+      <c r="Z22" s="193"/>
+      <c r="AA22" s="194" t="s">
         <v>29</v>
       </c>
-      <c r="AB22" s="165"/>
-      <c r="AC22" s="165"/>
-      <c r="AD22" s="165"/>
-      <c r="AE22" s="165"/>
-      <c r="AF22" s="165"/>
-      <c r="AG22" s="165"/>
-      <c r="AH22" s="165"/>
-      <c r="AI22" s="165"/>
-      <c r="AJ22" s="165"/>
-      <c r="AK22" s="165"/>
-      <c r="AL22" s="165"/>
-      <c r="AM22" s="165"/>
-      <c r="AN22" s="165"/>
-      <c r="AO22" s="165"/>
-      <c r="AP22" s="165"/>
+      <c r="AB22" s="194"/>
+      <c r="AC22" s="194"/>
+      <c r="AD22" s="194"/>
+      <c r="AE22" s="194"/>
+      <c r="AF22" s="194"/>
+      <c r="AG22" s="194"/>
+      <c r="AH22" s="194"/>
+      <c r="AI22" s="194"/>
+      <c r="AJ22" s="194"/>
+      <c r="AK22" s="194"/>
+      <c r="AL22" s="194"/>
+      <c r="AM22" s="194"/>
+      <c r="AN22" s="194"/>
+      <c r="AO22" s="194"/>
+      <c r="AP22" s="194"/>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="19"/>
       <c r="AS22" s="19"/>
@@ -10618,20 +10765,20 @@
       <c r="A23" s="1"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="182" t="s">
+      <c r="D23" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="182"/>
-      <c r="F23" s="182"/>
-      <c r="G23" s="183"/>
-      <c r="H23" s="184" t="s">
+      <c r="E23" s="154"/>
+      <c r="F23" s="154"/>
+      <c r="G23" s="155"/>
+      <c r="H23" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="I23" s="185"/>
-      <c r="J23" s="186"/>
-      <c r="K23" s="187"/>
-      <c r="L23" s="172"/>
-      <c r="M23" s="188"/>
+      <c r="I23" s="161"/>
+      <c r="J23" s="162"/>
+      <c r="K23" s="163"/>
+      <c r="L23" s="164"/>
+      <c r="M23" s="165"/>
       <c r="N23" s="36"/>
       <c r="O23" s="37" t="s">
         <v>58</v>
@@ -10639,9 +10786,9 @@
       <c r="P23" s="37"/>
       <c r="Q23" s="37"/>
       <c r="R23" s="37"/>
-      <c r="S23" s="172"/>
-      <c r="T23" s="172"/>
-      <c r="U23" s="172"/>
+      <c r="S23" s="164"/>
+      <c r="T23" s="164"/>
+      <c r="U23" s="164"/>
       <c r="V23" s="37" t="s">
         <v>59</v>
       </c>
@@ -10653,8 +10800,8 @@
       <c r="Z23" s="37"/>
       <c r="AA23" s="37"/>
       <c r="AB23" s="37"/>
-      <c r="AC23" s="172"/>
-      <c r="AD23" s="172"/>
+      <c r="AC23" s="164"/>
+      <c r="AD23" s="164"/>
       <c r="AE23" s="37" t="s">
         <v>61</v>
       </c>
@@ -10669,8 +10816,8 @@
       <c r="AL23" s="37"/>
       <c r="AM23" s="37"/>
       <c r="AN23" s="37"/>
-      <c r="AO23" s="172"/>
-      <c r="AP23" s="172"/>
+      <c r="AO23" s="164"/>
+      <c r="AP23" s="164"/>
       <c r="AQ23" s="37" t="s">
         <v>63</v>
       </c>
@@ -10683,50 +10830,50 @@
       <c r="A24" s="1"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="173" t="s">
+      <c r="D24" s="156"/>
+      <c r="E24" s="156"/>
+      <c r="F24" s="156"/>
+      <c r="G24" s="157"/>
+      <c r="H24" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="174"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="169"/>
-      <c r="L24" s="170"/>
-      <c r="M24" s="171"/>
-      <c r="N24" s="176"/>
-      <c r="O24" s="177"/>
-      <c r="P24" s="177"/>
-      <c r="Q24" s="177"/>
-      <c r="R24" s="177"/>
-      <c r="S24" s="177"/>
-      <c r="T24" s="177"/>
-      <c r="U24" s="177"/>
-      <c r="V24" s="177"/>
-      <c r="W24" s="177"/>
-      <c r="X24" s="177"/>
-      <c r="Y24" s="177"/>
-      <c r="Z24" s="177"/>
-      <c r="AA24" s="177"/>
-      <c r="AB24" s="177"/>
-      <c r="AC24" s="177"/>
-      <c r="AD24" s="177"/>
-      <c r="AE24" s="177"/>
-      <c r="AF24" s="177"/>
-      <c r="AG24" s="177"/>
-      <c r="AH24" s="177"/>
-      <c r="AI24" s="177"/>
-      <c r="AJ24" s="177"/>
-      <c r="AK24" s="177"/>
-      <c r="AL24" s="177"/>
-      <c r="AM24" s="177"/>
-      <c r="AN24" s="177"/>
-      <c r="AO24" s="177"/>
-      <c r="AP24" s="177"/>
-      <c r="AQ24" s="177"/>
-      <c r="AR24" s="177"/>
-      <c r="AS24" s="177"/>
+      <c r="I24" s="176"/>
+      <c r="J24" s="177"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="178"/>
+      <c r="O24" s="179"/>
+      <c r="P24" s="179"/>
+      <c r="Q24" s="179"/>
+      <c r="R24" s="179"/>
+      <c r="S24" s="179"/>
+      <c r="T24" s="179"/>
+      <c r="U24" s="179"/>
+      <c r="V24" s="179"/>
+      <c r="W24" s="179"/>
+      <c r="X24" s="179"/>
+      <c r="Y24" s="179"/>
+      <c r="Z24" s="179"/>
+      <c r="AA24" s="179"/>
+      <c r="AB24" s="179"/>
+      <c r="AC24" s="179"/>
+      <c r="AD24" s="179"/>
+      <c r="AE24" s="179"/>
+      <c r="AF24" s="179"/>
+      <c r="AG24" s="179"/>
+      <c r="AH24" s="179"/>
+      <c r="AI24" s="179"/>
+      <c r="AJ24" s="179"/>
+      <c r="AK24" s="179"/>
+      <c r="AL24" s="179"/>
+      <c r="AM24" s="179"/>
+      <c r="AN24" s="179"/>
+      <c r="AO24" s="179"/>
+      <c r="AP24" s="179"/>
+      <c r="AQ24" s="179"/>
+      <c r="AR24" s="179"/>
+      <c r="AS24" s="179"/>
       <c r="AT24" s="4"/>
       <c r="AU24" s="1"/>
     </row>
@@ -10734,50 +10881,50 @@
       <c r="A25" s="1"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="178" t="s">
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="157"/>
+      <c r="H25" s="180" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="179"/>
-      <c r="J25" s="179"/>
-      <c r="K25" s="179"/>
-      <c r="L25" s="179"/>
-      <c r="M25" s="179"/>
-      <c r="N25" s="179"/>
-      <c r="O25" s="179"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="179"/>
-      <c r="R25" s="179"/>
-      <c r="S25" s="179"/>
-      <c r="T25" s="179"/>
-      <c r="U25" s="179"/>
-      <c r="V25" s="179"/>
-      <c r="W25" s="179"/>
-      <c r="X25" s="179"/>
-      <c r="Y25" s="179"/>
-      <c r="Z25" s="179"/>
-      <c r="AA25" s="179"/>
-      <c r="AB25" s="179"/>
-      <c r="AC25" s="179"/>
-      <c r="AD25" s="179"/>
-      <c r="AE25" s="179"/>
-      <c r="AF25" s="179"/>
-      <c r="AG25" s="179"/>
-      <c r="AH25" s="179"/>
-      <c r="AI25" s="179"/>
-      <c r="AJ25" s="179"/>
-      <c r="AK25" s="179"/>
-      <c r="AL25" s="179"/>
-      <c r="AM25" s="179"/>
-      <c r="AN25" s="179"/>
-      <c r="AO25" s="179"/>
-      <c r="AP25" s="179"/>
-      <c r="AQ25" s="179"/>
-      <c r="AR25" s="179"/>
-      <c r="AS25" s="179"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="181"/>
+      <c r="L25" s="181"/>
+      <c r="M25" s="181"/>
+      <c r="N25" s="181"/>
+      <c r="O25" s="181"/>
+      <c r="P25" s="181"/>
+      <c r="Q25" s="181"/>
+      <c r="R25" s="181"/>
+      <c r="S25" s="181"/>
+      <c r="T25" s="181"/>
+      <c r="U25" s="181"/>
+      <c r="V25" s="181"/>
+      <c r="W25" s="181"/>
+      <c r="X25" s="181"/>
+      <c r="Y25" s="181"/>
+      <c r="Z25" s="181"/>
+      <c r="AA25" s="181"/>
+      <c r="AB25" s="181"/>
+      <c r="AC25" s="181"/>
+      <c r="AD25" s="181"/>
+      <c r="AE25" s="181"/>
+      <c r="AF25" s="181"/>
+      <c r="AG25" s="181"/>
+      <c r="AH25" s="181"/>
+      <c r="AI25" s="181"/>
+      <c r="AJ25" s="181"/>
+      <c r="AK25" s="181"/>
+      <c r="AL25" s="181"/>
+      <c r="AM25" s="181"/>
+      <c r="AN25" s="181"/>
+      <c r="AO25" s="181"/>
+      <c r="AP25" s="181"/>
+      <c r="AQ25" s="181"/>
+      <c r="AR25" s="181"/>
+      <c r="AS25" s="181"/>
       <c r="AT25" s="4"/>
       <c r="AU25" s="1"/>
     </row>
@@ -10785,48 +10932,48 @@
       <c r="A26" s="1"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="180"/>
-      <c r="I26" s="181"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="181"/>
-      <c r="L26" s="181"/>
-      <c r="M26" s="181"/>
-      <c r="N26" s="181"/>
-      <c r="O26" s="181"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="181"/>
-      <c r="R26" s="181"/>
-      <c r="S26" s="181"/>
-      <c r="T26" s="181"/>
-      <c r="U26" s="181"/>
-      <c r="V26" s="181"/>
-      <c r="W26" s="181"/>
-      <c r="X26" s="181"/>
-      <c r="Y26" s="181"/>
-      <c r="Z26" s="181"/>
-      <c r="AA26" s="181"/>
-      <c r="AB26" s="181"/>
-      <c r="AC26" s="181"/>
-      <c r="AD26" s="181"/>
-      <c r="AE26" s="181"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="181"/>
-      <c r="AH26" s="181"/>
-      <c r="AI26" s="181"/>
-      <c r="AJ26" s="181"/>
-      <c r="AK26" s="181"/>
-      <c r="AL26" s="181"/>
-      <c r="AM26" s="181"/>
-      <c r="AN26" s="181"/>
-      <c r="AO26" s="181"/>
-      <c r="AP26" s="181"/>
-      <c r="AQ26" s="181"/>
-      <c r="AR26" s="181"/>
-      <c r="AS26" s="181"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="156"/>
+      <c r="G26" s="157"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="183"/>
+      <c r="J26" s="183"/>
+      <c r="K26" s="183"/>
+      <c r="L26" s="183"/>
+      <c r="M26" s="183"/>
+      <c r="N26" s="183"/>
+      <c r="O26" s="183"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="183"/>
+      <c r="R26" s="183"/>
+      <c r="S26" s="183"/>
+      <c r="T26" s="183"/>
+      <c r="U26" s="183"/>
+      <c r="V26" s="183"/>
+      <c r="W26" s="183"/>
+      <c r="X26" s="183"/>
+      <c r="Y26" s="183"/>
+      <c r="Z26" s="183"/>
+      <c r="AA26" s="183"/>
+      <c r="AB26" s="183"/>
+      <c r="AC26" s="183"/>
+      <c r="AD26" s="183"/>
+      <c r="AE26" s="183"/>
+      <c r="AF26" s="183"/>
+      <c r="AG26" s="183"/>
+      <c r="AH26" s="183"/>
+      <c r="AI26" s="183"/>
+      <c r="AJ26" s="183"/>
+      <c r="AK26" s="183"/>
+      <c r="AL26" s="183"/>
+      <c r="AM26" s="183"/>
+      <c r="AN26" s="183"/>
+      <c r="AO26" s="183"/>
+      <c r="AP26" s="183"/>
+      <c r="AQ26" s="183"/>
+      <c r="AR26" s="183"/>
+      <c r="AS26" s="183"/>
       <c r="AT26" s="4"/>
       <c r="AU26" s="1"/>
     </row>
@@ -10834,56 +10981,56 @@
       <c r="A27" s="1"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="189" t="s">
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="157"/>
+      <c r="H27" s="166" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="190"/>
-      <c r="J27" s="191"/>
-      <c r="K27" s="195" t="s">
+      <c r="I27" s="167"/>
+      <c r="J27" s="168"/>
+      <c r="K27" s="172" t="s">
         <v>35</v>
       </c>
-      <c r="L27" s="196"/>
-      <c r="M27" s="196"/>
-      <c r="N27" s="196"/>
-      <c r="O27" s="196"/>
-      <c r="P27" s="196"/>
-      <c r="Q27" s="196"/>
-      <c r="R27" s="196"/>
-      <c r="S27" s="197"/>
-      <c r="T27" s="169" t="s">
+      <c r="L27" s="173"/>
+      <c r="M27" s="173"/>
+      <c r="N27" s="173"/>
+      <c r="O27" s="173"/>
+      <c r="P27" s="173"/>
+      <c r="Q27" s="173"/>
+      <c r="R27" s="173"/>
+      <c r="S27" s="174"/>
+      <c r="T27" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="U27" s="170"/>
-      <c r="V27" s="170"/>
-      <c r="W27" s="170"/>
-      <c r="X27" s="170"/>
-      <c r="Y27" s="170"/>
-      <c r="Z27" s="170"/>
-      <c r="AA27" s="170"/>
-      <c r="AB27" s="170"/>
-      <c r="AC27" s="170"/>
-      <c r="AD27" s="171"/>
-      <c r="AE27" s="209" t="s">
+      <c r="U27" s="84"/>
+      <c r="V27" s="84"/>
+      <c r="W27" s="84"/>
+      <c r="X27" s="84"/>
+      <c r="Y27" s="84"/>
+      <c r="Z27" s="84"/>
+      <c r="AA27" s="84"/>
+      <c r="AB27" s="84"/>
+      <c r="AC27" s="84"/>
+      <c r="AD27" s="85"/>
+      <c r="AE27" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="AF27" s="210"/>
-      <c r="AG27" s="210"/>
-      <c r="AH27" s="211"/>
-      <c r="AI27" s="215"/>
-      <c r="AJ27" s="216"/>
-      <c r="AK27" s="216"/>
-      <c r="AL27" s="216"/>
-      <c r="AM27" s="216"/>
-      <c r="AN27" s="216"/>
-      <c r="AO27" s="216"/>
-      <c r="AP27" s="216"/>
-      <c r="AQ27" s="216"/>
-      <c r="AR27" s="216"/>
-      <c r="AS27" s="216"/>
+      <c r="AF27" s="141"/>
+      <c r="AG27" s="141"/>
+      <c r="AH27" s="142"/>
+      <c r="AI27" s="146"/>
+      <c r="AJ27" s="147"/>
+      <c r="AK27" s="147"/>
+      <c r="AL27" s="147"/>
+      <c r="AM27" s="147"/>
+      <c r="AN27" s="147"/>
+      <c r="AO27" s="147"/>
+      <c r="AP27" s="147"/>
+      <c r="AQ27" s="147"/>
+      <c r="AR27" s="147"/>
+      <c r="AS27" s="147"/>
       <c r="AT27" s="4"/>
       <c r="AU27" s="1"/>
     </row>
@@ -10891,49 +11038,49 @@
       <c r="A28" s="1"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="113"/>
-      <c r="H28" s="192"/>
-      <c r="I28" s="193"/>
-      <c r="J28" s="194"/>
-      <c r="K28" s="217" t="s">
+      <c r="D28" s="158"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="159"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="171"/>
+      <c r="K28" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="218"/>
-      <c r="M28" s="218"/>
-      <c r="N28" s="218"/>
-      <c r="O28" s="218"/>
-      <c r="P28" s="218"/>
-      <c r="Q28" s="218"/>
-      <c r="R28" s="218"/>
-      <c r="S28" s="219"/>
-      <c r="T28" s="220"/>
-      <c r="U28" s="221"/>
-      <c r="V28" s="221"/>
-      <c r="W28" s="221"/>
-      <c r="X28" s="221"/>
-      <c r="Y28" s="221"/>
-      <c r="Z28" s="221"/>
-      <c r="AA28" s="221"/>
-      <c r="AB28" s="221"/>
-      <c r="AC28" s="221"/>
-      <c r="AD28" s="222"/>
-      <c r="AE28" s="212"/>
-      <c r="AF28" s="213"/>
-      <c r="AG28" s="213"/>
-      <c r="AH28" s="214"/>
-      <c r="AI28" s="220"/>
-      <c r="AJ28" s="221"/>
-      <c r="AK28" s="221"/>
-      <c r="AL28" s="221"/>
-      <c r="AM28" s="221"/>
-      <c r="AN28" s="221"/>
-      <c r="AO28" s="221"/>
-      <c r="AP28" s="221"/>
-      <c r="AQ28" s="221"/>
-      <c r="AR28" s="221"/>
+      <c r="L28" s="149"/>
+      <c r="M28" s="149"/>
+      <c r="N28" s="149"/>
+      <c r="O28" s="149"/>
+      <c r="P28" s="149"/>
+      <c r="Q28" s="149"/>
+      <c r="R28" s="149"/>
+      <c r="S28" s="150"/>
+      <c r="T28" s="151"/>
+      <c r="U28" s="152"/>
+      <c r="V28" s="152"/>
+      <c r="W28" s="152"/>
+      <c r="X28" s="152"/>
+      <c r="Y28" s="152"/>
+      <c r="Z28" s="152"/>
+      <c r="AA28" s="152"/>
+      <c r="AB28" s="152"/>
+      <c r="AC28" s="152"/>
+      <c r="AD28" s="153"/>
+      <c r="AE28" s="143"/>
+      <c r="AF28" s="144"/>
+      <c r="AG28" s="144"/>
+      <c r="AH28" s="145"/>
+      <c r="AI28" s="151"/>
+      <c r="AJ28" s="152"/>
+      <c r="AK28" s="152"/>
+      <c r="AL28" s="152"/>
+      <c r="AM28" s="152"/>
+      <c r="AN28" s="152"/>
+      <c r="AO28" s="152"/>
+      <c r="AP28" s="152"/>
+      <c r="AQ28" s="152"/>
+      <c r="AR28" s="152"/>
       <c r="AS28" s="20"/>
       <c r="AT28" s="4"/>
       <c r="AU28" s="1"/>
@@ -10991,52 +11138,52 @@
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="245" t="s">
+      <c r="D30" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="245"/>
-      <c r="F30" s="245"/>
-      <c r="G30" s="246"/>
-      <c r="H30" s="250" t="s">
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="251"/>
-      <c r="J30" s="251"/>
-      <c r="K30" s="251"/>
-      <c r="L30" s="251"/>
-      <c r="M30" s="251"/>
-      <c r="N30" s="251"/>
-      <c r="O30" s="251"/>
-      <c r="P30" s="251"/>
-      <c r="Q30" s="251"/>
-      <c r="R30" s="251"/>
-      <c r="S30" s="251"/>
-      <c r="T30" s="251"/>
-      <c r="U30" s="251"/>
-      <c r="V30" s="251"/>
-      <c r="W30" s="251"/>
-      <c r="X30" s="251"/>
-      <c r="Y30" s="251"/>
-      <c r="Z30" s="251"/>
-      <c r="AA30" s="251"/>
-      <c r="AB30" s="251"/>
-      <c r="AC30" s="251"/>
-      <c r="AD30" s="251"/>
-      <c r="AE30" s="251"/>
-      <c r="AF30" s="251"/>
-      <c r="AG30" s="251"/>
-      <c r="AH30" s="251"/>
-      <c r="AI30" s="251"/>
-      <c r="AJ30" s="251"/>
-      <c r="AK30" s="251"/>
-      <c r="AL30" s="251"/>
-      <c r="AM30" s="251"/>
-      <c r="AN30" s="251"/>
-      <c r="AO30" s="251"/>
-      <c r="AP30" s="251"/>
-      <c r="AQ30" s="251"/>
-      <c r="AR30" s="251"/>
-      <c r="AS30" s="251"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="93"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="93"/>
+      <c r="N30" s="93"/>
+      <c r="O30" s="93"/>
+      <c r="P30" s="93"/>
+      <c r="Q30" s="93"/>
+      <c r="R30" s="93"/>
+      <c r="S30" s="93"/>
+      <c r="T30" s="93"/>
+      <c r="U30" s="93"/>
+      <c r="V30" s="93"/>
+      <c r="W30" s="93"/>
+      <c r="X30" s="93"/>
+      <c r="Y30" s="93"/>
+      <c r="Z30" s="93"/>
+      <c r="AA30" s="93"/>
+      <c r="AB30" s="93"/>
+      <c r="AC30" s="93"/>
+      <c r="AD30" s="93"/>
+      <c r="AE30" s="93"/>
+      <c r="AF30" s="93"/>
+      <c r="AG30" s="93"/>
+      <c r="AH30" s="93"/>
+      <c r="AI30" s="93"/>
+      <c r="AJ30" s="93"/>
+      <c r="AK30" s="93"/>
+      <c r="AL30" s="93"/>
+      <c r="AM30" s="93"/>
+      <c r="AN30" s="93"/>
+      <c r="AO30" s="93"/>
+      <c r="AP30" s="93"/>
+      <c r="AQ30" s="93"/>
+      <c r="AR30" s="93"/>
+      <c r="AS30" s="93"/>
       <c r="AT30" s="4"/>
       <c r="AU30" s="1"/>
     </row>
@@ -11044,58 +11191,58 @@
       <c r="A31" s="1"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="247"/>
-      <c r="E31" s="247"/>
-      <c r="F31" s="247"/>
-      <c r="G31" s="247"/>
-      <c r="H31" s="252" t="s">
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="253"/>
+      <c r="I31" s="95"/>
       <c r="J31" s="21"/>
-      <c r="K31" s="256" t="s">
+      <c r="K31" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="L31" s="257"/>
-      <c r="M31" s="257"/>
-      <c r="N31" s="257"/>
-      <c r="O31" s="257"/>
-      <c r="P31" s="258"/>
-      <c r="Q31" s="259" t="s">
+      <c r="L31" s="99"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="100"/>
+      <c r="Q31" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="R31" s="260"/>
-      <c r="S31" s="260"/>
-      <c r="T31" s="260"/>
-      <c r="U31" s="260"/>
-      <c r="V31" s="260"/>
-      <c r="W31" s="263" t="s">
+      <c r="R31" s="102"/>
+      <c r="S31" s="102"/>
+      <c r="T31" s="102"/>
+      <c r="U31" s="102"/>
+      <c r="V31" s="102"/>
+      <c r="W31" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="X31" s="264"/>
-      <c r="Y31" s="265"/>
-      <c r="Z31" s="266"/>
-      <c r="AA31" s="267"/>
-      <c r="AB31" s="267"/>
-      <c r="AC31" s="267"/>
-      <c r="AD31" s="267"/>
-      <c r="AE31" s="267"/>
-      <c r="AF31" s="268"/>
-      <c r="AG31" s="269" t="s">
+      <c r="X31" s="106"/>
+      <c r="Y31" s="107"/>
+      <c r="Z31" s="108"/>
+      <c r="AA31" s="109"/>
+      <c r="AB31" s="109"/>
+      <c r="AC31" s="109"/>
+      <c r="AD31" s="109"/>
+      <c r="AE31" s="109"/>
+      <c r="AF31" s="110"/>
+      <c r="AG31" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="AH31" s="269"/>
-      <c r="AI31" s="269"/>
-      <c r="AJ31" s="270"/>
-      <c r="AK31" s="271"/>
-      <c r="AL31" s="271"/>
-      <c r="AM31" s="271"/>
-      <c r="AN31" s="271"/>
-      <c r="AO31" s="271"/>
-      <c r="AP31" s="271"/>
-      <c r="AQ31" s="271"/>
-      <c r="AR31" s="271"/>
-      <c r="AS31" s="272"/>
+      <c r="AH31" s="111"/>
+      <c r="AI31" s="111"/>
+      <c r="AJ31" s="112"/>
+      <c r="AK31" s="113"/>
+      <c r="AL31" s="113"/>
+      <c r="AM31" s="113"/>
+      <c r="AN31" s="113"/>
+      <c r="AO31" s="113"/>
+      <c r="AP31" s="113"/>
+      <c r="AQ31" s="113"/>
+      <c r="AR31" s="113"/>
+      <c r="AS31" s="114"/>
       <c r="AT31" s="4"/>
       <c r="AU31" s="1"/>
     </row>
@@ -11103,54 +11250,54 @@
       <c r="A32" s="1"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="247"/>
-      <c r="E32" s="247"/>
-      <c r="F32" s="247"/>
-      <c r="G32" s="247"/>
-      <c r="H32" s="254"/>
-      <c r="I32" s="255"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="97"/>
       <c r="J32" s="22"/>
-      <c r="K32" s="273" t="s">
+      <c r="K32" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="273"/>
-      <c r="M32" s="273"/>
-      <c r="N32" s="273"/>
-      <c r="O32" s="273"/>
-      <c r="P32" s="274"/>
-      <c r="Q32" s="261"/>
-      <c r="R32" s="262"/>
-      <c r="S32" s="262"/>
-      <c r="T32" s="262"/>
-      <c r="U32" s="262"/>
-      <c r="V32" s="262"/>
-      <c r="W32" s="198" t="s">
+      <c r="L32" s="115"/>
+      <c r="M32" s="115"/>
+      <c r="N32" s="115"/>
+      <c r="O32" s="115"/>
+      <c r="P32" s="116"/>
+      <c r="Q32" s="103"/>
+      <c r="R32" s="104"/>
+      <c r="S32" s="104"/>
+      <c r="T32" s="104"/>
+      <c r="U32" s="104"/>
+      <c r="V32" s="104"/>
+      <c r="W32" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="X32" s="199"/>
-      <c r="Y32" s="200"/>
-      <c r="Z32" s="198"/>
-      <c r="AA32" s="199"/>
-      <c r="AB32" s="199"/>
-      <c r="AC32" s="199"/>
-      <c r="AD32" s="199"/>
-      <c r="AE32" s="199"/>
-      <c r="AF32" s="200"/>
-      <c r="AG32" s="201" t="s">
+      <c r="X32" s="118"/>
+      <c r="Y32" s="119"/>
+      <c r="Z32" s="117"/>
+      <c r="AA32" s="118"/>
+      <c r="AB32" s="118"/>
+      <c r="AC32" s="118"/>
+      <c r="AD32" s="118"/>
+      <c r="AE32" s="118"/>
+      <c r="AF32" s="119"/>
+      <c r="AG32" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="AH32" s="202"/>
-      <c r="AI32" s="203"/>
-      <c r="AJ32" s="204"/>
-      <c r="AK32" s="205"/>
-      <c r="AL32" s="205"/>
-      <c r="AM32" s="205"/>
-      <c r="AN32" s="205"/>
-      <c r="AO32" s="205"/>
-      <c r="AP32" s="205"/>
-      <c r="AQ32" s="205"/>
-      <c r="AR32" s="205"/>
-      <c r="AS32" s="206"/>
+      <c r="AH32" s="133"/>
+      <c r="AI32" s="134"/>
+      <c r="AJ32" s="135"/>
+      <c r="AK32" s="136"/>
+      <c r="AL32" s="136"/>
+      <c r="AM32" s="136"/>
+      <c r="AN32" s="136"/>
+      <c r="AO32" s="136"/>
+      <c r="AP32" s="136"/>
+      <c r="AQ32" s="136"/>
+      <c r="AR32" s="136"/>
+      <c r="AS32" s="137"/>
       <c r="AT32" s="4"/>
       <c r="AU32" s="1"/>
     </row>
@@ -11158,50 +11305,50 @@
       <c r="A33" s="1"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="207" t="s">
+      <c r="D33" s="90"/>
+      <c r="E33" s="90"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="I33" s="208"/>
-      <c r="J33" s="208"/>
-      <c r="K33" s="208"/>
-      <c r="L33" s="208"/>
-      <c r="M33" s="208"/>
-      <c r="N33" s="208"/>
-      <c r="O33" s="208"/>
-      <c r="P33" s="208"/>
-      <c r="Q33" s="208"/>
-      <c r="R33" s="208"/>
-      <c r="S33" s="208"/>
-      <c r="T33" s="208"/>
-      <c r="U33" s="208"/>
-      <c r="V33" s="208"/>
-      <c r="W33" s="208"/>
-      <c r="X33" s="208"/>
-      <c r="Y33" s="208"/>
-      <c r="Z33" s="208"/>
-      <c r="AA33" s="208"/>
-      <c r="AB33" s="208"/>
-      <c r="AC33" s="208"/>
-      <c r="AD33" s="208"/>
-      <c r="AE33" s="208"/>
-      <c r="AF33" s="208"/>
-      <c r="AG33" s="208"/>
-      <c r="AH33" s="208"/>
-      <c r="AI33" s="208"/>
-      <c r="AJ33" s="208"/>
-      <c r="AK33" s="208"/>
-      <c r="AL33" s="208"/>
-      <c r="AM33" s="208"/>
-      <c r="AN33" s="208"/>
-      <c r="AO33" s="208"/>
-      <c r="AP33" s="208"/>
-      <c r="AQ33" s="208"/>
-      <c r="AR33" s="208"/>
-      <c r="AS33" s="208"/>
+      <c r="I33" s="139"/>
+      <c r="J33" s="139"/>
+      <c r="K33" s="139"/>
+      <c r="L33" s="139"/>
+      <c r="M33" s="139"/>
+      <c r="N33" s="139"/>
+      <c r="O33" s="139"/>
+      <c r="P33" s="139"/>
+      <c r="Q33" s="139"/>
+      <c r="R33" s="139"/>
+      <c r="S33" s="139"/>
+      <c r="T33" s="139"/>
+      <c r="U33" s="139"/>
+      <c r="V33" s="139"/>
+      <c r="W33" s="139"/>
+      <c r="X33" s="139"/>
+      <c r="Y33" s="139"/>
+      <c r="Z33" s="139"/>
+      <c r="AA33" s="139"/>
+      <c r="AB33" s="139"/>
+      <c r="AC33" s="139"/>
+      <c r="AD33" s="139"/>
+      <c r="AE33" s="139"/>
+      <c r="AF33" s="139"/>
+      <c r="AG33" s="139"/>
+      <c r="AH33" s="139"/>
+      <c r="AI33" s="139"/>
+      <c r="AJ33" s="139"/>
+      <c r="AK33" s="139"/>
+      <c r="AL33" s="139"/>
+      <c r="AM33" s="139"/>
+      <c r="AN33" s="139"/>
+      <c r="AO33" s="139"/>
+      <c r="AP33" s="139"/>
+      <c r="AQ33" s="139"/>
+      <c r="AR33" s="139"/>
+      <c r="AS33" s="139"/>
       <c r="AT33" s="4"/>
       <c r="AU33" s="1"/>
     </row>
@@ -11254,19 +11401,19 @@
       <c r="AT34" s="4"/>
       <c r="AU34" s="1"/>
     </row>
-    <row r="35" spans="1:47" ht="16.5">
+    <row r="35" spans="1:47" ht="17">
       <c r="A35" s="1"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="233" t="s">
+      <c r="D35" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="234"/>
-      <c r="F35" s="234"/>
-      <c r="G35" s="234"/>
-      <c r="H35" s="234"/>
-      <c r="I35" s="234"/>
-      <c r="J35" s="234"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="131"/>
+      <c r="J35" s="131"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
@@ -11305,7 +11452,7 @@
       <c r="AT35" s="4"/>
       <c r="AU35" s="1"/>
     </row>
-    <row r="36" spans="1:47" ht="16.5">
+    <row r="36" spans="1:47" ht="17">
       <c r="A36" s="1"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -11403,7 +11550,7 @@
       <c r="AT37" s="4"/>
       <c r="AU37" s="1"/>
     </row>
-    <row r="38" spans="1:47" ht="16.5">
+    <row r="38" spans="1:47" ht="17">
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -11440,7 +11587,7 @@
       <c r="AT38" s="4"/>
       <c r="AU38" s="1"/>
     </row>
-    <row r="39" spans="1:47" ht="16.5">
+    <row r="39" spans="1:47" ht="17">
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -11477,22 +11624,22 @@
       <c r="AT39" s="4"/>
       <c r="AU39" s="1"/>
     </row>
-    <row r="40" spans="1:47" ht="16.5">
+    <row r="40" spans="1:47" ht="17">
       <c r="A40" s="1"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
-      <c r="M40" s="244"/>
-      <c r="N40" s="244"/>
-      <c r="O40" s="244"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="86"/>
+      <c r="M40" s="86"/>
+      <c r="N40" s="86"/>
+      <c r="O40" s="86"/>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
@@ -11526,7 +11673,7 @@
       <c r="AT40" s="4"/>
       <c r="AU40" s="1"/>
     </row>
-    <row r="41" spans="1:47" ht="16.5">
+    <row r="41" spans="1:47" ht="17">
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -11624,54 +11771,54 @@
       <c r="AT42" s="4"/>
       <c r="AU42" s="1"/>
     </row>
-    <row r="43" spans="1:47" ht="16.5">
+    <row r="43" spans="1:47" ht="17">
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="223">
+      <c r="D43" s="120">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="223"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="223"/>
-      <c r="K43" s="223"/>
-      <c r="L43" s="223"/>
-      <c r="M43" s="223"/>
-      <c r="N43" s="223"/>
-      <c r="O43" s="223"/>
-      <c r="P43" s="223"/>
-      <c r="Q43" s="223"/>
-      <c r="R43" s="223"/>
-      <c r="S43" s="223"/>
-      <c r="T43" s="223"/>
-      <c r="U43" s="223"/>
-      <c r="V43" s="223"/>
-      <c r="W43" s="223"/>
-      <c r="X43" s="223"/>
-      <c r="Y43" s="223"/>
-      <c r="Z43" s="223"/>
-      <c r="AA43" s="223"/>
-      <c r="AB43" s="223"/>
-      <c r="AC43" s="223"/>
-      <c r="AD43" s="223"/>
-      <c r="AE43" s="223"/>
-      <c r="AF43" s="223"/>
-      <c r="AG43" s="223"/>
-      <c r="AH43" s="223"/>
-      <c r="AI43" s="223"/>
-      <c r="AJ43" s="223"/>
-      <c r="AK43" s="223"/>
-      <c r="AL43" s="223"/>
-      <c r="AM43" s="223"/>
-      <c r="AN43" s="223"/>
-      <c r="AO43" s="223"/>
-      <c r="AP43" s="223"/>
-      <c r="AQ43" s="223"/>
-      <c r="AR43" s="223"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="120"/>
+      <c r="I43" s="120"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="120"/>
+      <c r="P43" s="120"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="120"/>
+      <c r="S43" s="120"/>
+      <c r="T43" s="120"/>
+      <c r="U43" s="120"/>
+      <c r="V43" s="120"/>
+      <c r="W43" s="120"/>
+      <c r="X43" s="120"/>
+      <c r="Y43" s="120"/>
+      <c r="Z43" s="120"/>
+      <c r="AA43" s="120"/>
+      <c r="AB43" s="120"/>
+      <c r="AC43" s="120"/>
+      <c r="AD43" s="120"/>
+      <c r="AE43" s="120"/>
+      <c r="AF43" s="120"/>
+      <c r="AG43" s="120"/>
+      <c r="AH43" s="120"/>
+      <c r="AI43" s="120"/>
+      <c r="AJ43" s="120"/>
+      <c r="AK43" s="120"/>
+      <c r="AL43" s="120"/>
+      <c r="AM43" s="120"/>
+      <c r="AN43" s="120"/>
+      <c r="AO43" s="120"/>
+      <c r="AP43" s="120"/>
+      <c r="AQ43" s="120"/>
+      <c r="AR43" s="120"/>
       <c r="AS43" s="4"/>
       <c r="AT43" s="4"/>
       <c r="AU43" s="1"/>
@@ -11725,7 +11872,7 @@
       <c r="AT44" s="4"/>
       <c r="AU44" s="1"/>
     </row>
-    <row r="45" spans="1:47" ht="16.5">
+    <row r="45" spans="1:47" ht="17">
       <c r="A45" s="1"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -11829,7 +11976,7 @@
       <c r="AT46" s="4"/>
       <c r="AU46" s="1"/>
     </row>
-    <row r="47" spans="1:47" ht="5.0999999999999996" customHeight="1">
+    <row r="47" spans="1:47" ht="5" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -11932,54 +12079,54 @@
       <c r="B49" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="224" t="s">
+      <c r="C49" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="224"/>
-      <c r="E49" s="224"/>
-      <c r="F49" s="224"/>
-      <c r="G49" s="224"/>
-      <c r="H49" s="224"/>
-      <c r="I49" s="224"/>
-      <c r="J49" s="224"/>
-      <c r="K49" s="224"/>
-      <c r="L49" s="224"/>
-      <c r="M49" s="224"/>
-      <c r="N49" s="224"/>
-      <c r="O49" s="224"/>
-      <c r="P49" s="224"/>
-      <c r="Q49" s="224"/>
-      <c r="R49" s="224"/>
-      <c r="S49" s="224"/>
-      <c r="T49" s="224"/>
-      <c r="U49" s="224"/>
-      <c r="V49" s="225"/>
+      <c r="D49" s="121"/>
+      <c r="E49" s="121"/>
+      <c r="F49" s="121"/>
+      <c r="G49" s="121"/>
+      <c r="H49" s="121"/>
+      <c r="I49" s="121"/>
+      <c r="J49" s="121"/>
+      <c r="K49" s="121"/>
+      <c r="L49" s="121"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="121"/>
+      <c r="R49" s="121"/>
+      <c r="S49" s="121"/>
+      <c r="T49" s="121"/>
+      <c r="U49" s="121"/>
+      <c r="V49" s="122"/>
       <c r="W49" s="28"/>
       <c r="X49" s="28"/>
       <c r="Y49" s="28"/>
-      <c r="Z49" s="226" t="s">
+      <c r="Z49" s="123" t="s">
         <v>55</v>
       </c>
-      <c r="AA49" s="227"/>
-      <c r="AB49" s="227"/>
-      <c r="AC49" s="227"/>
-      <c r="AD49" s="227"/>
-      <c r="AE49" s="227"/>
-      <c r="AF49" s="227"/>
-      <c r="AG49" s="227"/>
-      <c r="AH49" s="227"/>
-      <c r="AI49" s="227"/>
-      <c r="AJ49" s="227"/>
-      <c r="AK49" s="227"/>
-      <c r="AL49" s="227"/>
-      <c r="AM49" s="227"/>
-      <c r="AN49" s="227"/>
-      <c r="AO49" s="227"/>
-      <c r="AP49" s="227"/>
-      <c r="AQ49" s="227"/>
-      <c r="AR49" s="227"/>
-      <c r="AS49" s="227"/>
-      <c r="AT49" s="228"/>
+      <c r="AA49" s="124"/>
+      <c r="AB49" s="124"/>
+      <c r="AC49" s="124"/>
+      <c r="AD49" s="124"/>
+      <c r="AE49" s="124"/>
+      <c r="AF49" s="124"/>
+      <c r="AG49" s="124"/>
+      <c r="AH49" s="124"/>
+      <c r="AI49" s="124"/>
+      <c r="AJ49" s="124"/>
+      <c r="AK49" s="124"/>
+      <c r="AL49" s="124"/>
+      <c r="AM49" s="124"/>
+      <c r="AN49" s="124"/>
+      <c r="AO49" s="124"/>
+      <c r="AP49" s="124"/>
+      <c r="AQ49" s="124"/>
+      <c r="AR49" s="124"/>
+      <c r="AS49" s="124"/>
+      <c r="AT49" s="125"/>
       <c r="AU49" s="4"/>
     </row>
     <row r="50" spans="1:47" ht="18.75" customHeight="1" thickBot="1">
@@ -12012,27 +12159,27 @@
       <c r="W50" s="28"/>
       <c r="X50" s="28"/>
       <c r="Y50" s="28"/>
-      <c r="Z50" s="229"/>
-      <c r="AA50" s="230"/>
-      <c r="AB50" s="230"/>
-      <c r="AC50" s="230"/>
-      <c r="AD50" s="230"/>
-      <c r="AE50" s="230"/>
-      <c r="AF50" s="230"/>
-      <c r="AG50" s="230"/>
-      <c r="AH50" s="230"/>
-      <c r="AI50" s="230"/>
-      <c r="AJ50" s="230"/>
-      <c r="AK50" s="230"/>
-      <c r="AL50" s="230"/>
-      <c r="AM50" s="230"/>
-      <c r="AN50" s="230"/>
-      <c r="AO50" s="230"/>
-      <c r="AP50" s="230"/>
-      <c r="AQ50" s="230"/>
-      <c r="AR50" s="230"/>
-      <c r="AS50" s="230"/>
-      <c r="AT50" s="231"/>
+      <c r="Z50" s="126"/>
+      <c r="AA50" s="127"/>
+      <c r="AB50" s="127"/>
+      <c r="AC50" s="127"/>
+      <c r="AD50" s="127"/>
+      <c r="AE50" s="127"/>
+      <c r="AF50" s="127"/>
+      <c r="AG50" s="127"/>
+      <c r="AH50" s="127"/>
+      <c r="AI50" s="127"/>
+      <c r="AJ50" s="127"/>
+      <c r="AK50" s="127"/>
+      <c r="AL50" s="127"/>
+      <c r="AM50" s="127"/>
+      <c r="AN50" s="127"/>
+      <c r="AO50" s="127"/>
+      <c r="AP50" s="127"/>
+      <c r="AQ50" s="127"/>
+      <c r="AR50" s="127"/>
+      <c r="AS50" s="127"/>
+      <c r="AT50" s="128"/>
       <c r="AU50" s="4"/>
     </row>
     <row r="51" spans="1:47" ht="7.5" customHeight="1"/>
@@ -12043,33 +12190,112 @@
     <row r="57" spans="1:47" ht="14.25" customHeight="1">
       <c r="G57" s="34"/>
       <c r="H57" s="34"/>
-      <c r="AP57" s="232"/>
-      <c r="AQ57" s="232"/>
-      <c r="AR57" s="232"/>
-      <c r="AS57" s="232"/>
-      <c r="AT57" s="232"/>
-      <c r="AU57" s="232"/>
+      <c r="AP57" s="129"/>
+      <c r="AQ57" s="129"/>
+      <c r="AR57" s="129"/>
+      <c r="AS57" s="129"/>
+      <c r="AT57" s="129"/>
+      <c r="AU57" s="129"/>
     </row>
     <row r="58" spans="1:47" ht="14.25" customHeight="1">
       <c r="G58" s="35"/>
       <c r="H58" s="35"/>
-      <c r="AP58" s="232"/>
-      <c r="AQ58" s="232"/>
-      <c r="AR58" s="232"/>
-      <c r="AS58" s="232"/>
-      <c r="AT58" s="232"/>
-      <c r="AU58" s="232"/>
+      <c r="AP58" s="129"/>
+      <c r="AQ58" s="129"/>
+      <c r="AR58" s="129"/>
+      <c r="AS58" s="129"/>
+      <c r="AT58" s="129"/>
+      <c r="AU58" s="129"/>
     </row>
     <row r="59" spans="1:47">
-      <c r="AP59" s="232"/>
-      <c r="AQ59" s="232"/>
-      <c r="AR59" s="232"/>
-      <c r="AS59" s="232"/>
-      <c r="AT59" s="232"/>
-      <c r="AU59" s="232"/>
+      <c r="AP59" s="129"/>
+      <c r="AQ59" s="129"/>
+      <c r="AR59" s="129"/>
+      <c r="AS59" s="129"/>
+      <c r="AT59" s="129"/>
+      <c r="AU59" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="95">
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H7:AR7"/>
+    <mergeCell ref="I2:AM3"/>
+    <mergeCell ref="I4:AM4"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:AK6"/>
+    <mergeCell ref="AL6:AS6"/>
+    <mergeCell ref="AL8:AS8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="T9:AG9"/>
+    <mergeCell ref="AN9:AO9"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:P8"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="T8:AG8"/>
+    <mergeCell ref="AH8:AK8"/>
+    <mergeCell ref="D12:G14"/>
+    <mergeCell ref="H12:J14"/>
+    <mergeCell ref="K12:V12"/>
+    <mergeCell ref="W12:Z12"/>
+    <mergeCell ref="AA12:AC14"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:AG11"/>
+    <mergeCell ref="AH11:AK11"/>
+    <mergeCell ref="AL11:AO11"/>
+    <mergeCell ref="AD12:AO12"/>
+    <mergeCell ref="AP12:AS12"/>
+    <mergeCell ref="K13:M14"/>
+    <mergeCell ref="N13:Z14"/>
+    <mergeCell ref="AD13:AF14"/>
+    <mergeCell ref="AG13:AS14"/>
+    <mergeCell ref="I20:V20"/>
+    <mergeCell ref="W20:AT20"/>
+    <mergeCell ref="D21:G22"/>
+    <mergeCell ref="N21:X21"/>
+    <mergeCell ref="H22:Z22"/>
+    <mergeCell ref="AA22:AP22"/>
+    <mergeCell ref="D16:G20"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:T16"/>
+    <mergeCell ref="I17:N17"/>
+    <mergeCell ref="O17:T17"/>
+    <mergeCell ref="I18:N18"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="O19:T19"/>
+    <mergeCell ref="U19:Z19"/>
+    <mergeCell ref="AO23:AP23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:AS24"/>
+    <mergeCell ref="H25:AS26"/>
+    <mergeCell ref="D23:G28"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="S23:U23"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="H27:J28"/>
+    <mergeCell ref="K27:S27"/>
+    <mergeCell ref="T27:AD27"/>
+    <mergeCell ref="Z32:AF32"/>
+    <mergeCell ref="AG32:AI32"/>
+    <mergeCell ref="AJ32:AS32"/>
+    <mergeCell ref="H33:AS33"/>
+    <mergeCell ref="AE27:AH28"/>
+    <mergeCell ref="AI27:AS27"/>
+    <mergeCell ref="K28:S28"/>
+    <mergeCell ref="T28:AD28"/>
+    <mergeCell ref="AI28:AR28"/>
+    <mergeCell ref="D43:AR43"/>
+    <mergeCell ref="C49:V49"/>
+    <mergeCell ref="Z49:AT50"/>
+    <mergeCell ref="AP57:AU59"/>
+    <mergeCell ref="D35:J35"/>
     <mergeCell ref="AA16:AS19"/>
     <mergeCell ref="U16:Z16"/>
     <mergeCell ref="U17:Z17"/>
@@ -12086,85 +12312,6 @@
     <mergeCell ref="AJ31:AS31"/>
     <mergeCell ref="K32:P32"/>
     <mergeCell ref="W32:Y32"/>
-    <mergeCell ref="D43:AR43"/>
-    <mergeCell ref="C49:V49"/>
-    <mergeCell ref="Z49:AT50"/>
-    <mergeCell ref="AP57:AU59"/>
-    <mergeCell ref="D35:J35"/>
-    <mergeCell ref="Z32:AF32"/>
-    <mergeCell ref="AG32:AI32"/>
-    <mergeCell ref="AJ32:AS32"/>
-    <mergeCell ref="H33:AS33"/>
-    <mergeCell ref="AE27:AH28"/>
-    <mergeCell ref="AI27:AS27"/>
-    <mergeCell ref="K28:S28"/>
-    <mergeCell ref="T28:AD28"/>
-    <mergeCell ref="AI28:AR28"/>
-    <mergeCell ref="D23:G28"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="AC23:AD23"/>
-    <mergeCell ref="H27:J28"/>
-    <mergeCell ref="K27:S27"/>
-    <mergeCell ref="T27:AD27"/>
-    <mergeCell ref="AO23:AP23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:AS24"/>
-    <mergeCell ref="H25:AS26"/>
-    <mergeCell ref="I20:V20"/>
-    <mergeCell ref="W20:AT20"/>
-    <mergeCell ref="D21:G22"/>
-    <mergeCell ref="N21:X21"/>
-    <mergeCell ref="H22:Z22"/>
-    <mergeCell ref="AA22:AP22"/>
-    <mergeCell ref="D16:G20"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:T16"/>
-    <mergeCell ref="I17:N17"/>
-    <mergeCell ref="O17:T17"/>
-    <mergeCell ref="I18:N18"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="O19:T19"/>
-    <mergeCell ref="U19:Z19"/>
-    <mergeCell ref="AD12:AO12"/>
-    <mergeCell ref="AP12:AS12"/>
-    <mergeCell ref="K13:M14"/>
-    <mergeCell ref="N13:Z14"/>
-    <mergeCell ref="AD13:AF14"/>
-    <mergeCell ref="AG13:AS14"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:AG11"/>
-    <mergeCell ref="AH11:AK11"/>
-    <mergeCell ref="AL11:AO11"/>
-    <mergeCell ref="D12:G14"/>
-    <mergeCell ref="H12:J14"/>
-    <mergeCell ref="K12:V12"/>
-    <mergeCell ref="W12:Z12"/>
-    <mergeCell ref="AA12:AC14"/>
-    <mergeCell ref="AL8:AS8"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="T9:AG9"/>
-    <mergeCell ref="AN9:AO9"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:P8"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="T8:AG8"/>
-    <mergeCell ref="AH8:AK8"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="H7:AR7"/>
-    <mergeCell ref="I2:AM3"/>
-    <mergeCell ref="I4:AM4"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:AK6"/>
-    <mergeCell ref="AL6:AS6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -12175,18 +12322,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AU59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="1.375" style="3" customWidth="1"/>
-    <col min="2" max="3" width="1.75" style="3" customWidth="1"/>
+    <col min="1" max="1" width="1.33203125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="1.6640625" style="3" customWidth="1"/>
     <col min="4" max="45" width="2" style="3" customWidth="1"/>
-    <col min="46" max="46" width="1.75" style="3" customWidth="1"/>
-    <col min="47" max="47" width="1.625" style="3" customWidth="1"/>
+    <col min="46" max="47" width="1.6640625" style="3" customWidth="1"/>
     <col min="48" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -12241,2375 +12387,2048 @@
     </row>
     <row r="2" spans="1:47" ht="9.75" customHeight="1">
       <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="275" t="s">
-        <v>69</v>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="267" t="s">
+        <v>67</v>
       </c>
-      <c r="J2" s="276"/>
-      <c r="K2" s="276"/>
-      <c r="L2" s="276"/>
-      <c r="M2" s="276"/>
-      <c r="N2" s="276"/>
-      <c r="O2" s="276"/>
-      <c r="P2" s="276"/>
-      <c r="Q2" s="276"/>
-      <c r="R2" s="276"/>
-      <c r="S2" s="276"/>
-      <c r="T2" s="276"/>
-      <c r="U2" s="276"/>
-      <c r="V2" s="276"/>
-      <c r="W2" s="276"/>
-      <c r="X2" s="276"/>
-      <c r="Y2" s="276"/>
-      <c r="Z2" s="276"/>
-      <c r="AA2" s="276"/>
-      <c r="AB2" s="276"/>
-      <c r="AC2" s="276"/>
-      <c r="AD2" s="276"/>
-      <c r="AE2" s="276"/>
-      <c r="AF2" s="276"/>
-      <c r="AG2" s="276"/>
-      <c r="AH2" s="276"/>
-      <c r="AI2" s="276"/>
-      <c r="AJ2" s="276"/>
-      <c r="AK2" s="276"/>
-      <c r="AL2" s="276"/>
-      <c r="AM2" s="276"/>
-      <c r="AN2" s="45"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="43"/>
-      <c r="AS2" s="43"/>
-      <c r="AT2" s="43"/>
-      <c r="AU2" s="46"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="268"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="268"/>
+      <c r="Q2" s="268"/>
+      <c r="R2" s="268"/>
+      <c r="S2" s="268"/>
+      <c r="T2" s="268"/>
+      <c r="U2" s="268"/>
+      <c r="V2" s="268"/>
+      <c r="W2" s="268"/>
+      <c r="X2" s="268"/>
+      <c r="Y2" s="268"/>
+      <c r="Z2" s="268"/>
+      <c r="AA2" s="268"/>
+      <c r="AB2" s="268"/>
+      <c r="AC2" s="268"/>
+      <c r="AD2" s="268"/>
+      <c r="AE2" s="268"/>
+      <c r="AF2" s="268"/>
+      <c r="AG2" s="268"/>
+      <c r="AH2" s="268"/>
+      <c r="AI2" s="268"/>
+      <c r="AJ2" s="268"/>
+      <c r="AK2" s="268"/>
+      <c r="AL2" s="268"/>
+      <c r="AM2" s="268"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="43"/>
+      <c r="AP2" s="43"/>
+      <c r="AU2" s="44"/>
     </row>
     <row r="3" spans="1:47" ht="19.5" customHeight="1">
       <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="276"/>
-      <c r="J3" s="276"/>
-      <c r="K3" s="276"/>
-      <c r="L3" s="276"/>
-      <c r="M3" s="276"/>
-      <c r="N3" s="276"/>
-      <c r="O3" s="276"/>
-      <c r="P3" s="276"/>
-      <c r="Q3" s="276"/>
-      <c r="R3" s="276"/>
-      <c r="S3" s="276"/>
-      <c r="T3" s="276"/>
-      <c r="U3" s="276"/>
-      <c r="V3" s="276"/>
-      <c r="W3" s="276"/>
-      <c r="X3" s="276"/>
-      <c r="Y3" s="276"/>
-      <c r="Z3" s="276"/>
-      <c r="AA3" s="276"/>
-      <c r="AB3" s="276"/>
-      <c r="AC3" s="276"/>
-      <c r="AD3" s="276"/>
-      <c r="AE3" s="276"/>
-      <c r="AF3" s="276"/>
-      <c r="AG3" s="276"/>
-      <c r="AH3" s="276"/>
-      <c r="AI3" s="276"/>
-      <c r="AJ3" s="276"/>
-      <c r="AK3" s="276"/>
-      <c r="AL3" s="276"/>
-      <c r="AM3" s="276"/>
-      <c r="AN3" s="45"/>
-      <c r="AO3" s="45"/>
-      <c r="AP3" s="45"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="46"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="268"/>
+      <c r="M3" s="268"/>
+      <c r="N3" s="268"/>
+      <c r="O3" s="268"/>
+      <c r="P3" s="268"/>
+      <c r="Q3" s="268"/>
+      <c r="R3" s="268"/>
+      <c r="S3" s="268"/>
+      <c r="T3" s="268"/>
+      <c r="U3" s="268"/>
+      <c r="V3" s="268"/>
+      <c r="W3" s="268"/>
+      <c r="X3" s="268"/>
+      <c r="Y3" s="268"/>
+      <c r="Z3" s="268"/>
+      <c r="AA3" s="268"/>
+      <c r="AB3" s="268"/>
+      <c r="AC3" s="268"/>
+      <c r="AD3" s="268"/>
+      <c r="AE3" s="268"/>
+      <c r="AF3" s="268"/>
+      <c r="AG3" s="268"/>
+      <c r="AH3" s="268"/>
+      <c r="AI3" s="268"/>
+      <c r="AJ3" s="268"/>
+      <c r="AK3" s="268"/>
+      <c r="AL3" s="268"/>
+      <c r="AM3" s="268"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AU3" s="44"/>
     </row>
     <row r="4" spans="1:47" ht="15" customHeight="1">
       <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="277"/>
-      <c r="J4" s="277"/>
-      <c r="K4" s="277"/>
-      <c r="L4" s="277"/>
-      <c r="M4" s="277"/>
-      <c r="N4" s="277"/>
-      <c r="O4" s="277"/>
-      <c r="P4" s="277"/>
-      <c r="Q4" s="277"/>
-      <c r="R4" s="277"/>
-      <c r="S4" s="277"/>
-      <c r="T4" s="277"/>
-      <c r="U4" s="277"/>
-      <c r="V4" s="277"/>
-      <c r="W4" s="277"/>
-      <c r="X4" s="277"/>
-      <c r="Y4" s="277"/>
-      <c r="Z4" s="277"/>
-      <c r="AA4" s="277"/>
-      <c r="AB4" s="277"/>
-      <c r="AC4" s="277"/>
-      <c r="AD4" s="277"/>
-      <c r="AE4" s="277"/>
-      <c r="AF4" s="277"/>
-      <c r="AG4" s="277"/>
-      <c r="AH4" s="277"/>
-      <c r="AI4" s="277"/>
-      <c r="AJ4" s="277"/>
-      <c r="AK4" s="277"/>
-      <c r="AL4" s="277"/>
-      <c r="AM4" s="277"/>
-      <c r="AN4" s="45"/>
-      <c r="AO4" s="45"/>
-      <c r="AP4" s="45"/>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="43"/>
-      <c r="AS4" s="43"/>
-      <c r="AT4" s="43"/>
-      <c r="AU4" s="46"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
+      <c r="M4" s="269"/>
+      <c r="N4" s="269"/>
+      <c r="O4" s="269"/>
+      <c r="P4" s="269"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="269"/>
+      <c r="AB4" s="269"/>
+      <c r="AC4" s="269"/>
+      <c r="AD4" s="269"/>
+      <c r="AE4" s="269"/>
+      <c r="AF4" s="269"/>
+      <c r="AG4" s="269"/>
+      <c r="AH4" s="269"/>
+      <c r="AI4" s="269"/>
+      <c r="AJ4" s="269"/>
+      <c r="AK4" s="269"/>
+      <c r="AL4" s="269"/>
+      <c r="AM4" s="269"/>
+      <c r="AN4" s="43"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AU4" s="44"/>
     </row>
     <row r="5" spans="1:47" ht="10.5" customHeight="1">
       <c r="A5" s="42"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="47"/>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="47"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="44"/>
-      <c r="AR5" s="43"/>
-      <c r="AS5" s="43"/>
-      <c r="AT5" s="43"/>
-      <c r="AU5" s="46"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="45"/>
+      <c r="AC5" s="45"/>
+      <c r="AD5" s="45"/>
+      <c r="AE5" s="45"/>
+      <c r="AF5" s="45"/>
+      <c r="AG5" s="45"/>
+      <c r="AH5" s="45"/>
+      <c r="AI5" s="45"/>
+      <c r="AJ5" s="45"/>
+      <c r="AK5" s="45"/>
+      <c r="AL5" s="45"/>
+      <c r="AM5" s="45"/>
+      <c r="AN5" s="45"/>
+      <c r="AO5" s="45"/>
+      <c r="AP5" s="45"/>
+      <c r="AU5" s="44"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1">
       <c r="A6" s="42"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="49"/>
-      <c r="AD6" s="49"/>
-      <c r="AE6" s="49"/>
-      <c r="AF6" s="49"/>
-      <c r="AG6" s="49"/>
-      <c r="AH6" s="49"/>
-      <c r="AI6" s="49"/>
-      <c r="AJ6" s="49"/>
-      <c r="AK6" s="49"/>
-      <c r="AL6" s="49"/>
-      <c r="AM6" s="49"/>
-      <c r="AN6" s="49"/>
-      <c r="AO6" s="49"/>
-      <c r="AP6" s="49"/>
-      <c r="AQ6" s="49"/>
-      <c r="AR6" s="49"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="43"/>
-      <c r="AU6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="47"/>
+      <c r="AB6" s="47"/>
+      <c r="AC6" s="47"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="47"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="47"/>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="47"/>
+      <c r="AJ6" s="47"/>
+      <c r="AK6" s="47"/>
+      <c r="AL6" s="47"/>
+      <c r="AM6" s="47"/>
+      <c r="AN6" s="47"/>
+      <c r="AO6" s="47"/>
+      <c r="AP6" s="47"/>
+      <c r="AQ6" s="47"/>
+      <c r="AR6" s="47"/>
+      <c r="AU6" s="44"/>
     </row>
     <row r="7" spans="1:47" ht="18" customHeight="1">
       <c r="A7" s="42"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="49" t="s">
-        <v>70</v>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="47" t="s">
+        <v>68</v>
       </c>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="49"/>
-      <c r="AE7" s="49"/>
-      <c r="AF7" s="49"/>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="49"/>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
-      <c r="AL7" s="49"/>
-      <c r="AM7" s="49"/>
-      <c r="AN7" s="49"/>
-      <c r="AO7" s="49"/>
-      <c r="AP7" s="49"/>
-      <c r="AQ7" s="49"/>
-      <c r="AR7" s="49"/>
-      <c r="AS7" s="43"/>
-      <c r="AT7" s="43"/>
-      <c r="AU7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="47"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="47"/>
+      <c r="AD7" s="47"/>
+      <c r="AE7" s="47"/>
+      <c r="AF7" s="47"/>
+      <c r="AG7" s="47"/>
+      <c r="AH7" s="47"/>
+      <c r="AI7" s="47"/>
+      <c r="AJ7" s="47"/>
+      <c r="AK7" s="47"/>
+      <c r="AL7" s="47"/>
+      <c r="AM7" s="47"/>
+      <c r="AN7" s="47"/>
+      <c r="AO7" s="47"/>
+      <c r="AP7" s="47"/>
+      <c r="AQ7" s="47"/>
+      <c r="AR7" s="47"/>
+      <c r="AU7" s="44"/>
     </row>
     <row r="8" spans="1:47" ht="18" customHeight="1">
       <c r="A8" s="42"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="49"/>
-      <c r="AI8" s="49"/>
-      <c r="AJ8" s="49"/>
-      <c r="AK8" s="49"/>
-      <c r="AL8" s="51" t="s">
-        <v>71</v>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="48"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="49"/>
+      <c r="AB8" s="48"/>
+      <c r="AC8" s="48"/>
+      <c r="AD8" s="48"/>
+      <c r="AE8" s="48"/>
+      <c r="AF8" s="48"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47"/>
+      <c r="AK8" s="47"/>
+      <c r="AL8" s="48" t="s">
+        <v>69</v>
       </c>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="51"/>
-      <c r="AP8" s="51"/>
-      <c r="AQ8" s="51"/>
-      <c r="AR8" s="51"/>
-      <c r="AS8" s="43"/>
-      <c r="AT8" s="43"/>
-      <c r="AU8" s="46"/>
+      <c r="AM8" s="48"/>
+      <c r="AN8" s="48"/>
+      <c r="AO8" s="48"/>
+      <c r="AP8" s="48"/>
+      <c r="AQ8" s="48"/>
+      <c r="AR8" s="48"/>
+      <c r="AU8" s="44"/>
     </row>
     <row r="9" spans="1:47" ht="18" customHeight="1">
       <c r="A9" s="42"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="49"/>
-      <c r="AN9" s="49"/>
-      <c r="AO9" s="49"/>
-      <c r="AP9" s="49"/>
-      <c r="AQ9" s="49"/>
-      <c r="AR9" s="49"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
+      <c r="AG9" s="48"/>
+      <c r="AH9" s="47"/>
+      <c r="AI9" s="47"/>
+      <c r="AJ9" s="47"/>
+      <c r="AK9" s="47"/>
+      <c r="AL9" s="47"/>
+      <c r="AM9" s="47"/>
+      <c r="AN9" s="47"/>
+      <c r="AO9" s="47"/>
+      <c r="AP9" s="47"/>
+      <c r="AQ9" s="47"/>
+      <c r="AR9" s="47"/>
+      <c r="AU9" s="44"/>
     </row>
     <row r="10" spans="1:47" ht="9" customHeight="1">
       <c r="A10" s="42"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="53"/>
-      <c r="AB10" s="53"/>
-      <c r="AC10" s="53"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="53"/>
-      <c r="AG10" s="53"/>
-      <c r="AH10" s="53"/>
-      <c r="AI10" s="53"/>
-      <c r="AJ10" s="53"/>
-      <c r="AK10" s="53"/>
-      <c r="AL10" s="53"/>
-      <c r="AM10" s="53"/>
-      <c r="AN10" s="53"/>
-      <c r="AO10" s="53"/>
-      <c r="AP10" s="53"/>
-      <c r="AQ10" s="53"/>
-      <c r="AR10" s="53"/>
-      <c r="AS10" s="43"/>
-      <c r="AT10" s="43"/>
-      <c r="AU10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="49"/>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="49"/>
+      <c r="AE10" s="49"/>
+      <c r="AF10" s="49"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
+      <c r="AL10" s="49"/>
+      <c r="AM10" s="49"/>
+      <c r="AN10" s="49"/>
+      <c r="AO10" s="49"/>
+      <c r="AP10" s="49"/>
+      <c r="AQ10" s="49"/>
+      <c r="AR10" s="49"/>
+      <c r="AU10" s="44"/>
     </row>
     <row r="11" spans="1:47" ht="19.5" customHeight="1">
       <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="52"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="52"/>
-      <c r="Z11" s="52"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52"/>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
-      <c r="AL11" s="52">
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
+      <c r="AL11" s="49">
         <v>16</v>
       </c>
-      <c r="AM11" s="52"/>
-      <c r="AN11" s="52"/>
-      <c r="AO11" s="52"/>
-      <c r="AP11" s="52"/>
-      <c r="AQ11" s="52"/>
-      <c r="AR11" s="52"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="46"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
+      <c r="AO11" s="49"/>
+      <c r="AP11" s="49"/>
+      <c r="AQ11" s="49"/>
+      <c r="AR11" s="49"/>
+      <c r="AU11" s="44"/>
     </row>
     <row r="12" spans="1:47" ht="19.5" customHeight="1">
       <c r="A12" s="42"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="55"/>
-      <c r="Y12" s="55"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="54">
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="47"/>
+      <c r="AB12" s="47"/>
+      <c r="AC12" s="47"/>
+      <c r="AD12" s="50">
         <v>45945</v>
       </c>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="54"/>
-      <c r="AH12" s="54"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54"/>
-      <c r="AK12" s="54"/>
-      <c r="AL12" s="54"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="55"/>
-      <c r="AO12" s="55"/>
-      <c r="AP12" s="55"/>
-      <c r="AQ12" s="55"/>
-      <c r="AR12" s="53"/>
-      <c r="AS12" s="43"/>
-      <c r="AT12" s="43"/>
-      <c r="AU12" s="46"/>
+      <c r="AE12" s="50"/>
+      <c r="AF12" s="50"/>
+      <c r="AG12" s="50"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="50"/>
+      <c r="AK12" s="50"/>
+      <c r="AL12" s="50"/>
+      <c r="AM12" s="50"/>
+      <c r="AN12" s="51"/>
+      <c r="AO12" s="51"/>
+      <c r="AP12" s="51"/>
+      <c r="AQ12" s="51"/>
+      <c r="AR12" s="49"/>
+      <c r="AU12" s="44"/>
     </row>
     <row r="13" spans="1:47" ht="12" customHeight="1">
       <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="53"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="53"/>
-      <c r="AB13" s="53"/>
-      <c r="AC13" s="53"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="53"/>
-      <c r="AG13" s="53"/>
-      <c r="AH13" s="53"/>
-      <c r="AI13" s="53"/>
-      <c r="AJ13" s="53"/>
-      <c r="AK13" s="53"/>
-      <c r="AL13" s="53"/>
-      <c r="AM13" s="53"/>
-      <c r="AN13" s="53"/>
-      <c r="AO13" s="53"/>
-      <c r="AP13" s="53"/>
-      <c r="AQ13" s="53"/>
-      <c r="AR13" s="53"/>
-      <c r="AS13" s="43"/>
-      <c r="AT13" s="43"/>
-      <c r="AU13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="49"/>
+      <c r="AE13" s="49"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
+      <c r="AL13" s="49"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="49"/>
+      <c r="AQ13" s="49"/>
+      <c r="AR13" s="49"/>
+      <c r="AU13" s="44"/>
     </row>
     <row r="14" spans="1:47" ht="12" customHeight="1">
       <c r="A14" s="42"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="53"/>
-      <c r="AB14" s="53"/>
-      <c r="AC14" s="53"/>
-      <c r="AD14" s="53"/>
-      <c r="AE14" s="53"/>
-      <c r="AF14" s="53"/>
-      <c r="AG14" s="53"/>
-      <c r="AH14" s="53"/>
-      <c r="AI14" s="53"/>
-      <c r="AJ14" s="53"/>
-      <c r="AK14" s="53"/>
-      <c r="AL14" s="53"/>
-      <c r="AM14" s="53"/>
-      <c r="AN14" s="53"/>
-      <c r="AO14" s="53"/>
-      <c r="AP14" s="53"/>
-      <c r="AQ14" s="53"/>
-      <c r="AR14" s="53"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="49"/>
+      <c r="AC14" s="49"/>
+      <c r="AD14" s="49"/>
+      <c r="AE14" s="49"/>
+      <c r="AF14" s="49"/>
+      <c r="AG14" s="49"/>
+      <c r="AH14" s="49"/>
+      <c r="AI14" s="49"/>
+      <c r="AJ14" s="49"/>
+      <c r="AK14" s="49"/>
+      <c r="AL14" s="49"/>
+      <c r="AM14" s="49"/>
+      <c r="AN14" s="49"/>
+      <c r="AO14" s="49"/>
+      <c r="AP14" s="49"/>
+      <c r="AQ14" s="49"/>
+      <c r="AR14" s="49"/>
+      <c r="AU14" s="44"/>
     </row>
     <row r="15" spans="1:47" ht="9.75" customHeight="1">
       <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="53"/>
-      <c r="V15" s="53"/>
-      <c r="W15" s="53"/>
-      <c r="X15" s="53"/>
-      <c r="Y15" s="53"/>
-      <c r="Z15" s="53"/>
-      <c r="AA15" s="53"/>
-      <c r="AB15" s="53"/>
-      <c r="AC15" s="53"/>
-      <c r="AD15" s="53"/>
-      <c r="AE15" s="53"/>
-      <c r="AF15" s="53"/>
-      <c r="AG15" s="53"/>
-      <c r="AH15" s="53"/>
-      <c r="AI15" s="53"/>
-      <c r="AJ15" s="53"/>
-      <c r="AK15" s="53"/>
-      <c r="AL15" s="53"/>
-      <c r="AM15" s="53"/>
-      <c r="AN15" s="53"/>
-      <c r="AO15" s="53"/>
-      <c r="AP15" s="53"/>
-      <c r="AQ15" s="53"/>
-      <c r="AR15" s="53"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="49"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="49"/>
+      <c r="AM15" s="49"/>
+      <c r="AN15" s="49"/>
+      <c r="AO15" s="49"/>
+      <c r="AP15" s="49"/>
+      <c r="AQ15" s="49"/>
+      <c r="AR15" s="49"/>
+      <c r="AU15" s="44"/>
     </row>
     <row r="16" spans="1:47" ht="15" customHeight="1">
       <c r="A16" s="42"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="57"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
-      <c r="U16" s="57" t="s">
-        <v>72</v>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
+      <c r="U16" s="53" t="s">
+        <v>70</v>
       </c>
-      <c r="V16" s="57"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="57"/>
-      <c r="Y16" s="57"/>
-      <c r="Z16" s="57"/>
-      <c r="AA16" s="57"/>
-      <c r="AB16" s="57"/>
-      <c r="AC16" s="57"/>
-      <c r="AD16" s="57"/>
-      <c r="AE16" s="57"/>
-      <c r="AF16" s="57"/>
-      <c r="AG16" s="57"/>
-      <c r="AH16" s="57"/>
-      <c r="AI16" s="57"/>
-      <c r="AJ16" s="57"/>
-      <c r="AK16" s="57"/>
-      <c r="AL16" s="57"/>
-      <c r="AM16" s="57"/>
-      <c r="AN16" s="57"/>
-      <c r="AO16" s="57"/>
-      <c r="AP16" s="57"/>
-      <c r="AQ16" s="57"/>
-      <c r="AR16" s="57"/>
-      <c r="AS16" s="43"/>
-      <c r="AT16" s="43"/>
-      <c r="AU16" s="46"/>
+      <c r="V16" s="53"/>
+      <c r="W16" s="53"/>
+      <c r="X16" s="53"/>
+      <c r="Y16" s="53"/>
+      <c r="Z16" s="53"/>
+      <c r="AA16" s="53"/>
+      <c r="AB16" s="53"/>
+      <c r="AC16" s="53"/>
+      <c r="AD16" s="53"/>
+      <c r="AE16" s="53"/>
+      <c r="AF16" s="53"/>
+      <c r="AG16" s="53"/>
+      <c r="AH16" s="53"/>
+      <c r="AI16" s="53"/>
+      <c r="AJ16" s="53"/>
+      <c r="AK16" s="53"/>
+      <c r="AL16" s="53"/>
+      <c r="AM16" s="53"/>
+      <c r="AN16" s="53"/>
+      <c r="AO16" s="53"/>
+      <c r="AP16" s="53"/>
+      <c r="AQ16" s="53"/>
+      <c r="AR16" s="53"/>
+      <c r="AU16" s="44"/>
     </row>
     <row r="17" spans="1:47" ht="15" customHeight="1">
       <c r="A17" s="42"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="59">
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="54"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="55">
         <v>33</v>
       </c>
-      <c r="P17" s="59">
+      <c r="P17" s="55">
         <v>16</v>
       </c>
-      <c r="Q17" s="59">
+      <c r="Q17" s="55">
         <v>16</v>
       </c>
-      <c r="R17" s="59">
+      <c r="R17" s="55">
         <v>16</v>
       </c>
-      <c r="S17" s="59"/>
-      <c r="T17" s="59"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
-      <c r="AD17" s="60"/>
-      <c r="AE17" s="60"/>
-      <c r="AF17" s="60"/>
-      <c r="AG17" s="60"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="60"/>
-      <c r="AK17" s="60"/>
-      <c r="AL17" s="60"/>
-      <c r="AM17" s="60"/>
-      <c r="AN17" s="60"/>
-      <c r="AO17" s="60"/>
-      <c r="AP17" s="60"/>
-      <c r="AQ17" s="60"/>
-      <c r="AR17" s="60"/>
-      <c r="AS17" s="43"/>
-      <c r="AT17" s="43"/>
-      <c r="AU17" s="46"/>
+      <c r="S17" s="55"/>
+      <c r="T17" s="55"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="56"/>
+      <c r="Z17" s="56"/>
+      <c r="AA17" s="56"/>
+      <c r="AB17" s="56"/>
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="56"/>
+      <c r="AF17" s="56"/>
+      <c r="AG17" s="56"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="56"/>
+      <c r="AJ17" s="56"/>
+      <c r="AK17" s="56"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="56"/>
+      <c r="AO17" s="56"/>
+      <c r="AP17" s="56"/>
+      <c r="AQ17" s="56"/>
+      <c r="AR17" s="56"/>
+      <c r="AU17" s="44"/>
     </row>
     <row r="18" spans="1:47" ht="15" customHeight="1">
       <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="61">
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="57">
         <v>32</v>
       </c>
-      <c r="J18" s="61">
+      <c r="J18" s="57">
         <v>16</v>
       </c>
-      <c r="K18" s="61">
+      <c r="K18" s="57">
         <v>16</v>
       </c>
-      <c r="L18" s="61">
+      <c r="L18" s="57">
         <v>16</v>
       </c>
-      <c r="M18" s="61">
+      <c r="M18" s="57">
         <v>16</v>
       </c>
-      <c r="N18" s="61">
+      <c r="N18" s="57">
         <v>16</v>
       </c>
-      <c r="O18" s="61"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="61"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="61"/>
-      <c r="T18" s="61"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="52"/>
-      <c r="X18" s="52"/>
-      <c r="Y18" s="52"/>
-      <c r="Z18" s="52"/>
-      <c r="AA18" s="52"/>
-      <c r="AB18" s="52"/>
-      <c r="AC18" s="52"/>
-      <c r="AD18" s="52"/>
-      <c r="AE18" s="52"/>
-      <c r="AF18" s="52"/>
-      <c r="AG18" s="52"/>
-      <c r="AH18" s="52"/>
-      <c r="AI18" s="52"/>
-      <c r="AJ18" s="52"/>
-      <c r="AK18" s="52"/>
-      <c r="AL18" s="52"/>
-      <c r="AM18" s="52"/>
-      <c r="AN18" s="52"/>
-      <c r="AO18" s="52"/>
-      <c r="AP18" s="52"/>
-      <c r="AQ18" s="52"/>
-      <c r="AR18" s="52"/>
-      <c r="AS18" s="43"/>
-      <c r="AT18" s="43"/>
-      <c r="AU18" s="46"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="47"/>
+      <c r="V18" s="47"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="49"/>
+      <c r="AC18" s="49"/>
+      <c r="AD18" s="49"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="49"/>
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49"/>
+      <c r="AI18" s="49"/>
+      <c r="AJ18" s="49"/>
+      <c r="AK18" s="49"/>
+      <c r="AL18" s="49"/>
+      <c r="AM18" s="49"/>
+      <c r="AN18" s="49"/>
+      <c r="AO18" s="49"/>
+      <c r="AP18" s="49"/>
+      <c r="AQ18" s="49"/>
+      <c r="AR18" s="49"/>
+      <c r="AU18" s="44"/>
     </row>
     <row r="19" spans="1:47" ht="15" customHeight="1">
       <c r="A19" s="42"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="52"/>
-      <c r="X19" s="52"/>
-      <c r="Y19" s="52"/>
-      <c r="Z19" s="52"/>
-      <c r="AA19" s="52"/>
-      <c r="AB19" s="52"/>
-      <c r="AC19" s="52"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="52"/>
-      <c r="AF19" s="52"/>
-      <c r="AG19" s="52"/>
-      <c r="AH19" s="52"/>
-      <c r="AI19" s="52"/>
-      <c r="AJ19" s="52"/>
-      <c r="AK19" s="52"/>
-      <c r="AL19" s="52"/>
-      <c r="AM19" s="52"/>
-      <c r="AN19" s="52"/>
-      <c r="AO19" s="52"/>
-      <c r="AP19" s="52"/>
-      <c r="AQ19" s="52"/>
-      <c r="AR19" s="52"/>
-      <c r="AS19" s="43"/>
-      <c r="AT19" s="43"/>
-      <c r="AU19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="47"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="49"/>
+      <c r="AB19" s="49"/>
+      <c r="AC19" s="49"/>
+      <c r="AD19" s="49"/>
+      <c r="AE19" s="49"/>
+      <c r="AF19" s="49"/>
+      <c r="AG19" s="49"/>
+      <c r="AH19" s="49"/>
+      <c r="AI19" s="49"/>
+      <c r="AJ19" s="49"/>
+      <c r="AK19" s="49"/>
+      <c r="AL19" s="49"/>
+      <c r="AM19" s="49"/>
+      <c r="AN19" s="49"/>
+      <c r="AO19" s="49"/>
+      <c r="AP19" s="49"/>
+      <c r="AQ19" s="49"/>
+      <c r="AR19" s="49"/>
+      <c r="AU19" s="44"/>
     </row>
     <row r="20" spans="1:47" ht="15" customHeight="1">
       <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="63"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="53"/>
-      <c r="U20" s="53"/>
-      <c r="V20" s="53"/>
-      <c r="W20" s="53"/>
-      <c r="X20" s="53"/>
-      <c r="Y20" s="53"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="53"/>
-      <c r="AB20" s="53"/>
-      <c r="AC20" s="53"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="53"/>
-      <c r="AF20" s="53"/>
-      <c r="AG20" s="53"/>
-      <c r="AH20" s="53"/>
-      <c r="AI20" s="53"/>
-      <c r="AJ20" s="53"/>
-      <c r="AK20" s="53"/>
-      <c r="AL20" s="53"/>
-      <c r="AM20" s="53"/>
-      <c r="AN20" s="53"/>
-      <c r="AO20" s="53"/>
-      <c r="AP20" s="53"/>
-      <c r="AQ20" s="53"/>
-      <c r="AR20" s="53"/>
-      <c r="AS20" s="43"/>
-      <c r="AT20" s="43"/>
-      <c r="AU20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="49"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="49"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="49"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="49"/>
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="49"/>
+      <c r="AF20" s="49"/>
+      <c r="AG20" s="49"/>
+      <c r="AH20" s="49"/>
+      <c r="AI20" s="49"/>
+      <c r="AJ20" s="49"/>
+      <c r="AK20" s="49"/>
+      <c r="AL20" s="49"/>
+      <c r="AM20" s="49"/>
+      <c r="AN20" s="49"/>
+      <c r="AO20" s="49"/>
+      <c r="AP20" s="49"/>
+      <c r="AQ20" s="49"/>
+      <c r="AR20" s="49"/>
+      <c r="AU20" s="44"/>
     </row>
     <row r="21" spans="1:47" ht="21" customHeight="1">
       <c r="A21" s="42"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="53"/>
-      <c r="T21" s="53"/>
-      <c r="U21" s="53"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="53"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="53"/>
-      <c r="AA21" s="53"/>
-      <c r="AB21" s="53"/>
-      <c r="AC21" s="53"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="53"/>
-      <c r="AF21" s="53"/>
-      <c r="AG21" s="53"/>
-      <c r="AH21" s="53"/>
-      <c r="AI21" s="53"/>
-      <c r="AJ21" s="53"/>
-      <c r="AK21" s="53"/>
-      <c r="AL21" s="53"/>
-      <c r="AM21" s="53"/>
-      <c r="AN21" s="53"/>
-      <c r="AO21" s="53"/>
-      <c r="AP21" s="53"/>
-      <c r="AQ21" s="53"/>
-      <c r="AR21" s="53"/>
-      <c r="AS21" s="43"/>
-      <c r="AT21" s="43"/>
-      <c r="AU21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49"/>
+      <c r="AE21" s="49"/>
+      <c r="AF21" s="49"/>
+      <c r="AG21" s="49"/>
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="49"/>
+      <c r="AJ21" s="49"/>
+      <c r="AK21" s="49"/>
+      <c r="AL21" s="49"/>
+      <c r="AM21" s="49"/>
+      <c r="AN21" s="49"/>
+      <c r="AO21" s="49"/>
+      <c r="AP21" s="49"/>
+      <c r="AQ21" s="49"/>
+      <c r="AR21" s="49"/>
+      <c r="AU21" s="44"/>
     </row>
     <row r="22" spans="1:47" ht="21" customHeight="1">
       <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="67"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="67"/>
-      <c r="AH22" s="67"/>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="67"/>
-      <c r="AK22" s="67"/>
-      <c r="AL22" s="67"/>
-      <c r="AM22" s="67"/>
-      <c r="AN22" s="67"/>
-      <c r="AO22" s="67"/>
-      <c r="AP22" s="67"/>
-      <c r="AQ22" s="67"/>
-      <c r="AR22" s="67"/>
-      <c r="AS22" s="43"/>
-      <c r="AT22" s="43"/>
-      <c r="AU22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="47"/>
+      <c r="AN22" s="47"/>
+      <c r="AO22" s="47"/>
+      <c r="AP22" s="47"/>
+      <c r="AQ22" s="47"/>
+      <c r="AR22" s="47"/>
+      <c r="AU22" s="44"/>
     </row>
     <row r="23" spans="1:47" ht="20.25" customHeight="1">
       <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="66"/>
-      <c r="AA23" s="66"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="67"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="67"/>
-      <c r="AM23" s="67"/>
-      <c r="AN23" s="67"/>
-      <c r="AO23" s="67"/>
-      <c r="AP23" s="67"/>
-      <c r="AQ23" s="67"/>
-      <c r="AR23" s="67"/>
-      <c r="AS23" s="43"/>
-      <c r="AT23" s="43"/>
-      <c r="AU23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
+      <c r="Z23" s="61"/>
+      <c r="AA23" s="61"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="61"/>
+      <c r="AD23" s="47"/>
+      <c r="AE23" s="47"/>
+      <c r="AF23" s="47"/>
+      <c r="AG23" s="47"/>
+      <c r="AH23" s="47"/>
+      <c r="AI23" s="47"/>
+      <c r="AJ23" s="47"/>
+      <c r="AK23" s="47"/>
+      <c r="AL23" s="47"/>
+      <c r="AM23" s="47"/>
+      <c r="AN23" s="47"/>
+      <c r="AO23" s="47"/>
+      <c r="AP23" s="47"/>
+      <c r="AQ23" s="47"/>
+      <c r="AR23" s="47"/>
+      <c r="AU23" s="44"/>
     </row>
     <row r="24" spans="1:47" ht="20.25" customHeight="1">
       <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="68"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="69"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="69"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="69"/>
-      <c r="AD24" s="69"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="69"/>
-      <c r="AG24" s="69"/>
-      <c r="AH24" s="69"/>
-      <c r="AI24" s="69"/>
-      <c r="AJ24" s="69"/>
-      <c r="AK24" s="69"/>
-      <c r="AL24" s="69"/>
-      <c r="AM24" s="69"/>
-      <c r="AN24" s="69"/>
-      <c r="AO24" s="69"/>
-      <c r="AP24" s="69"/>
-      <c r="AQ24" s="69"/>
-      <c r="AR24" s="70"/>
-      <c r="AS24" s="43"/>
-      <c r="AT24" s="43"/>
-      <c r="AU24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="62"/>
+      <c r="V24" s="62"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="62"/>
+      <c r="AA24" s="62"/>
+      <c r="AB24" s="62"/>
+      <c r="AC24" s="62"/>
+      <c r="AD24" s="62"/>
+      <c r="AE24" s="62"/>
+      <c r="AF24" s="62"/>
+      <c r="AG24" s="62"/>
+      <c r="AH24" s="62"/>
+      <c r="AI24" s="62"/>
+      <c r="AJ24" s="62"/>
+      <c r="AK24" s="62"/>
+      <c r="AL24" s="62"/>
+      <c r="AM24" s="62"/>
+      <c r="AN24" s="62"/>
+      <c r="AO24" s="62"/>
+      <c r="AP24" s="62"/>
+      <c r="AQ24" s="62"/>
+      <c r="AR24" s="63"/>
+      <c r="AU24" s="44"/>
     </row>
     <row r="25" spans="1:47" ht="20.25" customHeight="1">
       <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="49"/>
-      <c r="L25" s="49"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="69"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="69"/>
-      <c r="AB25" s="69"/>
-      <c r="AC25" s="69"/>
-      <c r="AD25" s="69"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="69"/>
-      <c r="AG25" s="69"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="69"/>
-      <c r="AJ25" s="69"/>
-      <c r="AK25" s="69"/>
-      <c r="AL25" s="69"/>
-      <c r="AM25" s="69"/>
-      <c r="AN25" s="69"/>
-      <c r="AO25" s="69"/>
-      <c r="AP25" s="69"/>
-      <c r="AQ25" s="69"/>
-      <c r="AR25" s="70"/>
-      <c r="AS25" s="43"/>
-      <c r="AT25" s="43"/>
-      <c r="AU25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="62"/>
+      <c r="X25" s="62"/>
+      <c r="Y25" s="62"/>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="62"/>
+      <c r="AB25" s="62"/>
+      <c r="AC25" s="62"/>
+      <c r="AD25" s="62"/>
+      <c r="AE25" s="62"/>
+      <c r="AF25" s="62"/>
+      <c r="AG25" s="62"/>
+      <c r="AH25" s="62"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="62"/>
+      <c r="AK25" s="62"/>
+      <c r="AL25" s="62"/>
+      <c r="AM25" s="62"/>
+      <c r="AN25" s="62"/>
+      <c r="AO25" s="62"/>
+      <c r="AP25" s="62"/>
+      <c r="AQ25" s="62"/>
+      <c r="AR25" s="63"/>
+      <c r="AU25" s="44"/>
     </row>
     <row r="26" spans="1:47" ht="20.25" customHeight="1">
       <c r="A26" s="42"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="49"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="49"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="49"/>
-      <c r="AE26" s="49"/>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="49"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
-      <c r="AL26" s="49"/>
-      <c r="AM26" s="49"/>
-      <c r="AN26" s="49"/>
-      <c r="AO26" s="49"/>
-      <c r="AP26" s="49"/>
-      <c r="AQ26" s="49"/>
-      <c r="AR26" s="49"/>
-      <c r="AS26" s="43"/>
-      <c r="AT26" s="43"/>
-      <c r="AU26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="47"/>
+      <c r="U26" s="47"/>
+      <c r="V26" s="47"/>
+      <c r="W26" s="47"/>
+      <c r="X26" s="47"/>
+      <c r="Y26" s="47"/>
+      <c r="Z26" s="47"/>
+      <c r="AA26" s="47"/>
+      <c r="AB26" s="47"/>
+      <c r="AC26" s="47"/>
+      <c r="AD26" s="47"/>
+      <c r="AE26" s="47"/>
+      <c r="AF26" s="47"/>
+      <c r="AG26" s="47"/>
+      <c r="AH26" s="47"/>
+      <c r="AI26" s="47"/>
+      <c r="AJ26" s="47"/>
+      <c r="AK26" s="47"/>
+      <c r="AL26" s="47"/>
+      <c r="AM26" s="47"/>
+      <c r="AN26" s="47"/>
+      <c r="AO26" s="47"/>
+      <c r="AP26" s="47"/>
+      <c r="AQ26" s="47"/>
+      <c r="AR26" s="47"/>
+      <c r="AU26" s="44"/>
     </row>
     <row r="27" spans="1:47" ht="20.25" customHeight="1">
       <c r="A27" s="42"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
-      <c r="U27" s="49"/>
-      <c r="V27" s="49"/>
-      <c r="W27" s="49"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="49"/>
-      <c r="AA27" s="49"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="49"/>
-      <c r="AD27" s="49"/>
-      <c r="AE27" s="49"/>
-      <c r="AF27" s="49"/>
-      <c r="AG27" s="49"/>
-      <c r="AH27" s="49"/>
-      <c r="AI27" s="49"/>
-      <c r="AJ27" s="49"/>
-      <c r="AK27" s="49"/>
-      <c r="AL27" s="49"/>
-      <c r="AM27" s="49"/>
-      <c r="AN27" s="49"/>
-      <c r="AO27" s="49"/>
-      <c r="AP27" s="49"/>
-      <c r="AQ27" s="49"/>
-      <c r="AR27" s="49"/>
-      <c r="AS27" s="43"/>
-      <c r="AT27" s="43"/>
-      <c r="AU27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="47"/>
+      <c r="AA27" s="47"/>
+      <c r="AB27" s="47"/>
+      <c r="AC27" s="47"/>
+      <c r="AD27" s="47"/>
+      <c r="AE27" s="47"/>
+      <c r="AF27" s="47"/>
+      <c r="AG27" s="47"/>
+      <c r="AH27" s="47"/>
+      <c r="AI27" s="47"/>
+      <c r="AJ27" s="47"/>
+      <c r="AK27" s="47"/>
+      <c r="AL27" s="47"/>
+      <c r="AM27" s="47"/>
+      <c r="AN27" s="47"/>
+      <c r="AO27" s="47"/>
+      <c r="AP27" s="47"/>
+      <c r="AQ27" s="47"/>
+      <c r="AR27" s="47"/>
+      <c r="AU27" s="44"/>
     </row>
     <row r="28" spans="1:47" ht="20.25" customHeight="1">
       <c r="A28" s="42"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="53"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="53"/>
-      <c r="AB28" s="53"/>
-      <c r="AC28" s="53"/>
-      <c r="AD28" s="53"/>
-      <c r="AE28" s="53"/>
-      <c r="AF28" s="53"/>
-      <c r="AG28" s="53"/>
-      <c r="AH28" s="53"/>
-      <c r="AI28" s="53"/>
-      <c r="AJ28" s="53"/>
-      <c r="AK28" s="53"/>
-      <c r="AL28" s="53"/>
-      <c r="AM28" s="53"/>
-      <c r="AN28" s="53"/>
-      <c r="AO28" s="53"/>
-      <c r="AP28" s="53"/>
-      <c r="AQ28" s="53"/>
-      <c r="AR28" s="53"/>
-      <c r="AS28" s="43"/>
-      <c r="AT28" s="43"/>
-      <c r="AU28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
+      <c r="AM28" s="49"/>
+      <c r="AN28" s="49"/>
+      <c r="AO28" s="49"/>
+      <c r="AP28" s="49"/>
+      <c r="AQ28" s="49"/>
+      <c r="AR28" s="49"/>
+      <c r="AU28" s="44"/>
     </row>
     <row r="29" spans="1:47" ht="9" customHeight="1">
       <c r="A29" s="42"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="49"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="49"/>
-      <c r="W29" s="49"/>
-      <c r="X29" s="49"/>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="49"/>
-      <c r="AA29" s="49"/>
-      <c r="AB29" s="49"/>
-      <c r="AC29" s="49"/>
-      <c r="AD29" s="49"/>
-      <c r="AE29" s="49"/>
-      <c r="AF29" s="49"/>
-      <c r="AG29" s="49"/>
-      <c r="AH29" s="49"/>
-      <c r="AI29" s="49"/>
-      <c r="AJ29" s="49"/>
-      <c r="AK29" s="49"/>
-      <c r="AL29" s="49"/>
-      <c r="AM29" s="49"/>
-      <c r="AN29" s="49"/>
-      <c r="AO29" s="49"/>
-      <c r="AP29" s="49"/>
-      <c r="AQ29" s="49"/>
-      <c r="AR29" s="49"/>
-      <c r="AS29" s="43"/>
-      <c r="AT29" s="43"/>
-      <c r="AU29" s="46"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="47"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="47"/>
+      <c r="V29" s="47"/>
+      <c r="W29" s="47"/>
+      <c r="X29" s="47"/>
+      <c r="Y29" s="47"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="47"/>
+      <c r="AB29" s="47"/>
+      <c r="AC29" s="47"/>
+      <c r="AD29" s="47"/>
+      <c r="AE29" s="47"/>
+      <c r="AF29" s="47"/>
+      <c r="AG29" s="47"/>
+      <c r="AH29" s="47"/>
+      <c r="AI29" s="47"/>
+      <c r="AJ29" s="47"/>
+      <c r="AK29" s="47"/>
+      <c r="AL29" s="47"/>
+      <c r="AM29" s="47"/>
+      <c r="AN29" s="47"/>
+      <c r="AO29" s="47"/>
+      <c r="AP29" s="47"/>
+      <c r="AQ29" s="47"/>
+      <c r="AR29" s="47"/>
+      <c r="AU29" s="44"/>
     </row>
     <row r="30" spans="1:47" ht="18.75" customHeight="1">
       <c r="A30" s="42"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="73"/>
-      <c r="S30" s="73"/>
-      <c r="T30" s="73"/>
-      <c r="U30" s="73"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="49"/>
-      <c r="X30" s="49"/>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="49"/>
-      <c r="AA30" s="49"/>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="49"/>
-      <c r="AD30" s="49"/>
-      <c r="AE30" s="49"/>
-      <c r="AF30" s="49"/>
-      <c r="AG30" s="49"/>
-      <c r="AH30" s="49"/>
-      <c r="AI30" s="49"/>
-      <c r="AJ30" s="52"/>
-      <c r="AK30" s="52"/>
-      <c r="AL30" s="52"/>
-      <c r="AM30" s="52"/>
-      <c r="AN30" s="52"/>
-      <c r="AO30" s="52"/>
-      <c r="AP30" s="52"/>
-      <c r="AQ30" s="52"/>
-      <c r="AR30" s="52"/>
-      <c r="AS30" s="43"/>
-      <c r="AT30" s="43"/>
-      <c r="AU30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="66"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="66"/>
+      <c r="U30" s="66"/>
+      <c r="V30" s="66"/>
+      <c r="W30" s="47"/>
+      <c r="X30" s="47"/>
+      <c r="Y30" s="47"/>
+      <c r="Z30" s="47"/>
+      <c r="AA30" s="47"/>
+      <c r="AB30" s="47"/>
+      <c r="AC30" s="47"/>
+      <c r="AD30" s="47"/>
+      <c r="AE30" s="47"/>
+      <c r="AF30" s="47"/>
+      <c r="AG30" s="47"/>
+      <c r="AH30" s="47"/>
+      <c r="AI30" s="47"/>
+      <c r="AJ30" s="49"/>
+      <c r="AK30" s="49"/>
+      <c r="AL30" s="49"/>
+      <c r="AM30" s="49"/>
+      <c r="AN30" s="49"/>
+      <c r="AO30" s="49"/>
+      <c r="AP30" s="49"/>
+      <c r="AQ30" s="49"/>
+      <c r="AR30" s="49"/>
+      <c r="AU30" s="44"/>
     </row>
     <row r="31" spans="1:47" ht="18.75" customHeight="1">
       <c r="A31" s="42"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="73"/>
-      <c r="S31" s="73"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="73"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="49"/>
-      <c r="X31" s="49"/>
-      <c r="Y31" s="49"/>
-      <c r="Z31" s="49"/>
-      <c r="AA31" s="49"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="49"/>
-      <c r="AE31" s="49"/>
-      <c r="AF31" s="49"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="52"/>
-      <c r="AK31" s="52"/>
-      <c r="AL31" s="52"/>
-      <c r="AM31" s="52"/>
-      <c r="AN31" s="52"/>
-      <c r="AO31" s="52"/>
-      <c r="AP31" s="52"/>
-      <c r="AQ31" s="52"/>
-      <c r="AR31" s="52"/>
-      <c r="AS31" s="43"/>
-      <c r="AT31" s="43"/>
-      <c r="AU31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="66"/>
+      <c r="U31" s="66"/>
+      <c r="V31" s="66"/>
+      <c r="W31" s="47"/>
+      <c r="X31" s="47"/>
+      <c r="Y31" s="47"/>
+      <c r="Z31" s="47"/>
+      <c r="AA31" s="47"/>
+      <c r="AB31" s="47"/>
+      <c r="AC31" s="47"/>
+      <c r="AD31" s="47"/>
+      <c r="AE31" s="47"/>
+      <c r="AF31" s="47"/>
+      <c r="AG31" s="47"/>
+      <c r="AH31" s="47"/>
+      <c r="AI31" s="47"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
+      <c r="AL31" s="49"/>
+      <c r="AM31" s="49"/>
+      <c r="AN31" s="49"/>
+      <c r="AO31" s="49"/>
+      <c r="AP31" s="49"/>
+      <c r="AQ31" s="49"/>
+      <c r="AR31" s="49"/>
+      <c r="AU31" s="44"/>
     </row>
     <row r="32" spans="1:47" ht="18" customHeight="1">
       <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="73"/>
-      <c r="S32" s="73"/>
-      <c r="T32" s="73"/>
-      <c r="U32" s="73"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="49"/>
-      <c r="X32" s="49"/>
-      <c r="Y32" s="49"/>
-      <c r="Z32" s="49"/>
-      <c r="AA32" s="49"/>
-      <c r="AB32" s="49"/>
-      <c r="AC32" s="49"/>
-      <c r="AD32" s="49"/>
-      <c r="AE32" s="49"/>
-      <c r="AF32" s="49"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="49"/>
-      <c r="AI32" s="49"/>
-      <c r="AJ32" s="52"/>
-      <c r="AK32" s="52"/>
-      <c r="AL32" s="52"/>
-      <c r="AM32" s="52"/>
-      <c r="AN32" s="52"/>
-      <c r="AO32" s="52"/>
-      <c r="AP32" s="52"/>
-      <c r="AQ32" s="52"/>
-      <c r="AR32" s="52"/>
-      <c r="AS32" s="43"/>
-      <c r="AT32" s="43"/>
-      <c r="AU32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="66"/>
+      <c r="V32" s="66"/>
+      <c r="W32" s="47"/>
+      <c r="X32" s="47"/>
+      <c r="Y32" s="47"/>
+      <c r="Z32" s="47"/>
+      <c r="AA32" s="47"/>
+      <c r="AB32" s="47"/>
+      <c r="AC32" s="47"/>
+      <c r="AD32" s="47"/>
+      <c r="AE32" s="47"/>
+      <c r="AF32" s="47"/>
+      <c r="AG32" s="47"/>
+      <c r="AH32" s="47"/>
+      <c r="AI32" s="47"/>
+      <c r="AJ32" s="49"/>
+      <c r="AK32" s="49"/>
+      <c r="AL32" s="49"/>
+      <c r="AM32" s="49"/>
+      <c r="AN32" s="49"/>
+      <c r="AO32" s="49"/>
+      <c r="AP32" s="49"/>
+      <c r="AQ32" s="49"/>
+      <c r="AR32" s="49"/>
+      <c r="AU32" s="44"/>
     </row>
     <row r="33" spans="1:47" ht="18" customHeight="1">
       <c r="A33" s="42"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="53"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="53"/>
-      <c r="AB33" s="53"/>
-      <c r="AC33" s="53"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="53"/>
-      <c r="AG33" s="53"/>
-      <c r="AH33" s="53"/>
-      <c r="AI33" s="53"/>
-      <c r="AJ33" s="53"/>
-      <c r="AK33" s="53"/>
-      <c r="AL33" s="53"/>
-      <c r="AM33" s="53"/>
-      <c r="AN33" s="53"/>
-      <c r="AO33" s="53"/>
-      <c r="AP33" s="53"/>
-      <c r="AQ33" s="53"/>
-      <c r="AR33" s="53"/>
-      <c r="AS33" s="43"/>
-      <c r="AT33" s="43"/>
-      <c r="AU33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="49"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="49"/>
+      <c r="W33" s="49"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="49"/>
+      <c r="AA33" s="49"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="49"/>
+      <c r="AD33" s="49"/>
+      <c r="AE33" s="49"/>
+      <c r="AF33" s="49"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="49"/>
+      <c r="AK33" s="49"/>
+      <c r="AL33" s="49"/>
+      <c r="AM33" s="49"/>
+      <c r="AN33" s="49"/>
+      <c r="AO33" s="49"/>
+      <c r="AP33" s="49"/>
+      <c r="AQ33" s="49"/>
+      <c r="AR33" s="49"/>
+      <c r="AU33" s="44"/>
     </row>
     <row r="34" spans="1:47" ht="9.75" customHeight="1">
       <c r="A34" s="42"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="53"/>
-      <c r="Q34" s="53"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="53"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="53"/>
-      <c r="V34" s="53"/>
-      <c r="W34" s="53"/>
-      <c r="X34" s="53"/>
-      <c r="Y34" s="53"/>
-      <c r="Z34" s="53"/>
-      <c r="AA34" s="53"/>
-      <c r="AB34" s="53"/>
-      <c r="AC34" s="53"/>
-      <c r="AD34" s="53"/>
-      <c r="AE34" s="53"/>
-      <c r="AF34" s="53"/>
-      <c r="AG34" s="53"/>
-      <c r="AH34" s="53"/>
-      <c r="AI34" s="53"/>
-      <c r="AJ34" s="53"/>
-      <c r="AK34" s="53"/>
-      <c r="AL34" s="53"/>
-      <c r="AM34" s="53"/>
-      <c r="AN34" s="53"/>
-      <c r="AO34" s="53"/>
-      <c r="AP34" s="53"/>
-      <c r="AQ34" s="53"/>
-      <c r="AR34" s="53"/>
-      <c r="AS34" s="43"/>
-      <c r="AT34" s="43"/>
-      <c r="AU34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
+      <c r="L34" s="49"/>
+      <c r="M34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="49"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="49"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
+      <c r="AA34" s="49"/>
+      <c r="AB34" s="49"/>
+      <c r="AC34" s="49"/>
+      <c r="AD34" s="49"/>
+      <c r="AE34" s="49"/>
+      <c r="AF34" s="49"/>
+      <c r="AG34" s="49"/>
+      <c r="AH34" s="49"/>
+      <c r="AI34" s="49"/>
+      <c r="AJ34" s="49"/>
+      <c r="AK34" s="49"/>
+      <c r="AL34" s="49"/>
+      <c r="AM34" s="49"/>
+      <c r="AN34" s="49"/>
+      <c r="AO34" s="49"/>
+      <c r="AP34" s="49"/>
+      <c r="AQ34" s="49"/>
+      <c r="AR34" s="49"/>
+      <c r="AU34" s="44"/>
     </row>
-    <row r="35" spans="1:47" ht="16.5">
+    <row r="35" spans="1:47" ht="17">
       <c r="A35" s="42"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="53"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="53"/>
-      <c r="V35" s="53"/>
-      <c r="W35" s="53"/>
-      <c r="X35" s="53"/>
-      <c r="Y35" s="53"/>
-      <c r="Z35" s="53"/>
-      <c r="AA35" s="53"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="53"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="53"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="53"/>
-      <c r="AH35" s="53"/>
-      <c r="AI35" s="53"/>
-      <c r="AJ35" s="53"/>
-      <c r="AK35" s="53"/>
-      <c r="AL35" s="53"/>
-      <c r="AM35" s="53"/>
-      <c r="AN35" s="53"/>
-      <c r="AO35" s="53"/>
-      <c r="AP35" s="53"/>
-      <c r="AQ35" s="53"/>
-      <c r="AR35" s="53"/>
-      <c r="AS35" s="43"/>
-      <c r="AT35" s="43"/>
-      <c r="AU35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="49"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="49"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
+      <c r="Z35" s="49"/>
+      <c r="AA35" s="49"/>
+      <c r="AB35" s="49"/>
+      <c r="AC35" s="49"/>
+      <c r="AD35" s="49"/>
+      <c r="AE35" s="49"/>
+      <c r="AF35" s="49"/>
+      <c r="AG35" s="49"/>
+      <c r="AH35" s="49"/>
+      <c r="AI35" s="49"/>
+      <c r="AJ35" s="49"/>
+      <c r="AK35" s="49"/>
+      <c r="AL35" s="49"/>
+      <c r="AM35" s="49"/>
+      <c r="AN35" s="49"/>
+      <c r="AO35" s="49"/>
+      <c r="AP35" s="49"/>
+      <c r="AQ35" s="49"/>
+      <c r="AR35" s="49"/>
+      <c r="AU35" s="44"/>
     </row>
-    <row r="36" spans="1:47" ht="16.5">
+    <row r="36" spans="1:47" ht="17">
       <c r="A36" s="42"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="53"/>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="53"/>
-      <c r="U36" s="53"/>
-      <c r="V36" s="53"/>
-      <c r="W36" s="53"/>
-      <c r="X36" s="53"/>
-      <c r="Y36" s="53"/>
-      <c r="Z36" s="53"/>
-      <c r="AA36" s="53"/>
-      <c r="AB36" s="53"/>
-      <c r="AC36" s="53"/>
-      <c r="AD36" s="53"/>
-      <c r="AE36" s="53"/>
-      <c r="AF36" s="53"/>
-      <c r="AG36" s="53"/>
-      <c r="AH36" s="53"/>
-      <c r="AI36" s="53"/>
-      <c r="AJ36" s="53"/>
-      <c r="AK36" s="53"/>
-      <c r="AL36" s="53"/>
-      <c r="AM36" s="53"/>
-      <c r="AN36" s="53"/>
-      <c r="AO36" s="53"/>
-      <c r="AP36" s="53"/>
-      <c r="AQ36" s="53"/>
-      <c r="AR36" s="53"/>
-      <c r="AS36" s="43"/>
-      <c r="AT36" s="43"/>
-      <c r="AU36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="49"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="49"/>
+      <c r="P36" s="49"/>
+      <c r="Q36" s="49"/>
+      <c r="R36" s="49"/>
+      <c r="S36" s="49"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
+      <c r="W36" s="49"/>
+      <c r="X36" s="49"/>
+      <c r="Y36" s="49"/>
+      <c r="Z36" s="49"/>
+      <c r="AA36" s="49"/>
+      <c r="AB36" s="49"/>
+      <c r="AC36" s="49"/>
+      <c r="AD36" s="49"/>
+      <c r="AE36" s="49"/>
+      <c r="AF36" s="49"/>
+      <c r="AG36" s="49"/>
+      <c r="AH36" s="49"/>
+      <c r="AI36" s="49"/>
+      <c r="AJ36" s="49"/>
+      <c r="AK36" s="49"/>
+      <c r="AL36" s="49"/>
+      <c r="AM36" s="49"/>
+      <c r="AN36" s="49"/>
+      <c r="AO36" s="49"/>
+      <c r="AP36" s="49"/>
+      <c r="AQ36" s="49"/>
+      <c r="AR36" s="49"/>
+      <c r="AU36" s="44"/>
     </row>
     <row r="37" spans="1:47" ht="12" customHeight="1">
       <c r="A37" s="42"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="53"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="53"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="53"/>
-      <c r="V37" s="53"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
-      <c r="AA37" s="53"/>
-      <c r="AB37" s="53"/>
-      <c r="AC37" s="53"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="53"/>
-      <c r="AF37" s="53"/>
-      <c r="AG37" s="53"/>
-      <c r="AH37" s="53"/>
-      <c r="AI37" s="53"/>
-      <c r="AJ37" s="53"/>
-      <c r="AK37" s="53"/>
-      <c r="AL37" s="53"/>
-      <c r="AM37" s="53"/>
-      <c r="AN37" s="53"/>
-      <c r="AO37" s="53"/>
-      <c r="AP37" s="53"/>
-      <c r="AQ37" s="53"/>
-      <c r="AR37" s="53"/>
-      <c r="AS37" s="43"/>
-      <c r="AT37" s="43"/>
-      <c r="AU37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49"/>
+      <c r="O37" s="49"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
+      <c r="W37" s="49"/>
+      <c r="X37" s="49"/>
+      <c r="Y37" s="49"/>
+      <c r="Z37" s="49"/>
+      <c r="AA37" s="49"/>
+      <c r="AB37" s="49"/>
+      <c r="AC37" s="49"/>
+      <c r="AD37" s="49"/>
+      <c r="AE37" s="49"/>
+      <c r="AF37" s="49"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
+      <c r="AM37" s="49"/>
+      <c r="AN37" s="49"/>
+      <c r="AO37" s="49"/>
+      <c r="AP37" s="49"/>
+      <c r="AQ37" s="49"/>
+      <c r="AR37" s="49"/>
+      <c r="AU37" s="44"/>
     </row>
-    <row r="38" spans="1:47" ht="16.5">
+    <row r="38" spans="1:47" ht="17">
       <c r="A38" s="42"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="53"/>
-      <c r="Q38" s="53"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="53"/>
-      <c r="T38" s="53"/>
-      <c r="U38" s="53"/>
-      <c r="V38" s="53"/>
-      <c r="W38" s="53"/>
-      <c r="X38" s="53"/>
-      <c r="Y38" s="53"/>
-      <c r="Z38" s="53"/>
-      <c r="AA38" s="53"/>
-      <c r="AB38" s="53"/>
-      <c r="AC38" s="53"/>
-      <c r="AD38" s="53"/>
-      <c r="AE38" s="53"/>
-      <c r="AF38" s="53"/>
-      <c r="AG38" s="53"/>
-      <c r="AH38" s="53"/>
-      <c r="AI38" s="53"/>
-      <c r="AJ38" s="53"/>
-      <c r="AK38" s="53"/>
-      <c r="AL38" s="53"/>
-      <c r="AM38" s="53"/>
-      <c r="AN38" s="53"/>
-      <c r="AO38" s="53"/>
-      <c r="AP38" s="53"/>
-      <c r="AQ38" s="53"/>
-      <c r="AR38" s="53"/>
-      <c r="AS38" s="43"/>
-      <c r="AT38" s="43"/>
-      <c r="AU38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="49"/>
+      <c r="P38" s="49"/>
+      <c r="Q38" s="49"/>
+      <c r="R38" s="49"/>
+      <c r="S38" s="49"/>
+      <c r="T38" s="49"/>
+      <c r="U38" s="49"/>
+      <c r="V38" s="49"/>
+      <c r="W38" s="49"/>
+      <c r="X38" s="49"/>
+      <c r="Y38" s="49"/>
+      <c r="Z38" s="49"/>
+      <c r="AA38" s="49"/>
+      <c r="AB38" s="49"/>
+      <c r="AC38" s="49"/>
+      <c r="AD38" s="49"/>
+      <c r="AE38" s="49"/>
+      <c r="AF38" s="49"/>
+      <c r="AG38" s="49"/>
+      <c r="AH38" s="49"/>
+      <c r="AI38" s="49"/>
+      <c r="AJ38" s="49"/>
+      <c r="AK38" s="49"/>
+      <c r="AL38" s="49"/>
+      <c r="AM38" s="49"/>
+      <c r="AN38" s="49"/>
+      <c r="AO38" s="49"/>
+      <c r="AP38" s="49"/>
+      <c r="AQ38" s="49"/>
+      <c r="AR38" s="49"/>
+      <c r="AU38" s="44"/>
     </row>
-    <row r="39" spans="1:47" ht="16.5">
+    <row r="39" spans="1:47" ht="17">
       <c r="A39" s="42"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
-      <c r="P39" s="53"/>
-      <c r="Q39" s="53"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="53"/>
-      <c r="T39" s="53"/>
-      <c r="U39" s="53"/>
-      <c r="V39" s="53"/>
-      <c r="W39" s="53"/>
-      <c r="X39" s="53"/>
-      <c r="Y39" s="53"/>
-      <c r="Z39" s="53"/>
-      <c r="AA39" s="53"/>
-      <c r="AB39" s="53"/>
-      <c r="AC39" s="53"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="53"/>
-      <c r="AG39" s="53"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="53"/>
-      <c r="AJ39" s="53"/>
-      <c r="AK39" s="53"/>
-      <c r="AL39" s="53"/>
-      <c r="AM39" s="53"/>
-      <c r="AN39" s="53"/>
-      <c r="AO39" s="53"/>
-      <c r="AP39" s="53"/>
-      <c r="AQ39" s="53"/>
-      <c r="AR39" s="53"/>
-      <c r="AS39" s="43"/>
-      <c r="AT39" s="43"/>
-      <c r="AU39" s="46"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="49"/>
+      <c r="N39" s="49"/>
+      <c r="O39" s="49"/>
+      <c r="P39" s="49"/>
+      <c r="Q39" s="49"/>
+      <c r="R39" s="49"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="49"/>
+      <c r="W39" s="49"/>
+      <c r="X39" s="49"/>
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AE39" s="49"/>
+      <c r="AF39" s="49"/>
+      <c r="AG39" s="49"/>
+      <c r="AH39" s="49"/>
+      <c r="AI39" s="49"/>
+      <c r="AJ39" s="49"/>
+      <c r="AK39" s="49"/>
+      <c r="AL39" s="49"/>
+      <c r="AM39" s="49"/>
+      <c r="AN39" s="49"/>
+      <c r="AO39" s="49"/>
+      <c r="AP39" s="49"/>
+      <c r="AQ39" s="49"/>
+      <c r="AR39" s="49"/>
+      <c r="AU39" s="44"/>
     </row>
-    <row r="40" spans="1:47" ht="16.5">
+    <row r="40" spans="1:47" ht="17">
       <c r="A40" s="42"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
-      <c r="P40" s="53"/>
-      <c r="Q40" s="53"/>
-      <c r="R40" s="53"/>
-      <c r="S40" s="53"/>
-      <c r="T40" s="53"/>
-      <c r="U40" s="53"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="53"/>
-      <c r="X40" s="53"/>
-      <c r="Y40" s="53"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="53"/>
-      <c r="AC40" s="53"/>
-      <c r="AD40" s="53"/>
-      <c r="AE40" s="53"/>
-      <c r="AF40" s="53"/>
-      <c r="AG40" s="53"/>
-      <c r="AH40" s="53"/>
-      <c r="AI40" s="53"/>
-      <c r="AJ40" s="53"/>
-      <c r="AK40" s="53"/>
-      <c r="AL40" s="53"/>
-      <c r="AM40" s="53"/>
-      <c r="AN40" s="53"/>
-      <c r="AO40" s="53"/>
-      <c r="AP40" s="53"/>
-      <c r="AQ40" s="53"/>
-      <c r="AR40" s="53"/>
-      <c r="AS40" s="43"/>
-      <c r="AT40" s="43"/>
-      <c r="AU40" s="46"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="49"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="49"/>
+      <c r="N40" s="49"/>
+      <c r="O40" s="49"/>
+      <c r="P40" s="49"/>
+      <c r="Q40" s="49"/>
+      <c r="R40" s="49"/>
+      <c r="S40" s="49"/>
+      <c r="T40" s="49"/>
+      <c r="U40" s="49"/>
+      <c r="V40" s="49"/>
+      <c r="W40" s="49"/>
+      <c r="X40" s="49"/>
+      <c r="Y40" s="49"/>
+      <c r="Z40" s="49"/>
+      <c r="AA40" s="49"/>
+      <c r="AB40" s="49"/>
+      <c r="AC40" s="49"/>
+      <c r="AD40" s="49"/>
+      <c r="AE40" s="49"/>
+      <c r="AF40" s="49"/>
+      <c r="AG40" s="49"/>
+      <c r="AH40" s="49"/>
+      <c r="AI40" s="49"/>
+      <c r="AJ40" s="49"/>
+      <c r="AK40" s="49"/>
+      <c r="AL40" s="49"/>
+      <c r="AM40" s="49"/>
+      <c r="AN40" s="49"/>
+      <c r="AO40" s="49"/>
+      <c r="AP40" s="49"/>
+      <c r="AQ40" s="49"/>
+      <c r="AR40" s="49"/>
+      <c r="AU40" s="44"/>
     </row>
-    <row r="41" spans="1:47" ht="16.5">
+    <row r="41" spans="1:47" ht="17">
       <c r="A41" s="42"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="53"/>
-      <c r="T41" s="53"/>
-      <c r="U41" s="53"/>
-      <c r="V41" s="53"/>
-      <c r="W41" s="53"/>
-      <c r="X41" s="53"/>
-      <c r="Y41" s="53"/>
-      <c r="Z41" s="53"/>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="53"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="53"/>
-      <c r="AF41" s="53"/>
-      <c r="AG41" s="53"/>
-      <c r="AH41" s="53"/>
-      <c r="AI41" s="53"/>
-      <c r="AJ41" s="53"/>
-      <c r="AK41" s="53"/>
-      <c r="AL41" s="53"/>
-      <c r="AM41" s="53"/>
-      <c r="AN41" s="53"/>
-      <c r="AO41" s="53"/>
-      <c r="AP41" s="53"/>
-      <c r="AQ41" s="53"/>
-      <c r="AR41" s="53"/>
-      <c r="AS41" s="43"/>
-      <c r="AT41" s="43"/>
-      <c r="AU41" s="46"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
+      <c r="P41" s="49"/>
+      <c r="Q41" s="49"/>
+      <c r="R41" s="49"/>
+      <c r="S41" s="49"/>
+      <c r="T41" s="49"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="49"/>
+      <c r="W41" s="49"/>
+      <c r="X41" s="49"/>
+      <c r="Y41" s="49"/>
+      <c r="Z41" s="49"/>
+      <c r="AA41" s="49"/>
+      <c r="AB41" s="49"/>
+      <c r="AC41" s="49"/>
+      <c r="AD41" s="49"/>
+      <c r="AE41" s="49"/>
+      <c r="AF41" s="49"/>
+      <c r="AG41" s="49"/>
+      <c r="AH41" s="49"/>
+      <c r="AI41" s="49"/>
+      <c r="AJ41" s="49"/>
+      <c r="AK41" s="49"/>
+      <c r="AL41" s="49"/>
+      <c r="AM41" s="49"/>
+      <c r="AN41" s="49"/>
+      <c r="AO41" s="49"/>
+      <c r="AP41" s="49"/>
+      <c r="AQ41" s="49"/>
+      <c r="AR41" s="49"/>
+      <c r="AU41" s="44"/>
     </row>
     <row r="42" spans="1:47" ht="21.75" customHeight="1">
       <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="74"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="74"/>
-      <c r="L42" s="74"/>
-      <c r="M42" s="74"/>
-      <c r="N42" s="74"/>
-      <c r="O42" s="74"/>
-      <c r="P42" s="74"/>
-      <c r="Q42" s="74"/>
-      <c r="R42" s="74"/>
-      <c r="S42" s="74"/>
-      <c r="T42" s="74"/>
-      <c r="U42" s="74"/>
-      <c r="V42" s="74"/>
-      <c r="W42" s="74"/>
-      <c r="X42" s="74"/>
-      <c r="Y42" s="74"/>
-      <c r="Z42" s="74"/>
-      <c r="AA42" s="74"/>
-      <c r="AB42" s="74"/>
-      <c r="AC42" s="74"/>
-      <c r="AD42" s="74"/>
-      <c r="AE42" s="74"/>
-      <c r="AF42" s="74"/>
-      <c r="AG42" s="74"/>
-      <c r="AH42" s="74"/>
-      <c r="AI42" s="74"/>
-      <c r="AJ42" s="74"/>
-      <c r="AK42" s="74"/>
-      <c r="AL42" s="74"/>
-      <c r="AM42" s="74"/>
-      <c r="AN42" s="74"/>
-      <c r="AO42" s="74"/>
-      <c r="AP42" s="74"/>
-      <c r="AQ42" s="74"/>
-      <c r="AR42" s="74"/>
-      <c r="AS42" s="43"/>
-      <c r="AT42" s="43"/>
-      <c r="AU42" s="46"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="67"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="67"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="67"/>
+      <c r="U42" s="67"/>
+      <c r="V42" s="67"/>
+      <c r="W42" s="67"/>
+      <c r="X42" s="67"/>
+      <c r="Y42" s="67"/>
+      <c r="Z42" s="67"/>
+      <c r="AA42" s="67"/>
+      <c r="AB42" s="67"/>
+      <c r="AC42" s="67"/>
+      <c r="AD42" s="67"/>
+      <c r="AE42" s="67"/>
+      <c r="AF42" s="67"/>
+      <c r="AG42" s="67"/>
+      <c r="AH42" s="67"/>
+      <c r="AI42" s="67"/>
+      <c r="AJ42" s="67"/>
+      <c r="AK42" s="67"/>
+      <c r="AL42" s="67"/>
+      <c r="AM42" s="67"/>
+      <c r="AN42" s="67"/>
+      <c r="AO42" s="67"/>
+      <c r="AP42" s="67"/>
+      <c r="AQ42" s="67"/>
+      <c r="AR42" s="67"/>
+      <c r="AU42" s="44"/>
     </row>
-    <row r="43" spans="1:47" ht="16.5">
+    <row r="43" spans="1:47" ht="17">
       <c r="A43" s="42"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="53"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="53"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="53"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="53"/>
-      <c r="P43" s="53"/>
-      <c r="Q43" s="53"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="53"/>
-      <c r="T43" s="53"/>
-      <c r="U43" s="53"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="53"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="53"/>
-      <c r="Z43" s="53"/>
-      <c r="AA43" s="53"/>
-      <c r="AB43" s="53"/>
-      <c r="AC43" s="53"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="53"/>
-      <c r="AG43" s="53"/>
-      <c r="AH43" s="53"/>
-      <c r="AI43" s="53"/>
-      <c r="AJ43" s="53"/>
-      <c r="AK43" s="53"/>
-      <c r="AL43" s="53"/>
-      <c r="AM43" s="53"/>
-      <c r="AN43" s="53"/>
-      <c r="AO43" s="53"/>
-      <c r="AP43" s="53"/>
-      <c r="AQ43" s="53"/>
-      <c r="AR43" s="53"/>
-      <c r="AS43" s="43"/>
-      <c r="AT43" s="43"/>
-      <c r="AU43" s="46"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="49"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="49"/>
+      <c r="O43" s="49"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="49"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="49"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="49"/>
+      <c r="W43" s="49"/>
+      <c r="X43" s="49"/>
+      <c r="Y43" s="49"/>
+      <c r="Z43" s="49"/>
+      <c r="AA43" s="49"/>
+      <c r="AB43" s="49"/>
+      <c r="AC43" s="49"/>
+      <c r="AD43" s="49"/>
+      <c r="AE43" s="49"/>
+      <c r="AF43" s="49"/>
+      <c r="AG43" s="49"/>
+      <c r="AH43" s="49"/>
+      <c r="AI43" s="49"/>
+      <c r="AJ43" s="49"/>
+      <c r="AK43" s="49"/>
+      <c r="AL43" s="49"/>
+      <c r="AM43" s="49"/>
+      <c r="AN43" s="49"/>
+      <c r="AO43" s="49"/>
+      <c r="AP43" s="49"/>
+      <c r="AQ43" s="49"/>
+      <c r="AR43" s="49"/>
+      <c r="AU43" s="44"/>
     </row>
     <row r="44" spans="1:47" ht="11.25" customHeight="1">
       <c r="A44" s="42"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="53"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="53"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="53"/>
-      <c r="P44" s="53"/>
-      <c r="Q44" s="53"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="53"/>
-      <c r="T44" s="75"/>
-      <c r="U44" s="53"/>
-      <c r="V44" s="53"/>
-      <c r="W44" s="53"/>
-      <c r="X44" s="53"/>
-      <c r="Y44" s="53"/>
-      <c r="Z44" s="67"/>
-      <c r="AA44" s="53"/>
-      <c r="AB44" s="53"/>
-      <c r="AC44" s="53"/>
-      <c r="AD44" s="53"/>
-      <c r="AE44" s="53"/>
-      <c r="AF44" s="53"/>
-      <c r="AG44" s="53"/>
-      <c r="AH44" s="53"/>
-      <c r="AI44" s="53"/>
-      <c r="AJ44" s="53"/>
-      <c r="AK44" s="53"/>
-      <c r="AL44" s="53"/>
-      <c r="AM44" s="53"/>
-      <c r="AN44" s="75"/>
-      <c r="AO44" s="53"/>
-      <c r="AP44" s="53"/>
-      <c r="AQ44" s="53"/>
-      <c r="AR44" s="53"/>
-      <c r="AS44" s="43"/>
-      <c r="AT44" s="43"/>
-      <c r="AU44" s="46"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="49"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="49"/>
+      <c r="P44" s="49"/>
+      <c r="Q44" s="49"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="68"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="49"/>
+      <c r="W44" s="49"/>
+      <c r="X44" s="49"/>
+      <c r="Y44" s="49"/>
+      <c r="Z44" s="47"/>
+      <c r="AA44" s="49"/>
+      <c r="AB44" s="49"/>
+      <c r="AC44" s="49"/>
+      <c r="AD44" s="49"/>
+      <c r="AE44" s="49"/>
+      <c r="AF44" s="49"/>
+      <c r="AG44" s="49"/>
+      <c r="AH44" s="49"/>
+      <c r="AI44" s="49"/>
+      <c r="AJ44" s="49"/>
+      <c r="AK44" s="49"/>
+      <c r="AL44" s="49"/>
+      <c r="AM44" s="49"/>
+      <c r="AN44" s="68"/>
+      <c r="AO44" s="49"/>
+      <c r="AP44" s="49"/>
+      <c r="AQ44" s="49"/>
+      <c r="AR44" s="49"/>
+      <c r="AU44" s="44"/>
     </row>
     <row r="45" spans="1:47">
       <c r="A45" s="42"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
-      <c r="O45" s="43"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="43"/>
-      <c r="X45" s="43"/>
-      <c r="Y45" s="43"/>
-      <c r="Z45" s="43"/>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
-      <c r="AC45" s="43"/>
-      <c r="AD45" s="43"/>
-      <c r="AE45" s="43"/>
-      <c r="AF45" s="43"/>
-      <c r="AG45" s="43"/>
-      <c r="AH45" s="43"/>
-      <c r="AI45" s="43"/>
-      <c r="AJ45" s="43"/>
-      <c r="AK45" s="43"/>
-      <c r="AL45" s="43"/>
-      <c r="AM45" s="43"/>
-      <c r="AN45" s="43"/>
-      <c r="AO45" s="43"/>
-      <c r="AP45" s="43"/>
-      <c r="AQ45" s="43"/>
-      <c r="AR45" s="43"/>
-      <c r="AS45" s="43"/>
-      <c r="AT45" s="43"/>
-      <c r="AU45" s="46"/>
+      <c r="AU45" s="44"/>
     </row>
     <row r="46" spans="1:47" ht="6.75" customHeight="1">
       <c r="A46" s="42"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
-      <c r="M46" s="44"/>
-      <c r="N46" s="44"/>
-      <c r="O46" s="44"/>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="44"/>
-      <c r="R46" s="44"/>
-      <c r="S46" s="44"/>
-      <c r="T46" s="44"/>
-      <c r="U46" s="44"/>
-      <c r="V46" s="44"/>
-      <c r="W46" s="44"/>
-      <c r="X46" s="44"/>
-      <c r="Y46" s="44"/>
-      <c r="Z46" s="44"/>
-      <c r="AA46" s="44"/>
-      <c r="AB46" s="44"/>
-      <c r="AC46" s="44"/>
-      <c r="AD46" s="44"/>
-      <c r="AE46" s="44"/>
-      <c r="AF46" s="44"/>
-      <c r="AG46" s="44"/>
-      <c r="AH46" s="44"/>
-      <c r="AI46" s="44"/>
-      <c r="AJ46" s="44"/>
-      <c r="AK46" s="44"/>
-      <c r="AL46" s="44"/>
-      <c r="AM46" s="44"/>
-      <c r="AN46" s="44"/>
-      <c r="AO46" s="44"/>
-      <c r="AP46" s="44"/>
-      <c r="AQ46" s="44"/>
-      <c r="AR46" s="44"/>
-      <c r="AS46" s="44"/>
-      <c r="AT46" s="44"/>
-      <c r="AU46" s="46"/>
+      <c r="AU46" s="44"/>
     </row>
-    <row r="47" spans="1:47" ht="5.0999999999999996" customHeight="1">
-      <c r="A47" s="76"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
-      <c r="M47" s="44"/>
-      <c r="N47" s="44"/>
-      <c r="O47" s="44"/>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="44"/>
-      <c r="S47" s="44"/>
-      <c r="T47" s="44"/>
-      <c r="U47" s="44"/>
-      <c r="V47" s="44"/>
-      <c r="W47" s="44"/>
-      <c r="X47" s="44"/>
-      <c r="Y47" s="44"/>
-      <c r="Z47" s="44"/>
-      <c r="AA47" s="44"/>
-      <c r="AB47" s="44"/>
-      <c r="AC47" s="44"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="44"/>
-      <c r="AF47" s="44"/>
-      <c r="AG47" s="44"/>
-      <c r="AH47" s="44"/>
-      <c r="AI47" s="44"/>
-      <c r="AJ47" s="44"/>
-      <c r="AK47" s="44"/>
-      <c r="AL47" s="44"/>
-      <c r="AM47" s="44"/>
-      <c r="AN47" s="44"/>
-      <c r="AO47" s="44"/>
-      <c r="AP47" s="44"/>
-      <c r="AQ47" s="44"/>
-      <c r="AR47" s="44"/>
-      <c r="AS47" s="44"/>
-      <c r="AT47" s="44"/>
-      <c r="AU47" s="77"/>
+    <row r="47" spans="1:47" ht="5" customHeight="1">
+      <c r="A47" s="69"/>
+      <c r="AU47" s="70"/>
     </row>
     <row r="48" spans="1:47" ht="6" customHeight="1">
-      <c r="A48" s="78"/>
-      <c r="AU48" s="78"/>
+      <c r="A48" s="70"/>
+      <c r="AU48" s="70"/>
     </row>
     <row r="49" spans="1:47" ht="18.75" customHeight="1">
-      <c r="A49" s="78"/>
-      <c r="AU49" s="78"/>
+      <c r="A49" s="70"/>
+      <c r="AU49" s="70"/>
     </row>
     <row r="50" spans="1:47" ht="18.75" customHeight="1">
-      <c r="A50" s="78"/>
-      <c r="AU50" s="78"/>
+      <c r="A50" s="70"/>
+      <c r="AU50" s="70"/>
     </row>
     <row r="51" spans="1:47" ht="7.5" customHeight="1">
-      <c r="A51" s="78"/>
-      <c r="B51" s="78"/>
-      <c r="C51" s="78"/>
-      <c r="D51" s="78"/>
-      <c r="E51" s="78"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="78"/>
-      <c r="H51" s="78"/>
-      <c r="I51" s="78"/>
-      <c r="J51" s="78"/>
-      <c r="K51" s="78"/>
-      <c r="L51" s="78"/>
-      <c r="M51" s="78"/>
-      <c r="N51" s="78"/>
-      <c r="O51" s="78"/>
-      <c r="P51" s="78"/>
-      <c r="Q51" s="78"/>
-      <c r="R51" s="78"/>
-      <c r="S51" s="78"/>
-      <c r="T51" s="78"/>
-      <c r="U51" s="78"/>
-      <c r="V51" s="78"/>
-      <c r="W51" s="78"/>
-      <c r="X51" s="78"/>
-      <c r="Y51" s="78"/>
-      <c r="Z51" s="78"/>
-      <c r="AA51" s="78"/>
-      <c r="AB51" s="78"/>
-      <c r="AC51" s="78"/>
-      <c r="AD51" s="78"/>
-      <c r="AE51" s="78"/>
-      <c r="AF51" s="78"/>
-      <c r="AG51" s="78"/>
-      <c r="AH51" s="78"/>
-      <c r="AI51" s="78"/>
-      <c r="AJ51" s="78"/>
-      <c r="AK51" s="78"/>
-      <c r="AL51" s="78"/>
-      <c r="AM51" s="78"/>
-      <c r="AN51" s="78"/>
-      <c r="AO51" s="78"/>
-      <c r="AP51" s="78"/>
-      <c r="AQ51" s="78"/>
-      <c r="AR51" s="78"/>
-      <c r="AS51" s="78"/>
-      <c r="AT51" s="78"/>
-      <c r="AU51" s="78"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="70"/>
+      <c r="M51" s="70"/>
+      <c r="N51" s="70"/>
+      <c r="O51" s="70"/>
+      <c r="P51" s="70"/>
+      <c r="Q51" s="70"/>
+      <c r="R51" s="70"/>
+      <c r="S51" s="70"/>
+      <c r="T51" s="70"/>
+      <c r="U51" s="70"/>
+      <c r="V51" s="70"/>
+      <c r="W51" s="70"/>
+      <c r="X51" s="70"/>
+      <c r="Y51" s="70"/>
+      <c r="Z51" s="70"/>
+      <c r="AA51" s="70"/>
+      <c r="AB51" s="70"/>
+      <c r="AC51" s="70"/>
+      <c r="AD51" s="70"/>
+      <c r="AE51" s="70"/>
+      <c r="AF51" s="70"/>
+      <c r="AG51" s="70"/>
+      <c r="AH51" s="70"/>
+      <c r="AI51" s="70"/>
+      <c r="AJ51" s="70"/>
+      <c r="AK51" s="70"/>
+      <c r="AL51" s="70"/>
+      <c r="AM51" s="70"/>
+      <c r="AN51" s="70"/>
+      <c r="AO51" s="70"/>
+      <c r="AP51" s="70"/>
+      <c r="AQ51" s="70"/>
+      <c r="AR51" s="70"/>
+      <c r="AS51" s="70"/>
+      <c r="AT51" s="70"/>
+      <c r="AU51" s="70"/>
     </row>
     <row r="56" spans="1:47" ht="14.25" customHeight="1"/>
     <row r="57" spans="1:47" ht="14.25" customHeight="1">
-      <c r="A57" s="232"/>
-      <c r="B57" s="232"/>
-      <c r="C57" s="232"/>
-      <c r="D57" s="232"/>
-      <c r="E57" s="232"/>
-      <c r="F57" s="232"/>
+      <c r="A57" s="129"/>
+      <c r="B57" s="129"/>
+      <c r="C57" s="129"/>
+      <c r="D57" s="129"/>
+      <c r="E57" s="129"/>
+      <c r="F57" s="129"/>
     </row>
     <row r="58" spans="1:47" ht="14.25" customHeight="1">
-      <c r="A58" s="232"/>
-      <c r="B58" s="232"/>
-      <c r="C58" s="232"/>
-      <c r="D58" s="232"/>
-      <c r="E58" s="232"/>
-      <c r="F58" s="232"/>
+      <c r="A58" s="129"/>
+      <c r="B58" s="129"/>
+      <c r="C58" s="129"/>
+      <c r="D58" s="129"/>
+      <c r="E58" s="129"/>
+      <c r="F58" s="129"/>
     </row>
     <row r="59" spans="1:47">
-      <c r="A59" s="232"/>
-      <c r="B59" s="232"/>
-      <c r="C59" s="232"/>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
+      <c r="A59" s="129"/>
+      <c r="B59" s="129"/>
+      <c r="C59" s="129"/>
+      <c r="D59" s="129"/>
+      <c r="E59" s="129"/>
+      <c r="F59" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="3">
